--- a/data/cartones.xlsx
+++ b/data/cartones.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User Win\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96383BC-F4E0-49DB-A016-49766204F941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8505" windowHeight="7185"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>codigo</t>
   </si>
@@ -95,15 +96,9 @@
     <t>BELEN AGUSTIN</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
     <t>DUILIO PALLOTTI</t>
   </si>
   <si>
-    <t>127</t>
-  </si>
-  <si>
     <t xml:space="preserve">PABLO CANELO </t>
   </si>
   <si>
@@ -134,30 +129,15 @@
     <t>CHOF A PRUEBA</t>
   </si>
   <si>
-    <t>226</t>
-  </si>
-  <si>
     <t>MAURO IRIARTE</t>
   </si>
   <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
     <t>GUSTAVO NIETO</t>
   </si>
   <si>
-    <t>229</t>
-  </si>
-  <si>
     <t>LEONARDO GUEVARA</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>201 CAM 1 MARTES</t>
   </si>
   <si>
@@ -230,13 +210,103 @@
     <t>500 Deposito clientes esp</t>
   </si>
   <si>
-    <t>128</t>
+    <t>801 PyP La Francia</t>
+  </si>
+  <si>
+    <t>124 CAM 24 LUNES</t>
+  </si>
+  <si>
+    <t>313 CAM 13 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>312 CAM 12 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>314 CAM 14 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>302 CAM 2 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>304 CAM 4 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>303 CAM 3 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>305 CAM 5 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>307 CAM 7 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>308 CAM 8 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>311 CAM 11 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>123 CAM 23 LUNES</t>
+  </si>
+  <si>
+    <t>125 CAM 25 LUNES</t>
+  </si>
+  <si>
+    <t>503 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>MENDIZABAL FRANCO</t>
+  </si>
+  <si>
+    <t>315 CAM 15 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>113 CAM 13 LUNES</t>
+  </si>
+  <si>
+    <t>114 CAM 14 LUNES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO ROMANO </t>
+  </si>
+  <si>
+    <t>101 CAM 1 LUNES</t>
+  </si>
+  <si>
+    <t>102 CAM 2 LUNES</t>
+  </si>
+  <si>
+    <t>103 CAM 3 LUNES</t>
+  </si>
+  <si>
+    <t>105 CAM 5 LUNES</t>
+  </si>
+  <si>
+    <t>106 CAM 6 LUNES</t>
+  </si>
+  <si>
+    <t>107 CAM 7 LUNES</t>
+  </si>
+  <si>
+    <t>108 CAM 8 LUNES</t>
+  </si>
+  <si>
+    <t>109 CAM 9 LUNES</t>
+  </si>
+  <si>
+    <t>110 CAM 10 LUNES</t>
+  </si>
+  <si>
+    <t>111 CAM 11 LUNES</t>
+  </si>
+  <si>
+    <t>112 CAM 12 LUNES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -548,8 +618,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -601,447 +671,471 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>9231</v>
+        <v>9250</v>
       </c>
       <c r="B2">
-        <v>800</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E2" s="1">
         <v>46174</v>
       </c>
       <c r="F2">
-        <v>200150</v>
+        <v>20066</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="J2">
+        <v>0.54166666699999999</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="N2">
+        <v>0.54166666699999999</v>
       </c>
       <c r="O2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>9230</v>
+        <v>9254</v>
       </c>
       <c r="B3">
-        <v>202</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="C3">
+        <v>229</v>
       </c>
       <c r="D3" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E3" s="1">
         <v>46174</v>
       </c>
       <c r="F3">
-        <v>20057</v>
+        <v>20008</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J3">
+        <v>0.75</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N3">
+        <v>0.75</v>
       </c>
       <c r="O3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>9220</v>
+        <v>9255</v>
       </c>
       <c r="B4">
-        <v>121</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
+        <v>230</v>
+      </c>
+      <c r="C4">
+        <v>230</v>
       </c>
       <c r="D4" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E4" s="1">
         <v>46174</v>
       </c>
-      <c r="E4" s="1">
-        <v>46172</v>
-      </c>
       <c r="F4">
-        <v>20005</v>
+        <v>20006</v>
       </c>
       <c r="G4">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="I4">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="J4">
-        <v>0.66666666665999996</v>
+        <v>0.75555555600000002</v>
       </c>
       <c r="K4">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="L4">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="M4">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="N4">
-        <v>0.66666666665999996</v>
+        <v>0.75555555600000002</v>
       </c>
       <c r="O4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>9221</v>
+        <v>9252</v>
       </c>
       <c r="B5">
-        <v>122</v>
-      </c>
-      <c r="C5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5">
+        <v>227</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E5" s="1">
+        <v>46174</v>
+      </c>
+      <c r="F5">
+        <v>20003</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+      <c r="H5">
         <v>21</v>
       </c>
-      <c r="D5" s="1">
-        <v>46174</v>
-      </c>
-      <c r="E5" s="1">
-        <v>46172</v>
-      </c>
-      <c r="F5">
-        <v>20130</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="O5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>9229</v>
+        <v>9285</v>
       </c>
       <c r="B6">
-        <v>130</v>
+        <v>801</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="D6" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="E6" s="1">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="F6">
-        <v>20006</v>
+        <v>200150</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-2</v>
-      </c>
-      <c r="J6">
-        <v>0.85714285714000005</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>-2</v>
-      </c>
-      <c r="N6">
-        <v>0.85714285714000005</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>9226</v>
+        <v>9231</v>
       </c>
       <c r="B7">
-        <v>127</v>
+        <v>800</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1">
         <v>46174</v>
       </c>
       <c r="E7" s="1">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="F7">
-        <v>20003</v>
+        <v>200150</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-7</v>
-      </c>
-      <c r="J7">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>-7</v>
-      </c>
-      <c r="N7">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9245</v>
+        <v>9269</v>
       </c>
       <c r="B8">
-        <v>501</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
+        <v>338</v>
+      </c>
+      <c r="C8">
+        <v>338</v>
       </c>
       <c r="D8" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="E8" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F8">
-        <v>200150</v>
+        <v>20007</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J8">
+        <v>0.69565217400000001</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N8">
+        <v>0.69565217400000001</v>
       </c>
       <c r="O8" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>9246</v>
+        <v>9267</v>
       </c>
       <c r="B9">
-        <v>221</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
+        <v>336</v>
+      </c>
+      <c r="C9">
+        <v>336</v>
       </c>
       <c r="D9" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="E9" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F9">
-        <v>20005</v>
+        <v>20111</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J9">
+        <v>0.75</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N9">
+        <v>0.75</v>
       </c>
       <c r="O9" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9247</v>
+        <v>9271</v>
       </c>
       <c r="B10">
-        <v>222</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
+        <v>340</v>
+      </c>
+      <c r="C10">
+        <v>340</v>
       </c>
       <c r="D10" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="E10" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F10">
-        <v>20130</v>
+        <v>20005</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J10">
+        <v>0.68</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="N10">
+        <v>0.68</v>
       </c>
       <c r="O10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>9248</v>
+        <v>9268</v>
       </c>
       <c r="B11">
-        <v>223</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
+        <v>337</v>
+      </c>
+      <c r="C11">
+        <v>337</v>
       </c>
       <c r="D11" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="E11" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="F11">
-        <v>200158</v>
+        <v>20003</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J11">
+        <v>0.8</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="N11">
+        <v>0.8</v>
       </c>
       <c r="O11" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>9249</v>
+        <v>9230</v>
       </c>
       <c r="B12">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1">
         <v>46174</v>
@@ -1050,7 +1144,7 @@
         <v>46174</v>
       </c>
       <c r="F12">
-        <v>20112</v>
+        <v>20057</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1071,833 +1165,3563 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>9250</v>
+        <v>9220</v>
       </c>
       <c r="B13">
-        <v>225</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D13" s="1">
         <v>46174</v>
       </c>
       <c r="E13" s="1">
-        <v>46174</v>
+        <v>46172</v>
       </c>
       <c r="F13">
-        <v>20066</v>
+        <v>20005</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J13">
+        <v>0.66666666699999999</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N13">
+        <v>0.66666666699999999</v>
       </c>
       <c r="O13" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>9251</v>
+        <v>9221</v>
       </c>
       <c r="B14">
-        <v>226</v>
+        <v>122</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1">
         <v>46174</v>
       </c>
       <c r="E14" s="1">
-        <v>46174</v>
+        <v>46172</v>
       </c>
       <c r="F14">
-        <v>20111</v>
+        <v>20130</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
       <c r="O14" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>9252</v>
+        <v>9240</v>
       </c>
       <c r="B15">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E15" s="1">
         <v>46174</v>
       </c>
       <c r="F15">
-        <v>20003</v>
+        <v>20058</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="J15">
+        <v>0.76923076899999998</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="N15">
+        <v>0.76923076899999998</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9253</v>
+        <v>9242</v>
       </c>
       <c r="B16">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E16" s="1">
         <v>46174</v>
       </c>
       <c r="F16">
-        <v>20007</v>
+        <v>20043</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J16">
+        <v>0.83333333300000001</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N16">
+        <v>0.83333333300000001</v>
       </c>
       <c r="O16" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>9254</v>
+        <v>9235</v>
       </c>
       <c r="B17">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E17" s="1">
         <v>46174</v>
       </c>
       <c r="F17">
-        <v>20008</v>
+        <v>20047</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="J17">
+        <v>0.76595744700000001</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="N17">
+        <v>0.76595744700000001</v>
       </c>
       <c r="O17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9255</v>
+        <v>9234</v>
       </c>
       <c r="B18">
-        <v>230</v>
+        <v>204</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D18" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E18" s="1">
         <v>46174</v>
       </c>
       <c r="F18">
-        <v>20006</v>
+        <v>20095</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>-13</v>
+      </c>
+      <c r="J18">
+        <v>0.70454545499999999</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>-13</v>
+      </c>
+      <c r="N18">
+        <v>0.70454545499999999</v>
       </c>
       <c r="O18" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>9232</v>
+        <v>9243</v>
       </c>
       <c r="B19">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D19" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E19" s="1">
         <v>46174</v>
       </c>
       <c r="F19">
-        <v>20153</v>
+        <v>20086</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
       <c r="O19" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>9233</v>
+        <v>9236</v>
       </c>
       <c r="B20">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E20" s="1">
         <v>46174</v>
       </c>
       <c r="F20">
-        <v>20155</v>
+        <v>20076</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J20">
+        <v>0.80555555599999995</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N20">
+        <v>0.80555555599999995</v>
       </c>
       <c r="O20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>9234</v>
+        <v>9239</v>
       </c>
       <c r="B21">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D21" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E21" s="1">
         <v>46174</v>
       </c>
       <c r="F21">
-        <v>20095</v>
+        <v>20105</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="J21">
+        <v>0.675675676</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="N21">
+        <v>0.675675676</v>
       </c>
       <c r="O21" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>9235</v>
+        <v>9237</v>
       </c>
       <c r="B22">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D22" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E22" s="1">
         <v>46174</v>
       </c>
       <c r="F22">
-        <v>20047</v>
+        <v>20106</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="J22">
+        <v>1.1000000000000001</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="N22">
+        <v>1.1000000000000001</v>
       </c>
       <c r="O22" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>9236</v>
+        <v>9232</v>
       </c>
       <c r="B23">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D23" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E23" s="1">
         <v>46174</v>
       </c>
       <c r="F23">
-        <v>20076</v>
+        <v>20153</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J23">
+        <v>0.75</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N23">
+        <v>0.75</v>
       </c>
       <c r="O23" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>9237</v>
+        <v>9238</v>
       </c>
       <c r="B24">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D24" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E24" s="1">
         <v>46174</v>
       </c>
       <c r="F24">
-        <v>20106</v>
+        <v>11215</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J24">
+        <v>0.98</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="N24">
+        <v>0.98</v>
       </c>
       <c r="O24" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>9238</v>
+        <v>9233</v>
       </c>
       <c r="B25">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D25" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E25" s="1">
         <v>46174</v>
       </c>
       <c r="F25">
-        <v>11215</v>
+        <v>20155</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
       <c r="O25" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>9239</v>
+        <v>9241</v>
       </c>
       <c r="B26">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D26" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E26" s="1">
         <v>46174</v>
       </c>
       <c r="F26">
-        <v>20105</v>
+        <v>20057</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
       <c r="K26">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
       <c r="O26" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>9240</v>
+        <v>9223</v>
       </c>
       <c r="B27">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D27" s="1">
         <v>46174</v>
       </c>
       <c r="E27" s="1">
-        <v>46174</v>
+        <v>46172</v>
       </c>
       <c r="F27">
-        <v>20058</v>
+        <v>20112</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
       <c r="K27">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
       <c r="O27" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>9241</v>
+        <v>9225</v>
       </c>
       <c r="B28">
-        <v>212</v>
-      </c>
-      <c r="C28" t="s">
-        <v>62</v>
+        <v>126</v>
+      </c>
+      <c r="C28">
+        <v>126</v>
       </c>
       <c r="D28" s="1">
         <v>46174</v>
       </c>
       <c r="E28" s="1">
-        <v>46174</v>
+        <v>46172</v>
       </c>
       <c r="F28">
-        <v>20057</v>
+        <v>20111</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J28">
+        <v>0.7</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N28">
+        <v>0.7</v>
       </c>
       <c r="O28" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>9242</v>
+        <v>9246</v>
       </c>
       <c r="B29">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D29" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E29" s="1">
         <v>46174</v>
       </c>
       <c r="F29">
-        <v>20043</v>
+        <v>20005</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J29">
+        <v>0.89361702099999996</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N29">
+        <v>0.89361702099999996</v>
       </c>
       <c r="O29" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>9243</v>
+        <v>9248</v>
       </c>
       <c r="B30">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="D30" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E30" s="1">
         <v>46174</v>
       </c>
       <c r="F30">
-        <v>20086</v>
+        <v>200158</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
       <c r="K30">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
       <c r="O30" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9244</v>
+        <v>9249</v>
       </c>
       <c r="B31">
-        <v>500</v>
+        <v>224</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D31" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E31" s="1">
         <v>46174</v>
       </c>
       <c r="F31">
-        <v>200150</v>
+        <v>20112</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
       <c r="K31">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
       <c r="O31" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
+        <v>9251</v>
+      </c>
+      <c r="B32">
+        <v>226</v>
+      </c>
+      <c r="C32">
+        <v>226</v>
+      </c>
+      <c r="D32" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E32" s="1">
+        <v>46174</v>
+      </c>
+      <c r="F32">
+        <v>20111</v>
+      </c>
+      <c r="G32">
+        <v>30</v>
+      </c>
+      <c r="H32">
+        <v>21</v>
+      </c>
+      <c r="I32">
+        <v>-9</v>
+      </c>
+      <c r="J32">
+        <v>0.7</v>
+      </c>
+      <c r="K32">
+        <v>30</v>
+      </c>
+      <c r="L32">
+        <v>21</v>
+      </c>
+      <c r="M32">
+        <v>-9</v>
+      </c>
+      <c r="N32">
+        <v>0.7</v>
+      </c>
+      <c r="O32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>9227</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>128</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33">
+        <v>128</v>
+      </c>
+      <c r="D33" s="1">
+        <v>46174</v>
+      </c>
+      <c r="E33" s="1">
+        <v>46172</v>
+      </c>
+      <c r="F33">
+        <v>20007</v>
+      </c>
+      <c r="G33">
+        <v>35</v>
+      </c>
+      <c r="H33">
+        <v>24</v>
+      </c>
+      <c r="I33">
+        <v>-11</v>
+      </c>
+      <c r="J33">
+        <v>0.68571428599999995</v>
+      </c>
+      <c r="K33">
+        <v>35</v>
+      </c>
+      <c r="L33">
+        <v>24</v>
+      </c>
+      <c r="M33">
+        <v>-11</v>
+      </c>
+      <c r="N33">
+        <v>0.68571428599999995</v>
+      </c>
+      <c r="O33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>9244</v>
+      </c>
+      <c r="B34">
+        <v>500</v>
+      </c>
+      <c r="C34" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E34" s="1">
+        <v>46174</v>
+      </c>
+      <c r="F34">
+        <v>200150</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>9245</v>
+      </c>
+      <c r="B35">
+        <v>501</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E35" s="1">
+        <v>46174</v>
+      </c>
+      <c r="F35">
+        <v>200150</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>9280</v>
+      </c>
+      <c r="B36">
+        <v>313</v>
+      </c>
+      <c r="C36" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E36" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F36">
+        <v>11215</v>
+      </c>
+      <c r="G36">
+        <v>22</v>
+      </c>
+      <c r="H36">
+        <v>12</v>
+      </c>
+      <c r="I36">
+        <v>-10</v>
+      </c>
+      <c r="J36">
+        <v>0.54545454500000001</v>
+      </c>
+      <c r="K36">
+        <v>22</v>
+      </c>
+      <c r="L36">
+        <v>12</v>
+      </c>
+      <c r="M36">
+        <v>-10</v>
+      </c>
+      <c r="N36">
+        <v>0.54545454500000001</v>
+      </c>
+      <c r="O36" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>9279</v>
+      </c>
+      <c r="B37">
+        <v>312</v>
+      </c>
+      <c r="C37" t="s">
+        <v>64</v>
+      </c>
+      <c r="D37" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E37" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F37">
+        <v>20095</v>
+      </c>
+      <c r="G37">
+        <v>29</v>
+      </c>
+      <c r="H37">
+        <v>29</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>29</v>
+      </c>
+      <c r="L37">
+        <v>29</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="O37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>9281</v>
+      </c>
+      <c r="B38">
+        <v>314</v>
+      </c>
+      <c r="C38" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E38" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F38">
+        <v>20076</v>
+      </c>
+      <c r="G38">
+        <v>32</v>
+      </c>
+      <c r="H38">
+        <v>24</v>
+      </c>
+      <c r="I38">
+        <v>-8</v>
+      </c>
+      <c r="J38">
+        <v>0.75</v>
+      </c>
+      <c r="K38">
+        <v>32</v>
+      </c>
+      <c r="L38">
+        <v>24</v>
+      </c>
+      <c r="M38">
+        <v>-8</v>
+      </c>
+      <c r="N38">
+        <v>0.75</v>
+      </c>
+      <c r="O38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>9272</v>
+      </c>
+      <c r="B39">
+        <v>302</v>
+      </c>
+      <c r="C39" t="s">
+        <v>66</v>
+      </c>
+      <c r="D39" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E39" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F39">
+        <v>20058</v>
+      </c>
+      <c r="G39">
+        <v>54</v>
+      </c>
+      <c r="H39">
+        <v>25</v>
+      </c>
+      <c r="I39">
+        <v>-29</v>
+      </c>
+      <c r="J39">
+        <v>0.46296296300000001</v>
+      </c>
+      <c r="K39">
+        <v>54</v>
+      </c>
+      <c r="L39">
+        <v>25</v>
+      </c>
+      <c r="M39">
+        <v>-29</v>
+      </c>
+      <c r="N39">
+        <v>0.46296296300000001</v>
+      </c>
+      <c r="O39" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>9274</v>
+      </c>
+      <c r="B40">
+        <v>304</v>
+      </c>
+      <c r="C40" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E40" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F40">
+        <v>20086</v>
+      </c>
+      <c r="G40">
+        <v>42</v>
+      </c>
+      <c r="H40">
+        <v>31</v>
+      </c>
+      <c r="I40">
+        <v>-11</v>
+      </c>
+      <c r="J40">
+        <v>0.73809523799999999</v>
+      </c>
+      <c r="K40">
+        <v>42</v>
+      </c>
+      <c r="L40">
+        <v>31</v>
+      </c>
+      <c r="M40">
+        <v>-11</v>
+      </c>
+      <c r="N40">
+        <v>0.73809523799999999</v>
+      </c>
+      <c r="O40" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>9283</v>
+      </c>
+      <c r="B41">
+        <v>303</v>
+      </c>
+      <c r="C41" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D41" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E41" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F41">
+        <v>20153</v>
+      </c>
+      <c r="G41">
+        <v>37</v>
+      </c>
+      <c r="H41">
+        <v>48</v>
+      </c>
+      <c r="I41">
+        <v>11</v>
+      </c>
+      <c r="J41">
+        <v>1.2972972970000001</v>
+      </c>
+      <c r="K41">
+        <v>37</v>
+      </c>
+      <c r="L41">
+        <v>48</v>
+      </c>
+      <c r="M41">
+        <v>11</v>
+      </c>
+      <c r="N41">
+        <v>1.2972972970000001</v>
+      </c>
+      <c r="O41" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>9275</v>
+      </c>
+      <c r="B42">
+        <v>305</v>
+      </c>
+      <c r="C42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D42" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E42" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F42">
+        <v>20043</v>
+      </c>
+      <c r="G42">
+        <v>46</v>
+      </c>
+      <c r="H42">
+        <v>48</v>
+      </c>
+      <c r="I42">
+        <v>2</v>
+      </c>
+      <c r="J42">
+        <v>1.043478261</v>
+      </c>
+      <c r="K42">
+        <v>46</v>
+      </c>
+      <c r="L42">
+        <v>48</v>
+      </c>
+      <c r="M42">
+        <v>2</v>
+      </c>
+      <c r="N42">
+        <v>1.043478261</v>
+      </c>
+      <c r="O42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>9276</v>
+      </c>
+      <c r="B43">
+        <v>307</v>
+      </c>
+      <c r="C43" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E43" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F43">
+        <v>20105</v>
+      </c>
+      <c r="G43">
+        <v>45</v>
+      </c>
+      <c r="H43">
+        <v>39</v>
+      </c>
+      <c r="I43">
+        <v>-6</v>
+      </c>
+      <c r="J43">
+        <v>0.86666666699999995</v>
+      </c>
+      <c r="K43">
+        <v>45</v>
+      </c>
+      <c r="L43">
+        <v>39</v>
+      </c>
+      <c r="M43">
+        <v>-6</v>
+      </c>
+      <c r="N43">
+        <v>0.86666666699999995</v>
+      </c>
+      <c r="O43" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>9277</v>
+      </c>
+      <c r="B44">
+        <v>308</v>
+      </c>
+      <c r="C44" t="s">
+        <v>71</v>
+      </c>
+      <c r="D44" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E44" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F44">
+        <v>20057</v>
+      </c>
+      <c r="G44">
+        <v>39</v>
+      </c>
+      <c r="H44">
+        <v>39</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
+        <v>39</v>
+      </c>
+      <c r="L44">
+        <v>39</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>9278</v>
+      </c>
+      <c r="B45">
+        <v>311</v>
+      </c>
+      <c r="C45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E45" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F45">
+        <v>20047</v>
+      </c>
+      <c r="G45">
+        <v>45</v>
+      </c>
+      <c r="H45">
+        <v>40</v>
+      </c>
+      <c r="I45">
+        <v>-5</v>
+      </c>
+      <c r="J45">
+        <v>0.88888888899999996</v>
+      </c>
+      <c r="K45">
+        <v>45</v>
+      </c>
+      <c r="L45">
+        <v>40</v>
+      </c>
+      <c r="M45">
+        <v>-5</v>
+      </c>
+      <c r="N45">
+        <v>0.88888888899999996</v>
+      </c>
+      <c r="O45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>9262</v>
+      </c>
+      <c r="B46">
+        <v>331</v>
+      </c>
+      <c r="C46">
+        <v>331</v>
+      </c>
+      <c r="D46" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E46" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F46">
+        <v>20006</v>
+      </c>
+      <c r="G46">
+        <v>33</v>
+      </c>
+      <c r="H46">
+        <v>21</v>
+      </c>
+      <c r="I46">
+        <v>-12</v>
+      </c>
+      <c r="J46">
+        <v>0.63636363600000001</v>
+      </c>
+      <c r="K46">
+        <v>33</v>
+      </c>
+      <c r="L46">
+        <v>21</v>
+      </c>
+      <c r="M46">
+        <v>-12</v>
+      </c>
+      <c r="N46">
+        <v>0.63636363600000001</v>
+      </c>
+      <c r="O46" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>9253</v>
+      </c>
+      <c r="B47">
+        <v>228</v>
+      </c>
+      <c r="C47">
+        <v>228</v>
+      </c>
+      <c r="D47" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E47" s="1">
         <v>46174</v>
       </c>
-      <c r="E32" s="1">
+      <c r="F47">
+        <v>20007</v>
+      </c>
+      <c r="G47">
+        <v>10</v>
+      </c>
+      <c r="H47">
+        <v>5</v>
+      </c>
+      <c r="I47">
+        <v>-5</v>
+      </c>
+      <c r="J47">
+        <v>0.5</v>
+      </c>
+      <c r="K47">
+        <v>10</v>
+      </c>
+      <c r="L47">
+        <v>5</v>
+      </c>
+      <c r="M47">
+        <v>-5</v>
+      </c>
+      <c r="N47">
+        <v>0.5</v>
+      </c>
+      <c r="O47" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>9263</v>
+      </c>
+      <c r="B48">
+        <v>332</v>
+      </c>
+      <c r="C48">
+        <v>332</v>
+      </c>
+      <c r="D48" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E48" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F48">
+        <v>20130</v>
+      </c>
+      <c r="G48">
+        <v>24</v>
+      </c>
+      <c r="H48">
+        <v>24</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48">
+        <v>24</v>
+      </c>
+      <c r="L48">
+        <v>24</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>1</v>
+      </c>
+      <c r="O48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>9247</v>
+      </c>
+      <c r="B49">
+        <v>222</v>
+      </c>
+      <c r="C49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E49" s="1">
+        <v>46174</v>
+      </c>
+      <c r="F49">
+        <v>20130</v>
+      </c>
+      <c r="G49">
+        <v>10</v>
+      </c>
+      <c r="H49">
+        <v>10</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>10</v>
+      </c>
+      <c r="L49">
+        <v>10</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>1</v>
+      </c>
+      <c r="O49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>9228</v>
+      </c>
+      <c r="B50">
+        <v>129</v>
+      </c>
+      <c r="C50">
+        <v>129</v>
+      </c>
+      <c r="D50" s="1">
+        <v>46174</v>
+      </c>
+      <c r="E50" s="1">
         <v>46172</v>
       </c>
-      <c r="F32">
+      <c r="F50">
+        <v>20008</v>
+      </c>
+      <c r="G50">
+        <v>12</v>
+      </c>
+      <c r="H50">
+        <v>8</v>
+      </c>
+      <c r="I50">
+        <v>-4</v>
+      </c>
+      <c r="J50">
+        <v>0.66666666699999999</v>
+      </c>
+      <c r="K50">
+        <v>12</v>
+      </c>
+      <c r="L50">
+        <v>8</v>
+      </c>
+      <c r="M50">
+        <v>-4</v>
+      </c>
+      <c r="N50">
+        <v>0.66666666699999999</v>
+      </c>
+      <c r="O50" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>9229</v>
+      </c>
+      <c r="B51">
+        <v>130</v>
+      </c>
+      <c r="C51">
+        <v>130</v>
+      </c>
+      <c r="D51" s="1">
+        <v>46174</v>
+      </c>
+      <c r="E51" s="1">
+        <v>46172</v>
+      </c>
+      <c r="F51">
+        <v>20006</v>
+      </c>
+      <c r="G51">
+        <v>14</v>
+      </c>
+      <c r="H51">
+        <v>12</v>
+      </c>
+      <c r="I51">
+        <v>-2</v>
+      </c>
+      <c r="J51">
+        <v>0.85714285700000004</v>
+      </c>
+      <c r="K51">
+        <v>14</v>
+      </c>
+      <c r="L51">
+        <v>12</v>
+      </c>
+      <c r="M51">
+        <v>-2</v>
+      </c>
+      <c r="N51">
+        <v>0.85714285700000004</v>
+      </c>
+      <c r="O51" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>9259</v>
+      </c>
+      <c r="B52">
+        <v>302</v>
+      </c>
+      <c r="C52" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E52" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F52">
+        <v>20047</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="O52" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>9260</v>
+      </c>
+      <c r="B53">
+        <v>302</v>
+      </c>
+      <c r="C53" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E53" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F53">
+        <v>20047</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="O53" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>9226</v>
+      </c>
+      <c r="B54">
+        <v>127</v>
+      </c>
+      <c r="C54">
+        <v>127</v>
+      </c>
+      <c r="D54" s="1">
+        <v>46174</v>
+      </c>
+      <c r="E54" s="1">
+        <v>46172</v>
+      </c>
+      <c r="F54">
+        <v>20003</v>
+      </c>
+      <c r="G54">
+        <v>8</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>-7</v>
+      </c>
+      <c r="J54">
+        <v>0.125</v>
+      </c>
+      <c r="K54">
+        <v>8</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="M54">
+        <v>-7</v>
+      </c>
+      <c r="N54">
+        <v>0.125</v>
+      </c>
+      <c r="O54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>9222</v>
+      </c>
+      <c r="B55">
+        <v>123</v>
+      </c>
+      <c r="C55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="1">
+        <v>46174</v>
+      </c>
+      <c r="E55" s="1">
+        <v>46172</v>
+      </c>
+      <c r="F55">
+        <v>200158</v>
+      </c>
+      <c r="G55">
+        <v>26</v>
+      </c>
+      <c r="H55">
+        <v>26</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>26</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>-26</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>9224</v>
+      </c>
+      <c r="B56">
+        <v>125</v>
+      </c>
+      <c r="C56" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56" s="1">
+        <v>46174</v>
+      </c>
+      <c r="E56" s="1">
+        <v>46172</v>
+      </c>
+      <c r="F56">
+        <v>20066</v>
+      </c>
+      <c r="G56">
+        <v>104</v>
+      </c>
+      <c r="H56">
+        <v>89</v>
+      </c>
+      <c r="I56">
+        <v>-15</v>
+      </c>
+      <c r="J56">
+        <v>0.85576923100000002</v>
+      </c>
+      <c r="K56">
+        <v>104</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>-104</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>9256</v>
+      </c>
+      <c r="B57">
+        <v>800</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E57" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F57">
+        <v>200150</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="O57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>9257</v>
+      </c>
+      <c r="B58">
+        <v>800</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E58" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F58">
+        <v>200150</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="O58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>9284</v>
+      </c>
+      <c r="B59">
+        <v>800</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E59" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F59">
+        <v>200150</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="O59" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>9261</v>
+      </c>
+      <c r="B60">
+        <v>303</v>
+      </c>
+      <c r="C60" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E60" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F60">
+        <v>20047</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="O60" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>9258</v>
+      </c>
+      <c r="B61">
+        <v>503</v>
+      </c>
+      <c r="C61" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E61" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F61">
+        <v>20048</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>-1</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>-1</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>9309</v>
+      </c>
+      <c r="B62">
+        <v>500</v>
+      </c>
+      <c r="C62" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E62" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F62">
+        <v>200150</v>
+      </c>
+      <c r="G62">
+        <v>2</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62">
+        <v>2</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>-2</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>9310</v>
+      </c>
+      <c r="B63">
+        <v>500</v>
+      </c>
+      <c r="C63" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E63" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F63">
+        <v>200150</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>-1</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>9270</v>
+      </c>
+      <c r="B64">
+        <v>339</v>
+      </c>
+      <c r="C64">
+        <v>339</v>
+      </c>
+      <c r="D64" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E64" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F64">
+        <v>20008</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="O64" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>9273</v>
+      </c>
+      <c r="B65">
+        <v>303</v>
+      </c>
+      <c r="C65" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E65" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F65">
+        <v>20153</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="O65" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>9282</v>
+      </c>
+      <c r="B66">
+        <v>315</v>
+      </c>
+      <c r="C66" t="s">
+        <v>77</v>
+      </c>
+      <c r="D66" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E66" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F66">
+        <v>20106</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="O66" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>9297</v>
+      </c>
+      <c r="B67">
+        <v>113</v>
+      </c>
+      <c r="C67" t="s">
+        <v>78</v>
+      </c>
+      <c r="D67" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E67" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F67">
+        <v>20043</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="O67" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>9298</v>
+      </c>
+      <c r="B68">
+        <v>114</v>
+      </c>
+      <c r="C68" t="s">
+        <v>79</v>
+      </c>
+      <c r="D68" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E68" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F68">
+        <v>200150</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="O68" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>9299</v>
+      </c>
+      <c r="B69">
+        <v>131</v>
+      </c>
+      <c r="C69">
+        <v>131</v>
+      </c>
+      <c r="D69" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E69" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F69">
+        <v>20005</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="O69" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>9300</v>
+      </c>
+      <c r="B70">
+        <v>132</v>
+      </c>
+      <c r="C70">
+        <v>132</v>
+      </c>
+      <c r="D70" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E70" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F70">
+        <v>20130</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="O70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>9301</v>
+      </c>
+      <c r="B71">
+        <v>133</v>
+      </c>
+      <c r="C71">
+        <v>133</v>
+      </c>
+      <c r="D71" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E71" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F71">
+        <v>200158</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="O71" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>9302</v>
+      </c>
+      <c r="B72">
+        <v>134</v>
+      </c>
+      <c r="C72">
+        <v>134</v>
+      </c>
+      <c r="D72" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E72" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F72">
+        <v>20112</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="O72" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>9303</v>
+      </c>
+      <c r="B73">
+        <v>135</v>
+      </c>
+      <c r="C73">
+        <v>135</v>
+      </c>
+      <c r="D73" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E73" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F73">
+        <v>20113</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="O73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>9304</v>
+      </c>
+      <c r="B74">
+        <v>136</v>
+      </c>
+      <c r="C74">
+        <v>136</v>
+      </c>
+      <c r="D74" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E74" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F74">
+        <v>20111</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="O74" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>9305</v>
+      </c>
+      <c r="B75">
+        <v>137</v>
+      </c>
+      <c r="C75">
+        <v>137</v>
+      </c>
+      <c r="D75" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E75" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F75">
+        <v>20003</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="O75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>9306</v>
+      </c>
+      <c r="B76">
+        <v>138</v>
+      </c>
+      <c r="C76">
+        <v>138</v>
+      </c>
+      <c r="D76" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E76" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F76">
         <v>20007</v>
       </c>
-      <c r="G32">
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="O76" t="s">
         <v>35</v>
       </c>
-      <c r="H32">
-        <v>24</v>
-      </c>
-      <c r="I32">
-        <v>-11</v>
-      </c>
-      <c r="J32">
-        <v>0.68571428571000004</v>
-      </c>
-      <c r="K32">
-        <v>35</v>
-      </c>
-      <c r="L32">
-        <v>24</v>
-      </c>
-      <c r="M32">
-        <v>-11</v>
-      </c>
-      <c r="N32">
-        <v>0.68571428571000004</v>
-      </c>
-      <c r="O32" t="s">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>9307</v>
+      </c>
+      <c r="B77">
+        <v>139</v>
+      </c>
+      <c r="C77">
+        <v>139</v>
+      </c>
+      <c r="D77" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E77" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F77">
+        <v>20008</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="O77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>9308</v>
+      </c>
+      <c r="B78">
+        <v>140</v>
+      </c>
+      <c r="C78">
+        <v>140</v>
+      </c>
+      <c r="D78" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E78" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F78">
+        <v>20006</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="O78" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>9286</v>
+      </c>
+      <c r="B79">
+        <v>101</v>
+      </c>
+      <c r="C79" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E79" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F79">
+        <v>20076</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="O79" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>9287</v>
+      </c>
+      <c r="B80">
+        <v>102</v>
+      </c>
+      <c r="C80" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E80" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F80">
+        <v>20086</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="O80" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>9288</v>
+      </c>
+      <c r="B81">
+        <v>103</v>
+      </c>
+      <c r="C81" t="s">
+        <v>83</v>
+      </c>
+      <c r="D81" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E81" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F81">
+        <v>20153</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="O81" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>9289</v>
+      </c>
+      <c r="B82">
+        <v>105</v>
+      </c>
+      <c r="C82" t="s">
+        <v>84</v>
+      </c>
+      <c r="D82" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E82" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F82">
+        <v>20058</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="O82" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>9290</v>
+      </c>
+      <c r="B83">
+        <v>106</v>
+      </c>
+      <c r="C83" t="s">
+        <v>85</v>
+      </c>
+      <c r="D83" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E83" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F83">
+        <v>11215</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="O83" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>9291</v>
+      </c>
+      <c r="B84">
+        <v>107</v>
+      </c>
+      <c r="C84" t="s">
+        <v>86</v>
+      </c>
+      <c r="D84" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E84" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F84">
+        <v>20155</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="O84" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>9292</v>
+      </c>
+      <c r="B85">
+        <v>108</v>
+      </c>
+      <c r="C85" t="s">
+        <v>87</v>
+      </c>
+      <c r="D85" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E85" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F85">
+        <v>20057</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="O85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>9293</v>
+      </c>
+      <c r="B86">
+        <v>109</v>
+      </c>
+      <c r="C86" t="s">
+        <v>88</v>
+      </c>
+      <c r="D86" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E86" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F86">
+        <v>20105</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="O86" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>9294</v>
+      </c>
+      <c r="B87">
+        <v>110</v>
+      </c>
+      <c r="C87" t="s">
+        <v>89</v>
+      </c>
+      <c r="D87" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E87" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F87">
+        <v>20095</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="O87" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>9295</v>
+      </c>
+      <c r="B88">
+        <v>111</v>
+      </c>
+      <c r="C88" t="s">
+        <v>90</v>
+      </c>
+      <c r="D88" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E88" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F88">
+        <v>20047</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="O88" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>9296</v>
+      </c>
+      <c r="B89">
+        <v>112</v>
+      </c>
+      <c r="C89" t="s">
+        <v>91</v>
+      </c>
+      <c r="D89" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E89" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F89">
+        <v>20106</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="O89" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>9266</v>
+      </c>
+      <c r="B90">
+        <v>335</v>
+      </c>
+      <c r="C90">
+        <v>335</v>
+      </c>
+      <c r="D90" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E90" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F90">
+        <v>20066</v>
+      </c>
+      <c r="G90">
+        <v>18</v>
+      </c>
+      <c r="H90">
+        <v>8</v>
+      </c>
+      <c r="I90">
+        <v>-10</v>
+      </c>
+      <c r="J90">
+        <v>0.44444444399999999</v>
+      </c>
+      <c r="K90">
+        <v>18</v>
+      </c>
+      <c r="L90">
+        <v>8</v>
+      </c>
+      <c r="M90">
+        <v>-10</v>
+      </c>
+      <c r="N90">
+        <v>0.44444444399999999</v>
+      </c>
+      <c r="O90" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>9265</v>
+      </c>
+      <c r="B91">
+        <v>334</v>
+      </c>
+      <c r="C91">
+        <v>334</v>
+      </c>
+      <c r="D91" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E91" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F91">
+        <v>20112</v>
+      </c>
+      <c r="G91">
+        <v>21</v>
+      </c>
+      <c r="H91">
+        <v>18</v>
+      </c>
+      <c r="I91">
+        <v>-3</v>
+      </c>
+      <c r="J91">
+        <v>0.85714285700000004</v>
+      </c>
+      <c r="K91">
+        <v>21</v>
+      </c>
+      <c r="L91">
+        <v>18</v>
+      </c>
+      <c r="M91">
+        <v>-3</v>
+      </c>
+      <c r="N91">
+        <v>0.85714285700000004</v>
+      </c>
+      <c r="O91" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>9264</v>
+      </c>
+      <c r="B92">
+        <v>333</v>
+      </c>
+      <c r="C92">
+        <v>333</v>
+      </c>
+      <c r="D92" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E92" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F92">
+        <v>200158</v>
+      </c>
+      <c r="G92">
+        <v>23</v>
+      </c>
+      <c r="H92">
+        <v>23</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>23</v>
+      </c>
+      <c r="L92">
+        <v>23</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data/cartones.xlsx
+++ b/data/cartones.xlsx
@@ -1,31 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96383BC-F4E0-49DB-A016-49766204F941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D6FAA2D-B151-4D43-B4D9-8CF64BFC7E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3540" yWindow="3015" windowWidth="15375" windowHeight="7785" xr2:uid="{22493E18-AF0A-488C-9B26-FC8129E5AAFC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="150">
   <si>
     <t>codigo</t>
   </si>
@@ -72,10 +81,109 @@
     <t>razon_social</t>
   </si>
   <si>
+    <t>225 CAM 25 MARTES</t>
+  </si>
+  <si>
+    <t>CHOF A PRUEBA</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>LEONARDO GUEVARA</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>DUILIO PALLOTTI</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABLO CANELO </t>
+  </si>
+  <si>
+    <t>801 PyP La Francia</t>
+  </si>
+  <si>
+    <t>CHOF A PRUE 1</t>
+  </si>
+  <si>
     <t>800 CAM 800 ADMIN</t>
   </si>
   <si>
-    <t>CHOF A PRUE 1</t>
+    <t>338</t>
+  </si>
+  <si>
+    <t>GUSTAVO NIETO</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>MAURO IRIARTE</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>CECILIA GONZALEZ</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>114 CAM 14 LUNES</t>
+  </si>
+  <si>
+    <t>SERGIO BARRIONUEVO</t>
+  </si>
+  <si>
+    <t>113 CAM 13 LUNES</t>
+  </si>
+  <si>
+    <t>GUZMAN DIEGO N.</t>
+  </si>
+  <si>
+    <t>303 CAM 3 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>DIEGO RAFAELLI</t>
+  </si>
+  <si>
+    <t>112 CAM 12 LUNES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORGE MOLINA </t>
+  </si>
+  <si>
+    <t>110 CAM 10 LUNES</t>
+  </si>
+  <si>
+    <t>RODRIGO AVALOS</t>
+  </si>
+  <si>
+    <t>106 CAM 6 LUNES</t>
+  </si>
+  <si>
+    <t>SUAREZ EMIR</t>
+  </si>
+  <si>
+    <t>101 CAM 1 LUNES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS LUJAN </t>
+  </si>
+  <si>
+    <t>102 CAM 2 LUNES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GASTON OYOLA </t>
+  </si>
+  <si>
+    <t>103 CAM 3 LUNES</t>
   </si>
   <si>
     <t>202 CAM 2 MARTES</t>
@@ -87,220 +195,295 @@
     <t>121 CAM 21 LUNES</t>
   </si>
   <si>
-    <t>CECILIA GONZALEZ</t>
+    <t>211 CAM 11 MARTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MAXIMILANO  CARO </t>
+  </si>
+  <si>
+    <t>213 CAM 13 MARTES</t>
+  </si>
+  <si>
+    <t>201 CAM 1 MARTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTINEZ P. J. LEANDRO </t>
+  </si>
+  <si>
+    <t>204 CAM 4 MARTES</t>
+  </si>
+  <si>
+    <t>214 CAM 14 MARTES</t>
+  </si>
+  <si>
+    <t>206 CAM 6 MARTES</t>
+  </si>
+  <si>
+    <t>209 CAM 9 MARTES</t>
+  </si>
+  <si>
+    <t>LUIS JUAREZ</t>
+  </si>
+  <si>
+    <t>207 CAM 7 MARTES</t>
+  </si>
+  <si>
+    <t>208 CAM 8 MARTES</t>
+  </si>
+  <si>
+    <t>203 CAM 3 MARTES</t>
+  </si>
+  <si>
+    <t>212 CAM 12 MARTES</t>
+  </si>
+  <si>
+    <t>124 CAM 24 LUNES</t>
+  </si>
+  <si>
+    <t>EZEQUIEL JUNCOS</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>221 CAM 21 MARTES</t>
+  </si>
+  <si>
+    <t>223 CAM 23 MARTES</t>
+  </si>
+  <si>
+    <t>LUIS GUIRAO</t>
+  </si>
+  <si>
+    <t>224 CAM 24 MARTES</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>500 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>501 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>311 CAM 11 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>313 CAM 13 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>312 CAM 12 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>314 CAM 14 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>302 CAM 2 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>107 CAM 7 LUNES</t>
+  </si>
+  <si>
+    <t>305 CAM 5 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>307 CAM 7 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>308 CAM 8 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>BELEN AGUSTIN</t>
+  </si>
+  <si>
+    <t>222 CAM 22 MARTES</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JOSE RICAPA</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>123 CAM 23 LUNES</t>
+  </si>
+  <si>
+    <t>125 CAM 25 LUNES</t>
+  </si>
+  <si>
+    <t>108 CAM 8 LUNES</t>
+  </si>
+  <si>
+    <t>109 CAM 9 LUNES</t>
+  </si>
+  <si>
+    <t>111 CAM 11 LUNES</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>210 CAM 10 MARTES</t>
+  </si>
+  <si>
+    <t>503 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>MENDIZABAL FRANCO</t>
+  </si>
+  <si>
+    <t>205 CAM 5 MARTES</t>
+  </si>
+  <si>
+    <t>304 CAM 4 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO ROMANO </t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>315 CAM 15 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>502 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>238</t>
   </si>
   <si>
     <t>122 CAM 22 LUNES</t>
   </si>
   <si>
-    <t>BELEN AGUSTIN</t>
-  </si>
-  <si>
-    <t>DUILIO PALLOTTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PABLO CANELO </t>
-  </si>
-  <si>
-    <t>501 Deposito clientes esp</t>
-  </si>
-  <si>
-    <t>221 CAM 21 MARTES</t>
-  </si>
-  <si>
-    <t>222 CAM 22 MARTES</t>
-  </si>
-  <si>
-    <t>223 CAM 23 MARTES</t>
-  </si>
-  <si>
-    <t>LUIS GUIRAO</t>
-  </si>
-  <si>
-    <t>224 CAM 24 MARTES</t>
-  </si>
-  <si>
-    <t>EZEQUIEL JUNCOS</t>
-  </si>
-  <si>
-    <t>225 CAM 25 MARTES</t>
-  </si>
-  <si>
-    <t>CHOF A PRUEBA</t>
-  </si>
-  <si>
-    <t>MAURO IRIARTE</t>
-  </si>
-  <si>
-    <t>GUSTAVO NIETO</t>
-  </si>
-  <si>
-    <t>LEONARDO GUEVARA</t>
-  </si>
-  <si>
-    <t>201 CAM 1 MARTES</t>
-  </si>
-  <si>
-    <t>DIEGO RAFAELLI</t>
-  </si>
-  <si>
-    <t>203 CAM 3 MARTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARTINEZ P. J. LEANDRO </t>
-  </si>
-  <si>
-    <t>204 CAM 4 MARTES</t>
-  </si>
-  <si>
-    <t>RODRIGO AVALOS</t>
-  </si>
-  <si>
-    <t>205 CAM 5 MARTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> JOSE RICAPA</t>
-  </si>
-  <si>
-    <t>206 CAM 6 MARTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUCAS LUJAN </t>
-  </si>
-  <si>
-    <t>207 CAM 7 MARTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JORGE MOLINA </t>
-  </si>
-  <si>
-    <t>208 CAM 8 MARTES</t>
-  </si>
-  <si>
-    <t>SUAREZ EMIR</t>
-  </si>
-  <si>
-    <t>209 CAM 9 MARTES</t>
-  </si>
-  <si>
-    <t>LUIS JUAREZ</t>
-  </si>
-  <si>
-    <t>211 CAM 11 MARTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MAXIMILANO  CARO </t>
-  </si>
-  <si>
-    <t>212 CAM 12 MARTES</t>
-  </si>
-  <si>
-    <t>213 CAM 13 MARTES</t>
-  </si>
-  <si>
-    <t>GUZMAN DIEGO N.</t>
-  </si>
-  <si>
-    <t>214 CAM 14 MARTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GASTON OYOLA </t>
-  </si>
-  <si>
-    <t>500 Deposito clientes esp</t>
-  </si>
-  <si>
-    <t>801 PyP La Francia</t>
-  </si>
-  <si>
-    <t>124 CAM 24 LUNES</t>
-  </si>
-  <si>
-    <t>313 CAM 13 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>312 CAM 12 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>314 CAM 14 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>302 CAM 2 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>304 CAM 4 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>303 CAM 3 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>305 CAM 5 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>307 CAM 7 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>308 CAM 8 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>311 CAM 11 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>123 CAM 23 LUNES</t>
-  </si>
-  <si>
-    <t>125 CAM 25 LUNES</t>
-  </si>
-  <si>
-    <t>503 Deposito clientes esp</t>
-  </si>
-  <si>
-    <t>MENDIZABAL FRANCO</t>
-  </si>
-  <si>
-    <t>315 CAM 15 MIÉRCOLES</t>
-  </si>
-  <si>
-    <t>113 CAM 13 LUNES</t>
-  </si>
-  <si>
-    <t>114 CAM 14 LUNES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODRIGO ROMANO </t>
-  </si>
-  <si>
-    <t>101 CAM 1 LUNES</t>
-  </si>
-  <si>
-    <t>102 CAM 2 LUNES</t>
-  </si>
-  <si>
-    <t>103 CAM 3 LUNES</t>
+    <t>137</t>
   </si>
   <si>
     <t>105 CAM 5 LUNES</t>
   </si>
   <si>
-    <t>106 CAM 6 LUNES</t>
-  </si>
-  <si>
-    <t>107 CAM 7 LUNES</t>
-  </si>
-  <si>
-    <t>108 CAM 8 LUNES</t>
-  </si>
-  <si>
-    <t>109 CAM 9 LUNES</t>
-  </si>
-  <si>
-    <t>110 CAM 10 LUNES</t>
-  </si>
-  <si>
-    <t>111 CAM 11 LUNES</t>
-  </si>
-  <si>
-    <t>112 CAM 12 LUNES</t>
+    <t>335</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>316 CAM 16 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>317 CAM 17 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>318 CAM 18 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>319 CAM 19 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>320 CAM 20 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>321 CAM 21 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>322 CAM 22 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>323 CAM 23 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>324 CAM 24 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>325 CAM 25 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>306 CAM 6 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>310 CAM 10 MIÉRCOLES</t>
   </si>
 </sst>
 </file>
@@ -373,7 +556,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -385,7 +568,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -432,6 +615,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -467,6 +667,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -618,8 +835,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O92"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45344EE1-844E-488C-87B7-5E4BE39AF234}">
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -677,7 +894,7 @@
         <v>225</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1">
         <v>46175</v>
@@ -698,7 +915,7 @@
         <v>-11</v>
       </c>
       <c r="J2">
-        <v>0.54166666699999999</v>
+        <v>0.54166666665999996</v>
       </c>
       <c r="K2">
         <v>24</v>
@@ -710,10 +927,10 @@
         <v>-11</v>
       </c>
       <c r="N2">
-        <v>0.54166666699999999</v>
+        <v>0.54166666665999996</v>
       </c>
       <c r="O2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -723,8 +940,8 @@
       <c r="B3">
         <v>229</v>
       </c>
-      <c r="C3">
-        <v>229</v>
+      <c r="C3" t="s">
+        <v>17</v>
       </c>
       <c r="D3" s="1">
         <v>46175</v>
@@ -760,7 +977,7 @@
         <v>0.75</v>
       </c>
       <c r="O3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -770,8 +987,8 @@
       <c r="B4">
         <v>230</v>
       </c>
-      <c r="C4">
-        <v>230</v>
+      <c r="C4" t="s">
+        <v>19</v>
       </c>
       <c r="D4" s="1">
         <v>46175</v>
@@ -792,7 +1009,7 @@
         <v>-11</v>
       </c>
       <c r="J4">
-        <v>0.75555555600000002</v>
+        <v>0.75555555554999998</v>
       </c>
       <c r="K4">
         <v>45</v>
@@ -804,10 +1021,10 @@
         <v>-11</v>
       </c>
       <c r="N4">
-        <v>0.75555555600000002</v>
+        <v>0.75555555554999998</v>
       </c>
       <c r="O4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -817,8 +1034,8 @@
       <c r="B5">
         <v>227</v>
       </c>
-      <c r="C5">
-        <v>227</v>
+      <c r="C5" t="s">
+        <v>21</v>
       </c>
       <c r="D5" s="1">
         <v>46175</v>
@@ -854,7 +1071,7 @@
         <v>1.05</v>
       </c>
       <c r="O5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -865,7 +1082,7 @@
         <v>801</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
         <v>46176</v>
@@ -895,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -906,7 +1123,7 @@
         <v>800</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1">
         <v>46174</v>
@@ -936,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -946,8 +1163,8 @@
       <c r="B8">
         <v>338</v>
       </c>
-      <c r="C8">
-        <v>338</v>
+      <c r="C8" t="s">
+        <v>26</v>
       </c>
       <c r="D8" s="1">
         <v>46176</v>
@@ -968,7 +1185,7 @@
         <v>-7</v>
       </c>
       <c r="J8">
-        <v>0.69565217400000001</v>
+        <v>0.69565217391</v>
       </c>
       <c r="K8">
         <v>23</v>
@@ -980,10 +1197,10 @@
         <v>-7</v>
       </c>
       <c r="N8">
-        <v>0.69565217400000001</v>
+        <v>0.69565217391</v>
       </c>
       <c r="O8" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -993,8 +1210,8 @@
       <c r="B9">
         <v>336</v>
       </c>
-      <c r="C9">
-        <v>336</v>
+      <c r="C9" t="s">
+        <v>28</v>
       </c>
       <c r="D9" s="1">
         <v>46176</v>
@@ -1030,7 +1247,7 @@
         <v>0.75</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1040,8 +1257,8 @@
       <c r="B10">
         <v>340</v>
       </c>
-      <c r="C10">
-        <v>340</v>
+      <c r="C10" t="s">
+        <v>30</v>
       </c>
       <c r="D10" s="1">
         <v>46176</v>
@@ -1077,7 +1294,7 @@
         <v>0.68</v>
       </c>
       <c r="O10" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1087,8 +1304,8 @@
       <c r="B11">
         <v>337</v>
       </c>
-      <c r="C11">
-        <v>337</v>
+      <c r="C11" t="s">
+        <v>32</v>
       </c>
       <c r="D11" s="1">
         <v>46176</v>
@@ -1124,280 +1341,280 @@
         <v>0.8</v>
       </c>
       <c r="O11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>9230</v>
+        <v>9298</v>
       </c>
       <c r="B12">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D12" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="E12" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F12">
-        <v>20057</v>
+        <v>20052</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
+        <v>-40</v>
+      </c>
+      <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
+        <v>-40</v>
+      </c>
+      <c r="N12">
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>9220</v>
+        <v>9297</v>
       </c>
       <c r="B13">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D13" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="E13" s="1">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="F13">
-        <v>20005</v>
+        <v>20043</v>
       </c>
       <c r="G13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>-4</v>
-      </c>
-      <c r="J13">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>-4</v>
-      </c>
-      <c r="N13">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="O13" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>9221</v>
+        <v>9283</v>
       </c>
       <c r="B14">
-        <v>122</v>
+        <v>303</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D14" s="1">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="E14" s="1">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="F14">
-        <v>20130</v>
+        <v>20153</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>1.2972972972900001</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>1.2972972972900001</v>
       </c>
       <c r="O14" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>9240</v>
+        <v>9296</v>
       </c>
       <c r="B15">
-        <v>211</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D15" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="E15" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F15">
-        <v>20058</v>
+        <v>20106</v>
       </c>
       <c r="G15">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="H15">
+        <v>15</v>
+      </c>
+      <c r="I15">
+        <v>-23</v>
+      </c>
+      <c r="J15">
+        <v>0.39473684209999998</v>
+      </c>
+      <c r="K15">
+        <v>38</v>
+      </c>
+      <c r="L15">
+        <v>15</v>
+      </c>
+      <c r="M15">
+        <v>-23</v>
+      </c>
+      <c r="N15">
+        <v>0.39473684209999998</v>
+      </c>
+      <c r="O15" t="s">
         <v>40</v>
-      </c>
-      <c r="I15">
-        <v>-12</v>
-      </c>
-      <c r="J15">
-        <v>0.76923076899999998</v>
-      </c>
-      <c r="K15">
-        <v>52</v>
-      </c>
-      <c r="L15">
-        <v>40</v>
-      </c>
-      <c r="M15">
-        <v>-12</v>
-      </c>
-      <c r="N15">
-        <v>0.76923076899999998</v>
-      </c>
-      <c r="O15" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9242</v>
+        <v>9294</v>
       </c>
       <c r="B16">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D16" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="E16" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F16">
-        <v>20043</v>
+        <v>20095</v>
       </c>
       <c r="G16">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H16">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I16">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="J16">
-        <v>0.83333333300000001</v>
+        <v>0.7</v>
       </c>
       <c r="K16">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L16">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M16">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="N16">
-        <v>0.83333333300000001</v>
+        <v>0.7</v>
       </c>
       <c r="O16" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>9235</v>
+        <v>9290</v>
       </c>
       <c r="B17">
-        <v>205</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
         <v>43</v>
       </c>
       <c r="D17" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="E17" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F17">
-        <v>20047</v>
+        <v>11215</v>
       </c>
       <c r="G17">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H17">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I17">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="J17">
-        <v>0.76595744700000001</v>
+        <v>0.72727272727000003</v>
       </c>
       <c r="K17">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="L17">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="M17">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="N17">
-        <v>0.76595744700000001</v>
+        <v>0.72727272727000003</v>
       </c>
       <c r="O17" t="s">
         <v>44</v>
@@ -1405,248 +1622,242 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9234</v>
+        <v>9286</v>
       </c>
       <c r="B18">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="E18" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F18">
-        <v>20095</v>
+        <v>20076</v>
       </c>
       <c r="G18">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H18">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I18">
-        <v>-13</v>
+        <v>-22</v>
       </c>
       <c r="J18">
-        <v>0.70454545499999999</v>
+        <v>0.61403508771000004</v>
       </c>
       <c r="K18">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L18">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M18">
-        <v>-13</v>
+        <v>-22</v>
       </c>
       <c r="N18">
-        <v>0.70454545499999999</v>
+        <v>0.61403508771000004</v>
       </c>
       <c r="O18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>9243</v>
+        <v>9287</v>
       </c>
       <c r="B19">
-        <v>214</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D19" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="E19" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F19">
         <v>20086</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="O19" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>9236</v>
+        <v>9288</v>
       </c>
       <c r="B20">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D20" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="E20" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F20">
-        <v>20076</v>
+        <v>20153</v>
       </c>
       <c r="G20">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H20">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I20">
-        <v>-7</v>
+        <v>-25</v>
       </c>
       <c r="J20">
-        <v>0.80555555599999995</v>
+        <v>0.48979591836000003</v>
       </c>
       <c r="K20">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L20">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M20">
-        <v>-7</v>
+        <v>-25</v>
       </c>
       <c r="N20">
-        <v>0.80555555599999995</v>
+        <v>0.48979591836000003</v>
       </c>
       <c r="O20" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>9239</v>
+        <v>9230</v>
       </c>
       <c r="B21">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="E21" s="1">
         <v>46174</v>
       </c>
       <c r="F21">
-        <v>20105</v>
+        <v>20057</v>
       </c>
       <c r="G21">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>-12</v>
-      </c>
-      <c r="J21">
-        <v>0.675675676</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>-12</v>
-      </c>
-      <c r="N21">
-        <v>0.675675676</v>
+        <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>9237</v>
+        <v>9220</v>
       </c>
       <c r="B22">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="E22" s="1">
-        <v>46174</v>
+        <v>46172</v>
       </c>
       <c r="F22">
-        <v>20106</v>
+        <v>20005</v>
       </c>
       <c r="G22">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H22">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="J22">
-        <v>1.1000000000000001</v>
+        <v>0.66666666665999996</v>
       </c>
       <c r="K22">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="L22">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="N22">
-        <v>1.1000000000000001</v>
+        <v>0.66666666665999996</v>
       </c>
       <c r="O22" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>9232</v>
+        <v>9240</v>
       </c>
       <c r="B23">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D23" s="1">
         <v>46175</v>
@@ -1655,45 +1866,45 @@
         <v>46174</v>
       </c>
       <c r="F23">
-        <v>20153</v>
+        <v>20058</v>
       </c>
       <c r="G23">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="H23">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="I23">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="J23">
-        <v>0.75</v>
+        <v>0.76923076923</v>
       </c>
       <c r="K23">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="L23">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="M23">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="N23">
-        <v>0.75</v>
+        <v>0.76923076923</v>
       </c>
       <c r="O23" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>9238</v>
+        <v>9242</v>
       </c>
       <c r="B24">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D24" s="1">
         <v>46175</v>
@@ -1702,92 +1913,92 @@
         <v>46174</v>
       </c>
       <c r="F24">
-        <v>11215</v>
+        <v>20043</v>
       </c>
       <c r="G24">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="H24">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="J24">
-        <v>0.98</v>
+        <v>0.83333333333000004</v>
       </c>
       <c r="K24">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="L24">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="N24">
-        <v>0.98</v>
+        <v>0.83333333333000004</v>
       </c>
       <c r="O24" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>9233</v>
+        <v>9314</v>
       </c>
       <c r="B25">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D25" s="1">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="E25" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="F25">
         <v>20155</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0.91304347825999999</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0.91304347825999999</v>
       </c>
       <c r="O25" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>9241</v>
+        <v>9234</v>
       </c>
       <c r="B26">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D26" s="1">
         <v>46175</v>
@@ -1796,60 +2007,60 @@
         <v>46174</v>
       </c>
       <c r="F26">
-        <v>20057</v>
+        <v>20095</v>
       </c>
       <c r="G26">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="H26">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0.70454545453999995</v>
       </c>
       <c r="K26">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="L26">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0.70454545453999995</v>
       </c>
       <c r="O26" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>9223</v>
+        <v>9243</v>
       </c>
       <c r="B27">
-        <v>124</v>
+        <v>214</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D27" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E27" s="1">
         <v>46174</v>
       </c>
-      <c r="E27" s="1">
-        <v>46172</v>
-      </c>
       <c r="F27">
-        <v>20112</v>
+        <v>20086</v>
       </c>
       <c r="G27">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1858,10 +2069,10 @@
         <v>1</v>
       </c>
       <c r="K27">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -1870,65 +2081,65 @@
         <v>1</v>
       </c>
       <c r="O27" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>9225</v>
+        <v>9236</v>
       </c>
       <c r="B28">
-        <v>126</v>
-      </c>
-      <c r="C28">
-        <v>126</v>
+        <v>206</v>
+      </c>
+      <c r="C28" t="s">
+        <v>60</v>
       </c>
       <c r="D28" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E28" s="1">
         <v>46174</v>
       </c>
-      <c r="E28" s="1">
-        <v>46172</v>
-      </c>
       <c r="F28">
-        <v>20111</v>
+        <v>20076</v>
       </c>
       <c r="G28">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H28">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I28">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="J28">
-        <v>0.7</v>
+        <v>0.80555555555000002</v>
       </c>
       <c r="K28">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="L28">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="M28">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="N28">
-        <v>0.7</v>
+        <v>0.80555555555000002</v>
       </c>
       <c r="O28" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>9246</v>
+        <v>9239</v>
       </c>
       <c r="B29">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D29" s="1">
         <v>46175</v>
@@ -1937,45 +2148,45 @@
         <v>46174</v>
       </c>
       <c r="F29">
-        <v>20005</v>
+        <v>20105</v>
       </c>
       <c r="G29">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H29">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="I29">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="J29">
-        <v>0.89361702099999996</v>
+        <v>0.67567567566999998</v>
       </c>
       <c r="K29">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L29">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="M29">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="N29">
-        <v>0.89361702099999996</v>
+        <v>0.67567567566999998</v>
       </c>
       <c r="O29" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>9248</v>
+        <v>9237</v>
       </c>
       <c r="B30">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D30" s="1">
         <v>46175</v>
@@ -1984,45 +2195,45 @@
         <v>46174</v>
       </c>
       <c r="F30">
-        <v>200158</v>
+        <v>20106</v>
       </c>
       <c r="G30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H30">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K30">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L30">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O30" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9249</v>
+        <v>9232</v>
       </c>
       <c r="B31">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D31" s="1">
         <v>46175</v>
@@ -2031,45 +2242,45 @@
         <v>46174</v>
       </c>
       <c r="F31">
-        <v>20112</v>
+        <v>20153</v>
       </c>
       <c r="G31">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H31">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K31">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L31">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O31" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>9251</v>
+        <v>9238</v>
       </c>
       <c r="B32">
-        <v>226</v>
-      </c>
-      <c r="C32">
-        <v>226</v>
+        <v>208</v>
+      </c>
+      <c r="C32" t="s">
+        <v>64</v>
       </c>
       <c r="D32" s="1">
         <v>46175</v>
@@ -2078,92 +2289,92 @@
         <v>46174</v>
       </c>
       <c r="F32">
-        <v>20111</v>
+        <v>11215</v>
       </c>
       <c r="G32">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H32">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="I32">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="J32">
-        <v>0.7</v>
+        <v>0.98</v>
       </c>
       <c r="K32">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L32">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="M32">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="N32">
-        <v>0.7</v>
+        <v>0.98</v>
       </c>
       <c r="O32" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>9227</v>
+        <v>9233</v>
       </c>
       <c r="B33">
-        <v>128</v>
-      </c>
-      <c r="C33">
-        <v>128</v>
+        <v>203</v>
+      </c>
+      <c r="C33" t="s">
+        <v>65</v>
       </c>
       <c r="D33" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E33" s="1">
         <v>46174</v>
       </c>
-      <c r="E33" s="1">
-        <v>46172</v>
-      </c>
       <c r="F33">
-        <v>20007</v>
+        <v>20155</v>
       </c>
       <c r="G33">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>0.68571428599999995</v>
+        <v>1</v>
       </c>
       <c r="K33">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="L33">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M33">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>0.68571428599999995</v>
+        <v>1</v>
       </c>
       <c r="O33" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>9244</v>
+        <v>9241</v>
       </c>
       <c r="B34">
-        <v>500</v>
+        <v>212</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D34" s="1">
         <v>46175</v>
@@ -2172,459 +2383,459 @@
         <v>46174</v>
       </c>
       <c r="F34">
-        <v>200150</v>
+        <v>20057</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
       <c r="K34">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
       <c r="O34" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>9245</v>
+        <v>9223</v>
       </c>
       <c r="B35">
-        <v>501</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D35" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="E35" s="1">
-        <v>46174</v>
+        <v>46172</v>
       </c>
       <c r="F35">
-        <v>200150</v>
+        <v>20112</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
       <c r="K35">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
       <c r="O35" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>9280</v>
+        <v>9225</v>
       </c>
       <c r="B36">
-        <v>313</v>
+        <v>126</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D36" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="E36" s="1">
-        <v>46175</v>
+        <v>46172</v>
       </c>
       <c r="F36">
-        <v>11215</v>
+        <v>20111</v>
       </c>
       <c r="G36">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H36">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I36">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="J36">
-        <v>0.54545454500000001</v>
+        <v>0.7</v>
       </c>
       <c r="K36">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M36">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="N36">
-        <v>0.54545454500000001</v>
+        <v>0.7</v>
       </c>
       <c r="O36" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>9279</v>
+        <v>9246</v>
       </c>
       <c r="B37">
-        <v>312</v>
+        <v>221</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D37" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E37" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="F37">
-        <v>20095</v>
+        <v>20005</v>
       </c>
       <c r="G37">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="H37">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0.89361702126999998</v>
       </c>
       <c r="K37">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="L37">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0.89361702126999998</v>
       </c>
       <c r="O37" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>9281</v>
+        <v>9248</v>
       </c>
       <c r="B38">
-        <v>314</v>
+        <v>223</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D38" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E38" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="F38">
-        <v>20076</v>
+        <v>200158</v>
       </c>
       <c r="G38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H38">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I38">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L38">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="M38">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O38" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>9272</v>
+        <v>9249</v>
       </c>
       <c r="B39">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D39" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E39" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="F39">
-        <v>20058</v>
+        <v>20112</v>
       </c>
       <c r="G39">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="H39">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I39">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>0.46296296300000001</v>
+        <v>1</v>
       </c>
       <c r="K39">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="L39">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M39">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>0.46296296300000001</v>
+        <v>1</v>
       </c>
       <c r="O39" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>9274</v>
+        <v>9251</v>
       </c>
       <c r="B40">
-        <v>304</v>
+        <v>226</v>
       </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D40" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E40" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="F40">
-        <v>20086</v>
+        <v>20111</v>
       </c>
       <c r="G40">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H40">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="I40">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="J40">
-        <v>0.73809523799999999</v>
+        <v>0.7</v>
       </c>
       <c r="K40">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L40">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="M40">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="N40">
-        <v>0.73809523799999999</v>
+        <v>0.7</v>
       </c>
       <c r="O40" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>9283</v>
+        <v>9227</v>
       </c>
       <c r="B41">
-        <v>303</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D41" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="E41" s="1">
-        <v>46175</v>
+        <v>46172</v>
       </c>
       <c r="F41">
-        <v>20153</v>
+        <v>20007</v>
       </c>
       <c r="G41">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H41">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="I41">
-        <v>11</v>
+        <v>-11</v>
       </c>
       <c r="J41">
-        <v>1.2972972970000001</v>
+        <v>0.68571428571000004</v>
       </c>
       <c r="K41">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L41">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="M41">
-        <v>11</v>
+        <v>-11</v>
       </c>
       <c r="N41">
-        <v>1.2972972970000001</v>
+        <v>0.68571428571000004</v>
       </c>
       <c r="O41" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>9275</v>
+        <v>9244</v>
       </c>
       <c r="B42">
-        <v>305</v>
+        <v>500</v>
       </c>
       <c r="C42" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D42" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E42" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="F42">
-        <v>20043</v>
+        <v>200150</v>
       </c>
       <c r="G42">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>2</v>
-      </c>
-      <c r="J42">
-        <v>1.043478261</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>2</v>
-      </c>
-      <c r="N42">
-        <v>1.043478261</v>
+        <v>0</v>
       </c>
       <c r="O42" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>9276</v>
+        <v>9245</v>
       </c>
       <c r="B43">
-        <v>307</v>
+        <v>501</v>
       </c>
       <c r="C43" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D43" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E43" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="F43">
-        <v>20105</v>
+        <v>200150</v>
       </c>
       <c r="G43">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>-6</v>
-      </c>
-      <c r="J43">
-        <v>0.86666666699999995</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>-6</v>
-      </c>
-      <c r="N43">
-        <v>0.86666666699999995</v>
+        <v>0</v>
       </c>
       <c r="O43" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>9277</v>
+        <v>9278</v>
       </c>
       <c r="B44">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D44" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E44" s="1">
         <v>46175</v>
@@ -2633,42 +2844,42 @@
         <v>20057</v>
       </c>
       <c r="G44">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H44">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>0.88888888887999995</v>
       </c>
       <c r="K44">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L44">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>0.88888888887999995</v>
       </c>
       <c r="O44" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>9278</v>
+        <v>9280</v>
       </c>
       <c r="B45">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C45" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D45" s="1">
         <v>46176</v>
@@ -2677,31 +2888,31 @@
         <v>46175</v>
       </c>
       <c r="F45">
-        <v>20047</v>
+        <v>11215</v>
       </c>
       <c r="G45">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="H45">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I45">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="J45">
-        <v>0.88888888899999996</v>
+        <v>0.54545454545000005</v>
       </c>
       <c r="K45">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="L45">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="M45">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="N45">
-        <v>0.88888888899999996</v>
+        <v>0.54545454545000005</v>
       </c>
       <c r="O45" t="s">
         <v>44</v>
@@ -2709,13 +2920,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>9262</v>
+        <v>9279</v>
       </c>
       <c r="B46">
-        <v>331</v>
-      </c>
-      <c r="C46">
-        <v>331</v>
+        <v>312</v>
+      </c>
+      <c r="C46" t="s">
+        <v>80</v>
       </c>
       <c r="D46" s="1">
         <v>46176</v>
@@ -2724,92 +2935,92 @@
         <v>46175</v>
       </c>
       <c r="F46">
-        <v>20006</v>
+        <v>20095</v>
       </c>
       <c r="G46">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H46">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I46">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>0.63636363600000001</v>
+        <v>1</v>
       </c>
       <c r="K46">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L46">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M46">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>0.63636363600000001</v>
+        <v>1</v>
       </c>
       <c r="O46" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>9253</v>
+        <v>9281</v>
       </c>
       <c r="B47">
-        <v>228</v>
-      </c>
-      <c r="C47">
-        <v>228</v>
+        <v>314</v>
+      </c>
+      <c r="C47" t="s">
+        <v>81</v>
       </c>
       <c r="D47" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E47" s="1">
         <v>46175</v>
       </c>
-      <c r="E47" s="1">
-        <v>46174</v>
-      </c>
       <c r="F47">
-        <v>20007</v>
+        <v>20076</v>
       </c>
       <c r="G47">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H47">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I47">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J47">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K47">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="L47">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="M47">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="N47">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="O47" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>9263</v>
+        <v>9272</v>
       </c>
       <c r="B48">
-        <v>332</v>
-      </c>
-      <c r="C48">
-        <v>332</v>
+        <v>302</v>
+      </c>
+      <c r="C48" t="s">
+        <v>82</v>
       </c>
       <c r="D48" s="1">
         <v>46176</v>
@@ -2818,532 +3029,562 @@
         <v>46175</v>
       </c>
       <c r="F48">
-        <v>20130</v>
+        <v>20058</v>
       </c>
       <c r="G48">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="H48">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="J48">
-        <v>1</v>
+        <v>0.46296296296</v>
       </c>
       <c r="K48">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L48">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0.46296296296</v>
       </c>
       <c r="O48" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>9247</v>
+        <v>9325</v>
       </c>
       <c r="B49">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="D49" s="1">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="E49" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="F49">
-        <v>20130</v>
+        <v>20005</v>
       </c>
       <c r="G49">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H49">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0.68571428571000004</v>
       </c>
       <c r="K49">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L49">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="N49">
-        <v>1</v>
+        <v>0.68571428571000004</v>
       </c>
       <c r="O49" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>9228</v>
+        <v>9291</v>
       </c>
       <c r="B50">
-        <v>129</v>
-      </c>
-      <c r="C50">
-        <v>129</v>
+        <v>107</v>
+      </c>
+      <c r="C50" t="s">
+        <v>84</v>
       </c>
       <c r="D50" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="E50" s="1">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="F50">
-        <v>20008</v>
+        <v>20155</v>
       </c>
       <c r="G50">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H50">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I50">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="J50">
-        <v>0.66666666699999999</v>
+        <v>0.77419354837999999</v>
       </c>
       <c r="K50">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="L50">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="M50">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="N50">
-        <v>0.66666666699999999</v>
+        <v>0.77419354837999999</v>
       </c>
       <c r="O50" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>9229</v>
+        <v>9275</v>
       </c>
       <c r="B51">
-        <v>130</v>
-      </c>
-      <c r="C51">
-        <v>130</v>
+        <v>305</v>
+      </c>
+      <c r="C51" t="s">
+        <v>85</v>
       </c>
       <c r="D51" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="E51" s="1">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="F51">
-        <v>20006</v>
+        <v>20043</v>
       </c>
       <c r="G51">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H51">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I51">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>0.85714285700000004</v>
+        <v>1.04347826086</v>
       </c>
       <c r="K51">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="L51">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="M51">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="N51">
-        <v>0.85714285700000004</v>
+        <v>1.04347826086</v>
       </c>
       <c r="O51" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>9259</v>
+        <v>9276</v>
       </c>
       <c r="B52">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D52" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="E52" s="1">
         <v>46175</v>
       </c>
       <c r="F52">
-        <v>20047</v>
+        <v>20105</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J52">
+        <v>0.86666666666000003</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N52">
+        <v>0.86666666666000003</v>
       </c>
       <c r="O52" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>9260</v>
+        <v>9277</v>
       </c>
       <c r="B53">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C53" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D53" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="E53" s="1">
         <v>46175</v>
       </c>
       <c r="F53">
-        <v>20047</v>
+        <v>20057</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
       <c r="K53">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M53">
         <v>0</v>
       </c>
+      <c r="N53">
+        <v>1</v>
+      </c>
       <c r="O53" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>9226</v>
+        <v>9262</v>
       </c>
       <c r="B54">
-        <v>127</v>
-      </c>
-      <c r="C54">
-        <v>127</v>
+        <v>331</v>
+      </c>
+      <c r="C54" t="s">
+        <v>88</v>
       </c>
       <c r="D54" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="E54" s="1">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="F54">
-        <v>20003</v>
+        <v>20006</v>
       </c>
       <c r="G54">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I54">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="J54">
-        <v>0.125</v>
+        <v>0.63636363636000004</v>
       </c>
       <c r="K54">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="L54">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="M54">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="N54">
-        <v>0.125</v>
+        <v>0.63636363636000004</v>
       </c>
       <c r="O54" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>9222</v>
+        <v>9253</v>
       </c>
       <c r="B55">
-        <v>123</v>
+        <v>228</v>
       </c>
       <c r="C55" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D55" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E55" s="1">
         <v>46174</v>
       </c>
-      <c r="E55" s="1">
-        <v>46172</v>
-      </c>
       <c r="F55">
-        <v>200158</v>
+        <v>20007</v>
       </c>
       <c r="G55">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H55">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K55">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M55">
-        <v>-26</v>
+        <v>-5</v>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O55" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>9224</v>
+        <v>9263</v>
       </c>
       <c r="B56">
-        <v>125</v>
+        <v>332</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="D56" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="E56" s="1">
-        <v>46172</v>
+        <v>46175</v>
       </c>
       <c r="F56">
-        <v>20066</v>
+        <v>20130</v>
       </c>
       <c r="G56">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="H56">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="I56">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>0.85576923100000002</v>
+        <v>1</v>
       </c>
       <c r="K56">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M56">
-        <v>-104</v>
+        <v>0</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>9256</v>
+        <v>9247</v>
       </c>
       <c r="B57">
-        <v>800</v>
+        <v>222</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D57" s="1">
         <v>46175</v>
       </c>
       <c r="E57" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="F57">
-        <v>200150</v>
+        <v>20130</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
       <c r="K57">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M57">
         <v>0</v>
       </c>
+      <c r="N57">
+        <v>1</v>
+      </c>
       <c r="O57" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>9257</v>
+        <v>9228</v>
       </c>
       <c r="B58">
-        <v>800</v>
+        <v>129</v>
       </c>
       <c r="C58" t="s">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="D58" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="E58" s="1">
-        <v>46175</v>
+        <v>46172</v>
       </c>
       <c r="F58">
-        <v>200150</v>
+        <v>20008</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J58">
+        <v>0.66666666665999996</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N58">
+        <v>0.66666666665999996</v>
       </c>
       <c r="O58" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>9284</v>
+        <v>9229</v>
       </c>
       <c r="B59">
-        <v>800</v>
+        <v>130</v>
       </c>
       <c r="C59" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="D59" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="E59" s="1">
-        <v>46176</v>
+        <v>46172</v>
       </c>
       <c r="F59">
-        <v>200150</v>
+        <v>20006</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J59">
+        <v>0.85714285714000005</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="N59">
+        <v>0.85714285714000005</v>
       </c>
       <c r="O59" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>9261</v>
+        <v>9259</v>
       </c>
       <c r="B60">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D60" s="1">
         <v>46175</v>
@@ -3373,127 +3614,121 @@
         <v>0</v>
       </c>
       <c r="O60" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>9258</v>
+        <v>9260</v>
       </c>
       <c r="B61">
-        <v>503</v>
+        <v>302</v>
       </c>
       <c r="C61" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D61" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E61" s="1">
         <v>46175</v>
       </c>
       <c r="F61">
-        <v>20048</v>
+        <v>20047</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
       <c r="I61">
-        <v>-1</v>
-      </c>
-      <c r="J61">
         <v>0</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
       <c r="M61">
-        <v>-1</v>
-      </c>
-      <c r="N61">
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>9309</v>
+        <v>9226</v>
       </c>
       <c r="B62">
-        <v>500</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="D62" s="1">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="E62" s="1">
-        <v>46177</v>
+        <v>46172</v>
       </c>
       <c r="F62">
-        <v>200150</v>
+        <v>20003</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="J62">
+        <v>0.125</v>
+      </c>
+      <c r="K62">
+        <v>8</v>
+      </c>
+      <c r="L62">
         <v>1</v>
       </c>
-      <c r="K62">
-        <v>2</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
       <c r="M62">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="O62" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>9310</v>
+        <v>9222</v>
       </c>
       <c r="B63">
-        <v>500</v>
+        <v>123</v>
       </c>
       <c r="C63" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="D63" s="1">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="E63" s="1">
-        <v>46177</v>
+        <v>46172</v>
       </c>
       <c r="F63">
-        <v>200150</v>
+        <v>200158</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3502,71 +3737,77 @@
         <v>1</v>
       </c>
       <c r="K63">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63">
-        <v>-1</v>
+        <v>-26</v>
       </c>
       <c r="N63">
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>9270</v>
+        <v>9224</v>
       </c>
       <c r="B64">
-        <v>339</v>
-      </c>
-      <c r="C64">
-        <v>339</v>
+        <v>125</v>
+      </c>
+      <c r="C64" t="s">
+        <v>98</v>
       </c>
       <c r="D64" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="E64" s="1">
-        <v>46175</v>
+        <v>46172</v>
       </c>
       <c r="F64">
-        <v>20008</v>
+        <v>20066</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="J64">
+        <v>0.85576923076</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64">
+        <v>-104</v>
+      </c>
+      <c r="N64">
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>9273</v>
+        <v>9256</v>
       </c>
       <c r="B65">
-        <v>303</v>
+        <v>800</v>
       </c>
       <c r="C65" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="D65" s="1">
         <v>46175</v>
@@ -3575,7 +3816,7 @@
         <v>46175</v>
       </c>
       <c r="F65">
-        <v>20153</v>
+        <v>200150</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -3596,27 +3837,27 @@
         <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>9282</v>
+        <v>9257</v>
       </c>
       <c r="B66">
-        <v>315</v>
+        <v>800</v>
       </c>
       <c r="C66" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="D66" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E66" s="1">
         <v>46175</v>
       </c>
       <c r="F66">
-        <v>20106</v>
+        <v>200150</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3637,18 +3878,18 @@
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>9297</v>
+        <v>9284</v>
       </c>
       <c r="B67">
-        <v>113</v>
+        <v>800</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="D67" s="1">
         <v>46176</v>
@@ -3657,7 +3898,7 @@
         <v>46176</v>
       </c>
       <c r="F67">
-        <v>20043</v>
+        <v>200150</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -3678,191 +3919,215 @@
         <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>9298</v>
+        <v>9292</v>
       </c>
       <c r="B68">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D68" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E68" s="1">
         <v>46176</v>
       </c>
       <c r="F68">
-        <v>200150</v>
+        <v>20057</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J68">
+        <v>0.96666666666000001</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="N68">
+        <v>0.96666666666000001</v>
       </c>
       <c r="O68" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>9299</v>
+        <v>9293</v>
       </c>
       <c r="B69">
-        <v>131</v>
-      </c>
-      <c r="C69">
-        <v>131</v>
+        <v>109</v>
+      </c>
+      <c r="C69" t="s">
+        <v>100</v>
       </c>
       <c r="D69" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E69" s="1">
         <v>46176</v>
       </c>
       <c r="F69">
-        <v>20005</v>
+        <v>20105</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>0</v>
       </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
       <c r="K69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69">
         <v>0</v>
       </c>
+      <c r="N69">
+        <v>1</v>
+      </c>
       <c r="O69" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>9300</v>
+        <v>9295</v>
       </c>
       <c r="B70">
-        <v>132</v>
-      </c>
-      <c r="C70">
-        <v>132</v>
+        <v>111</v>
+      </c>
+      <c r="C70" t="s">
+        <v>101</v>
       </c>
       <c r="D70" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E70" s="1">
         <v>46176</v>
       </c>
       <c r="F70">
-        <v>20130</v>
+        <v>20047</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="J70">
+        <v>0.7</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="N70">
+        <v>0.7</v>
       </c>
       <c r="O70" t="s">
-        <v>22</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>9301</v>
+        <v>9299</v>
       </c>
       <c r="B71">
-        <v>133</v>
-      </c>
-      <c r="C71">
-        <v>133</v>
+        <v>131</v>
+      </c>
+      <c r="C71" t="s">
+        <v>102</v>
       </c>
       <c r="D71" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E71" s="1">
         <v>46176</v>
       </c>
       <c r="F71">
-        <v>200158</v>
+        <v>20005</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J71">
+        <v>0.8</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N71">
+        <v>0.8</v>
       </c>
       <c r="O71" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>9302</v>
+        <v>9326</v>
       </c>
       <c r="B72">
-        <v>134</v>
-      </c>
-      <c r="C72">
-        <v>134</v>
+        <v>232</v>
+      </c>
+      <c r="C72" t="s">
+        <v>103</v>
       </c>
       <c r="D72" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E72" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F72">
-        <v>20112</v>
+        <v>20130</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -3883,27 +4148,27 @@
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>9303</v>
+        <v>9331</v>
       </c>
       <c r="B73">
-        <v>135</v>
-      </c>
-      <c r="C73">
-        <v>135</v>
+        <v>237</v>
+      </c>
+      <c r="C73" t="s">
+        <v>104</v>
       </c>
       <c r="D73" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E73" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F73">
-        <v>20113</v>
+        <v>20003</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -3924,27 +4189,27 @@
         <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>9304</v>
+        <v>9333</v>
       </c>
       <c r="B74">
-        <v>136</v>
-      </c>
-      <c r="C74">
-        <v>136</v>
+        <v>239</v>
+      </c>
+      <c r="C74" t="s">
+        <v>105</v>
       </c>
       <c r="D74" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E74" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F74">
-        <v>20111</v>
+        <v>20008</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -3965,27 +4230,27 @@
         <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>9305</v>
+        <v>9337</v>
       </c>
       <c r="B75">
-        <v>137</v>
-      </c>
-      <c r="C75">
-        <v>137</v>
+        <v>800</v>
+      </c>
+      <c r="C75" t="s">
+        <v>25</v>
       </c>
       <c r="D75" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E75" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="F75">
-        <v>20003</v>
+        <v>200150</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -4011,22 +4276,22 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>9306</v>
+        <v>9341</v>
       </c>
       <c r="B76">
-        <v>138</v>
-      </c>
-      <c r="C76">
-        <v>138</v>
+        <v>800</v>
+      </c>
+      <c r="C76" t="s">
+        <v>25</v>
       </c>
       <c r="D76" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E76" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="F76">
-        <v>20007</v>
+        <v>200150</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -4047,109 +4312,121 @@
         <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>9307</v>
+        <v>9321</v>
       </c>
       <c r="B77">
-        <v>139</v>
-      </c>
-      <c r="C77">
-        <v>139</v>
+        <v>210</v>
+      </c>
+      <c r="C77" t="s">
+        <v>106</v>
       </c>
       <c r="D77" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E77" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F77">
-        <v>20008</v>
+        <v>20095</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J77">
+        <v>0.65517241379000002</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="N77">
+        <v>0.65517241379000002</v>
       </c>
       <c r="O77" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>9308</v>
+        <v>9339</v>
       </c>
       <c r="B78">
-        <v>140</v>
-      </c>
-      <c r="C78">
-        <v>140</v>
+        <v>501</v>
+      </c>
+      <c r="C78" t="s">
+        <v>77</v>
       </c>
       <c r="D78" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E78" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="F78">
-        <v>20006</v>
+        <v>11215</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I78">
         <v>0</v>
       </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
       <c r="K78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M78">
         <v>0</v>
       </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
       <c r="O78" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>9286</v>
+        <v>9324</v>
       </c>
       <c r="B79">
-        <v>101</v>
+        <v>214</v>
       </c>
       <c r="C79" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D79" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E79" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F79">
-        <v>20076</v>
+        <v>11215</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -4170,109 +4447,121 @@
         <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>9287</v>
+        <v>9319</v>
       </c>
       <c r="B80">
-        <v>102</v>
+        <v>206</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D80" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E80" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F80">
-        <v>20086</v>
+        <v>20106</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="J80">
+        <v>0.4</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="N80">
+        <v>0.4</v>
       </c>
       <c r="O80" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>9288</v>
+        <v>9316</v>
       </c>
       <c r="B81">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="C81" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D81" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E81" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F81">
-        <v>20153</v>
+        <v>20086</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="J81">
+        <v>0.70588235294000001</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="N81">
+        <v>0.70588235294000001</v>
       </c>
       <c r="O81" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>9289</v>
+        <v>9261</v>
       </c>
       <c r="B82">
-        <v>105</v>
+        <v>303</v>
       </c>
       <c r="C82" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="D82" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E82" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="F82">
-        <v>20058</v>
+        <v>20047</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -4293,68 +4582,74 @@
         <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>9290</v>
+        <v>9258</v>
       </c>
       <c r="B83">
-        <v>106</v>
+        <v>503</v>
       </c>
       <c r="C83" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="D83" s="1">
         <v>46176</v>
       </c>
       <c r="E83" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="F83">
-        <v>11215</v>
+        <v>20048</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83">
         <v>0</v>
       </c>
       <c r="I83">
+        <v>-1</v>
+      </c>
+      <c r="J83">
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
       <c r="M83">
+        <v>-1</v>
+      </c>
+      <c r="N83">
         <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>9291</v>
+        <v>9336</v>
       </c>
       <c r="B84">
-        <v>107</v>
+        <v>501</v>
       </c>
       <c r="C84" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D84" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="E84" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="F84">
-        <v>20155</v>
+        <v>200150</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -4375,109 +4670,121 @@
         <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>9292</v>
+        <v>9309</v>
       </c>
       <c r="B85">
-        <v>108</v>
+        <v>500</v>
       </c>
       <c r="C85" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D85" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E85" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F85">
-        <v>20057</v>
+        <v>200150</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I85">
         <v>0</v>
       </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
       <c r="K85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85">
         <v>0</v>
       </c>
       <c r="M85">
+        <v>-2</v>
+      </c>
+      <c r="N85">
         <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>9293</v>
+        <v>9310</v>
       </c>
       <c r="B86">
-        <v>109</v>
+        <v>500</v>
       </c>
       <c r="C86" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D86" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E86" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F86">
-        <v>20105</v>
+        <v>200150</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86">
         <v>0</v>
       </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
       <c r="K86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86">
         <v>0</v>
       </c>
       <c r="M86">
+        <v>-1</v>
+      </c>
+      <c r="N86">
         <v>0</v>
       </c>
       <c r="O86" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>9294</v>
+        <v>9311</v>
       </c>
       <c r="B87">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="C87" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D87" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E87" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F87">
-        <v>20095</v>
+        <v>200150</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -4498,194 +4805,200 @@
         <v>0</v>
       </c>
       <c r="O87" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>9295</v>
+        <v>9312</v>
       </c>
       <c r="B88">
-        <v>111</v>
+        <v>500</v>
       </c>
       <c r="C88" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D88" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E88" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F88">
-        <v>20047</v>
+        <v>200150</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88">
         <v>0</v>
       </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
       <c r="K88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
       <c r="M88">
+        <v>-1</v>
+      </c>
+      <c r="N88">
         <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>9296</v>
+        <v>9235</v>
       </c>
       <c r="B89">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="C89" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D89" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="E89" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="F89">
-        <v>20106</v>
+        <v>20047</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="J89">
+        <v>0.7659574468</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="N89">
+        <v>0.7659574468</v>
       </c>
       <c r="O89" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>9266</v>
+        <v>9313</v>
       </c>
       <c r="B90">
-        <v>335</v>
-      </c>
-      <c r="C90">
-        <v>335</v>
+        <v>800</v>
+      </c>
+      <c r="C90" t="s">
+        <v>25</v>
       </c>
       <c r="D90" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="E90" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="F90">
-        <v>20066</v>
+        <v>200150</v>
       </c>
       <c r="G90">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I90">
-        <v>-10</v>
-      </c>
-      <c r="J90">
-        <v>0.44444444399999999</v>
+        <v>0</v>
       </c>
       <c r="K90">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L90">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>-10</v>
-      </c>
-      <c r="N90">
-        <v>0.44444444399999999</v>
+        <v>0</v>
       </c>
       <c r="O90" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>9265</v>
+        <v>9274</v>
       </c>
       <c r="B91">
-        <v>334</v>
-      </c>
-      <c r="C91">
-        <v>334</v>
+        <v>304</v>
+      </c>
+      <c r="C91" t="s">
+        <v>110</v>
       </c>
       <c r="D91" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="E91" s="1">
         <v>46175</v>
       </c>
       <c r="F91">
-        <v>20112</v>
+        <v>20086</v>
       </c>
       <c r="G91">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H91">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I91">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="J91">
-        <v>0.85714285700000004</v>
+        <v>0.73809523808999999</v>
       </c>
       <c r="K91">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="L91">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="M91">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="N91">
-        <v>0.85714285700000004</v>
+        <v>0.73809523808999999</v>
       </c>
       <c r="O91" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>9264</v>
+        <v>9270</v>
       </c>
       <c r="B92">
-        <v>333</v>
-      </c>
-      <c r="C92">
-        <v>333</v>
+        <v>339</v>
+      </c>
+      <c r="C92" t="s">
+        <v>111</v>
       </c>
       <c r="D92" s="1">
         <v>46176</v>
@@ -4694,34 +5007,3323 @@
         <v>46175</v>
       </c>
       <c r="F92">
+        <v>20008</v>
+      </c>
+      <c r="G92">
+        <v>20</v>
+      </c>
+      <c r="H92">
+        <v>16</v>
+      </c>
+      <c r="I92">
+        <v>-4</v>
+      </c>
+      <c r="J92">
+        <v>0.8</v>
+      </c>
+      <c r="K92">
+        <v>20</v>
+      </c>
+      <c r="L92">
+        <v>16</v>
+      </c>
+      <c r="M92">
+        <v>-4</v>
+      </c>
+      <c r="N92">
+        <v>0.8</v>
+      </c>
+      <c r="O92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>9307</v>
+      </c>
+      <c r="B93">
+        <v>139</v>
+      </c>
+      <c r="C93" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E93" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F93">
+        <v>20008</v>
+      </c>
+      <c r="G93">
+        <v>15</v>
+      </c>
+      <c r="H93">
+        <v>12</v>
+      </c>
+      <c r="I93">
+        <v>-3</v>
+      </c>
+      <c r="J93">
+        <v>0.8</v>
+      </c>
+      <c r="K93">
+        <v>15</v>
+      </c>
+      <c r="L93">
+        <v>12</v>
+      </c>
+      <c r="M93">
+        <v>-3</v>
+      </c>
+      <c r="N93">
+        <v>0.8</v>
+      </c>
+      <c r="O93" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>9301</v>
+      </c>
+      <c r="B94">
+        <v>133</v>
+      </c>
+      <c r="C94" t="s">
+        <v>113</v>
+      </c>
+      <c r="D94" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E94" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F94">
         <v>200158</v>
       </c>
-      <c r="G92">
+      <c r="G94">
+        <v>18</v>
+      </c>
+      <c r="H94">
+        <v>18</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>18</v>
+      </c>
+      <c r="L94">
+        <v>18</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>9304</v>
+      </c>
+      <c r="B95">
+        <v>136</v>
+      </c>
+      <c r="C95" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E95" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F95">
+        <v>20111</v>
+      </c>
+      <c r="G95">
+        <v>14</v>
+      </c>
+      <c r="H95">
+        <v>10</v>
+      </c>
+      <c r="I95">
+        <v>-4</v>
+      </c>
+      <c r="J95">
+        <v>0.71428571427999998</v>
+      </c>
+      <c r="K95">
+        <v>14</v>
+      </c>
+      <c r="L95">
+        <v>10</v>
+      </c>
+      <c r="M95">
+        <v>-4</v>
+      </c>
+      <c r="N95">
+        <v>0.71428571427999998</v>
+      </c>
+      <c r="O95" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>9273</v>
+      </c>
+      <c r="B96">
+        <v>303</v>
+      </c>
+      <c r="C96" t="s">
+        <v>37</v>
+      </c>
+      <c r="D96" s="1">
+        <v>46175</v>
+      </c>
+      <c r="E96" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F96">
+        <v>20153</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="O96" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>9306</v>
+      </c>
+      <c r="B97">
+        <v>138</v>
+      </c>
+      <c r="C97" t="s">
+        <v>115</v>
+      </c>
+      <c r="D97" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E97" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F97">
+        <v>20007</v>
+      </c>
+      <c r="G97">
+        <v>33</v>
+      </c>
+      <c r="H97">
         <v>23</v>
       </c>
-      <c r="H92">
+      <c r="I97">
+        <v>-10</v>
+      </c>
+      <c r="J97">
+        <v>0.69696969696</v>
+      </c>
+      <c r="K97">
+        <v>33</v>
+      </c>
+      <c r="L97">
         <v>23</v>
       </c>
-      <c r="I92">
-        <v>0</v>
-      </c>
-      <c r="J92">
+      <c r="M97">
+        <v>-10</v>
+      </c>
+      <c r="N97">
+        <v>0.69696969696</v>
+      </c>
+      <c r="O97" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>9308</v>
+      </c>
+      <c r="B98">
+        <v>140</v>
+      </c>
+      <c r="C98" t="s">
+        <v>116</v>
+      </c>
+      <c r="D98" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E98" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F98">
+        <v>20006</v>
+      </c>
+      <c r="G98">
+        <v>23</v>
+      </c>
+      <c r="H98">
+        <v>22</v>
+      </c>
+      <c r="I98">
+        <v>-1</v>
+      </c>
+      <c r="J98">
+        <v>0.95652173913000005</v>
+      </c>
+      <c r="K98">
+        <v>23</v>
+      </c>
+      <c r="L98">
+        <v>22</v>
+      </c>
+      <c r="M98">
+        <v>-1</v>
+      </c>
+      <c r="N98">
+        <v>0.95652173913000005</v>
+      </c>
+      <c r="O98" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>9303</v>
+      </c>
+      <c r="B99">
+        <v>135</v>
+      </c>
+      <c r="C99" t="s">
+        <v>117</v>
+      </c>
+      <c r="D99" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E99" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F99">
+        <v>20113</v>
+      </c>
+      <c r="G99">
+        <v>16</v>
+      </c>
+      <c r="H99">
+        <v>14</v>
+      </c>
+      <c r="I99">
+        <v>-2</v>
+      </c>
+      <c r="J99">
+        <v>0.875</v>
+      </c>
+      <c r="K99">
+        <v>16</v>
+      </c>
+      <c r="L99">
+        <v>14</v>
+      </c>
+      <c r="M99">
+        <v>-2</v>
+      </c>
+      <c r="N99">
+        <v>0.875</v>
+      </c>
+      <c r="O99" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>9300</v>
+      </c>
+      <c r="B100">
+        <v>132</v>
+      </c>
+      <c r="C100" t="s">
+        <v>119</v>
+      </c>
+      <c r="D100" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E100" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F100">
+        <v>20130</v>
+      </c>
+      <c r="G100">
+        <v>15</v>
+      </c>
+      <c r="H100">
+        <v>15</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
         <v>1</v>
       </c>
-      <c r="K92">
+      <c r="K100">
+        <v>15</v>
+      </c>
+      <c r="L100">
+        <v>15</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>9342</v>
+      </c>
+      <c r="B101">
+        <v>500</v>
+      </c>
+      <c r="C101" t="s">
+        <v>76</v>
+      </c>
+      <c r="D101" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E101" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F101">
+        <v>20048</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="O101" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>9335</v>
+      </c>
+      <c r="B102">
+        <v>500</v>
+      </c>
+      <c r="C102" t="s">
+        <v>76</v>
+      </c>
+      <c r="D102" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E102" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F102">
+        <v>200150</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="O102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>9340</v>
+      </c>
+      <c r="B103">
+        <v>331</v>
+      </c>
+      <c r="C103" t="s">
+        <v>88</v>
+      </c>
+      <c r="D103" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E103" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F103">
+        <v>20006</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="O103" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>9315</v>
+      </c>
+      <c r="B104">
+        <v>202</v>
+      </c>
+      <c r="C104" t="s">
+        <v>50</v>
+      </c>
+      <c r="D104" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E104" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F104">
+        <v>20057</v>
+      </c>
+      <c r="G104">
+        <v>34</v>
+      </c>
+      <c r="H104">
+        <v>32</v>
+      </c>
+      <c r="I104">
+        <v>-2</v>
+      </c>
+      <c r="J104">
+        <v>0.94117647057999998</v>
+      </c>
+      <c r="K104">
+        <v>34</v>
+      </c>
+      <c r="L104">
+        <v>32</v>
+      </c>
+      <c r="M104">
+        <v>-2</v>
+      </c>
+      <c r="N104">
+        <v>0.94117647057999998</v>
+      </c>
+      <c r="O104" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>9282</v>
+      </c>
+      <c r="B105">
+        <v>315</v>
+      </c>
+      <c r="C105" t="s">
+        <v>120</v>
+      </c>
+      <c r="D105" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E105" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F105">
+        <v>20106</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="O105" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>9317</v>
+      </c>
+      <c r="B106">
+        <v>204</v>
+      </c>
+      <c r="C106" t="s">
+        <v>58</v>
+      </c>
+      <c r="D106" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E106" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F106">
+        <v>20076</v>
+      </c>
+      <c r="G106">
+        <v>28</v>
+      </c>
+      <c r="H106">
+        <v>25</v>
+      </c>
+      <c r="I106">
+        <v>-3</v>
+      </c>
+      <c r="J106">
+        <v>0.89285714284999995</v>
+      </c>
+      <c r="K106">
+        <v>28</v>
+      </c>
+      <c r="L106">
+        <v>25</v>
+      </c>
+      <c r="M106">
+        <v>-3</v>
+      </c>
+      <c r="N106">
+        <v>0.89285714284999995</v>
+      </c>
+      <c r="O106" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>9318</v>
+      </c>
+      <c r="B107">
+        <v>205</v>
+      </c>
+      <c r="C107" t="s">
+        <v>109</v>
+      </c>
+      <c r="D107" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E107" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F107">
+        <v>20047</v>
+      </c>
+      <c r="G107">
+        <v>64</v>
+      </c>
+      <c r="H107">
+        <v>45</v>
+      </c>
+      <c r="I107">
+        <v>-19</v>
+      </c>
+      <c r="J107">
+        <v>0.703125</v>
+      </c>
+      <c r="K107">
+        <v>64</v>
+      </c>
+      <c r="L107">
+        <v>45</v>
+      </c>
+      <c r="M107">
+        <v>-19</v>
+      </c>
+      <c r="N107">
+        <v>0.703125</v>
+      </c>
+      <c r="O107" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>9302</v>
+      </c>
+      <c r="B108">
+        <v>134</v>
+      </c>
+      <c r="C108" t="s">
+        <v>121</v>
+      </c>
+      <c r="D108" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E108" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F108">
+        <v>20112</v>
+      </c>
+      <c r="G108">
+        <v>13</v>
+      </c>
+      <c r="H108">
+        <v>10</v>
+      </c>
+      <c r="I108">
+        <v>-3</v>
+      </c>
+      <c r="J108">
+        <v>0.76923076923</v>
+      </c>
+      <c r="K108">
+        <v>13</v>
+      </c>
+      <c r="L108">
+        <v>10</v>
+      </c>
+      <c r="M108">
+        <v>-3</v>
+      </c>
+      <c r="N108">
+        <v>0.76923076923</v>
+      </c>
+      <c r="O108" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>9320</v>
+      </c>
+      <c r="B109">
+        <v>209</v>
+      </c>
+      <c r="C109" t="s">
+        <v>61</v>
+      </c>
+      <c r="D109" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E109" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F109">
+        <v>20105</v>
+      </c>
+      <c r="G109">
+        <v>34</v>
+      </c>
+      <c r="H109">
+        <v>30</v>
+      </c>
+      <c r="I109">
+        <v>-4</v>
+      </c>
+      <c r="J109">
+        <v>0.88235294116999996</v>
+      </c>
+      <c r="K109">
+        <v>34</v>
+      </c>
+      <c r="L109">
+        <v>30</v>
+      </c>
+      <c r="M109">
+        <v>-4</v>
+      </c>
+      <c r="N109">
+        <v>0.88235294116999996</v>
+      </c>
+      <c r="O109" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>9322</v>
+      </c>
+      <c r="B110">
+        <v>212</v>
+      </c>
+      <c r="C110" t="s">
+        <v>66</v>
+      </c>
+      <c r="D110" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E110" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F110">
+        <v>20153</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="O110" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>9328</v>
+      </c>
+      <c r="B111">
+        <v>234</v>
+      </c>
+      <c r="C111" t="s">
+        <v>122</v>
+      </c>
+      <c r="D111" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E111" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F111">
+        <v>20112</v>
+      </c>
+      <c r="G111">
+        <v>30</v>
+      </c>
+      <c r="H111">
+        <v>18</v>
+      </c>
+      <c r="I111">
+        <v>-12</v>
+      </c>
+      <c r="J111">
+        <v>0.6</v>
+      </c>
+      <c r="K111">
+        <v>30</v>
+      </c>
+      <c r="L111">
+        <v>18</v>
+      </c>
+      <c r="M111">
+        <v>-12</v>
+      </c>
+      <c r="N111">
+        <v>0.6</v>
+      </c>
+      <c r="O111" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>9327</v>
+      </c>
+      <c r="B112">
+        <v>233</v>
+      </c>
+      <c r="C112" t="s">
+        <v>123</v>
+      </c>
+      <c r="D112" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E112" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F112">
+        <v>200158</v>
+      </c>
+      <c r="G112">
+        <v>13</v>
+      </c>
+      <c r="H112">
+        <v>13</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>1</v>
+      </c>
+      <c r="K112">
+        <v>13</v>
+      </c>
+      <c r="L112">
+        <v>13</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>1</v>
+      </c>
+      <c r="O112" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>9334</v>
+      </c>
+      <c r="B113">
+        <v>240</v>
+      </c>
+      <c r="C113" t="s">
+        <v>124</v>
+      </c>
+      <c r="D113" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E113" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F113">
+        <v>20006</v>
+      </c>
+      <c r="G113">
+        <v>27</v>
+      </c>
+      <c r="H113">
+        <v>26</v>
+      </c>
+      <c r="I113">
+        <v>-1</v>
+      </c>
+      <c r="J113">
+        <v>0.96296296295999995</v>
+      </c>
+      <c r="K113">
+        <v>27</v>
+      </c>
+      <c r="L113">
+        <v>26</v>
+      </c>
+      <c r="M113">
+        <v>-1</v>
+      </c>
+      <c r="N113">
+        <v>0.96296296295999995</v>
+      </c>
+      <c r="O113" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>9329</v>
+      </c>
+      <c r="B114">
+        <v>235</v>
+      </c>
+      <c r="C114" t="s">
+        <v>125</v>
+      </c>
+      <c r="D114" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E114" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F114">
+        <v>20066</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="O114" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>9330</v>
+      </c>
+      <c r="B115">
+        <v>236</v>
+      </c>
+      <c r="C115" t="s">
+        <v>126</v>
+      </c>
+      <c r="D115" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E115" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F115">
+        <v>20111</v>
+      </c>
+      <c r="G115">
+        <v>39</v>
+      </c>
+      <c r="H115">
+        <v>27</v>
+      </c>
+      <c r="I115">
+        <v>-12</v>
+      </c>
+      <c r="J115">
+        <v>0.6923076923</v>
+      </c>
+      <c r="K115">
+        <v>39</v>
+      </c>
+      <c r="L115">
+        <v>27</v>
+      </c>
+      <c r="M115">
+        <v>-12</v>
+      </c>
+      <c r="N115">
+        <v>0.6923076923</v>
+      </c>
+      <c r="O115" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>9323</v>
+      </c>
+      <c r="B116">
+        <v>213</v>
+      </c>
+      <c r="C116" t="s">
+        <v>55</v>
+      </c>
+      <c r="D116" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E116" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F116">
+        <v>20058</v>
+      </c>
+      <c r="G116">
+        <v>43</v>
+      </c>
+      <c r="H116">
+        <v>27</v>
+      </c>
+      <c r="I116">
+        <v>-16</v>
+      </c>
+      <c r="J116">
+        <v>0.62790697673999996</v>
+      </c>
+      <c r="K116">
+        <v>43</v>
+      </c>
+      <c r="L116">
+        <v>27</v>
+      </c>
+      <c r="M116">
+        <v>-16</v>
+      </c>
+      <c r="N116">
+        <v>0.62790697673999996</v>
+      </c>
+      <c r="O116" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>9376</v>
+      </c>
+      <c r="B117">
+        <v>327</v>
+      </c>
+      <c r="C117" t="s">
+        <v>127</v>
+      </c>
+      <c r="D117" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E117" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F117">
+        <v>20076</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="O117" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>9377</v>
+      </c>
+      <c r="B118">
+        <v>502</v>
+      </c>
+      <c r="C118" t="s">
+        <v>128</v>
+      </c>
+      <c r="D118" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E118" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F118">
+        <v>200150</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="O118" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>9332</v>
+      </c>
+      <c r="B119">
+        <v>238</v>
+      </c>
+      <c r="C119" t="s">
+        <v>129</v>
+      </c>
+      <c r="D119" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E119" s="1">
+        <v>46177</v>
+      </c>
+      <c r="F119">
+        <v>20007</v>
+      </c>
+      <c r="G119">
+        <v>24</v>
+      </c>
+      <c r="H119">
+        <v>17</v>
+      </c>
+      <c r="I119">
+        <v>-7</v>
+      </c>
+      <c r="J119">
+        <v>0.70833333333000004</v>
+      </c>
+      <c r="K119">
+        <v>24</v>
+      </c>
+      <c r="L119">
+        <v>17</v>
+      </c>
+      <c r="M119">
+        <v>-7</v>
+      </c>
+      <c r="N119">
+        <v>0.70833333333000004</v>
+      </c>
+      <c r="O119" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>9378</v>
+      </c>
+      <c r="B120">
+        <v>327</v>
+      </c>
+      <c r="C120" t="s">
+        <v>127</v>
+      </c>
+      <c r="D120" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E120" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F120">
+        <v>20076</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="O120" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>9379</v>
+      </c>
+      <c r="B121">
+        <v>503</v>
+      </c>
+      <c r="C121" t="s">
+        <v>107</v>
+      </c>
+      <c r="D121" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E121" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F121">
+        <v>200150</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="O121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>9380</v>
+      </c>
+      <c r="B122">
+        <v>121</v>
+      </c>
+      <c r="C122" t="s">
+        <v>52</v>
+      </c>
+      <c r="D122" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E122" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F122">
+        <v>20005</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="O122" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>9381</v>
+      </c>
+      <c r="B123">
+        <v>122</v>
+      </c>
+      <c r="C123" t="s">
+        <v>130</v>
+      </c>
+      <c r="D123" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E123" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F123">
+        <v>20130</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="O123" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>9382</v>
+      </c>
+      <c r="B124">
+        <v>123</v>
+      </c>
+      <c r="C124" t="s">
+        <v>97</v>
+      </c>
+      <c r="D124" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E124" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F124">
+        <v>200158</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="O124" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>9383</v>
+      </c>
+      <c r="B125">
+        <v>124</v>
+      </c>
+      <c r="C125" t="s">
+        <v>67</v>
+      </c>
+      <c r="D125" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E125" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F125">
+        <v>20112</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="O125" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>9305</v>
+      </c>
+      <c r="B126">
+        <v>137</v>
+      </c>
+      <c r="C126" t="s">
+        <v>131</v>
+      </c>
+      <c r="D126" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E126" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F126">
+        <v>20003</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="O126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>9384</v>
+      </c>
+      <c r="B127">
+        <v>125</v>
+      </c>
+      <c r="C127" t="s">
+        <v>98</v>
+      </c>
+      <c r="D127" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E127" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F127">
+        <v>20066</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="O127" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>9385</v>
+      </c>
+      <c r="B128">
+        <v>126</v>
+      </c>
+      <c r="C128" t="s">
+        <v>69</v>
+      </c>
+      <c r="D128" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E128" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F128">
+        <v>20111</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="O128" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>9386</v>
+      </c>
+      <c r="B129">
+        <v>127</v>
+      </c>
+      <c r="C129" t="s">
+        <v>96</v>
+      </c>
+      <c r="D129" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E129" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F129">
+        <v>20003</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="O129" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>9387</v>
+      </c>
+      <c r="B130">
+        <v>128</v>
+      </c>
+      <c r="C130" t="s">
+        <v>75</v>
+      </c>
+      <c r="D130" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E130" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F130">
+        <v>20007</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="O130" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>9388</v>
+      </c>
+      <c r="B131">
+        <v>129</v>
+      </c>
+      <c r="C131" t="s">
+        <v>93</v>
+      </c>
+      <c r="D131" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E131" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F131">
+        <v>20008</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="O131" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>9389</v>
+      </c>
+      <c r="B132">
+        <v>130</v>
+      </c>
+      <c r="C132" t="s">
+        <v>94</v>
+      </c>
+      <c r="D132" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E132" s="1">
+        <v>46179</v>
+      </c>
+      <c r="F132">
+        <v>20006</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="O132" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>9289</v>
+      </c>
+      <c r="B133">
+        <v>105</v>
+      </c>
+      <c r="C133" t="s">
+        <v>132</v>
+      </c>
+      <c r="D133" s="1">
+        <v>46177</v>
+      </c>
+      <c r="E133" s="1">
+        <v>46176</v>
+      </c>
+      <c r="F133">
+        <v>20058</v>
+      </c>
+      <c r="G133">
+        <v>32</v>
+      </c>
+      <c r="H133">
+        <v>24</v>
+      </c>
+      <c r="I133">
+        <v>-8</v>
+      </c>
+      <c r="J133">
+        <v>0.75</v>
+      </c>
+      <c r="K133">
+        <v>32</v>
+      </c>
+      <c r="L133">
+        <v>24</v>
+      </c>
+      <c r="M133">
+        <v>-8</v>
+      </c>
+      <c r="N133">
+        <v>0.75</v>
+      </c>
+      <c r="O133" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>9266</v>
+      </c>
+      <c r="B134">
+        <v>335</v>
+      </c>
+      <c r="C134" t="s">
+        <v>133</v>
+      </c>
+      <c r="D134" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E134" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F134">
+        <v>20066</v>
+      </c>
+      <c r="G134">
+        <v>18</v>
+      </c>
+      <c r="H134">
+        <v>8</v>
+      </c>
+      <c r="I134">
+        <v>-10</v>
+      </c>
+      <c r="J134">
+        <v>0.44444444443999997</v>
+      </c>
+      <c r="K134">
+        <v>18</v>
+      </c>
+      <c r="L134">
+        <v>8</v>
+      </c>
+      <c r="M134">
+        <v>-10</v>
+      </c>
+      <c r="N134">
+        <v>0.44444444443999997</v>
+      </c>
+      <c r="O134" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>9265</v>
+      </c>
+      <c r="B135">
+        <v>334</v>
+      </c>
+      <c r="C135" t="s">
+        <v>134</v>
+      </c>
+      <c r="D135" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E135" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F135">
+        <v>20112</v>
+      </c>
+      <c r="G135">
+        <v>21</v>
+      </c>
+      <c r="H135">
+        <v>18</v>
+      </c>
+      <c r="I135">
+        <v>-3</v>
+      </c>
+      <c r="J135">
+        <v>0.85714285714000005</v>
+      </c>
+      <c r="K135">
+        <v>21</v>
+      </c>
+      <c r="L135">
+        <v>18</v>
+      </c>
+      <c r="M135">
+        <v>-3</v>
+      </c>
+      <c r="N135">
+        <v>0.85714285714000005</v>
+      </c>
+      <c r="O135" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>9264</v>
+      </c>
+      <c r="B136">
+        <v>333</v>
+      </c>
+      <c r="C136" t="s">
+        <v>135</v>
+      </c>
+      <c r="D136" s="1">
+        <v>46176</v>
+      </c>
+      <c r="E136" s="1">
+        <v>46175</v>
+      </c>
+      <c r="F136">
+        <v>200158</v>
+      </c>
+      <c r="G136">
         <v>23</v>
       </c>
-      <c r="L92">
+      <c r="H136">
         <v>23</v>
       </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92">
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
         <v>1</v>
       </c>
-      <c r="O92" t="s">
+      <c r="K136">
+        <v>23</v>
+      </c>
+      <c r="L136">
+        <v>23</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>1</v>
+      </c>
+      <c r="O136" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>9352</v>
+      </c>
+      <c r="B137">
+        <v>314</v>
+      </c>
+      <c r="C137" t="s">
+        <v>81</v>
+      </c>
+      <c r="D137" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E137" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F137">
+        <v>20076</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="O137" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>9353</v>
+      </c>
+      <c r="B138">
+        <v>315</v>
+      </c>
+      <c r="C138" t="s">
+        <v>120</v>
+      </c>
+      <c r="D138" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E138" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F138">
+        <v>20153</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="O138" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>9354</v>
+      </c>
+      <c r="B139">
+        <v>316</v>
+      </c>
+      <c r="C139" t="s">
+        <v>136</v>
+      </c>
+      <c r="D139" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E139" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F139">
+        <v>20047</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="O139" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>9355</v>
+      </c>
+      <c r="B140">
+        <v>317</v>
+      </c>
+      <c r="C140" t="s">
+        <v>137</v>
+      </c>
+      <c r="D140" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E140" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F140">
+        <v>20043</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="O140" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>9356</v>
+      </c>
+      <c r="B141">
+        <v>318</v>
+      </c>
+      <c r="C141" t="s">
+        <v>138</v>
+      </c>
+      <c r="D141" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E141" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F141">
+        <v>11215</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="O141" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>9357</v>
+      </c>
+      <c r="B142">
+        <v>319</v>
+      </c>
+      <c r="C142" t="s">
+        <v>139</v>
+      </c>
+      <c r="D142" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E142" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F142">
+        <v>20058</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="O142" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>9358</v>
+      </c>
+      <c r="B143">
+        <v>320</v>
+      </c>
+      <c r="C143" t="s">
+        <v>140</v>
+      </c>
+      <c r="D143" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E143" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F143">
+        <v>20043</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="O143" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>9359</v>
+      </c>
+      <c r="B144">
+        <v>321</v>
+      </c>
+      <c r="C144" t="s">
+        <v>141</v>
+      </c>
+      <c r="D144" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E144" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F144">
+        <v>20095</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="O144" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>9360</v>
+      </c>
+      <c r="B145">
+        <v>322</v>
+      </c>
+      <c r="C145" t="s">
+        <v>142</v>
+      </c>
+      <c r="D145" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E145" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F145">
+        <v>20095</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="O145" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>9361</v>
+      </c>
+      <c r="B146">
+        <v>323</v>
+      </c>
+      <c r="C146" t="s">
+        <v>143</v>
+      </c>
+      <c r="D146" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E146" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F146">
+        <v>20155</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="O146" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>9362</v>
+      </c>
+      <c r="B147">
+        <v>324</v>
+      </c>
+      <c r="C147" t="s">
+        <v>144</v>
+      </c>
+      <c r="D147" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E147" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F147">
+        <v>20153</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="O147" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>9363</v>
+      </c>
+      <c r="B148">
+        <v>325</v>
+      </c>
+      <c r="C148" t="s">
+        <v>145</v>
+      </c>
+      <c r="D148" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E148" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F148">
+        <v>200158</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="O148" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>9364</v>
+      </c>
+      <c r="B149">
+        <v>326</v>
+      </c>
+      <c r="C149" t="s">
+        <v>146</v>
+      </c>
+      <c r="D149" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E149" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F149">
+        <v>200150</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="O149" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>9365</v>
+      </c>
+      <c r="B150">
+        <v>501</v>
+      </c>
+      <c r="C150" t="s">
+        <v>77</v>
+      </c>
+      <c r="D150" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E150" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F150">
+        <v>200150</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="O150" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>9366</v>
+      </c>
+      <c r="B151">
+        <v>331</v>
+      </c>
+      <c r="C151" t="s">
+        <v>88</v>
+      </c>
+      <c r="D151" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E151" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F151">
+        <v>20006</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="O151" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>9367</v>
+      </c>
+      <c r="B152">
+        <v>332</v>
+      </c>
+      <c r="C152" t="s">
+        <v>90</v>
+      </c>
+      <c r="D152" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E152" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F152">
+        <v>20130</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="O152" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>9368</v>
+      </c>
+      <c r="B153">
+        <v>334</v>
+      </c>
+      <c r="C153" t="s">
+        <v>134</v>
+      </c>
+      <c r="D153" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E153" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F153">
+        <v>20007</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="O153" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>9369</v>
+      </c>
+      <c r="B154">
+        <v>335</v>
+      </c>
+      <c r="C154" t="s">
+        <v>133</v>
+      </c>
+      <c r="D154" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E154" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F154">
+        <v>20066</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="O154" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>9370</v>
+      </c>
+      <c r="B155">
+        <v>336</v>
+      </c>
+      <c r="C155" t="s">
+        <v>28</v>
+      </c>
+      <c r="D155" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E155" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F155">
+        <v>20111</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="O155" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>9371</v>
+      </c>
+      <c r="B156">
+        <v>337</v>
+      </c>
+      <c r="C156" t="s">
+        <v>32</v>
+      </c>
+      <c r="D156" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E156" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F156">
+        <v>20003</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="O156" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>9372</v>
+      </c>
+      <c r="B157">
+        <v>338</v>
+      </c>
+      <c r="C157" t="s">
+        <v>26</v>
+      </c>
+      <c r="D157" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E157" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F157">
+        <v>20112</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="O157" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>9373</v>
+      </c>
+      <c r="B158">
+        <v>339</v>
+      </c>
+      <c r="C158" t="s">
+        <v>111</v>
+      </c>
+      <c r="D158" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E158" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F158">
+        <v>20008</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="O158" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>9374</v>
+      </c>
+      <c r="B159">
+        <v>340</v>
+      </c>
+      <c r="C159" t="s">
+        <v>30</v>
+      </c>
+      <c r="D159" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E159" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F159">
+        <v>20005</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="O159" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>9375</v>
+      </c>
+      <c r="B160">
+        <v>341</v>
+      </c>
+      <c r="C160" t="s">
+        <v>147</v>
+      </c>
+      <c r="D160" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E160" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F160">
+        <v>200158</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="O160" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>9350</v>
+      </c>
+      <c r="B161">
+        <v>312</v>
+      </c>
+      <c r="C161" t="s">
+        <v>80</v>
+      </c>
+      <c r="D161" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E161" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F161">
+        <v>20086</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="O161" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>9351</v>
+      </c>
+      <c r="B162">
+        <v>313</v>
+      </c>
+      <c r="C162" t="s">
+        <v>79</v>
+      </c>
+      <c r="D162" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E162" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F162">
+        <v>20106</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="O162" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>9343</v>
+      </c>
+      <c r="B163">
+        <v>303</v>
+      </c>
+      <c r="C163" t="s">
+        <v>37</v>
+      </c>
+      <c r="D163" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E163" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F163">
+        <v>20047</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="O163" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>9344</v>
+      </c>
+      <c r="B164">
+        <v>304</v>
+      </c>
+      <c r="C164" t="s">
+        <v>110</v>
+      </c>
+      <c r="D164" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E164" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F164">
+        <v>20086</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="O164" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>9345</v>
+      </c>
+      <c r="B165">
+        <v>305</v>
+      </c>
+      <c r="C165" t="s">
+        <v>85</v>
+      </c>
+      <c r="D165" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E165" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F165">
+        <v>20106</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="O165" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>9346</v>
+      </c>
+      <c r="B166">
+        <v>306</v>
+      </c>
+      <c r="C166" t="s">
+        <v>148</v>
+      </c>
+      <c r="D166" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E166" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F166">
+        <v>20105</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="O166" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>9347</v>
+      </c>
+      <c r="B167">
+        <v>307</v>
+      </c>
+      <c r="C167" t="s">
+        <v>86</v>
+      </c>
+      <c r="D167" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E167" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F167">
+        <v>11215</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="O167" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>9348</v>
+      </c>
+      <c r="B168">
+        <v>310</v>
+      </c>
+      <c r="C168" t="s">
+        <v>149</v>
+      </c>
+      <c r="D168" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E168" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F168">
+        <v>20155</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="O168" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>9349</v>
+      </c>
+      <c r="B169">
+        <v>311</v>
+      </c>
+      <c r="C169" t="s">
+        <v>78</v>
+      </c>
+      <c r="D169" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E169" s="1">
+        <v>46178</v>
+      </c>
+      <c r="F169">
+        <v>20057</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="O169" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/data/cartones.xlsx
+++ b/data/cartones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C6DC43-E954-4309-8546-5DD6A7C1DE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8B7BDF-5EA2-43CA-841A-AA2F4CA48A43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{22493E18-AF0A-488C-9B26-FC8129E5AAFC}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="108">
   <si>
     <t>codigo</t>
   </si>
@@ -710,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45344EE1-844E-488C-87B7-5E4BE39AF234}">
-  <dimension ref="A1:O194"/>
+  <dimension ref="A1:O217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -4773,104 +4773,116 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>9326</v>
+        <v>9412</v>
       </c>
       <c r="B89">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C89">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D89" s="1">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="E89" s="1">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="F89">
-        <v>20130</v>
+        <v>20008</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J89">
+        <v>0.71428571399999996</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N89">
+        <v>0.71428571399999996</v>
       </c>
       <c r="O89" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>9403</v>
+        <v>9413</v>
       </c>
       <c r="B90">
-        <v>212</v>
-      </c>
-      <c r="C90" t="s">
-        <v>59</v>
+        <v>230</v>
+      </c>
+      <c r="C90">
+        <v>230</v>
       </c>
       <c r="D90" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E90" s="1">
         <v>46181</v>
       </c>
       <c r="F90">
-        <v>20057</v>
+        <v>20006</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J90">
+        <v>0.928571429</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N90">
+        <v>0.928571429</v>
       </c>
       <c r="O90" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>9404</v>
+        <v>9337</v>
       </c>
       <c r="B91">
-        <v>221</v>
+        <v>800</v>
       </c>
       <c r="C91" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="D91" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="E91" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="F91">
-        <v>20005</v>
+        <v>200150</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -4891,27 +4903,27 @@
         <v>0</v>
       </c>
       <c r="O91" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>9405</v>
+        <v>9341</v>
       </c>
       <c r="B92">
-        <v>222</v>
+        <v>800</v>
       </c>
       <c r="C92" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="D92" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="E92" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="F92">
-        <v>20130</v>
+        <v>200150</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -4932,109 +4944,121 @@
         <v>0</v>
       </c>
       <c r="O92" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>9406</v>
+        <v>9321</v>
       </c>
       <c r="B93">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C93" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="D93" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="E93" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="F93">
-        <v>200158</v>
+        <v>20095</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J93">
+        <v>0.65517241400000004</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L93">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="N93">
+        <v>0.65517241400000004</v>
       </c>
       <c r="O93" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>9407</v>
+        <v>9339</v>
       </c>
       <c r="B94">
-        <v>224</v>
+        <v>501</v>
       </c>
       <c r="C94" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D94" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="E94" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="F94">
-        <v>20112</v>
+        <v>11215</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I94">
         <v>0</v>
       </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
       <c r="K94">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M94">
         <v>0</v>
       </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
       <c r="O94" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>9408</v>
+        <v>9324</v>
       </c>
       <c r="B95">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="D95" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="E95" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="F95">
-        <v>20066</v>
+        <v>11215</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -5055,109 +5079,121 @@
         <v>0</v>
       </c>
       <c r="O95" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>9409</v>
+        <v>9319</v>
       </c>
       <c r="B96">
-        <v>226</v>
-      </c>
-      <c r="C96">
-        <v>226</v>
+        <v>206</v>
+      </c>
+      <c r="C96" t="s">
+        <v>53</v>
       </c>
       <c r="D96" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="E96" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="F96">
-        <v>20111</v>
+        <v>20106</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="J96">
+        <v>0.4</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M96">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="N96">
+        <v>0.4</v>
       </c>
       <c r="O96" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>9410</v>
+        <v>9316</v>
       </c>
       <c r="B97">
-        <v>227</v>
-      </c>
-      <c r="C97">
-        <v>227</v>
+        <v>203</v>
+      </c>
+      <c r="C97" t="s">
+        <v>58</v>
       </c>
       <c r="D97" s="1">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="E97" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="F97">
-        <v>20003</v>
+        <v>20086</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I97">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="J97">
+        <v>0.70588235300000002</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="N97">
+        <v>0.70588235300000002</v>
       </c>
       <c r="O97" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>9337</v>
+        <v>9411</v>
       </c>
       <c r="B98">
-        <v>800</v>
-      </c>
-      <c r="C98" t="s">
-        <v>22</v>
+        <v>228</v>
+      </c>
+      <c r="C98">
+        <v>228</v>
       </c>
       <c r="D98" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="E98" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="F98">
-        <v>200150</v>
+        <v>20007</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -5178,162 +5214,162 @@
         <v>0</v>
       </c>
       <c r="O98" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>9341</v>
+        <v>9384</v>
       </c>
       <c r="B99">
-        <v>800</v>
+        <v>125</v>
       </c>
       <c r="C99" t="s">
-        <v>22</v>
+        <v>81</v>
       </c>
       <c r="D99" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="E99" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F99">
-        <v>200150</v>
+        <v>20066</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I99">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="J99">
+        <v>0.37037037</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="N99">
+        <v>0.37037037</v>
       </c>
       <c r="O99" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>9321</v>
+        <v>9261</v>
       </c>
       <c r="B100">
-        <v>210</v>
+        <v>303</v>
       </c>
       <c r="C100" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="D100" s="1">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="E100" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="F100">
-        <v>20095</v>
+        <v>20047</v>
       </c>
       <c r="G100">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I100">
-        <v>-10</v>
-      </c>
-      <c r="J100">
-        <v>0.65517241400000004</v>
+        <v>0</v>
       </c>
       <c r="K100">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L100">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M100">
-        <v>-10</v>
-      </c>
-      <c r="N100">
-        <v>0.65517241400000004</v>
+        <v>0</v>
       </c>
       <c r="O100" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>9339</v>
+        <v>9258</v>
       </c>
       <c r="B101">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C101" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D101" s="1">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="E101" s="1">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="F101">
-        <v>11215</v>
+        <v>20048</v>
       </c>
       <c r="G101">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H101">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I101">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L101">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="s">
-        <v>37</v>
+        <v>87</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>9324</v>
+        <v>9336</v>
       </c>
       <c r="B102">
-        <v>214</v>
+        <v>501</v>
       </c>
       <c r="C102" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D102" s="1">
         <v>46178</v>
       </c>
       <c r="E102" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="F102">
-        <v>11215</v>
+        <v>200150</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -5354,121 +5390,121 @@
         <v>0</v>
       </c>
       <c r="O102" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>9319</v>
+        <v>9309</v>
       </c>
       <c r="B103">
-        <v>206</v>
+        <v>500</v>
       </c>
       <c r="C103" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D103" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="E103" s="1">
         <v>46177</v>
       </c>
       <c r="F103">
-        <v>20106</v>
+        <v>200150</v>
       </c>
       <c r="G103">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H103">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I103">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="J103">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="K103">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="L103">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M103">
-        <v>-18</v>
+        <v>-2</v>
       </c>
       <c r="N103">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O103" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>9316</v>
+        <v>9310</v>
       </c>
       <c r="B104">
-        <v>203</v>
+        <v>500</v>
       </c>
       <c r="C104" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D104" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="E104" s="1">
         <v>46177</v>
       </c>
       <c r="F104">
-        <v>20086</v>
+        <v>200150</v>
       </c>
       <c r="G104">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H104">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="I104">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="J104">
-        <v>0.70588235300000002</v>
+        <v>1</v>
       </c>
       <c r="K104">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="L104">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M104">
-        <v>-15</v>
+        <v>-1</v>
       </c>
       <c r="N104">
-        <v>0.70588235300000002</v>
+        <v>0</v>
       </c>
       <c r="O104" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>9411</v>
+        <v>9311</v>
       </c>
       <c r="B105">
-        <v>228</v>
-      </c>
-      <c r="C105">
-        <v>228</v>
+        <v>500</v>
+      </c>
+      <c r="C105" t="s">
+        <v>66</v>
       </c>
       <c r="D105" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="E105" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="F105">
-        <v>20007</v>
+        <v>200150</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -5489,147 +5525,153 @@
         <v>0</v>
       </c>
       <c r="O105" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>9412</v>
+        <v>9312</v>
       </c>
       <c r="B106">
-        <v>229</v>
-      </c>
-      <c r="C106">
-        <v>229</v>
+        <v>500</v>
+      </c>
+      <c r="C106" t="s">
+        <v>66</v>
       </c>
       <c r="D106" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="E106" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="F106">
-        <v>20008</v>
+        <v>200150</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106">
         <v>0</v>
       </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
       <c r="K106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106">
         <v>0</v>
       </c>
       <c r="M106">
+        <v>-1</v>
+      </c>
+      <c r="N106">
         <v>0</v>
       </c>
       <c r="O106" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>9413</v>
+        <v>9235</v>
       </c>
       <c r="B107">
-        <v>230</v>
-      </c>
-      <c r="C107">
-        <v>230</v>
+        <v>205</v>
+      </c>
+      <c r="C107" t="s">
+        <v>88</v>
       </c>
       <c r="D107" s="1">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="E107" s="1">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="F107">
-        <v>20006</v>
+        <v>20047</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="J107">
+        <v>0.76595744700000001</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="N107">
+        <v>0.76595744700000001</v>
       </c>
       <c r="O107" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>9384</v>
+        <v>9313</v>
       </c>
       <c r="B108">
-        <v>125</v>
+        <v>800</v>
       </c>
       <c r="C108" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="D108" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="E108" s="1">
-        <v>46179</v>
+        <v>46177</v>
       </c>
       <c r="F108">
-        <v>20066</v>
+        <v>200150</v>
       </c>
       <c r="G108">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H108">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I108">
-        <v>-17</v>
-      </c>
-      <c r="J108">
-        <v>0.37037037</v>
+        <v>0</v>
       </c>
       <c r="K108">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L108">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M108">
-        <v>-17</v>
-      </c>
-      <c r="N108">
-        <v>0.37037037</v>
+        <v>0</v>
       </c>
       <c r="O108" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>9261</v>
+        <v>9274</v>
       </c>
       <c r="B109">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="D109" s="1">
         <v>46175</v>
@@ -5638,39 +5680,45 @@
         <v>46175</v>
       </c>
       <c r="F109">
-        <v>20047</v>
+        <v>20086</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="J109">
+        <v>0.73809523799999999</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M109">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="N109">
+        <v>0.73809523799999999</v>
       </c>
       <c r="O109" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>9258</v>
+        <v>9270</v>
       </c>
       <c r="B110">
-        <v>503</v>
-      </c>
-      <c r="C110" t="s">
-        <v>86</v>
+        <v>339</v>
+      </c>
+      <c r="C110">
+        <v>339</v>
       </c>
       <c r="D110" s="1">
         <v>46176</v>
@@ -5679,101 +5727,107 @@
         <v>46175</v>
       </c>
       <c r="F110">
-        <v>20048</v>
+        <v>20008</v>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I110">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="J110">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K110">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L110">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M110">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O110" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>9336</v>
+        <v>9307</v>
       </c>
       <c r="B111">
-        <v>501</v>
-      </c>
-      <c r="C111" t="s">
-        <v>67</v>
+        <v>139</v>
+      </c>
+      <c r="C111">
+        <v>139</v>
       </c>
       <c r="D111" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="E111" s="1">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="F111">
-        <v>200150</v>
+        <v>20008</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J111">
+        <v>0.8</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N111">
+        <v>0.8</v>
       </c>
       <c r="O111" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>9309</v>
+        <v>9301</v>
       </c>
       <c r="B112">
-        <v>500</v>
-      </c>
-      <c r="C112" t="s">
-        <v>66</v>
+        <v>133</v>
+      </c>
+      <c r="C112">
+        <v>133</v>
       </c>
       <c r="D112" s="1">
         <v>46177</v>
       </c>
       <c r="E112" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="F112">
-        <v>200150</v>
+        <v>200158</v>
       </c>
       <c r="G112">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -5782,86 +5836,86 @@
         <v>1</v>
       </c>
       <c r="K112">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M112">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>9310</v>
+        <v>9304</v>
       </c>
       <c r="B113">
-        <v>500</v>
-      </c>
-      <c r="C113" t="s">
-        <v>66</v>
+        <v>136</v>
+      </c>
+      <c r="C113">
+        <v>136</v>
       </c>
       <c r="D113" s="1">
         <v>46177</v>
       </c>
       <c r="E113" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="F113">
-        <v>200150</v>
+        <v>20111</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H113">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I113">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="J113">
-        <v>1</v>
+        <v>0.71428571399999996</v>
       </c>
       <c r="K113">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M113">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>0.71428571399999996</v>
       </c>
       <c r="O113" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>9311</v>
+        <v>9273</v>
       </c>
       <c r="B114">
-        <v>500</v>
+        <v>303</v>
       </c>
       <c r="C114" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D114" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="E114" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="F114">
-        <v>200150</v>
+        <v>20153</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -5882,397 +5936,385 @@
         <v>0</v>
       </c>
       <c r="O114" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>9312</v>
+        <v>9306</v>
       </c>
       <c r="B115">
-        <v>500</v>
-      </c>
-      <c r="C115" t="s">
-        <v>66</v>
+        <v>138</v>
+      </c>
+      <c r="C115">
+        <v>138</v>
       </c>
       <c r="D115" s="1">
         <v>46177</v>
       </c>
       <c r="E115" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="F115">
-        <v>200150</v>
+        <v>20007</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H115">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>0.696969697</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M115">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>0.696969697</v>
       </c>
       <c r="O115" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>9235</v>
+        <v>9308</v>
       </c>
       <c r="B116">
-        <v>205</v>
-      </c>
-      <c r="C116" t="s">
-        <v>88</v>
+        <v>140</v>
+      </c>
+      <c r="C116">
+        <v>140</v>
       </c>
       <c r="D116" s="1">
-        <v>46174</v>
+        <v>46177</v>
       </c>
       <c r="E116" s="1">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="F116">
-        <v>20047</v>
+        <v>20006</v>
       </c>
       <c r="G116">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H116">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I116">
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="J116">
-        <v>0.76595744700000001</v>
+        <v>0.95652173900000004</v>
       </c>
       <c r="K116">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="L116">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M116">
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="N116">
-        <v>0.76595744700000001</v>
+        <v>0.95652173900000004</v>
       </c>
       <c r="O116" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>9313</v>
+        <v>9303</v>
       </c>
       <c r="B117">
-        <v>800</v>
-      </c>
-      <c r="C117" t="s">
-        <v>22</v>
+        <v>135</v>
+      </c>
+      <c r="C117">
+        <v>135</v>
       </c>
       <c r="D117" s="1">
         <v>46177</v>
       </c>
       <c r="E117" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="F117">
-        <v>200150</v>
+        <v>20113</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J117">
+        <v>0.875</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L117">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="N117">
+        <v>0.875</v>
       </c>
       <c r="O117" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>9274</v>
+        <v>9300</v>
       </c>
       <c r="B118">
-        <v>304</v>
-      </c>
-      <c r="C118" t="s">
-        <v>89</v>
+        <v>132</v>
+      </c>
+      <c r="C118">
+        <v>132</v>
       </c>
       <c r="D118" s="1">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="E118" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="F118">
-        <v>20086</v>
+        <v>20130</v>
       </c>
       <c r="G118">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H118">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I118">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="J118">
-        <v>0.73809523799999999</v>
+        <v>1</v>
       </c>
       <c r="K118">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="L118">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="M118">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="N118">
-        <v>0.73809523799999999</v>
+        <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>9270</v>
+        <v>9365</v>
       </c>
       <c r="B119">
-        <v>339</v>
-      </c>
-      <c r="C119">
-        <v>339</v>
+        <v>501</v>
+      </c>
+      <c r="C119" t="s">
+        <v>67</v>
       </c>
       <c r="D119" s="1">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="E119" s="1">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="F119">
-        <v>20008</v>
+        <v>200150</v>
       </c>
       <c r="G119">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I119">
-        <v>-4</v>
-      </c>
-      <c r="J119">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K119">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L119">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M119">
-        <v>-4</v>
-      </c>
-      <c r="N119">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O119" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>9307</v>
+        <v>9335</v>
       </c>
       <c r="B120">
-        <v>139</v>
-      </c>
-      <c r="C120">
-        <v>139</v>
+        <v>500</v>
+      </c>
+      <c r="C120" t="s">
+        <v>66</v>
       </c>
       <c r="D120" s="1">
         <v>46177</v>
       </c>
       <c r="E120" s="1">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="F120">
-        <v>20008</v>
+        <v>200150</v>
       </c>
       <c r="G120">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H120">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I120">
-        <v>-3</v>
-      </c>
-      <c r="J120">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K120">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L120">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M120">
-        <v>-3</v>
-      </c>
-      <c r="N120">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O120" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>9301</v>
+        <v>9340</v>
       </c>
       <c r="B121">
-        <v>133</v>
+        <v>331</v>
       </c>
       <c r="C121">
-        <v>133</v>
+        <v>331</v>
       </c>
       <c r="D121" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="E121" s="1">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="F121">
-        <v>200158</v>
+        <v>20006</v>
       </c>
       <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="O121" t="s">
         <v>18</v>
-      </c>
-      <c r="H121">
-        <v>18</v>
-      </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
-        <v>1</v>
-      </c>
-      <c r="K121">
-        <v>18</v>
-      </c>
-      <c r="L121">
-        <v>18</v>
-      </c>
-      <c r="M121">
-        <v>0</v>
-      </c>
-      <c r="N121">
-        <v>1</v>
-      </c>
-      <c r="O121" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>9304</v>
+        <v>9315</v>
       </c>
       <c r="B122">
-        <v>136</v>
-      </c>
-      <c r="C122">
-        <v>136</v>
+        <v>202</v>
+      </c>
+      <c r="C122" t="s">
+        <v>43</v>
       </c>
       <c r="D122" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E122" s="1">
         <v>46177</v>
       </c>
-      <c r="E122" s="1">
-        <v>46176</v>
-      </c>
       <c r="F122">
-        <v>20111</v>
+        <v>20057</v>
       </c>
       <c r="G122">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H122">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I122">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="J122">
-        <v>0.71428571399999996</v>
+        <v>0.94117647100000001</v>
       </c>
       <c r="K122">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="L122">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="M122">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="N122">
-        <v>0.71428571399999996</v>
+        <v>0.94117647100000001</v>
       </c>
       <c r="O122" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>9273</v>
+        <v>9282</v>
       </c>
       <c r="B123">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C123" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="D123" s="1">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="E123" s="1">
         <v>46175</v>
       </c>
       <c r="F123">
-        <v>20153</v>
+        <v>20106</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -6293,112 +6335,112 @@
         <v>0</v>
       </c>
       <c r="O123" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>9306</v>
+        <v>9317</v>
       </c>
       <c r="B124">
-        <v>138</v>
-      </c>
-      <c r="C124">
-        <v>138</v>
+        <v>204</v>
+      </c>
+      <c r="C124" t="s">
+        <v>51</v>
       </c>
       <c r="D124" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E124" s="1">
         <v>46177</v>
       </c>
-      <c r="E124" s="1">
-        <v>46176</v>
-      </c>
       <c r="F124">
-        <v>20007</v>
+        <v>20076</v>
       </c>
       <c r="G124">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="H124">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I124">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="J124">
-        <v>0.696969697</v>
+        <v>0.89285714299999996</v>
       </c>
       <c r="K124">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="L124">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M124">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="N124">
-        <v>0.696969697</v>
+        <v>0.89285714299999996</v>
       </c>
       <c r="O124" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>9308</v>
+        <v>9318</v>
       </c>
       <c r="B125">
-        <v>140</v>
-      </c>
-      <c r="C125">
-        <v>140</v>
+        <v>205</v>
+      </c>
+      <c r="C125" t="s">
+        <v>88</v>
       </c>
       <c r="D125" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E125" s="1">
         <v>46177</v>
       </c>
-      <c r="E125" s="1">
-        <v>46176</v>
-      </c>
       <c r="F125">
-        <v>20006</v>
+        <v>20047</v>
       </c>
       <c r="G125">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="H125">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="I125">
-        <v>-1</v>
+        <v>-19</v>
       </c>
       <c r="J125">
-        <v>0.95652173900000004</v>
+        <v>0.703125</v>
       </c>
       <c r="K125">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="L125">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="M125">
-        <v>-1</v>
+        <v>-19</v>
       </c>
       <c r="N125">
-        <v>0.95652173900000004</v>
+        <v>0.703125</v>
       </c>
       <c r="O125" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>9303</v>
+        <v>9302</v>
       </c>
       <c r="B126">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C126">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D126" s="1">
         <v>46177</v>
@@ -6407,92 +6449,92 @@
         <v>46176</v>
       </c>
       <c r="F126">
-        <v>20113</v>
+        <v>20112</v>
       </c>
       <c r="G126">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H126">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I126">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J126">
-        <v>0.875</v>
+        <v>0.76923076899999998</v>
       </c>
       <c r="K126">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L126">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M126">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="N126">
-        <v>0.875</v>
+        <v>0.76923076899999998</v>
       </c>
       <c r="O126" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>9300</v>
+        <v>9320</v>
       </c>
       <c r="B127">
-        <v>132</v>
-      </c>
-      <c r="C127">
-        <v>132</v>
+        <v>209</v>
+      </c>
+      <c r="C127" t="s">
+        <v>54</v>
       </c>
       <c r="D127" s="1">
+        <v>46178</v>
+      </c>
+      <c r="E127" s="1">
         <v>46177</v>
       </c>
-      <c r="E127" s="1">
-        <v>46176</v>
-      </c>
       <c r="F127">
-        <v>20130</v>
+        <v>20105</v>
       </c>
       <c r="G127">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H127">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I127">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="J127">
-        <v>1</v>
+        <v>0.88235294099999995</v>
       </c>
       <c r="K127">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="L127">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M127">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N127">
-        <v>1</v>
+        <v>0.88235294099999995</v>
       </c>
       <c r="O127" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>9365</v>
+        <v>9353</v>
       </c>
       <c r="B128">
-        <v>501</v>
+        <v>315</v>
       </c>
       <c r="C128" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D128" s="1">
         <v>46179</v>
@@ -6501,121 +6543,139 @@
         <v>46178</v>
       </c>
       <c r="F128">
-        <v>200150</v>
+        <v>20153</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J128">
+        <v>0.764705882</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L128">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M128">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N128">
+        <v>0.764705882</v>
       </c>
       <c r="O128" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>9335</v>
+        <v>9328</v>
       </c>
       <c r="B129">
-        <v>500</v>
-      </c>
-      <c r="C129" t="s">
-        <v>66</v>
+        <v>234</v>
+      </c>
+      <c r="C129">
+        <v>234</v>
       </c>
       <c r="D129" s="1">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="E129" s="1">
         <v>46177</v>
       </c>
       <c r="F129">
-        <v>200150</v>
+        <v>20112</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="J129">
+        <v>0.6</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="N129">
+        <v>0.6</v>
       </c>
       <c r="O129" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>9340</v>
+        <v>9327</v>
       </c>
       <c r="B130">
-        <v>331</v>
+        <v>233</v>
       </c>
       <c r="C130">
-        <v>331</v>
+        <v>233</v>
       </c>
       <c r="D130" s="1">
         <v>46178</v>
       </c>
       <c r="E130" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="F130">
-        <v>20006</v>
+        <v>200158</v>
       </c>
       <c r="G130">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I130">
         <v>0</v>
       </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
       <c r="K130">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L130">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M130">
         <v>0</v>
       </c>
+      <c r="N130">
+        <v>1</v>
+      </c>
       <c r="O130" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>9315</v>
+        <v>9334</v>
       </c>
       <c r="B131">
-        <v>202</v>
-      </c>
-      <c r="C131" t="s">
-        <v>43</v>
+        <v>240</v>
+      </c>
+      <c r="C131">
+        <v>240</v>
       </c>
       <c r="D131" s="1">
         <v>46178</v>
@@ -6624,54 +6684,54 @@
         <v>46177</v>
       </c>
       <c r="F131">
-        <v>20057</v>
+        <v>20006</v>
       </c>
       <c r="G131">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H131">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I131">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J131">
-        <v>0.94117647100000001</v>
+        <v>0.96296296299999995</v>
       </c>
       <c r="K131">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L131">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M131">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N131">
-        <v>0.94117647100000001</v>
+        <v>0.96296296299999995</v>
       </c>
       <c r="O131" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>9282</v>
+        <v>9390</v>
       </c>
       <c r="B132">
-        <v>315</v>
+        <v>221</v>
       </c>
       <c r="C132" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="D132" s="1">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="E132" s="1">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="F132">
-        <v>20106</v>
+        <v>20005</v>
       </c>
       <c r="G132">
         <v>0</v>
@@ -6692,18 +6752,18 @@
         <v>0</v>
       </c>
       <c r="O132" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>9317</v>
+        <v>9330</v>
       </c>
       <c r="B133">
-        <v>204</v>
-      </c>
-      <c r="C133" t="s">
-        <v>51</v>
+        <v>236</v>
+      </c>
+      <c r="C133">
+        <v>236</v>
       </c>
       <c r="D133" s="1">
         <v>46178</v>
@@ -6712,45 +6772,45 @@
         <v>46177</v>
       </c>
       <c r="F133">
-        <v>20076</v>
+        <v>20111</v>
       </c>
       <c r="G133">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H133">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I133">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="J133">
-        <v>0.89285714299999996</v>
+        <v>0.69230769199999997</v>
       </c>
       <c r="K133">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L133">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M133">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="N133">
-        <v>0.89285714299999996</v>
+        <v>0.69230769199999997</v>
       </c>
       <c r="O133" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>9318</v>
+        <v>9323</v>
       </c>
       <c r="B134">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C134" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="D134" s="1">
         <v>46178</v>
@@ -6759,248 +6819,236 @@
         <v>46177</v>
       </c>
       <c r="F134">
-        <v>20047</v>
+        <v>20058</v>
       </c>
       <c r="G134">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="H134">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I134">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="J134">
-        <v>0.703125</v>
+        <v>0.62790697699999998</v>
       </c>
       <c r="K134">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="L134">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="M134">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="N134">
-        <v>0.703125</v>
+        <v>0.62790697699999998</v>
       </c>
       <c r="O134" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>9302</v>
+        <v>9376</v>
       </c>
       <c r="B135">
-        <v>134</v>
+        <v>327</v>
       </c>
       <c r="C135">
-        <v>134</v>
+        <v>327</v>
       </c>
       <c r="D135" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="E135" s="1">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="F135">
-        <v>20112</v>
+        <v>20076</v>
       </c>
       <c r="G135">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I135">
-        <v>-3</v>
-      </c>
-      <c r="J135">
-        <v>0.76923076899999998</v>
+        <v>0</v>
       </c>
       <c r="K135">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L135">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M135">
-        <v>-3</v>
-      </c>
-      <c r="N135">
-        <v>0.76923076899999998</v>
+        <v>0</v>
       </c>
       <c r="O135" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>9320</v>
+        <v>9377</v>
       </c>
       <c r="B136">
-        <v>209</v>
+        <v>502</v>
       </c>
       <c r="C136" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="D136" s="1">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="E136" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="F136">
-        <v>20105</v>
+        <v>200150</v>
       </c>
       <c r="G136">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H136">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I136">
-        <v>-4</v>
-      </c>
-      <c r="J136">
-        <v>0.88235294099999995</v>
+        <v>0</v>
       </c>
       <c r="K136">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L136">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M136">
-        <v>-4</v>
-      </c>
-      <c r="N136">
-        <v>0.88235294099999995</v>
+        <v>0</v>
       </c>
       <c r="O136" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>9353</v>
+        <v>9332</v>
       </c>
       <c r="B137">
-        <v>315</v>
-      </c>
-      <c r="C137" t="s">
-        <v>91</v>
+        <v>238</v>
+      </c>
+      <c r="C137">
+        <v>238</v>
       </c>
       <c r="D137" s="1">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="E137" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="F137">
-        <v>20153</v>
+        <v>20007</v>
       </c>
       <c r="G137">
+        <v>24</v>
+      </c>
+      <c r="H137">
         <v>17</v>
       </c>
-      <c r="H137">
-        <v>13</v>
-      </c>
       <c r="I137">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="J137">
-        <v>0.764705882</v>
+        <v>0.70833333300000001</v>
       </c>
       <c r="K137">
+        <v>24</v>
+      </c>
+      <c r="L137">
         <v>17</v>
       </c>
-      <c r="L137">
-        <v>13</v>
-      </c>
       <c r="M137">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="N137">
-        <v>0.764705882</v>
+        <v>0.70833333300000001</v>
       </c>
       <c r="O137" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>9328</v>
+        <v>9343</v>
       </c>
       <c r="B138">
-        <v>234</v>
-      </c>
-      <c r="C138">
-        <v>234</v>
+        <v>303</v>
+      </c>
+      <c r="C138" t="s">
+        <v>30</v>
       </c>
       <c r="D138" s="1">
+        <v>46179</v>
+      </c>
+      <c r="E138" s="1">
         <v>46178</v>
       </c>
-      <c r="E138" s="1">
-        <v>46177</v>
-      </c>
       <c r="F138">
-        <v>20112</v>
+        <v>20047</v>
       </c>
       <c r="G138">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H138">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I138">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="J138">
-        <v>0.6</v>
+        <v>0.93548387099999997</v>
       </c>
       <c r="K138">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L138">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="M138">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="N138">
-        <v>0.6</v>
+        <v>0.93548387099999997</v>
       </c>
       <c r="O138" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>9327</v>
+        <v>9386</v>
       </c>
       <c r="B139">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="C139">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="D139" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="E139" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="F139">
-        <v>200158</v>
+        <v>20003</v>
       </c>
       <c r="G139">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H139">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I139">
         <v>0</v>
@@ -7009,10 +7057,10 @@
         <v>1</v>
       </c>
       <c r="K139">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L139">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M139">
         <v>0</v>
@@ -7021,92 +7069,98 @@
         <v>1</v>
       </c>
       <c r="O139" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>9334</v>
+        <v>9385</v>
       </c>
       <c r="B140">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="C140">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="D140" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="E140" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="F140">
-        <v>20006</v>
+        <v>20111</v>
       </c>
       <c r="G140">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H140">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I140">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="J140">
-        <v>0.96296296299999995</v>
+        <v>0.69565217400000001</v>
       </c>
       <c r="K140">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="L140">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M140">
-        <v>-1</v>
+        <v>-23</v>
       </c>
       <c r="N140">
-        <v>0.96296296299999995</v>
+        <v>0</v>
       </c>
       <c r="O140" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>9390</v>
+        <v>9380</v>
       </c>
       <c r="B141">
-        <v>221</v>
+        <v>121</v>
       </c>
       <c r="C141" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D141" s="1">
         <v>46181</v>
       </c>
       <c r="E141" s="1">
-        <v>46181</v>
+        <v>46179</v>
       </c>
       <c r="F141">
         <v>20005</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I141">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J141">
+        <v>0.76923076899999998</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L141">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M141">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N141">
+        <v>0.76923076899999998</v>
       </c>
       <c r="O141" t="s">
         <v>25</v>
@@ -7114,60 +7168,60 @@
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>9330</v>
+        <v>9387</v>
       </c>
       <c r="B142">
-        <v>236</v>
+        <v>128</v>
       </c>
       <c r="C142">
-        <v>236</v>
+        <v>128</v>
       </c>
       <c r="D142" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="E142" s="1">
-        <v>46177</v>
+        <v>46179</v>
       </c>
       <c r="F142">
-        <v>20111</v>
+        <v>20007</v>
       </c>
       <c r="G142">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H142">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I142">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J142">
-        <v>0.69230769199999997</v>
+        <v>0.60714285700000004</v>
       </c>
       <c r="K142">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L142">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M142">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="N142">
-        <v>0.69230769199999997</v>
+        <v>0.60714285700000004</v>
       </c>
       <c r="O142" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>9323</v>
+        <v>9326</v>
       </c>
       <c r="B143">
-        <v>213</v>
-      </c>
-      <c r="C143" t="s">
-        <v>48</v>
+        <v>232</v>
+      </c>
+      <c r="C143">
+        <v>232</v>
       </c>
       <c r="D143" s="1">
         <v>46178</v>
@@ -7176,254 +7230,260 @@
         <v>46177</v>
       </c>
       <c r="F143">
-        <v>20058</v>
+        <v>20130</v>
       </c>
       <c r="G143">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="H143">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I143">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="J143">
-        <v>0.62790697699999998</v>
+        <v>2.3333333330000001</v>
       </c>
       <c r="K143">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="L143">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="M143">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="N143">
-        <v>0.62790697699999998</v>
+        <v>2.3333333330000001</v>
       </c>
       <c r="O143" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>9376</v>
+        <v>9383</v>
       </c>
       <c r="B144">
-        <v>327</v>
-      </c>
-      <c r="C144">
-        <v>327</v>
+        <v>124</v>
+      </c>
+      <c r="C144" t="s">
+        <v>60</v>
       </c>
       <c r="D144" s="1">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="E144" s="1">
         <v>46179</v>
       </c>
       <c r="F144">
-        <v>20076</v>
+        <v>200158</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I144">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J144">
+        <v>0.625</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L144">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M144">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N144">
+        <v>0.625</v>
       </c>
       <c r="O144" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>9377</v>
+        <v>9347</v>
       </c>
       <c r="B145">
-        <v>502</v>
+        <v>307</v>
       </c>
       <c r="C145" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D145" s="1">
-        <v>46180</v>
+        <v>46178</v>
       </c>
       <c r="E145" s="1">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="F145">
-        <v>200150</v>
+        <v>11215</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I145">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J145">
+        <v>0.71428571399999996</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L145">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M145">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="N145">
+        <v>0.71428571399999996</v>
       </c>
       <c r="O145" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>9332</v>
+        <v>9414</v>
       </c>
       <c r="B146">
-        <v>238</v>
-      </c>
-      <c r="C146">
-        <v>238</v>
+        <v>501</v>
+      </c>
+      <c r="C146" t="s">
+        <v>67</v>
       </c>
       <c r="D146" s="1">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="E146" s="1">
-        <v>46177</v>
+        <v>46182</v>
       </c>
       <c r="F146">
-        <v>20007</v>
+        <v>200150</v>
       </c>
       <c r="G146">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I146">
-        <v>-7</v>
-      </c>
-      <c r="J146">
-        <v>0.70833333300000001</v>
+        <v>0</v>
       </c>
       <c r="K146">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L146">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M146">
-        <v>-7</v>
-      </c>
-      <c r="N146">
-        <v>0.70833333300000001</v>
+        <v>0</v>
       </c>
       <c r="O146" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>9343</v>
+        <v>9405</v>
       </c>
       <c r="B147">
-        <v>303</v>
+        <v>222</v>
       </c>
       <c r="C147" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="D147" s="1">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="E147" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="F147">
-        <v>20047</v>
+        <v>20130</v>
       </c>
       <c r="G147">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H147">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I147">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J147">
-        <v>0.93548387099999997</v>
+        <v>1</v>
       </c>
       <c r="K147">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="L147">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M147">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="N147">
-        <v>0.93548387099999997</v>
+        <v>1</v>
       </c>
       <c r="O147" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>9386</v>
+        <v>9410</v>
       </c>
       <c r="B148">
-        <v>127</v>
+        <v>227</v>
       </c>
       <c r="C148">
-        <v>127</v>
+        <v>227</v>
       </c>
       <c r="D148" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E148" s="1">
         <v>46181</v>
-      </c>
-      <c r="E148" s="1">
-        <v>46179</v>
       </c>
       <c r="F148">
         <v>20003</v>
       </c>
       <c r="G148">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="H148">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="J148">
-        <v>1</v>
+        <v>0.69230769199999997</v>
       </c>
       <c r="K148">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="L148">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M148">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="N148">
-        <v>1</v>
+        <v>0.69230769199999997</v>
       </c>
       <c r="O148" t="s">
         <v>19</v>
@@ -7431,60 +7491,60 @@
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>9385</v>
+        <v>9407</v>
       </c>
       <c r="B149">
-        <v>126</v>
-      </c>
-      <c r="C149">
-        <v>126</v>
+        <v>224</v>
+      </c>
+      <c r="C149" t="s">
+        <v>65</v>
       </c>
       <c r="D149" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E149" s="1">
         <v>46181</v>
       </c>
-      <c r="E149" s="1">
-        <v>46179</v>
-      </c>
       <c r="F149">
-        <v>20111</v>
+        <v>20112</v>
       </c>
       <c r="G149">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H149">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I149">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="J149">
-        <v>0.69565217400000001</v>
+        <v>0.75</v>
       </c>
       <c r="K149">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L149">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M149">
-        <v>-23</v>
+        <v>-5</v>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="O149" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>9380</v>
+        <v>9388</v>
       </c>
       <c r="B150">
-        <v>121</v>
-      </c>
-      <c r="C150" t="s">
-        <v>45</v>
+        <v>129</v>
+      </c>
+      <c r="C150">
+        <v>129</v>
       </c>
       <c r="D150" s="1">
         <v>46181</v>
@@ -7493,262 +7553,280 @@
         <v>46179</v>
       </c>
       <c r="F150">
-        <v>20005</v>
+        <v>20008</v>
       </c>
       <c r="G150">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H150">
         <v>10</v>
       </c>
       <c r="I150">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="J150">
-        <v>0.76923076899999998</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K150">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L150">
         <v>10</v>
       </c>
       <c r="M150">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="N150">
-        <v>0.76923076899999998</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O150" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>9387</v>
+        <v>9406</v>
       </c>
       <c r="B151">
-        <v>128</v>
-      </c>
-      <c r="C151">
-        <v>128</v>
+        <v>223</v>
+      </c>
+      <c r="C151" t="s">
+        <v>63</v>
       </c>
       <c r="D151" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E151" s="1">
         <v>46181</v>
       </c>
-      <c r="E151" s="1">
-        <v>46179</v>
-      </c>
       <c r="F151">
-        <v>20007</v>
+        <v>200158</v>
       </c>
       <c r="G151">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H151">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I151">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="J151">
-        <v>0.60714285700000004</v>
+        <v>1</v>
       </c>
       <c r="K151">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L151">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M151">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="N151">
-        <v>0.60714285700000004</v>
+        <v>1</v>
       </c>
       <c r="O151" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>9399</v>
+        <v>9289</v>
       </c>
       <c r="B152">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="C152" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D152" s="1">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="E152" s="1">
-        <v>46181</v>
+        <v>46176</v>
       </c>
       <c r="F152">
-        <v>11215</v>
+        <v>20058</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I152">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J152">
+        <v>0.75</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L152">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M152">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="N152">
+        <v>0.75</v>
       </c>
       <c r="O152" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>9383</v>
+        <v>9408</v>
       </c>
       <c r="B153">
-        <v>124</v>
+        <v>225</v>
       </c>
       <c r="C153" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D153" s="1">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="E153" s="1">
-        <v>46179</v>
+        <v>46181</v>
       </c>
       <c r="F153">
-        <v>20112</v>
+        <v>20066</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I153">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J153">
+        <v>0.63636363600000001</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L153">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M153">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="N153">
+        <v>0.63636363600000001</v>
       </c>
       <c r="O153" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>9388</v>
+        <v>9266</v>
       </c>
       <c r="B154">
-        <v>129</v>
+        <v>335</v>
       </c>
       <c r="C154">
-        <v>129</v>
+        <v>335</v>
       </c>
       <c r="D154" s="1">
-        <v>46179</v>
+        <v>46176</v>
       </c>
       <c r="E154" s="1">
-        <v>46179</v>
+        <v>46175</v>
       </c>
       <c r="F154">
-        <v>20008</v>
+        <v>20066</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I154">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J154">
+        <v>0.44444444399999999</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L154">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M154">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="N154">
+        <v>0.44444444399999999</v>
       </c>
       <c r="O154" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>9289</v>
+        <v>9265</v>
       </c>
       <c r="B155">
-        <v>105</v>
-      </c>
-      <c r="C155" t="s">
-        <v>94</v>
+        <v>334</v>
+      </c>
+      <c r="C155">
+        <v>334</v>
       </c>
       <c r="D155" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="E155" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="F155">
-        <v>20058</v>
+        <v>20112</v>
       </c>
       <c r="G155">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H155">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I155">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="J155">
-        <v>0.75</v>
+        <v>0.85714285700000004</v>
       </c>
       <c r="K155">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L155">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M155">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="N155">
-        <v>0.75</v>
+        <v>0.85714285700000004</v>
       </c>
       <c r="O155" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>9266</v>
+        <v>9264</v>
       </c>
       <c r="B156">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C156">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D156" s="1">
         <v>46176</v>
@@ -7757,107 +7835,101 @@
         <v>46175</v>
       </c>
       <c r="F156">
-        <v>20066</v>
+        <v>200158</v>
       </c>
       <c r="G156">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H156">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I156">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J156">
-        <v>0.44444444399999999</v>
+        <v>1</v>
       </c>
       <c r="K156">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L156">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="M156">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="N156">
-        <v>0.44444444399999999</v>
+        <v>1</v>
       </c>
       <c r="O156" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>9265</v>
+        <v>9379</v>
       </c>
       <c r="B157">
-        <v>334</v>
-      </c>
-      <c r="C157">
-        <v>334</v>
+        <v>503</v>
+      </c>
+      <c r="C157" t="s">
+        <v>86</v>
       </c>
       <c r="D157" s="1">
-        <v>46176</v>
+        <v>46180</v>
       </c>
       <c r="E157" s="1">
-        <v>46175</v>
+        <v>46179</v>
       </c>
       <c r="F157">
-        <v>20112</v>
+        <v>200150</v>
       </c>
       <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="O157" t="s">
         <v>21</v>
-      </c>
-      <c r="H157">
-        <v>18</v>
-      </c>
-      <c r="I157">
-        <v>-3</v>
-      </c>
-      <c r="J157">
-        <v>0.85714285700000004</v>
-      </c>
-      <c r="K157">
-        <v>21</v>
-      </c>
-      <c r="L157">
-        <v>18</v>
-      </c>
-      <c r="M157">
-        <v>-3</v>
-      </c>
-      <c r="N157">
-        <v>0.85714285700000004</v>
-      </c>
-      <c r="O157" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>9264</v>
+        <v>9354</v>
       </c>
       <c r="B158">
-        <v>333</v>
-      </c>
-      <c r="C158">
-        <v>333</v>
+        <v>316</v>
+      </c>
+      <c r="C158" t="s">
+        <v>95</v>
       </c>
       <c r="D158" s="1">
-        <v>46176</v>
+        <v>46179</v>
       </c>
       <c r="E158" s="1">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="F158">
-        <v>200158</v>
+        <v>20047</v>
       </c>
       <c r="G158">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H158">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I158">
         <v>0</v>
@@ -7866,10 +7938,10 @@
         <v>1</v>
       </c>
       <c r="K158">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L158">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M158">
         <v>0</v>
@@ -7878,59 +7950,65 @@
         <v>1</v>
       </c>
       <c r="O158" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>9379</v>
+        <v>9355</v>
       </c>
       <c r="B159">
-        <v>503</v>
+        <v>317</v>
       </c>
       <c r="C159" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D159" s="1">
-        <v>46180</v>
+        <v>46179</v>
       </c>
       <c r="E159" s="1">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="F159">
-        <v>200150</v>
+        <v>20043</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I159">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J159">
+        <v>1.1428571430000001</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L159">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M159">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="N159">
+        <v>1.1428571430000001</v>
       </c>
       <c r="O159" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>9354</v>
+        <v>9356</v>
       </c>
       <c r="B160">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C160" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D160" s="1">
         <v>46179</v>
@@ -7939,45 +8017,45 @@
         <v>46178</v>
       </c>
       <c r="F160">
-        <v>20047</v>
+        <v>11215</v>
       </c>
       <c r="G160">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H160">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I160">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="J160">
-        <v>1</v>
+        <v>0.764705882</v>
       </c>
       <c r="K160">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="L160">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="M160">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N160">
-        <v>1</v>
+        <v>0.764705882</v>
       </c>
       <c r="O160" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>9355</v>
+        <v>9360</v>
       </c>
       <c r="B161">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C161" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D161" s="1">
         <v>46179</v>
@@ -7986,45 +8064,45 @@
         <v>46178</v>
       </c>
       <c r="F161">
-        <v>20043</v>
+        <v>20095</v>
       </c>
       <c r="G161">
         <v>14</v>
       </c>
       <c r="H161">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I161">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="J161">
-        <v>1.1428571430000001</v>
+        <v>0.5</v>
       </c>
       <c r="K161">
         <v>14</v>
       </c>
       <c r="L161">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M161">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="N161">
-        <v>1.1428571430000001</v>
+        <v>0.5</v>
       </c>
       <c r="O161" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>9356</v>
+        <v>9357</v>
       </c>
       <c r="B162">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C162" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D162" s="1">
         <v>46179</v>
@@ -8033,45 +8111,45 @@
         <v>46178</v>
       </c>
       <c r="F162">
-        <v>11215</v>
+        <v>20058</v>
       </c>
       <c r="G162">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H162">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I162">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="J162">
-        <v>0.764705882</v>
+        <v>1</v>
       </c>
       <c r="K162">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="L162">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M162">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="N162">
-        <v>0.764705882</v>
+        <v>1</v>
       </c>
       <c r="O162" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>9360</v>
+        <v>9358</v>
       </c>
       <c r="B163">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C163" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D163" s="1">
         <v>46179</v>
@@ -8080,45 +8158,45 @@
         <v>46178</v>
       </c>
       <c r="F163">
-        <v>20095</v>
+        <v>20043</v>
       </c>
       <c r="G163">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H163">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I163">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="J163">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="K163">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L163">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M163">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="N163">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="O163" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>9357</v>
+        <v>9359</v>
       </c>
       <c r="B164">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C164" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D164" s="1">
         <v>46179</v>
@@ -8127,45 +8205,45 @@
         <v>46178</v>
       </c>
       <c r="F164">
-        <v>20058</v>
+        <v>20095</v>
       </c>
       <c r="G164">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H164">
         <v>4</v>
       </c>
       <c r="I164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K164">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L164">
         <v>4</v>
       </c>
       <c r="M164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O164" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>9358</v>
+        <v>9361</v>
       </c>
       <c r="B165">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C165" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D165" s="1">
         <v>46179</v>
@@ -8174,45 +8252,45 @@
         <v>46178</v>
       </c>
       <c r="F165">
-        <v>20043</v>
+        <v>20155</v>
       </c>
       <c r="G165">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H165">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I165">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="J165">
-        <v>3</v>
+        <v>0.88888888899999996</v>
       </c>
       <c r="K165">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L165">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M165">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="N165">
-        <v>3</v>
+        <v>0.88888888899999996</v>
       </c>
       <c r="O165" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>9359</v>
+        <v>9363</v>
       </c>
       <c r="B166">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C166" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D166" s="1">
         <v>46179</v>
@@ -8221,45 +8299,45 @@
         <v>46178</v>
       </c>
       <c r="F166">
-        <v>20095</v>
+        <v>200158</v>
       </c>
       <c r="G166">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H166">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I166">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="J166">
-        <v>2</v>
+        <v>0.909090909</v>
       </c>
       <c r="K166">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="L166">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M166">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="N166">
-        <v>2</v>
+        <v>0.909090909</v>
       </c>
       <c r="O166" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>9361</v>
+        <v>9362</v>
       </c>
       <c r="B167">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C167" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D167" s="1">
         <v>46179</v>
@@ -8268,45 +8346,45 @@
         <v>46178</v>
       </c>
       <c r="F167">
-        <v>20155</v>
+        <v>20153</v>
       </c>
       <c r="G167">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H167">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I167">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J167">
-        <v>0.88888888899999996</v>
+        <v>1</v>
       </c>
       <c r="K167">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L167">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M167">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="N167">
-        <v>0.88888888899999996</v>
+        <v>1</v>
       </c>
       <c r="O167" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>9363</v>
+        <v>9373</v>
       </c>
       <c r="B168">
-        <v>325</v>
-      </c>
-      <c r="C168" t="s">
-        <v>104</v>
+        <v>339</v>
+      </c>
+      <c r="C168">
+        <v>339</v>
       </c>
       <c r="D168" s="1">
         <v>46179</v>
@@ -8315,45 +8393,45 @@
         <v>46178</v>
       </c>
       <c r="F168">
-        <v>200158</v>
+        <v>20008</v>
       </c>
       <c r="G168">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H168">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I168">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J168">
-        <v>0.909090909</v>
+        <v>0.77777777800000003</v>
       </c>
       <c r="K168">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L168">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M168">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="N168">
-        <v>0.909090909</v>
+        <v>0.77777777800000003</v>
       </c>
       <c r="O168" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>9362</v>
+        <v>9364</v>
       </c>
       <c r="B169">
-        <v>324</v>
-      </c>
-      <c r="C169" t="s">
-        <v>103</v>
+        <v>326</v>
+      </c>
+      <c r="C169">
+        <v>326</v>
       </c>
       <c r="D169" s="1">
         <v>46179</v>
@@ -8362,45 +8440,39 @@
         <v>46178</v>
       </c>
       <c r="F169">
-        <v>20153</v>
+        <v>200150</v>
       </c>
       <c r="G169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169">
         <v>0</v>
       </c>
-      <c r="J169">
-        <v>1</v>
-      </c>
       <c r="K169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M169">
         <v>0</v>
       </c>
-      <c r="N169">
-        <v>1</v>
-      </c>
       <c r="O169" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>9373</v>
+        <v>9367</v>
       </c>
       <c r="B170">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C170">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="D170" s="1">
         <v>46179</v>
@@ -8409,45 +8481,45 @@
         <v>46178</v>
       </c>
       <c r="F170">
-        <v>20008</v>
+        <v>20130</v>
       </c>
       <c r="G170">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H170">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I170">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="J170">
-        <v>0.77777777800000003</v>
+        <v>1</v>
       </c>
       <c r="K170">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L170">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M170">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="N170">
-        <v>0.77777777800000003</v>
+        <v>1</v>
       </c>
       <c r="O170" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>9364</v>
+        <v>9346</v>
       </c>
       <c r="B171">
-        <v>326</v>
-      </c>
-      <c r="C171">
-        <v>326</v>
+        <v>306</v>
+      </c>
+      <c r="C171" t="s">
+        <v>105</v>
       </c>
       <c r="D171" s="1">
         <v>46179</v>
@@ -8456,39 +8528,45 @@
         <v>46178</v>
       </c>
       <c r="F171">
-        <v>200150</v>
+        <v>20105</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I171">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J171">
+        <v>0.909090909</v>
       </c>
       <c r="K171">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L171">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M171">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="N171">
+        <v>0.909090909</v>
       </c>
       <c r="O171" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>9367</v>
+        <v>9368</v>
       </c>
       <c r="B172">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C172">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D172" s="1">
         <v>46179</v>
@@ -8497,45 +8575,45 @@
         <v>46178</v>
       </c>
       <c r="F172">
-        <v>20130</v>
+        <v>20007</v>
       </c>
       <c r="G172">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H172">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I172">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="J172">
-        <v>1</v>
+        <v>0.69230769199999997</v>
       </c>
       <c r="K172">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L172">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M172">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N172">
-        <v>1</v>
+        <v>0.69230769199999997</v>
       </c>
       <c r="O172" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>9346</v>
+        <v>9348</v>
       </c>
       <c r="B173">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C173" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D173" s="1">
         <v>46179</v>
@@ -8544,92 +8622,92 @@
         <v>46178</v>
       </c>
       <c r="F173">
-        <v>20105</v>
+        <v>20155</v>
       </c>
       <c r="G173">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="H173">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I173">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="J173">
-        <v>0.909090909</v>
+        <v>0.80555555599999995</v>
       </c>
       <c r="K173">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="L173">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M173">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="N173">
-        <v>0.909090909</v>
+        <v>0.80555555599999995</v>
       </c>
       <c r="O173" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>9347</v>
+        <v>9370</v>
       </c>
       <c r="B174">
-        <v>307</v>
-      </c>
-      <c r="C174" t="s">
-        <v>75</v>
+        <v>336</v>
+      </c>
+      <c r="C174">
+        <v>336</v>
       </c>
       <c r="D174" s="1">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="E174" s="1">
         <v>46178</v>
       </c>
       <c r="F174">
-        <v>11215</v>
+        <v>20111</v>
       </c>
       <c r="G174">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H174">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I174">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="J174">
-        <v>0.71428571399999996</v>
+        <v>0.70588235300000002</v>
       </c>
       <c r="K174">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="L174">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M174">
-        <v>-8</v>
+        <v>-17</v>
       </c>
       <c r="N174">
-        <v>0.71428571399999996</v>
+        <v>0</v>
       </c>
       <c r="O174" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>9368</v>
+        <v>9371</v>
       </c>
       <c r="B175">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C175">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D175" s="1">
         <v>46179</v>
@@ -8638,45 +8716,45 @@
         <v>46178</v>
       </c>
       <c r="F175">
-        <v>20007</v>
+        <v>20003</v>
       </c>
       <c r="G175">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H175">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I175">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="J175">
-        <v>0.69230769199999997</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K175">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L175">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M175">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="N175">
-        <v>0.69230769199999997</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O175" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>9348</v>
+        <v>9344</v>
       </c>
       <c r="B176">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C176" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D176" s="1">
         <v>46179</v>
@@ -8685,139 +8763,133 @@
         <v>46178</v>
       </c>
       <c r="F176">
-        <v>20155</v>
+        <v>20086</v>
       </c>
       <c r="G176">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="H176">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I176">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="J176">
-        <v>0.80555555599999995</v>
+        <v>0.88461538500000003</v>
       </c>
       <c r="K176">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="L176">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="M176">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="N176">
-        <v>0.80555555599999995</v>
+        <v>0.88461538500000003</v>
       </c>
       <c r="O176" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>9370</v>
+        <v>9378</v>
       </c>
       <c r="B177">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C177">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="D177" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="E177" s="1">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="F177">
-        <v>20111</v>
+        <v>20076</v>
       </c>
       <c r="G177">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H177">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I177">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J177">
-        <v>0.70588235300000002</v>
+        <v>1</v>
       </c>
       <c r="K177">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="N177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>9371</v>
+        <v>9375</v>
       </c>
       <c r="B178">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C178">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D178" s="1">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="E178" s="1">
         <v>46178</v>
       </c>
       <c r="F178">
-        <v>20003</v>
+        <v>200158</v>
       </c>
       <c r="G178">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I178">
-        <v>-6</v>
-      </c>
-      <c r="J178">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K178">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L178">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M178">
-        <v>-6</v>
-      </c>
-      <c r="N178">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="O178" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>9344</v>
+        <v>9345</v>
       </c>
       <c r="B179">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C179" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D179" s="1">
         <v>46179</v>
@@ -8826,95 +8898,95 @@
         <v>46178</v>
       </c>
       <c r="F179">
-        <v>20086</v>
+        <v>20106</v>
       </c>
       <c r="G179">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H179">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I179">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="J179">
-        <v>0.88461538500000003</v>
+        <v>0.47058823500000002</v>
       </c>
       <c r="K179">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L179">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="M179">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="N179">
-        <v>0.88461538500000003</v>
+        <v>0.47058823500000002</v>
       </c>
       <c r="O179" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>9378</v>
+        <v>9349</v>
       </c>
       <c r="B180">
-        <v>327</v>
-      </c>
-      <c r="C180">
-        <v>327</v>
+        <v>311</v>
+      </c>
+      <c r="C180" t="s">
+        <v>68</v>
       </c>
       <c r="D180" s="1">
         <v>46179</v>
       </c>
       <c r="E180" s="1">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="F180">
-        <v>20076</v>
+        <v>20057</v>
       </c>
       <c r="G180">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="H180">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="I180">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="J180">
-        <v>1</v>
+        <v>0.93220338999999997</v>
       </c>
       <c r="K180">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="L180">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="M180">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N180">
-        <v>1</v>
+        <v>0.93220338999999997</v>
       </c>
       <c r="O180" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>9391</v>
+        <v>9392</v>
       </c>
       <c r="B181">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C181" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D181" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E181" s="1">
         <v>46181</v>
@@ -8946,22 +9018,22 @@
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>9375</v>
+        <v>9391</v>
       </c>
       <c r="B182">
-        <v>341</v>
-      </c>
-      <c r="C182">
-        <v>341</v>
+        <v>500</v>
+      </c>
+      <c r="C182" t="s">
+        <v>66</v>
       </c>
       <c r="D182" s="1">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="E182" s="1">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="F182">
-        <v>200158</v>
+        <v>20043</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -8982,191 +9054,215 @@
         <v>0</v>
       </c>
       <c r="O182" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>9392</v>
+        <v>9398</v>
       </c>
       <c r="B183">
-        <v>502</v>
+        <v>206</v>
       </c>
       <c r="C183" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="D183" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E183" s="1">
         <v>46181</v>
       </c>
       <c r="F183">
-        <v>200150</v>
+        <v>20086</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H183">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I183">
         <v>0</v>
       </c>
+      <c r="J183">
+        <v>1</v>
+      </c>
       <c r="K183">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L183">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M183">
         <v>0</v>
       </c>
+      <c r="N183">
+        <v>1</v>
+      </c>
       <c r="O183" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>9393</v>
+        <v>9396</v>
       </c>
       <c r="B184">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C184" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D184" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E184" s="1">
         <v>46181</v>
       </c>
       <c r="F184">
-        <v>20106</v>
+        <v>20095</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I184">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J184">
+        <v>0.77777777800000003</v>
       </c>
       <c r="K184">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L184">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M184">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="N184">
+        <v>0.77777777800000003</v>
       </c>
       <c r="O184" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>9394</v>
+        <v>9393</v>
       </c>
       <c r="B185">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C185" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D185" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E185" s="1">
         <v>46181</v>
       </c>
       <c r="F185">
-        <v>20076</v>
+        <v>20106</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I185">
         <v>0</v>
       </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
       <c r="K185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M185">
         <v>0</v>
       </c>
+      <c r="N185">
+        <v>1</v>
+      </c>
       <c r="O185" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>9395</v>
+        <v>9404</v>
       </c>
       <c r="B186">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="C186" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D186" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E186" s="1">
         <v>46181</v>
       </c>
       <c r="F186">
-        <v>20155</v>
+        <v>20005</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I186">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="J186">
+        <v>0.72093023300000003</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L186">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M186">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="N186">
+        <v>0.72093023300000003</v>
       </c>
       <c r="O186" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>9396</v>
+        <v>9415</v>
       </c>
       <c r="B187">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="C187" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D187" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E187" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F187">
-        <v>20095</v>
+        <v>20058</v>
       </c>
       <c r="G187">
         <v>0</v>
@@ -9187,74 +9283,68 @@
         <v>0</v>
       </c>
       <c r="O187" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>9345</v>
+        <v>9416</v>
       </c>
       <c r="B188">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C188" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="D188" s="1">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="E188" s="1">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="F188">
-        <v>20106</v>
+        <v>20153</v>
       </c>
       <c r="G188">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H188">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I188">
-        <v>-9</v>
-      </c>
-      <c r="J188">
-        <v>0.47058823500000002</v>
+        <v>0</v>
       </c>
       <c r="K188">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L188">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M188">
-        <v>-9</v>
-      </c>
-      <c r="N188">
-        <v>0.47058823500000002</v>
+        <v>0</v>
       </c>
       <c r="O188" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>9397</v>
+        <v>9417</v>
       </c>
       <c r="B189">
-        <v>205</v>
+        <v>304</v>
       </c>
       <c r="C189" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D189" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E189" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F189">
-        <v>20153</v>
+        <v>20086</v>
       </c>
       <c r="G189">
         <v>0</v>
@@ -9275,27 +9365,27 @@
         <v>0</v>
       </c>
       <c r="O189" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>9398</v>
+        <v>9418</v>
       </c>
       <c r="B190">
-        <v>206</v>
+        <v>305</v>
       </c>
       <c r="C190" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="D190" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E190" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F190">
-        <v>20086</v>
+        <v>20066</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -9316,74 +9406,68 @@
         <v>0</v>
       </c>
       <c r="O190" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>9349</v>
+        <v>9419</v>
       </c>
       <c r="B191">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="C191" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D191" s="1">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="E191" s="1">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="F191">
-        <v>20057</v>
+        <v>20105</v>
       </c>
       <c r="G191">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
+      </c>
+      <c r="O191" t="s">
         <v>55</v>
-      </c>
-      <c r="I191">
-        <v>-4</v>
-      </c>
-      <c r="J191">
-        <v>0.93220338999999997</v>
-      </c>
-      <c r="K191">
-        <v>59</v>
-      </c>
-      <c r="L191">
-        <v>55</v>
-      </c>
-      <c r="M191">
-        <v>-4</v>
-      </c>
-      <c r="N191">
-        <v>0.93220338999999997</v>
-      </c>
-      <c r="O191" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>9400</v>
+        <v>9420</v>
       </c>
       <c r="B192">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="C192" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D192" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E192" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F192">
-        <v>20105</v>
+        <v>20076</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -9404,27 +9488,27 @@
         <v>0</v>
       </c>
       <c r="O192" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>9401</v>
+        <v>9421</v>
       </c>
       <c r="B193">
-        <v>210</v>
+        <v>308</v>
       </c>
       <c r="C193" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D193" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="E193" s="1">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="F193">
-        <v>20058</v>
+        <v>20057</v>
       </c>
       <c r="G193">
         <v>0</v>
@@ -9445,48 +9529,1045 @@
         <v>0</v>
       </c>
       <c r="O193" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194">
+        <v>9422</v>
+      </c>
+      <c r="B194">
+        <v>311</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E194" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F194">
+        <v>20106</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
+      </c>
+      <c r="O194" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>9423</v>
+      </c>
+      <c r="B195">
+        <v>312</v>
+      </c>
+      <c r="C195" t="s">
+        <v>70</v>
+      </c>
+      <c r="D195" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E195" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F195">
+        <v>20095</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="O195" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>9424</v>
+      </c>
+      <c r="B196">
+        <v>313</v>
+      </c>
+      <c r="C196" t="s">
+        <v>69</v>
+      </c>
+      <c r="D196" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E196" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F196">
+        <v>11215</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+      <c r="O196" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>9425</v>
+      </c>
+      <c r="B197">
+        <v>314</v>
+      </c>
+      <c r="C197" t="s">
+        <v>71</v>
+      </c>
+      <c r="D197" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E197" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F197">
+        <v>20047</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
+      </c>
+      <c r="O197" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>9426</v>
+      </c>
+      <c r="B198">
+        <v>315</v>
+      </c>
+      <c r="C198" t="s">
+        <v>91</v>
+      </c>
+      <c r="D198" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E198" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F198">
+        <v>20043</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="O198" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>9427</v>
+      </c>
+      <c r="B199">
+        <v>331</v>
+      </c>
+      <c r="C199">
+        <v>331</v>
+      </c>
+      <c r="D199" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E199" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F199">
+        <v>20006</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="O199" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>9428</v>
+      </c>
+      <c r="B200">
+        <v>332</v>
+      </c>
+      <c r="C200">
+        <v>332</v>
+      </c>
+      <c r="D200" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E200" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F200">
+        <v>20130</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="O200" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>9429</v>
+      </c>
+      <c r="B201">
+        <v>333</v>
+      </c>
+      <c r="C201">
+        <v>333</v>
+      </c>
+      <c r="D201" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E201" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F201">
+        <v>200158</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
+      </c>
+      <c r="O201" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>9430</v>
+      </c>
+      <c r="B202">
+        <v>334</v>
+      </c>
+      <c r="C202">
+        <v>334</v>
+      </c>
+      <c r="D202" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E202" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F202">
+        <v>20112</v>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
+      </c>
+      <c r="O202" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>9431</v>
+      </c>
+      <c r="B203">
+        <v>335</v>
+      </c>
+      <c r="C203">
+        <v>335</v>
+      </c>
+      <c r="D203" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E203" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F203">
+        <v>20113</v>
+      </c>
+      <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="O203" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>9432</v>
+      </c>
+      <c r="B204">
+        <v>336</v>
+      </c>
+      <c r="C204">
+        <v>336</v>
+      </c>
+      <c r="D204" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E204" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F204">
+        <v>20111</v>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="O204" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>9433</v>
+      </c>
+      <c r="B205">
+        <v>337</v>
+      </c>
+      <c r="C205">
+        <v>337</v>
+      </c>
+      <c r="D205" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E205" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F205">
+        <v>20003</v>
+      </c>
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="O205" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>9434</v>
+      </c>
+      <c r="B206">
+        <v>338</v>
+      </c>
+      <c r="C206">
+        <v>338</v>
+      </c>
+      <c r="D206" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E206" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F206">
+        <v>20007</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206">
+        <v>0</v>
+      </c>
+      <c r="O206" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>9435</v>
+      </c>
+      <c r="B207">
+        <v>339</v>
+      </c>
+      <c r="C207">
+        <v>339</v>
+      </c>
+      <c r="D207" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E207" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F207">
+        <v>20008</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="O207" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>9436</v>
+      </c>
+      <c r="B208">
+        <v>340</v>
+      </c>
+      <c r="C208">
+        <v>340</v>
+      </c>
+      <c r="D208" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E208" s="1">
+        <v>46182</v>
+      </c>
+      <c r="F208">
+        <v>20005</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208">
+        <v>0</v>
+      </c>
+      <c r="O208" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>9394</v>
+      </c>
+      <c r="B209">
+        <v>202</v>
+      </c>
+      <c r="C209" t="s">
+        <v>43</v>
+      </c>
+      <c r="D209" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E209" s="1">
+        <v>46181</v>
+      </c>
+      <c r="F209">
+        <v>20076</v>
+      </c>
+      <c r="G209">
+        <v>35</v>
+      </c>
+      <c r="H209">
+        <v>24</v>
+      </c>
+      <c r="I209">
+        <v>-11</v>
+      </c>
+      <c r="J209">
+        <v>0.68571428599999995</v>
+      </c>
+      <c r="K209">
+        <v>35</v>
+      </c>
+      <c r="L209">
+        <v>24</v>
+      </c>
+      <c r="M209">
+        <v>-11</v>
+      </c>
+      <c r="N209">
+        <v>0.68571428599999995</v>
+      </c>
+      <c r="O209" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>9401</v>
+      </c>
+      <c r="B210">
+        <v>210</v>
+      </c>
+      <c r="C210" t="s">
+        <v>85</v>
+      </c>
+      <c r="D210" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E210" s="1">
+        <v>46181</v>
+      </c>
+      <c r="F210">
+        <v>20058</v>
+      </c>
+      <c r="G210">
+        <v>46</v>
+      </c>
+      <c r="H210">
+        <v>18</v>
+      </c>
+      <c r="I210">
+        <v>-28</v>
+      </c>
+      <c r="J210">
+        <v>0.39130434800000002</v>
+      </c>
+      <c r="K210">
+        <v>46</v>
+      </c>
+      <c r="L210">
+        <v>18</v>
+      </c>
+      <c r="M210">
+        <v>-28</v>
+      </c>
+      <c r="N210">
+        <v>0.39130434800000002</v>
+      </c>
+      <c r="O210" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>9399</v>
+      </c>
+      <c r="B211">
+        <v>208</v>
+      </c>
+      <c r="C211" t="s">
+        <v>57</v>
+      </c>
+      <c r="D211" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E211" s="1">
+        <v>46181</v>
+      </c>
+      <c r="F211">
+        <v>11215</v>
+      </c>
+      <c r="G211">
+        <v>48</v>
+      </c>
+      <c r="H211">
+        <v>42</v>
+      </c>
+      <c r="I211">
+        <v>-6</v>
+      </c>
+      <c r="J211">
+        <v>0.875</v>
+      </c>
+      <c r="K211">
+        <v>48</v>
+      </c>
+      <c r="L211">
+        <v>42</v>
+      </c>
+      <c r="M211">
+        <v>-6</v>
+      </c>
+      <c r="N211">
+        <v>0.875</v>
+      </c>
+      <c r="O211" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>9395</v>
+      </c>
+      <c r="B212">
+        <v>203</v>
+      </c>
+      <c r="C212" t="s">
+        <v>58</v>
+      </c>
+      <c r="D212" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E212" s="1">
+        <v>46181</v>
+      </c>
+      <c r="F212">
+        <v>20155</v>
+      </c>
+      <c r="G212">
+        <v>44</v>
+      </c>
+      <c r="H212">
+        <v>23</v>
+      </c>
+      <c r="I212">
+        <v>-21</v>
+      </c>
+      <c r="J212">
+        <v>0.52272727299999999</v>
+      </c>
+      <c r="K212">
+        <v>44</v>
+      </c>
+      <c r="L212">
+        <v>23</v>
+      </c>
+      <c r="M212">
+        <v>-21</v>
+      </c>
+      <c r="N212">
+        <v>0.52272727299999999</v>
+      </c>
+      <c r="O212" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>9397</v>
+      </c>
+      <c r="B213">
+        <v>205</v>
+      </c>
+      <c r="C213" t="s">
+        <v>88</v>
+      </c>
+      <c r="D213" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E213" s="1">
+        <v>46181</v>
+      </c>
+      <c r="F213">
+        <v>20153</v>
+      </c>
+      <c r="G213">
+        <v>42</v>
+      </c>
+      <c r="H213">
+        <v>15</v>
+      </c>
+      <c r="I213">
+        <v>-27</v>
+      </c>
+      <c r="J213">
+        <v>0.35714285699999998</v>
+      </c>
+      <c r="K213">
+        <v>42</v>
+      </c>
+      <c r="L213">
+        <v>15</v>
+      </c>
+      <c r="M213">
+        <v>-27</v>
+      </c>
+      <c r="N213">
+        <v>0.35714285699999998</v>
+      </c>
+      <c r="O213" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>9400</v>
+      </c>
+      <c r="B214">
+        <v>209</v>
+      </c>
+      <c r="C214" t="s">
+        <v>54</v>
+      </c>
+      <c r="D214" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E214" s="1">
+        <v>46181</v>
+      </c>
+      <c r="F214">
+        <v>20105</v>
+      </c>
+      <c r="G214">
+        <v>46</v>
+      </c>
+      <c r="H214">
+        <v>37</v>
+      </c>
+      <c r="I214">
+        <v>-9</v>
+      </c>
+      <c r="J214">
+        <v>0.80434782599999999</v>
+      </c>
+      <c r="K214">
+        <v>46</v>
+      </c>
+      <c r="L214">
+        <v>37</v>
+      </c>
+      <c r="M214">
+        <v>-9</v>
+      </c>
+      <c r="N214">
+        <v>0.80434782599999999</v>
+      </c>
+      <c r="O214" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A215">
         <v>9402</v>
       </c>
-      <c r="B194">
+      <c r="B215">
         <v>211</v>
       </c>
-      <c r="C194" t="s">
+      <c r="C215" t="s">
         <v>46</v>
       </c>
-      <c r="D194" s="1">
+      <c r="D215" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E215" s="1">
         <v>46181</v>
       </c>
-      <c r="E194" s="1">
+      <c r="F215">
+        <v>20047</v>
+      </c>
+      <c r="G215">
+        <v>60</v>
+      </c>
+      <c r="H215">
+        <v>37</v>
+      </c>
+      <c r="I215">
+        <v>-23</v>
+      </c>
+      <c r="J215">
+        <v>0.61666666699999995</v>
+      </c>
+      <c r="K215">
+        <v>60</v>
+      </c>
+      <c r="L215">
+        <v>37</v>
+      </c>
+      <c r="M215">
+        <v>-23</v>
+      </c>
+      <c r="N215">
+        <v>0.61666666699999995</v>
+      </c>
+      <c r="O215" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>9403</v>
+      </c>
+      <c r="B216">
+        <v>212</v>
+      </c>
+      <c r="C216" t="s">
+        <v>59</v>
+      </c>
+      <c r="D216" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E216" s="1">
         <v>46181</v>
       </c>
-      <c r="F194">
-        <v>20047</v>
-      </c>
-      <c r="G194">
-        <v>0</v>
-      </c>
-      <c r="H194">
-        <v>0</v>
-      </c>
-      <c r="I194">
-        <v>0</v>
-      </c>
-      <c r="K194">
-        <v>0</v>
-      </c>
-      <c r="L194">
-        <v>0</v>
-      </c>
-      <c r="M194">
-        <v>0</v>
-      </c>
-      <c r="O194" t="s">
-        <v>79</v>
+      <c r="F216">
+        <v>20057</v>
+      </c>
+      <c r="G216">
+        <v>69</v>
+      </c>
+      <c r="H216">
+        <v>61</v>
+      </c>
+      <c r="I216">
+        <v>-8</v>
+      </c>
+      <c r="J216">
+        <v>0.88405797100000005</v>
+      </c>
+      <c r="K216">
+        <v>69</v>
+      </c>
+      <c r="L216">
+        <v>61</v>
+      </c>
+      <c r="M216">
+        <v>-8</v>
+      </c>
+      <c r="N216">
+        <v>0.88405797100000005</v>
+      </c>
+      <c r="O216" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>9409</v>
+      </c>
+      <c r="B217">
+        <v>226</v>
+      </c>
+      <c r="C217">
+        <v>226</v>
+      </c>
+      <c r="D217" s="1">
+        <v>46182</v>
+      </c>
+      <c r="E217" s="1">
+        <v>46181</v>
+      </c>
+      <c r="F217">
+        <v>20111</v>
+      </c>
+      <c r="G217">
+        <v>29</v>
+      </c>
+      <c r="H217">
+        <v>21</v>
+      </c>
+      <c r="I217">
+        <v>-8</v>
+      </c>
+      <c r="J217">
+        <v>0.72413793100000001</v>
+      </c>
+      <c r="K217">
+        <v>29</v>
+      </c>
+      <c r="L217">
+        <v>21</v>
+      </c>
+      <c r="M217">
+        <v>-8</v>
+      </c>
+      <c r="N217">
+        <v>0.72413793100000001</v>
+      </c>
+      <c r="O217" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/cartones.xlsx
+++ b/data/cartones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E59664B7-4ECB-4411-96E6-99B2B690F398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF07236-40AD-4E67-8BB6-E6F1964A9275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF2EE928-F73E-4AAC-BA22-2F9F659AC8B2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="129">
   <si>
     <t>codigo</t>
   </si>
@@ -223,6 +223,204 @@
   </si>
   <si>
     <t>800 CAM 800 ADMIN</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+  <si>
+    <t>335</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>503 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>505 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>501 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>333</t>
+  </si>
+  <si>
+    <t>334</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>303 CAM 3 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>306 CAM 6 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>310 CAM 10 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>320 CAM 20 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>321 CAM 21 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>205 CAM 5 MARTES</t>
+  </si>
+  <si>
+    <t>206 CAM 6 MARTES</t>
+  </si>
+  <si>
+    <t>212 CAM 12 MARTES</t>
+  </si>
+  <si>
+    <t>216 CAM 16 MARTES</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>332</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>302 CAM 2 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>504 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>502 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>500 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>336</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>215 CAM 15 MARTES</t>
+  </si>
+  <si>
+    <t>201 CAM 1 MARTES</t>
+  </si>
+  <si>
+    <t>202 CAM 2 MARTES</t>
+  </si>
+  <si>
+    <t>203 CAM 3 MARTES</t>
+  </si>
+  <si>
+    <t>204 CAM 4 MARTES</t>
+  </si>
+  <si>
+    <t>207 CAM 7 MARTES</t>
+  </si>
+  <si>
+    <t>208 CAM 8 MARTES</t>
+  </si>
+  <si>
+    <t>213 CAM 13 MARTES</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>214 CAM 14 MARTES</t>
+  </si>
+  <si>
+    <t>301 CAM 1 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>316 CAM 16 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>317 CAM 17 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>318 CAM 18 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>319 CAM 19 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>323 CAM 23 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>324 CAM 24 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>325 CAM 25 MIÉRCOLES</t>
   </si>
 </sst>
 </file>
@@ -258,7 +456,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -579,2127 +779,5551 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="2">
+        <v>9889</v>
+      </c>
+      <c r="B2" s="2">
+        <v>305</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E2" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F2" s="2">
+        <v>20043</v>
+      </c>
+      <c r="G2" s="2">
+        <v>37</v>
+      </c>
+      <c r="H2" s="2">
+        <v>35</v>
+      </c>
+      <c r="I2" s="2">
+        <v>-2</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.94594594594000003</v>
+      </c>
+      <c r="K2" s="2">
+        <v>37</v>
+      </c>
+      <c r="L2" s="2">
+        <v>35</v>
+      </c>
+      <c r="M2" s="2">
+        <v>-2</v>
+      </c>
+      <c r="N2" s="2">
+        <v>0.94594594594000003</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>9890</v>
+      </c>
+      <c r="B3" s="2">
+        <v>307</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E3" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F3" s="2">
+        <v>20076</v>
+      </c>
+      <c r="G3" s="2">
+        <v>51</v>
+      </c>
+      <c r="H3" s="2">
+        <v>29</v>
+      </c>
+      <c r="I3" s="2">
+        <v>-22</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.56862745098</v>
+      </c>
+      <c r="K3" s="2">
+        <v>51</v>
+      </c>
+      <c r="L3" s="2">
+        <v>29</v>
+      </c>
+      <c r="M3" s="2">
+        <v>-22</v>
+      </c>
+      <c r="N3" s="2">
+        <v>0.56862745098</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>9918</v>
+      </c>
+      <c r="B4" s="2">
+        <v>111</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E4" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F4" s="2">
+        <v>20043</v>
+      </c>
+      <c r="G4" s="2">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2">
+        <v>-2</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.71428571427999998</v>
+      </c>
+      <c r="K4" s="2">
+        <v>7</v>
+      </c>
+      <c r="L4" s="2">
+        <v>5</v>
+      </c>
+      <c r="M4" s="2">
+        <v>-2</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0.71428571427999998</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>9906</v>
+      </c>
+      <c r="B5" s="2">
+        <v>340</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E5" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F5" s="2">
+        <v>20006</v>
+      </c>
+      <c r="G5" s="2">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>23</v>
+      </c>
+      <c r="L5" s="2">
+        <v>23</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>9897</v>
+      </c>
+      <c r="B6" s="2">
+        <v>331</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E6" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F6" s="2">
+        <v>20006</v>
+      </c>
+      <c r="G6" s="2">
+        <v>41</v>
+      </c>
+      <c r="H6" s="2">
+        <v>31</v>
+      </c>
+      <c r="I6" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.75609756097000003</v>
+      </c>
+      <c r="K6" s="2">
+        <v>41</v>
+      </c>
+      <c r="L6" s="2">
+        <v>31</v>
+      </c>
+      <c r="M6" s="2">
+        <v>-10</v>
+      </c>
+      <c r="N6" s="2">
+        <v>0.75609756097000003</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>9901</v>
+      </c>
+      <c r="B7" s="2">
+        <v>335</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E7" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F7" s="2">
+        <v>20113</v>
+      </c>
+      <c r="G7" s="2">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2">
+        <v>16</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>16</v>
+      </c>
+      <c r="L7" s="2">
+        <v>16</v>
+      </c>
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>9892</v>
+      </c>
+      <c r="B8" s="2">
+        <v>312</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E8" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F8" s="2">
+        <v>20095</v>
+      </c>
+      <c r="G8" s="2">
+        <v>33</v>
+      </c>
+      <c r="H8" s="2">
+        <v>32</v>
+      </c>
+      <c r="I8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.96969696968999997</v>
+      </c>
+      <c r="K8" s="2">
+        <v>33</v>
+      </c>
+      <c r="L8" s="2">
+        <v>32</v>
+      </c>
+      <c r="M8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.96969696968999997</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>9888</v>
+      </c>
+      <c r="B9" s="2">
+        <v>304</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E9" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F9" s="2">
+        <v>20086</v>
+      </c>
+      <c r="G9" s="2">
+        <v>45</v>
+      </c>
+      <c r="H9" s="2">
+        <v>40</v>
+      </c>
+      <c r="I9" s="2">
+        <v>-5</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.88888888887999995</v>
+      </c>
+      <c r="K9" s="2">
+        <v>45</v>
+      </c>
+      <c r="L9" s="2">
+        <v>40</v>
+      </c>
+      <c r="M9" s="2">
+        <v>-5</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.88888888887999995</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9926</v>
+      </c>
+      <c r="B10" s="2">
+        <v>136</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E10" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F10" s="2">
+        <v>20111</v>
+      </c>
+      <c r="G10" s="2">
+        <v>16</v>
+      </c>
+      <c r="H10" s="2">
+        <v>11</v>
+      </c>
+      <c r="I10" s="2">
+        <v>-5</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="K10" s="2">
+        <v>16</v>
+      </c>
+      <c r="L10" s="2">
+        <v>11</v>
+      </c>
+      <c r="M10" s="2">
+        <v>-5</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>9961</v>
+      </c>
+      <c r="B11" s="2">
+        <v>503</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E11" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F11" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>9963</v>
+      </c>
+      <c r="B12" s="2">
+        <v>505</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E12" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F12" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>9964</v>
+      </c>
+      <c r="B13" s="2">
+        <v>800</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E13" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F13" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>9966</v>
+      </c>
+      <c r="B14" s="2">
+        <v>800</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E14" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F14" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>9967</v>
+      </c>
+      <c r="B15" s="2">
+        <v>800</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E15" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F15" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>9884</v>
+      </c>
+      <c r="B16" s="2">
+        <v>501</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E16" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F16" s="2">
+        <v>20058</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>9893</v>
+      </c>
+      <c r="B17" s="2">
+        <v>311</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E17" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F17" s="2">
+        <v>20106</v>
+      </c>
+      <c r="G17" s="2">
+        <v>27</v>
+      </c>
+      <c r="H17" s="2">
+        <v>13</v>
+      </c>
+      <c r="I17" s="2">
+        <v>-14</v>
+      </c>
+      <c r="J17" s="2">
+        <v>0.48148148147999997</v>
+      </c>
+      <c r="K17" s="2">
+        <v>27</v>
+      </c>
+      <c r="L17" s="2">
+        <v>13</v>
+      </c>
+      <c r="M17" s="2">
+        <v>-14</v>
+      </c>
+      <c r="N17" s="2">
+        <v>0.48148148147999997</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>9894</v>
+      </c>
+      <c r="B18" s="2">
+        <v>313</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E18" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F18" s="2">
+        <v>11215</v>
+      </c>
+      <c r="G18" s="2">
+        <v>20</v>
+      </c>
+      <c r="H18" s="2">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2">
+        <v>-5</v>
+      </c>
+      <c r="J18" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="K18" s="2">
+        <v>20</v>
+      </c>
+      <c r="L18" s="2">
+        <v>15</v>
+      </c>
+      <c r="M18" s="2">
+        <v>-5</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>9895</v>
+      </c>
+      <c r="B19" s="2">
+        <v>314</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E19" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F19" s="2">
+        <v>20066</v>
+      </c>
+      <c r="G19" s="2">
+        <v>47</v>
+      </c>
+      <c r="H19" s="2">
+        <v>37</v>
+      </c>
+      <c r="I19" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.78723404254999996</v>
+      </c>
+      <c r="K19" s="2">
+        <v>47</v>
+      </c>
+      <c r="L19" s="2">
+        <v>37</v>
+      </c>
+      <c r="M19" s="2">
+        <v>-10</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0.78723404254999996</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>9896</v>
+      </c>
+      <c r="B20" s="2">
+        <v>315</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E20" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F20" s="2">
+        <v>20105</v>
+      </c>
+      <c r="G20" s="2">
+        <v>35</v>
+      </c>
+      <c r="H20" s="2">
+        <v>26</v>
+      </c>
+      <c r="I20" s="2">
+        <v>-9</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0.74285714285000004</v>
+      </c>
+      <c r="K20" s="2">
+        <v>35</v>
+      </c>
+      <c r="L20" s="2">
+        <v>26</v>
+      </c>
+      <c r="M20" s="2">
+        <v>-9</v>
+      </c>
+      <c r="N20" s="2">
+        <v>0.74285714285000004</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>9899</v>
+      </c>
+      <c r="B21" s="2">
+        <v>333</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E21" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F21" s="2">
+        <v>200158</v>
+      </c>
+      <c r="G21" s="2">
+        <v>18</v>
+      </c>
+      <c r="H21" s="2">
+        <v>18</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1</v>
+      </c>
+      <c r="K21" s="2">
+        <v>18</v>
+      </c>
+      <c r="L21" s="2">
+        <v>18</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>1</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>9900</v>
+      </c>
+      <c r="B22" s="2">
+        <v>334</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E22" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F22" s="2">
+        <v>20112</v>
+      </c>
+      <c r="G22" s="2">
+        <v>24</v>
+      </c>
+      <c r="H22" s="2">
+        <v>20</v>
+      </c>
+      <c r="I22" s="2">
+        <v>-4</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0.83333333333000004</v>
+      </c>
+      <c r="K22" s="2">
+        <v>24</v>
+      </c>
+      <c r="L22" s="2">
+        <v>20</v>
+      </c>
+      <c r="M22" s="2">
+        <v>-4</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0.83333333333000004</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>9903</v>
+      </c>
+      <c r="B23" s="2">
+        <v>337</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E23" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F23" s="2">
+        <v>20003</v>
+      </c>
+      <c r="G23" s="2">
+        <v>26</v>
+      </c>
+      <c r="H23" s="2">
+        <v>43</v>
+      </c>
+      <c r="I23" s="2">
+        <v>17</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1.65384615384</v>
+      </c>
+      <c r="K23" s="2">
+        <v>26</v>
+      </c>
+      <c r="L23" s="2">
+        <v>43</v>
+      </c>
+      <c r="M23" s="2">
+        <v>17</v>
+      </c>
+      <c r="N23" s="2">
+        <v>1.65384615384</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>9932</v>
+      </c>
+      <c r="B24" s="2">
+        <v>610</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E24" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F24" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>9980</v>
+      </c>
+      <c r="B25" s="2">
+        <v>303</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E25" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F25" s="2">
+        <v>20043</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>9981</v>
+      </c>
+      <c r="B26" s="2">
+        <v>304</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E26" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F26" s="2">
+        <v>20086</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>9982</v>
+      </c>
+      <c r="B27" s="2">
+        <v>305</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E27" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F27" s="2">
+        <v>20106</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>9983</v>
+      </c>
+      <c r="B28" s="2">
+        <v>306</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E28" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F28" s="2">
+        <v>20105</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>9984</v>
+      </c>
+      <c r="B29" s="2">
+        <v>307</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E29" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F29" s="2">
+        <v>11215</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>9985</v>
+      </c>
+      <c r="B30" s="2">
+        <v>310</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E30" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F30" s="2">
+        <v>20155</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>9986</v>
+      </c>
+      <c r="B31" s="2">
+        <v>311</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E31" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F31" s="2">
+        <v>20057</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>9995</v>
+      </c>
+      <c r="B32" s="2">
+        <v>320</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E32" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F32" s="2">
+        <v>20066</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>9996</v>
+      </c>
+      <c r="B33" s="2">
+        <v>321</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E33" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F33" s="2">
+        <v>20153</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2">
+        <v>0</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>10000</v>
+      </c>
+      <c r="B34" s="2">
+        <v>327</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E34" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F34" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2">
+        <v>0</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>9942</v>
+      </c>
+      <c r="B35" s="2">
+        <v>205</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E35" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F35" s="2">
+        <v>20043</v>
+      </c>
+      <c r="G35" s="2">
+        <v>51</v>
+      </c>
+      <c r="H35" s="2">
+        <v>47</v>
+      </c>
+      <c r="I35" s="2">
+        <v>-4</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0.92156862745000001</v>
+      </c>
+      <c r="K35" s="2">
+        <v>51</v>
+      </c>
+      <c r="L35" s="2">
+        <v>47</v>
+      </c>
+      <c r="M35" s="2">
+        <v>-4</v>
+      </c>
+      <c r="N35" s="2">
+        <v>0.92156862745000001</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>9943</v>
+      </c>
+      <c r="B36" s="2">
+        <v>206</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E36" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F36" s="2">
+        <v>20106</v>
+      </c>
+      <c r="G36" s="2">
+        <v>25</v>
+      </c>
+      <c r="H36" s="2">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="K36" s="2">
+        <v>25</v>
+      </c>
+      <c r="L36" s="2">
+        <v>15</v>
+      </c>
+      <c r="M36" s="2">
+        <v>-10</v>
+      </c>
+      <c r="N36" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>9946</v>
+      </c>
+      <c r="B37" s="2">
+        <v>212</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E37" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F37" s="2">
+        <v>20153</v>
+      </c>
+      <c r="G37" s="2">
+        <v>45</v>
+      </c>
+      <c r="H37" s="2">
+        <v>10</v>
+      </c>
+      <c r="I37" s="2">
+        <v>-35</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0.22222222221999999</v>
+      </c>
+      <c r="K37" s="2">
+        <v>45</v>
+      </c>
+      <c r="L37" s="2">
+        <v>10</v>
+      </c>
+      <c r="M37" s="2">
+        <v>-35</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0.22222222221999999</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>9950</v>
+      </c>
+      <c r="B38" s="2">
+        <v>216</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F38" s="2">
+        <v>20095</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>10002</v>
+      </c>
+      <c r="B39" s="2">
+        <v>326</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E39" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F39" s="2">
+        <v>20076</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>10003</v>
+      </c>
+      <c r="B40" s="2">
+        <v>328</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E40" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F40" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>9951</v>
+      </c>
+      <c r="B41" s="2">
+        <v>231</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E41" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F41" s="2">
+        <v>20005</v>
+      </c>
+      <c r="G41" s="2">
+        <v>43</v>
+      </c>
+      <c r="H41" s="2">
+        <v>29</v>
+      </c>
+      <c r="I41" s="2">
+        <v>-14</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0.67441860465000003</v>
+      </c>
+      <c r="K41" s="2">
+        <v>43</v>
+      </c>
+      <c r="L41" s="2">
+        <v>29</v>
+      </c>
+      <c r="M41" s="2">
+        <v>-14</v>
+      </c>
+      <c r="N41" s="2">
+        <v>0.67441860465000003</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>9952</v>
+      </c>
+      <c r="B42" s="2">
+        <v>232</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E42" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F42" s="2">
+        <v>20130</v>
+      </c>
+      <c r="G42" s="2">
+        <v>39</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2">
+        <v>-39</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0</v>
+      </c>
+      <c r="K42" s="2">
+        <v>39</v>
+      </c>
+      <c r="L42" s="2">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2">
+        <v>-39</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>9953</v>
+      </c>
+      <c r="B43" s="2">
+        <v>233</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E43" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F43" s="2">
+        <v>200158</v>
+      </c>
+      <c r="G43" s="2">
+        <v>15</v>
+      </c>
+      <c r="H43" s="2">
+        <v>15</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2">
+        <v>15</v>
+      </c>
+      <c r="L43" s="2">
+        <v>15</v>
+      </c>
+      <c r="M43" s="2">
+        <v>0</v>
+      </c>
+      <c r="N43" s="2">
+        <v>1</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>10004</v>
+      </c>
+      <c r="B44" s="2">
+        <v>131</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D44" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E44" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F44" s="2">
+        <v>20005</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>10005</v>
+      </c>
+      <c r="B45" s="2">
+        <v>133</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E45" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F45" s="2">
+        <v>200158</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2">
+        <v>0</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>10006</v>
+      </c>
+      <c r="B46" s="2">
+        <v>134</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E46" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F46" s="2">
+        <v>20112</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>10007</v>
+      </c>
+      <c r="B47" s="2">
+        <v>135</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E47" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F47" s="2">
+        <v>20113</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2">
+        <v>0</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>10008</v>
+      </c>
+      <c r="B48" s="2">
+        <v>136</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E48" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F48" s="2">
+        <v>20111</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>10009</v>
+      </c>
+      <c r="B49" s="2">
+        <v>137</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E49" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F49" s="2">
+        <v>20003</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>10010</v>
+      </c>
+      <c r="B50" s="2">
+        <v>138</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D50" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E50" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F50" s="2">
+        <v>20007</v>
+      </c>
+      <c r="G50" s="2">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2">
+        <v>0</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>10011</v>
+      </c>
+      <c r="B51" s="2">
+        <v>139</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E51" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F51" s="2">
+        <v>20008</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2">
+        <v>0</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2">
+        <v>0</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>10012</v>
+      </c>
+      <c r="B52" s="2">
+        <v>140</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" s="3">
+        <v>46207</v>
+      </c>
+      <c r="E52" s="3">
+        <v>46207</v>
+      </c>
+      <c r="F52" s="2">
+        <v>20006</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>9898</v>
+      </c>
+      <c r="B53" s="2">
+        <v>332</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D53" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E53" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F53" s="2">
+        <v>20130</v>
+      </c>
+      <c r="G53" s="2">
+        <v>25</v>
+      </c>
+      <c r="H53" s="2">
+        <v>20</v>
+      </c>
+      <c r="I53" s="2">
+        <v>-5</v>
+      </c>
+      <c r="J53" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="K53" s="2">
+        <v>25</v>
+      </c>
+      <c r="L53" s="2">
+        <v>20</v>
+      </c>
+      <c r="M53" s="2">
+        <v>-5</v>
+      </c>
+      <c r="N53" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>9910</v>
+      </c>
+      <c r="B54" s="2">
+        <v>103</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E54" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F54" s="2">
+        <v>20153</v>
+      </c>
+      <c r="G54" s="2">
+        <v>46</v>
+      </c>
+      <c r="H54" s="2">
+        <v>27</v>
+      </c>
+      <c r="I54" s="2">
+        <v>-19</v>
+      </c>
+      <c r="J54" s="2">
+        <v>0.58695652173000001</v>
+      </c>
+      <c r="K54" s="2">
+        <v>46</v>
+      </c>
+      <c r="L54" s="2">
+        <v>27</v>
+      </c>
+      <c r="M54" s="2">
+        <v>-19</v>
+      </c>
+      <c r="N54" s="2">
+        <v>0.58695652173000001</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>9933</v>
+      </c>
+      <c r="B55" s="2">
+        <v>800</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E55" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F55" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G55" s="2">
+        <v>1</v>
+      </c>
+      <c r="H55" s="2">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J55" s="2">
+        <v>0</v>
+      </c>
+      <c r="K55" s="2">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N55" s="2">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>9936</v>
+      </c>
+      <c r="B56" s="2">
+        <v>800</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E56" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F56" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G56" s="2">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2">
+        <v>0</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2">
+        <v>0</v>
+      </c>
+      <c r="L56" s="2">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2">
+        <v>0</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>9937</v>
+      </c>
+      <c r="B57" s="2">
+        <v>800</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E57" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F57" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G57" s="2">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2">
+        <v>0</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>9921</v>
+      </c>
+      <c r="B58" s="2">
+        <v>114</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D58" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E58" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F58" s="2">
+        <v>20048</v>
+      </c>
+      <c r="G58" s="2">
+        <v>28</v>
+      </c>
+      <c r="H58" s="2">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2">
+        <v>-28</v>
+      </c>
+      <c r="J58" s="2">
+        <v>0</v>
+      </c>
+      <c r="K58" s="2">
+        <v>28</v>
+      </c>
+      <c r="L58" s="2">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2">
+        <v>-28</v>
+      </c>
+      <c r="N58" s="2">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>9911</v>
+      </c>
+      <c r="B59" s="2">
+        <v>104</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E59" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F59" s="2">
+        <v>20105</v>
+      </c>
+      <c r="G59" s="2">
+        <v>54</v>
+      </c>
+      <c r="H59" s="2">
+        <v>37</v>
+      </c>
+      <c r="I59" s="2">
+        <v>-17</v>
+      </c>
+      <c r="J59" s="2">
+        <v>0.68518518518000004</v>
+      </c>
+      <c r="K59" s="2">
+        <v>54</v>
+      </c>
+      <c r="L59" s="2">
+        <v>37</v>
+      </c>
+      <c r="M59" s="2">
+        <v>-17</v>
+      </c>
+      <c r="N59" s="2">
+        <v>0.68518518518000004</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>9912</v>
+      </c>
+      <c r="B60" s="2">
+        <v>105</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E60" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F60" s="2">
+        <v>20058</v>
+      </c>
+      <c r="G60" s="2">
+        <v>48</v>
+      </c>
+      <c r="H60" s="2">
+        <v>20</v>
+      </c>
+      <c r="I60" s="2">
+        <v>-28</v>
+      </c>
+      <c r="J60" s="2">
+        <v>0.41666666666000002</v>
+      </c>
+      <c r="K60" s="2">
+        <v>48</v>
+      </c>
+      <c r="L60" s="2">
+        <v>20</v>
+      </c>
+      <c r="M60" s="2">
+        <v>-28</v>
+      </c>
+      <c r="N60" s="2">
+        <v>0.41666666666000002</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>9914</v>
+      </c>
+      <c r="B61" s="2">
+        <v>107</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E61" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F61" s="2">
+        <v>20155</v>
+      </c>
+      <c r="G61" s="2">
+        <v>1</v>
+      </c>
+      <c r="H61" s="2">
+        <v>1</v>
+      </c>
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2">
+        <v>1</v>
+      </c>
+      <c r="K61" s="2">
+        <v>1</v>
+      </c>
+      <c r="L61" s="2">
+        <v>1</v>
+      </c>
+      <c r="M61" s="2">
+        <v>0</v>
+      </c>
+      <c r="N61" s="2">
+        <v>1</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>9915</v>
+      </c>
+      <c r="B62" s="2">
+        <v>108</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D62" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E62" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F62" s="2">
+        <v>20057</v>
+      </c>
+      <c r="G62" s="2">
+        <v>71</v>
+      </c>
+      <c r="H62" s="2">
+        <v>62</v>
+      </c>
+      <c r="I62" s="2">
+        <v>-9</v>
+      </c>
+      <c r="J62" s="2">
+        <v>0.87323943661000003</v>
+      </c>
+      <c r="K62" s="2">
+        <v>71</v>
+      </c>
+      <c r="L62" s="2">
+        <v>62</v>
+      </c>
+      <c r="M62" s="2">
+        <v>-9</v>
+      </c>
+      <c r="N62" s="2">
+        <v>0.87323943661000003</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>9916</v>
+      </c>
+      <c r="B63" s="2">
+        <v>109</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E63" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F63" s="2">
+        <v>20112</v>
+      </c>
+      <c r="G63" s="2">
+        <v>31</v>
+      </c>
+      <c r="H63" s="2">
+        <v>12</v>
+      </c>
+      <c r="I63" s="2">
+        <v>-19</v>
+      </c>
+      <c r="J63" s="2">
+        <v>0.38709677418999999</v>
+      </c>
+      <c r="K63" s="2">
+        <v>31</v>
+      </c>
+      <c r="L63" s="2">
+        <v>12</v>
+      </c>
+      <c r="M63" s="2">
+        <v>-19</v>
+      </c>
+      <c r="N63" s="2">
+        <v>0.38709677418999999</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>9917</v>
+      </c>
+      <c r="B64" s="2">
+        <v>110</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D64" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E64" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F64" s="2">
+        <v>20066</v>
+      </c>
+      <c r="G64" s="2">
+        <v>46</v>
+      </c>
+      <c r="H64" s="2">
+        <v>28</v>
+      </c>
+      <c r="I64" s="2">
+        <v>-18</v>
+      </c>
+      <c r="J64" s="2">
+        <v>0.60869565216999999</v>
+      </c>
+      <c r="K64" s="2">
+        <v>46</v>
+      </c>
+      <c r="L64" s="2">
+        <v>28</v>
+      </c>
+      <c r="M64" s="2">
+        <v>-18</v>
+      </c>
+      <c r="N64" s="2">
+        <v>0.60869565216999999</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>9919</v>
+      </c>
+      <c r="B65" s="2">
+        <v>112</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D65" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E65" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F65" s="2">
+        <v>20106</v>
+      </c>
+      <c r="G65" s="2">
+        <v>50</v>
+      </c>
+      <c r="H65" s="2">
+        <v>13</v>
+      </c>
+      <c r="I65" s="2">
+        <v>-37</v>
+      </c>
+      <c r="J65" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="K65" s="2">
+        <v>50</v>
+      </c>
+      <c r="L65" s="2">
+        <v>13</v>
+      </c>
+      <c r="M65" s="2">
+        <v>-37</v>
+      </c>
+      <c r="N65" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>9924</v>
+      </c>
+      <c r="B66" s="2">
+        <v>133</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D66" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E66" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F66" s="2">
+        <v>200158</v>
+      </c>
+      <c r="G66" s="2">
+        <v>29</v>
+      </c>
+      <c r="H66" s="2">
+        <v>29</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2">
+        <v>1</v>
+      </c>
+      <c r="K66" s="2">
+        <v>29</v>
+      </c>
+      <c r="L66" s="2">
+        <v>29</v>
+      </c>
+      <c r="M66" s="2">
+        <v>0</v>
+      </c>
+      <c r="N66" s="2">
+        <v>1</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>9927</v>
+      </c>
+      <c r="B67" s="2">
+        <v>137</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D67" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E67" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F67" s="2">
+        <v>20003</v>
+      </c>
+      <c r="G67" s="2">
+        <v>17</v>
+      </c>
+      <c r="H67" s="2">
+        <v>12</v>
+      </c>
+      <c r="I67" s="2">
+        <v>-5</v>
+      </c>
+      <c r="J67" s="2">
+        <v>0.70588235294000001</v>
+      </c>
+      <c r="K67" s="2">
+        <v>17</v>
+      </c>
+      <c r="L67" s="2">
+        <v>12</v>
+      </c>
+      <c r="M67" s="2">
+        <v>-5</v>
+      </c>
+      <c r="N67" s="2">
+        <v>0.70588235294000001</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>9928</v>
+      </c>
+      <c r="B68" s="2">
+        <v>138</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D68" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E68" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F68" s="2">
+        <v>20007</v>
+      </c>
+      <c r="G68" s="2">
+        <v>31</v>
+      </c>
+      <c r="H68" s="2">
+        <v>22</v>
+      </c>
+      <c r="I68" s="2">
+        <v>-9</v>
+      </c>
+      <c r="J68" s="2">
+        <v>0.70967741934999995</v>
+      </c>
+      <c r="K68" s="2">
+        <v>31</v>
+      </c>
+      <c r="L68" s="2">
+        <v>22</v>
+      </c>
+      <c r="M68" s="2">
+        <v>-9</v>
+      </c>
+      <c r="N68" s="2">
+        <v>0.70967741934999995</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
         <v>9929</v>
       </c>
-      <c r="B2">
+      <c r="B69" s="2">
         <v>139</v>
       </c>
-      <c r="C2">
-        <v>139</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="C69" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E69" s="3">
         <v>46204</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F69" s="2">
+        <v>20008</v>
+      </c>
+      <c r="G69" s="2">
+        <v>18</v>
+      </c>
+      <c r="H69" s="2">
+        <v>12</v>
+      </c>
+      <c r="I69" s="2">
+        <v>-6</v>
+      </c>
+      <c r="J69" s="2">
+        <v>0.66666666665999996</v>
+      </c>
+      <c r="K69" s="2">
+        <v>18</v>
+      </c>
+      <c r="L69" s="2">
+        <v>12</v>
+      </c>
+      <c r="M69" s="2">
+        <v>-6</v>
+      </c>
+      <c r="N69" s="2">
+        <v>0.66666666665999996</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>9923</v>
+      </c>
+      <c r="B70" s="2">
+        <v>132</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E70" s="3">
         <v>46204</v>
       </c>
-      <c r="F2">
+      <c r="F70" s="2">
+        <v>20130</v>
+      </c>
+      <c r="G70" s="2">
+        <v>10</v>
+      </c>
+      <c r="H70" s="2">
+        <v>8</v>
+      </c>
+      <c r="I70" s="2">
+        <v>-2</v>
+      </c>
+      <c r="J70" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="K70" s="2">
+        <v>10</v>
+      </c>
+      <c r="L70" s="2">
+        <v>8</v>
+      </c>
+      <c r="M70" s="2">
+        <v>-2</v>
+      </c>
+      <c r="N70" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>9979</v>
+      </c>
+      <c r="B71" s="2">
+        <v>302</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D71" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E71" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F71" s="2">
+        <v>20058</v>
+      </c>
+      <c r="G71" s="2">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2">
+        <v>0</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2">
+        <v>0</v>
+      </c>
+      <c r="L71" s="2">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2">
+        <v>0</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>9955</v>
+      </c>
+      <c r="B72" s="2">
+        <v>235</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D72" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E72" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F72" s="2">
+        <v>20113</v>
+      </c>
+      <c r="G72" s="2">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2">
+        <v>0</v>
+      </c>
+      <c r="L72" s="2">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2">
+        <v>0</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>9958</v>
+      </c>
+      <c r="B73" s="2">
+        <v>238</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D73" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E73" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F73" s="2">
+        <v>20007</v>
+      </c>
+      <c r="G73" s="2">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2">
+        <v>0</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>9959</v>
+      </c>
+      <c r="B74" s="2">
+        <v>239</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D74" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E74" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F74" s="2">
         <v>20008</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="G74" s="2">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2">
+        <v>0</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>9962</v>
+      </c>
+      <c r="B75" s="2">
+        <v>504</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D75" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E75" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F75" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G75" s="2">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2">
+        <v>0</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2">
+        <v>0</v>
+      </c>
+      <c r="L75" s="2">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2">
+        <v>0</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>9935</v>
+      </c>
+      <c r="B76" s="2">
+        <v>502</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E76" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F76" s="2">
+        <v>20043</v>
+      </c>
+      <c r="G76" s="2">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2">
+        <v>0</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2">
+        <v>0</v>
+      </c>
+      <c r="L76" s="2">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2">
+        <v>0</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>9920</v>
+      </c>
+      <c r="B77" s="2">
+        <v>113</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D77" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E77" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F77" s="2">
+        <v>20095</v>
+      </c>
+      <c r="G77" s="2">
+        <v>44</v>
+      </c>
+      <c r="H77" s="2">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2">
+        <v>-14</v>
+      </c>
+      <c r="J77" s="2">
+        <v>0.68181818180999998</v>
+      </c>
+      <c r="K77" s="2">
+        <v>44</v>
+      </c>
+      <c r="L77" s="2">
+        <v>30</v>
+      </c>
+      <c r="M77" s="2">
+        <v>-14</v>
+      </c>
+      <c r="N77" s="2">
+        <v>0.68181818180999998</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>9909</v>
+      </c>
+      <c r="B78" s="2">
+        <v>102</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D78" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E78" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F78" s="2">
+        <v>20086</v>
+      </c>
+      <c r="G78" s="2">
+        <v>55</v>
+      </c>
+      <c r="H78" s="2">
+        <v>48</v>
+      </c>
+      <c r="I78" s="2">
+        <v>-7</v>
+      </c>
+      <c r="J78" s="2">
+        <v>0.87272727271999995</v>
+      </c>
+      <c r="K78" s="2">
+        <v>55</v>
+      </c>
+      <c r="L78" s="2">
+        <v>48</v>
+      </c>
+      <c r="M78" s="2">
+        <v>-7</v>
+      </c>
+      <c r="N78" s="2">
+        <v>0.87272727271999995</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>9922</v>
+      </c>
+      <c r="B79" s="2">
+        <v>131</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D79" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E79" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F79" s="2">
+        <v>20005</v>
+      </c>
+      <c r="G79" s="2">
+        <v>21</v>
+      </c>
+      <c r="H79" s="2">
+        <v>16</v>
+      </c>
+      <c r="I79" s="2">
+        <v>-5</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0.7619047619</v>
+      </c>
+      <c r="K79" s="2">
+        <v>21</v>
+      </c>
+      <c r="L79" s="2">
+        <v>16</v>
+      </c>
+      <c r="M79" s="2">
+        <v>-5</v>
+      </c>
+      <c r="N79" s="2">
+        <v>0.7619047619</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>9934</v>
+      </c>
+      <c r="B80" s="2">
+        <v>500</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D80" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E80" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F80" s="2">
+        <v>20006</v>
+      </c>
+      <c r="G80" s="2">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2">
+        <v>0</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
         <v>9930</v>
       </c>
-      <c r="B3">
+      <c r="B81" s="2">
         <v>140</v>
       </c>
-      <c r="C3">
-        <v>140</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C81" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D81" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E81" s="3">
         <v>46204</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F81" s="2">
+        <v>20006</v>
+      </c>
+      <c r="G81" s="2">
+        <v>31</v>
+      </c>
+      <c r="H81" s="2">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0.96774193547999998</v>
+      </c>
+      <c r="K81" s="2">
+        <v>31</v>
+      </c>
+      <c r="L81" s="2">
+        <v>30</v>
+      </c>
+      <c r="M81" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2">
+        <v>0.96774193547999998</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>9905</v>
+      </c>
+      <c r="B82" s="2">
+        <v>339</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D82" s="3">
         <v>46204</v>
       </c>
-      <c r="F3">
+      <c r="E82" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F82" s="2">
+        <v>20008</v>
+      </c>
+      <c r="G82" s="2">
+        <v>18</v>
+      </c>
+      <c r="H82" s="2">
+        <v>15</v>
+      </c>
+      <c r="I82" s="2">
+        <v>-3</v>
+      </c>
+      <c r="J82" s="2">
+        <v>0.83333333333000004</v>
+      </c>
+      <c r="K82" s="2">
+        <v>18</v>
+      </c>
+      <c r="L82" s="2">
+        <v>15</v>
+      </c>
+      <c r="M82" s="2">
+        <v>-3</v>
+      </c>
+      <c r="N82" s="2">
+        <v>0.83333333333000004</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>9908</v>
+      </c>
+      <c r="B83" s="2">
+        <v>101</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E83" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F83" s="2">
+        <v>20076</v>
+      </c>
+      <c r="G83" s="2">
+        <v>40</v>
+      </c>
+      <c r="H83" s="2">
+        <v>34</v>
+      </c>
+      <c r="I83" s="2">
+        <v>-6</v>
+      </c>
+      <c r="J83" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="K83" s="2">
+        <v>40</v>
+      </c>
+      <c r="L83" s="2">
+        <v>34</v>
+      </c>
+      <c r="M83" s="2">
+        <v>-6</v>
+      </c>
+      <c r="N83" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>9913</v>
+      </c>
+      <c r="B84" s="2">
+        <v>106</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D84" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E84" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F84" s="2">
+        <v>11215</v>
+      </c>
+      <c r="G84" s="2">
+        <v>61</v>
+      </c>
+      <c r="H84" s="2">
+        <v>32</v>
+      </c>
+      <c r="I84" s="2">
+        <v>-29</v>
+      </c>
+      <c r="J84" s="2">
+        <v>0.52459016393000002</v>
+      </c>
+      <c r="K84" s="2">
+        <v>61</v>
+      </c>
+      <c r="L84" s="2">
+        <v>32</v>
+      </c>
+      <c r="M84" s="2">
+        <v>-29</v>
+      </c>
+      <c r="N84" s="2">
+        <v>0.52459016393000002</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>9902</v>
+      </c>
+      <c r="B85" s="2">
+        <v>336</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D85" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E85" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F85" s="2">
+        <v>20111</v>
+      </c>
+      <c r="G85" s="2">
+        <v>19</v>
+      </c>
+      <c r="H85" s="2">
+        <v>14</v>
+      </c>
+      <c r="I85" s="2">
+        <v>-5</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0.73684210526000005</v>
+      </c>
+      <c r="K85" s="2">
+        <v>19</v>
+      </c>
+      <c r="L85" s="2">
+        <v>14</v>
+      </c>
+      <c r="M85" s="2">
+        <v>-5</v>
+      </c>
+      <c r="N85" s="2">
+        <v>0.73684210526000005</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>9904</v>
+      </c>
+      <c r="B86" s="2">
+        <v>338</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D86" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E86" s="3">
+        <v>46203</v>
+      </c>
+      <c r="F86" s="2">
+        <v>20007</v>
+      </c>
+      <c r="G86" s="2">
+        <v>22</v>
+      </c>
+      <c r="H86" s="2">
+        <v>15</v>
+      </c>
+      <c r="I86" s="2">
+        <v>-7</v>
+      </c>
+      <c r="J86" s="2">
+        <v>0.68181818180999998</v>
+      </c>
+      <c r="K86" s="2">
+        <v>22</v>
+      </c>
+      <c r="L86" s="2">
+        <v>15</v>
+      </c>
+      <c r="M86" s="2">
+        <v>-7</v>
+      </c>
+      <c r="N86" s="2">
+        <v>0.68181818180999998</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>9949</v>
+      </c>
+      <c r="B87" s="2">
+        <v>215</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D87" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E87" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F87" s="2">
+        <v>200150</v>
+      </c>
+      <c r="G87" s="2">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2">
+        <v>0</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0</v>
+      </c>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2">
+        <v>0</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>9965</v>
+      </c>
+      <c r="B88" s="2">
+        <v>502</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D88" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E88" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F88" s="2">
+        <v>20086</v>
+      </c>
+      <c r="G88" s="2">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2">
+        <v>0</v>
+      </c>
+      <c r="I88" s="2">
+        <v>0</v>
+      </c>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2">
+        <v>0</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>9925</v>
+      </c>
+      <c r="B89" s="2">
+        <v>135</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D89" s="3">
+        <v>46205</v>
+      </c>
+      <c r="E89" s="3">
+        <v>46204</v>
+      </c>
+      <c r="F89" s="2">
+        <v>20113</v>
+      </c>
+      <c r="G89" s="2">
+        <v>16</v>
+      </c>
+      <c r="H89" s="2">
+        <v>12</v>
+      </c>
+      <c r="I89" s="2">
+        <v>-4</v>
+      </c>
+      <c r="J89" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="K89" s="2">
+        <v>16</v>
+      </c>
+      <c r="L89" s="2">
+        <v>12</v>
+      </c>
+      <c r="M89" s="2">
+        <v>-4</v>
+      </c>
+      <c r="N89" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>9938</v>
+      </c>
+      <c r="B90" s="2">
+        <v>201</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D90" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E90" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F90" s="2">
+        <v>20155</v>
+      </c>
+      <c r="G90" s="2">
+        <v>38</v>
+      </c>
+      <c r="H90" s="2">
+        <v>34</v>
+      </c>
+      <c r="I90" s="2">
+        <v>-4</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0.89473684210000004</v>
+      </c>
+      <c r="K90" s="2">
+        <v>38</v>
+      </c>
+      <c r="L90" s="2">
+        <v>34</v>
+      </c>
+      <c r="M90" s="2">
+        <v>-4</v>
+      </c>
+      <c r="N90" s="2">
+        <v>0.89473684210000004</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>9939</v>
+      </c>
+      <c r="B91" s="2">
+        <v>202</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D91" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E91" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F91" s="2">
+        <v>20057</v>
+      </c>
+      <c r="G91" s="2">
+        <v>44</v>
+      </c>
+      <c r="H91" s="2">
+        <v>42</v>
+      </c>
+      <c r="I91" s="2">
+        <v>-2</v>
+      </c>
+      <c r="J91" s="2">
+        <v>0.95454545453999995</v>
+      </c>
+      <c r="K91" s="2">
+        <v>44</v>
+      </c>
+      <c r="L91" s="2">
+        <v>42</v>
+      </c>
+      <c r="M91" s="2">
+        <v>-2</v>
+      </c>
+      <c r="N91" s="2">
+        <v>0.95454545453999995</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>9940</v>
+      </c>
+      <c r="B92" s="2">
+        <v>203</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D92" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E92" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F92" s="2">
+        <v>20086</v>
+      </c>
+      <c r="G92" s="2">
+        <v>38</v>
+      </c>
+      <c r="H92" s="2">
+        <v>29</v>
+      </c>
+      <c r="I92" s="2">
+        <v>-9</v>
+      </c>
+      <c r="J92" s="2">
+        <v>0.76315789472999995</v>
+      </c>
+      <c r="K92" s="2">
+        <v>38</v>
+      </c>
+      <c r="L92" s="2">
+        <v>29</v>
+      </c>
+      <c r="M92" s="2">
+        <v>-9</v>
+      </c>
+      <c r="N92" s="2">
+        <v>0.76315789472999995</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>9941</v>
+      </c>
+      <c r="B93" s="2">
+        <v>204</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E93" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F93" s="2">
+        <v>20058</v>
+      </c>
+      <c r="G93" s="2">
+        <v>66</v>
+      </c>
+      <c r="H93" s="2">
+        <v>27</v>
+      </c>
+      <c r="I93" s="2">
+        <v>-39</v>
+      </c>
+      <c r="J93" s="2">
+        <v>0.40909090909000001</v>
+      </c>
+      <c r="K93" s="2">
+        <v>66</v>
+      </c>
+      <c r="L93" s="2">
+        <v>27</v>
+      </c>
+      <c r="M93" s="2">
+        <v>-39</v>
+      </c>
+      <c r="N93" s="2">
+        <v>0.40909090909000001</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>9944</v>
+      </c>
+      <c r="B94" s="2">
+        <v>207</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D94" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E94" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F94" s="2">
+        <v>20105</v>
+      </c>
+      <c r="G94" s="2">
+        <v>33</v>
+      </c>
+      <c r="H94" s="2">
+        <v>32</v>
+      </c>
+      <c r="I94" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J94" s="2">
+        <v>0.96969696968999997</v>
+      </c>
+      <c r="K94" s="2">
+        <v>33</v>
+      </c>
+      <c r="L94" s="2">
+        <v>32</v>
+      </c>
+      <c r="M94" s="2">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2">
+        <v>0.96969696968999997</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>9945</v>
+      </c>
+      <c r="B95" s="2">
+        <v>208</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E95" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F95" s="2">
+        <v>20076</v>
+      </c>
+      <c r="G95" s="2">
+        <v>39</v>
+      </c>
+      <c r="H95" s="2">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2">
+        <v>-9</v>
+      </c>
+      <c r="J95" s="2">
+        <v>0.76923076923</v>
+      </c>
+      <c r="K95" s="2">
+        <v>39</v>
+      </c>
+      <c r="L95" s="2">
+        <v>30</v>
+      </c>
+      <c r="M95" s="2">
+        <v>-9</v>
+      </c>
+      <c r="N95" s="2">
+        <v>0.76923076923</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>9947</v>
+      </c>
+      <c r="B96" s="2">
+        <v>213</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D96" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E96" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F96" s="2">
+        <v>20066</v>
+      </c>
+      <c r="G96" s="2">
+        <v>60</v>
+      </c>
+      <c r="H96" s="2">
+        <v>45</v>
+      </c>
+      <c r="I96" s="2">
+        <v>-15</v>
+      </c>
+      <c r="J96" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="K96" s="2">
+        <v>60</v>
+      </c>
+      <c r="L96" s="2">
+        <v>45</v>
+      </c>
+      <c r="M96" s="2">
+        <v>-15</v>
+      </c>
+      <c r="N96" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>9960</v>
+      </c>
+      <c r="B97" s="2">
+        <v>240</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D97" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E97" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F97" s="2">
         <v>20006</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="G97" s="2">
+        <v>27</v>
+      </c>
+      <c r="H97" s="2">
+        <v>25</v>
+      </c>
+      <c r="I97" s="2">
+        <v>-2</v>
+      </c>
+      <c r="J97" s="2">
+        <v>0.92592592592</v>
+      </c>
+      <c r="K97" s="2">
+        <v>27</v>
+      </c>
+      <c r="L97" s="2">
+        <v>25</v>
+      </c>
+      <c r="M97" s="2">
+        <v>-2</v>
+      </c>
+      <c r="N97" s="2">
+        <v>0.92592592592</v>
+      </c>
+      <c r="O97" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>9889</v>
-      </c>
-      <c r="B4">
-        <v>305</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E4" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F4">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>9957</v>
+      </c>
+      <c r="B98" s="2">
+        <v>237</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D98" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E98" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F98" s="2">
+        <v>20003</v>
+      </c>
+      <c r="G98" s="2">
+        <v>42</v>
+      </c>
+      <c r="H98" s="2">
+        <v>25</v>
+      </c>
+      <c r="I98" s="2">
+        <v>-17</v>
+      </c>
+      <c r="J98" s="2">
+        <v>0.59523809523000004</v>
+      </c>
+      <c r="K98" s="2">
+        <v>42</v>
+      </c>
+      <c r="L98" s="2">
+        <v>25</v>
+      </c>
+      <c r="M98" s="2">
+        <v>-17</v>
+      </c>
+      <c r="N98" s="2">
+        <v>0.59523809523000004</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>9956</v>
+      </c>
+      <c r="B99" s="2">
+        <v>236</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D99" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E99" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F99" s="2">
+        <v>20111</v>
+      </c>
+      <c r="G99" s="2">
+        <v>29</v>
+      </c>
+      <c r="H99" s="2">
+        <v>21</v>
+      </c>
+      <c r="I99" s="2">
+        <v>-8</v>
+      </c>
+      <c r="J99" s="2">
+        <v>0.72413793103000001</v>
+      </c>
+      <c r="K99" s="2">
+        <v>29</v>
+      </c>
+      <c r="L99" s="2">
+        <v>21</v>
+      </c>
+      <c r="M99" s="2">
+        <v>-8</v>
+      </c>
+      <c r="N99" s="2">
+        <v>0.72413793103000001</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>9954</v>
+      </c>
+      <c r="B100" s="2">
+        <v>234</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D100" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E100" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F100" s="2">
+        <v>20112</v>
+      </c>
+      <c r="G100" s="2">
+        <v>28</v>
+      </c>
+      <c r="H100" s="2">
+        <v>20</v>
+      </c>
+      <c r="I100" s="2">
+        <v>-8</v>
+      </c>
+      <c r="J100" s="2">
+        <v>0.71428571427999998</v>
+      </c>
+      <c r="K100" s="2">
+        <v>28</v>
+      </c>
+      <c r="L100" s="2">
+        <v>20</v>
+      </c>
+      <c r="M100" s="2">
+        <v>-8</v>
+      </c>
+      <c r="N100" s="2">
+        <v>0.71428571427999998</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>9948</v>
+      </c>
+      <c r="B101" s="2">
+        <v>214</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D101" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E101" s="3">
+        <v>46205</v>
+      </c>
+      <c r="F101" s="2">
+        <v>11215</v>
+      </c>
+      <c r="G101" s="2">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2">
+        <v>1</v>
+      </c>
+      <c r="I101" s="2">
+        <v>1</v>
+      </c>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2">
+        <v>1</v>
+      </c>
+      <c r="M101" s="2">
+        <v>1</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>9968</v>
+      </c>
+      <c r="B102" s="2">
+        <v>331</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D102" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E102" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F102" s="2">
+        <v>20006</v>
+      </c>
+      <c r="G102" s="2">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2">
+        <v>0</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>9969</v>
+      </c>
+      <c r="B103" s="2">
+        <v>332</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D103" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E103" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F103" s="2">
+        <v>20130</v>
+      </c>
+      <c r="G103" s="2">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2">
+        <v>0</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0</v>
+      </c>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2">
+        <v>0</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>9970</v>
+      </c>
+      <c r="B104" s="2">
+        <v>333</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D104" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E104" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F104" s="2">
+        <v>200158</v>
+      </c>
+      <c r="G104" s="2">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2">
+        <v>0</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2">
+        <v>0</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>9971</v>
+      </c>
+      <c r="B105" s="2">
+        <v>334</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D105" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E105" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F105" s="2">
+        <v>20007</v>
+      </c>
+      <c r="G105" s="2">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2">
+        <v>0</v>
+      </c>
+      <c r="I105" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2">
+        <v>0</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>9972</v>
+      </c>
+      <c r="B106" s="2">
+        <v>335</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D106" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E106" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F106" s="2">
+        <v>20113</v>
+      </c>
+      <c r="G106" s="2">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2">
+        <v>0</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2">
+        <v>0</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>9973</v>
+      </c>
+      <c r="B107" s="2">
+        <v>336</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D107" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E107" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F107" s="2">
+        <v>20111</v>
+      </c>
+      <c r="G107" s="2">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2">
+        <v>0</v>
+      </c>
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2">
+        <v>0</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>9974</v>
+      </c>
+      <c r="B108" s="2">
+        <v>337</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D108" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E108" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F108" s="2">
+        <v>20003</v>
+      </c>
+      <c r="G108" s="2">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2">
+        <v>0</v>
+      </c>
+      <c r="I108" s="2">
+        <v>0</v>
+      </c>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2">
+        <v>0</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>9975</v>
+      </c>
+      <c r="B109" s="2">
+        <v>338</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D109" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E109" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F109" s="2">
+        <v>20112</v>
+      </c>
+      <c r="G109" s="2">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2">
+        <v>0</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2">
+        <v>0</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>9976</v>
+      </c>
+      <c r="B110" s="2">
+        <v>339</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D110" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E110" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F110" s="2">
+        <v>20008</v>
+      </c>
+      <c r="G110" s="2">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2">
+        <v>0</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2">
+        <v>0</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>9977</v>
+      </c>
+      <c r="B111" s="2">
+        <v>340</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D111" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E111" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F111" s="2">
+        <v>20005</v>
+      </c>
+      <c r="G111" s="2">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2">
+        <v>0</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2">
+        <v>0</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>9978</v>
+      </c>
+      <c r="B112" s="2">
+        <v>301</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D112" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E112" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F112" s="2">
+        <v>20155</v>
+      </c>
+      <c r="G112" s="2">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2">
+        <v>0</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2">
+        <v>0</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>9987</v>
+      </c>
+      <c r="B113" s="2">
+        <v>312</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D113" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E113" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F113" s="2">
+        <v>20086</v>
+      </c>
+      <c r="G113" s="2">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2">
+        <v>0</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="2"/>
+      <c r="K113" s="2">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2">
+        <v>0</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>9988</v>
+      </c>
+      <c r="B114" s="2">
+        <v>313</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D114" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E114" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F114" s="2">
+        <v>20106</v>
+      </c>
+      <c r="G114" s="2">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2">
+        <v>0</v>
+      </c>
+      <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2">
+        <v>0</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>9989</v>
+      </c>
+      <c r="B115" s="2">
+        <v>315</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D115" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E115" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F115" s="2">
+        <v>20153</v>
+      </c>
+      <c r="G115" s="2">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2">
+        <v>0</v>
+      </c>
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2">
+        <v>0</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>9991</v>
+      </c>
+      <c r="B116" s="2">
+        <v>316</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D116" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E116" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F116" s="2">
+        <v>20066</v>
+      </c>
+      <c r="G116" s="2">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2">
+        <v>0</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2"/>
+      <c r="K116" s="2">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2">
+        <v>0</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>9992</v>
+      </c>
+      <c r="B117" s="2">
+        <v>317</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D117" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E117" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F117" s="2">
         <v>20043</v>
       </c>
-      <c r="G4">
-        <v>37</v>
-      </c>
-      <c r="H4">
-        <v>35</v>
-      </c>
-      <c r="I4">
-        <v>-2</v>
-      </c>
-      <c r="J4">
-        <v>0.94594594600000004</v>
-      </c>
-      <c r="K4">
-        <v>37</v>
-      </c>
-      <c r="L4">
-        <v>35</v>
-      </c>
-      <c r="M4">
-        <v>-2</v>
-      </c>
-      <c r="N4">
-        <v>0.94594594600000004</v>
-      </c>
-      <c r="O4" t="s">
+      <c r="G117" s="2">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2">
+        <v>0</v>
+      </c>
+      <c r="I117" s="2">
+        <v>0</v>
+      </c>
+      <c r="J117" s="2"/>
+      <c r="K117" s="2">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2">
+        <v>0</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>9890</v>
-      </c>
-      <c r="B5">
-        <v>307</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E5" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F5">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>9993</v>
+      </c>
+      <c r="B118" s="2">
+        <v>318</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D118" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E118" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F118" s="2">
+        <v>20058</v>
+      </c>
+      <c r="G118" s="2">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2">
+        <v>0</v>
+      </c>
+      <c r="I118" s="2">
+        <v>0</v>
+      </c>
+      <c r="J118" s="2"/>
+      <c r="K118" s="2">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2">
+        <v>0</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>9994</v>
+      </c>
+      <c r="B119" s="2">
+        <v>319</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D119" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E119" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F119" s="2">
+        <v>11215</v>
+      </c>
+      <c r="G119" s="2">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2">
+        <v>0</v>
+      </c>
+      <c r="I119" s="2">
+        <v>0</v>
+      </c>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2">
+        <v>0</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>9997</v>
+      </c>
+      <c r="B120" s="2">
+        <v>323</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D120" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E120" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F120" s="2">
         <v>20076</v>
       </c>
-      <c r="G5">
-        <v>51</v>
-      </c>
-      <c r="H5">
-        <v>29</v>
-      </c>
-      <c r="I5">
-        <v>-22</v>
-      </c>
-      <c r="J5">
-        <v>0.56862745100000001</v>
-      </c>
-      <c r="K5">
-        <v>51</v>
-      </c>
-      <c r="L5">
-        <v>29</v>
-      </c>
-      <c r="M5">
-        <v>-22</v>
-      </c>
-      <c r="N5">
-        <v>0.56862745100000001</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="G120" s="2">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2">
+        <v>0</v>
+      </c>
+      <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2">
+        <v>0</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>9922</v>
-      </c>
-      <c r="B6">
-        <v>131</v>
-      </c>
-      <c r="C6">
-        <v>131</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E6" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F6">
-        <v>20005</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>9923</v>
-      </c>
-      <c r="B7">
-        <v>132</v>
-      </c>
-      <c r="C7">
-        <v>132</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E7" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F7">
-        <v>20130</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>9924</v>
-      </c>
-      <c r="B8">
-        <v>133</v>
-      </c>
-      <c r="C8">
-        <v>133</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E8" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F8">
-        <v>200158</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>9925</v>
-      </c>
-      <c r="B9">
-        <v>135</v>
-      </c>
-      <c r="C9">
-        <v>135</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E9" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F9">
-        <v>20113</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9926</v>
-      </c>
-      <c r="B10">
-        <v>136</v>
-      </c>
-      <c r="C10">
-        <v>136</v>
-      </c>
-      <c r="D10" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E10" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F10">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>9998</v>
+      </c>
+      <c r="B121" s="2">
+        <v>324</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D121" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E121" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F121" s="2">
+        <v>20105</v>
+      </c>
+      <c r="G121" s="2">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2">
+        <v>0</v>
+      </c>
+      <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2">
+        <v>0</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122" s="2">
+        <v>9999</v>
+      </c>
+      <c r="B122" s="2">
+        <v>325</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D122" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E122" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F122" s="2">
+        <v>20095</v>
+      </c>
+      <c r="G122" s="2">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2">
+        <v>0</v>
+      </c>
+      <c r="I122" s="2">
+        <v>0</v>
+      </c>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2">
+        <v>0</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>10001</v>
+      </c>
+      <c r="B123" s="2">
+        <v>500</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D123" s="3">
+        <v>46206</v>
+      </c>
+      <c r="E123" s="3">
+        <v>46206</v>
+      </c>
+      <c r="F123" s="2">
         <v>20111</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="G123" s="2">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2">
+        <v>0</v>
+      </c>
+      <c r="I123" s="2">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2"/>
+      <c r="K123" s="2">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2">
+        <v>0</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9927</v>
-      </c>
-      <c r="B11">
-        <v>137</v>
-      </c>
-      <c r="C11">
-        <v>137</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E11" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F11">
-        <v>20003</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>9928</v>
-      </c>
-      <c r="B12">
-        <v>138</v>
-      </c>
-      <c r="C12">
-        <v>138</v>
-      </c>
-      <c r="D12" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E12" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F12">
-        <v>20007</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>9908</v>
-      </c>
-      <c r="B13">
-        <v>101</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E13" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F13">
-        <v>20076</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>9910</v>
-      </c>
-      <c r="B14">
-        <v>103</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E14" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F14">
-        <v>20153</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>9911</v>
-      </c>
-      <c r="B15">
-        <v>104</v>
-      </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E15" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F15">
-        <v>20105</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>9912</v>
-      </c>
-      <c r="B16">
-        <v>105</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E16" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F16">
-        <v>20058</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>9913</v>
-      </c>
-      <c r="B17">
-        <v>106</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E17" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F17">
-        <v>11215</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>9914</v>
-      </c>
-      <c r="B18">
-        <v>107</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E18" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F18">
-        <v>20155</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>9915</v>
-      </c>
-      <c r="B19">
-        <v>108</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E19" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F19">
-        <v>20057</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>9916</v>
-      </c>
-      <c r="B20">
-        <v>109</v>
-      </c>
-      <c r="C20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E20" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F20">
-        <v>20112</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>9917</v>
-      </c>
-      <c r="B21">
-        <v>110</v>
-      </c>
-      <c r="C21" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E21" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F21">
-        <v>20066</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>9918</v>
-      </c>
-      <c r="B22">
-        <v>111</v>
-      </c>
-      <c r="C22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E22" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F22">
-        <v>20043</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>9919</v>
-      </c>
-      <c r="B23">
-        <v>112</v>
-      </c>
-      <c r="C23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E23" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F23">
-        <v>20106</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>9920</v>
-      </c>
-      <c r="B24">
-        <v>113</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E24" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F24">
-        <v>20095</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="O24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>9921</v>
-      </c>
-      <c r="B25">
-        <v>114</v>
-      </c>
-      <c r="C25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E25" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F25">
-        <v>20048</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>9906</v>
-      </c>
-      <c r="B26">
-        <v>340</v>
-      </c>
-      <c r="C26">
-        <v>340</v>
-      </c>
-      <c r="D26" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E26" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F26">
-        <v>20006</v>
-      </c>
-      <c r="G26">
-        <v>23</v>
-      </c>
-      <c r="H26">
-        <v>23</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
-        <v>23</v>
-      </c>
-      <c r="L26">
-        <v>23</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>1</v>
-      </c>
-      <c r="O26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>9897</v>
-      </c>
-      <c r="B27">
-        <v>331</v>
-      </c>
-      <c r="C27">
-        <v>331</v>
-      </c>
-      <c r="D27" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E27" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F27">
-        <v>20006</v>
-      </c>
-      <c r="G27">
-        <v>41</v>
-      </c>
-      <c r="H27">
-        <v>31</v>
-      </c>
-      <c r="I27">
-        <v>-10</v>
-      </c>
-      <c r="J27">
-        <v>0.75609756100000003</v>
-      </c>
-      <c r="K27">
-        <v>41</v>
-      </c>
-      <c r="L27">
-        <v>31</v>
-      </c>
-      <c r="M27">
-        <v>-10</v>
-      </c>
-      <c r="N27">
-        <v>0.75609756100000003</v>
-      </c>
-      <c r="O27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>9901</v>
-      </c>
-      <c r="B28">
-        <v>335</v>
-      </c>
-      <c r="C28">
-        <v>335</v>
-      </c>
-      <c r="D28" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E28" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F28">
-        <v>20113</v>
-      </c>
-      <c r="G28">
-        <v>16</v>
-      </c>
-      <c r="H28">
-        <v>16</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
-        <v>16</v>
-      </c>
-      <c r="L28">
-        <v>16</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
-      </c>
-      <c r="O28" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>9892</v>
-      </c>
-      <c r="B29">
-        <v>312</v>
-      </c>
-      <c r="C29" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E29" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F29">
-        <v>20095</v>
-      </c>
-      <c r="G29">
-        <v>33</v>
-      </c>
-      <c r="H29">
-        <v>32</v>
-      </c>
-      <c r="I29">
-        <v>-1</v>
-      </c>
-      <c r="J29">
-        <v>0.96969696999999999</v>
-      </c>
-      <c r="K29">
-        <v>33</v>
-      </c>
-      <c r="L29">
-        <v>32</v>
-      </c>
-      <c r="M29">
-        <v>-1</v>
-      </c>
-      <c r="N29">
-        <v>0.96969696999999999</v>
-      </c>
-      <c r="O29" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>9888</v>
-      </c>
-      <c r="B30">
-        <v>304</v>
-      </c>
-      <c r="C30" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E30" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F30">
-        <v>20086</v>
-      </c>
-      <c r="G30">
-        <v>45</v>
-      </c>
-      <c r="H30">
-        <v>40</v>
-      </c>
-      <c r="I30">
-        <v>-5</v>
-      </c>
-      <c r="J30">
-        <v>0.88888888899999996</v>
-      </c>
-      <c r="K30">
-        <v>45</v>
-      </c>
-      <c r="L30">
-        <v>40</v>
-      </c>
-      <c r="M30">
-        <v>-5</v>
-      </c>
-      <c r="N30">
-        <v>0.88888888899999996</v>
-      </c>
-      <c r="O30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>9893</v>
-      </c>
-      <c r="B31">
-        <v>311</v>
-      </c>
-      <c r="C31" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E31" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F31">
-        <v>20106</v>
-      </c>
-      <c r="G31">
-        <v>27</v>
-      </c>
-      <c r="H31">
-        <v>13</v>
-      </c>
-      <c r="I31">
-        <v>-14</v>
-      </c>
-      <c r="J31">
-        <v>0.48148148099999999</v>
-      </c>
-      <c r="K31">
-        <v>27</v>
-      </c>
-      <c r="L31">
-        <v>13</v>
-      </c>
-      <c r="M31">
-        <v>-14</v>
-      </c>
-      <c r="N31">
-        <v>0.48148148099999999</v>
-      </c>
-      <c r="O31" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>9894</v>
-      </c>
-      <c r="B32">
-        <v>313</v>
-      </c>
-      <c r="C32" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E32" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F32">
-        <v>11215</v>
-      </c>
-      <c r="G32">
-        <v>20</v>
-      </c>
-      <c r="H32">
-        <v>15</v>
-      </c>
-      <c r="I32">
-        <v>-5</v>
-      </c>
-      <c r="J32">
-        <v>0.75</v>
-      </c>
-      <c r="K32">
-        <v>20</v>
-      </c>
-      <c r="L32">
-        <v>15</v>
-      </c>
-      <c r="M32">
-        <v>-5</v>
-      </c>
-      <c r="N32">
-        <v>0.75</v>
-      </c>
-      <c r="O32" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>9895</v>
-      </c>
-      <c r="B33">
-        <v>314</v>
-      </c>
-      <c r="C33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E33" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F33">
-        <v>20066</v>
-      </c>
-      <c r="G33">
-        <v>47</v>
-      </c>
-      <c r="H33">
-        <v>37</v>
-      </c>
-      <c r="I33">
-        <v>-10</v>
-      </c>
-      <c r="J33">
-        <v>0.78723404299999999</v>
-      </c>
-      <c r="K33">
-        <v>47</v>
-      </c>
-      <c r="L33">
-        <v>37</v>
-      </c>
-      <c r="M33">
-        <v>-10</v>
-      </c>
-      <c r="N33">
-        <v>0.78723404299999999</v>
-      </c>
-      <c r="O33" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>9896</v>
-      </c>
-      <c r="B34">
-        <v>315</v>
-      </c>
-      <c r="C34" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E34" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F34">
-        <v>20105</v>
-      </c>
-      <c r="G34">
-        <v>35</v>
-      </c>
-      <c r="H34">
-        <v>26</v>
-      </c>
-      <c r="I34">
-        <v>-9</v>
-      </c>
-      <c r="J34">
-        <v>0.74285714300000005</v>
-      </c>
-      <c r="K34">
-        <v>35</v>
-      </c>
-      <c r="L34">
-        <v>26</v>
-      </c>
-      <c r="M34">
-        <v>-9</v>
-      </c>
-      <c r="N34">
-        <v>0.74285714300000005</v>
-      </c>
-      <c r="O34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>9899</v>
-      </c>
-      <c r="B35">
-        <v>333</v>
-      </c>
-      <c r="C35">
-        <v>333</v>
-      </c>
-      <c r="D35" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E35" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F35">
-        <v>200158</v>
-      </c>
-      <c r="G35">
-        <v>18</v>
-      </c>
-      <c r="H35">
-        <v>18</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
-      </c>
-      <c r="K35">
-        <v>18</v>
-      </c>
-      <c r="L35">
-        <v>18</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>1</v>
-      </c>
-      <c r="O35" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>9900</v>
-      </c>
-      <c r="B36">
-        <v>334</v>
-      </c>
-      <c r="C36">
-        <v>334</v>
-      </c>
-      <c r="D36" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E36" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F36">
-        <v>20112</v>
-      </c>
-      <c r="G36">
-        <v>24</v>
-      </c>
-      <c r="H36">
-        <v>20</v>
-      </c>
-      <c r="I36">
-        <v>-4</v>
-      </c>
-      <c r="J36">
-        <v>0.83333333300000001</v>
-      </c>
-      <c r="K36">
-        <v>24</v>
-      </c>
-      <c r="L36">
-        <v>20</v>
-      </c>
-      <c r="M36">
-        <v>-4</v>
-      </c>
-      <c r="N36">
-        <v>0.83333333300000001</v>
-      </c>
-      <c r="O36" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>9903</v>
-      </c>
-      <c r="B37">
-        <v>337</v>
-      </c>
-      <c r="C37">
-        <v>337</v>
-      </c>
-      <c r="D37" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E37" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F37">
-        <v>20003</v>
-      </c>
-      <c r="G37">
-        <v>26</v>
-      </c>
-      <c r="H37">
-        <v>43</v>
-      </c>
-      <c r="I37">
-        <v>17</v>
-      </c>
-      <c r="J37">
-        <v>1.653846154</v>
-      </c>
-      <c r="K37">
-        <v>26</v>
-      </c>
-      <c r="L37">
-        <v>43</v>
-      </c>
-      <c r="M37">
-        <v>17</v>
-      </c>
-      <c r="N37">
-        <v>1.653846154</v>
-      </c>
-      <c r="O37" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>9932</v>
-      </c>
-      <c r="B38">
-        <v>610</v>
-      </c>
-      <c r="C38" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="1">
-        <v>46205</v>
-      </c>
-      <c r="E38" s="1">
-        <v>46205</v>
-      </c>
-      <c r="F38">
-        <v>200150</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>9898</v>
-      </c>
-      <c r="B39">
-        <v>332</v>
-      </c>
-      <c r="C39">
-        <v>332</v>
-      </c>
-      <c r="D39" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E39" s="1">
-        <v>46203</v>
-      </c>
-      <c r="F39">
-        <v>20130</v>
-      </c>
-      <c r="G39">
-        <v>25</v>
-      </c>
-      <c r="H39">
-        <v>20</v>
-      </c>
-      <c r="I39">
-        <v>-5</v>
-      </c>
-      <c r="J39">
-        <v>0.8</v>
-      </c>
-      <c r="K39">
-        <v>25</v>
-      </c>
-      <c r="L39">
-        <v>20</v>
-      </c>
-      <c r="M39">
-        <v>-5</v>
-      </c>
-      <c r="N39">
-        <v>0.8</v>
-      </c>
-      <c r="O39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>9909</v>
-      </c>
-      <c r="B40">
-        <v>102</v>
-      </c>
-      <c r="C40" t="s">
-        <v>61</v>
-      </c>
-      <c r="D40" s="1">
-        <v>46204</v>
-      </c>
-      <c r="E40" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F40">
-        <v>20086</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="O40" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>9933</v>
-      </c>
-      <c r="B41">
-        <v>800</v>
-      </c>
-      <c r="C41" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="1">
-        <v>46205</v>
-      </c>
-      <c r="E41" s="1">
-        <v>46205</v>
-      </c>
-      <c r="F41">
-        <v>200150</v>
-      </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-    </row>
-    <row r="49" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-    </row>
-    <row r="50" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-    </row>
-    <row r="51" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-    </row>
-    <row r="52" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-    </row>
-    <row r="53" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-    </row>
-    <row r="54" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-    </row>
-    <row r="55" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-    </row>
-    <row r="56" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-    </row>
-    <row r="57" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-    </row>
-    <row r="58" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-    </row>
-    <row r="59" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-    </row>
-    <row r="60" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-    </row>
-    <row r="61" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-    </row>
-    <row r="62" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-    </row>
-    <row r="63" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-    </row>
-    <row r="64" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-    </row>
-    <row r="65" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-    </row>
-    <row r="66" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-    </row>
-    <row r="67" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-    </row>
-    <row r="68" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-    </row>
-    <row r="69" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-    </row>
-    <row r="70" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-    </row>
-    <row r="71" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-    </row>
-    <row r="72" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-    </row>
-    <row r="73" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-    </row>
-    <row r="74" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-    </row>
-    <row r="75" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-    </row>
-    <row r="76" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-    </row>
-    <row r="77" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-    </row>
-    <row r="78" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-    </row>
-    <row r="79" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-    </row>
-    <row r="80" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-    </row>
-    <row r="81" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-    </row>
-    <row r="82" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-    </row>
-    <row r="83" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-    </row>
-    <row r="84" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-    </row>
-    <row r="85" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-    </row>
-    <row r="86" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-    </row>
-    <row r="87" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-    </row>
-    <row r="88" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-    </row>
-    <row r="89" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-    </row>
-    <row r="90" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-    </row>
-    <row r="91" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-    </row>
-    <row r="92" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-    </row>
-    <row r="93" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-    </row>
-    <row r="94" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-    </row>
-    <row r="95" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-    </row>
-    <row r="96" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-    </row>
-    <row r="97" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-    </row>
-    <row r="98" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-    </row>
-    <row r="99" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-    </row>
-    <row r="100" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-    </row>
-    <row r="101" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-    </row>
-    <row r="102" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-    </row>
-    <row r="103" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-    </row>
-    <row r="104" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-    </row>
-    <row r="105" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-    </row>
-    <row r="106" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-    </row>
-    <row r="107" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-    </row>
-    <row r="108" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-    </row>
-    <row r="109" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-    </row>
-    <row r="110" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-    </row>
-    <row r="111" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-    </row>
-    <row r="112" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-    </row>
-    <row r="113" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-    </row>
-    <row r="114" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
-    </row>
-    <row r="115" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
-    </row>
-    <row r="116" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-    </row>
-    <row r="117" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-    </row>
-    <row r="118" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
-    </row>
-    <row r="119" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D119" s="1"/>
-      <c r="E119" s="1"/>
-    </row>
-    <row r="120" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D120" s="1"/>
-      <c r="E120" s="1"/>
-    </row>
-    <row r="121" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
-    </row>
-    <row r="122" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-    </row>
-    <row r="123" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
-    </row>
-    <row r="124" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
     </row>
-    <row r="125" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
     </row>
-    <row r="126" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
     </row>
-    <row r="127" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
     </row>
-    <row r="128" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
     </row>

--- a/data/cartones.xlsx
+++ b/data/cartones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06A788A-0BD0-4769-B6A1-482DF3DC905B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFB8BEC-5219-420E-88F7-464BA5C9A6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF2EE928-F73E-4AAC-BA22-2F9F659AC8B2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="101">
   <si>
     <t>codigo</t>
   </si>
@@ -331,6 +331,12 @@
   </si>
   <si>
     <t>211 CAM 11 MARTES</t>
+  </si>
+  <si>
+    <t>308 CAM 8 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>322 CAM 22 MIÉRCOLES</t>
   </si>
 </sst>
 </file>
@@ -1774,13 +1780,13 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>9981</v>
+        <v>10000</v>
       </c>
       <c r="B25">
-        <v>304</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
+        <v>327</v>
+      </c>
+      <c r="C25">
+        <v>327</v>
       </c>
       <c r="D25" s="1">
         <v>46207</v>
@@ -1789,45 +1795,39 @@
         <v>46206</v>
       </c>
       <c r="F25">
-        <v>20086</v>
+        <v>200150</v>
       </c>
       <c r="G25">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>-4</v>
-      </c>
-      <c r="J25">
-        <v>0.89743589700000004</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>-4</v>
-      </c>
-      <c r="N25">
-        <v>0.89743589700000004</v>
+        <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>9984</v>
+        <v>9981</v>
       </c>
       <c r="B26">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="D26" s="1">
         <v>46207</v>
@@ -1836,403 +1836,415 @@
         <v>46206</v>
       </c>
       <c r="F26">
-        <v>11215</v>
+        <v>20086</v>
       </c>
       <c r="G26">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H26">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I26">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="J26">
-        <v>0.57575757599999999</v>
+        <v>0.89743589700000004</v>
       </c>
       <c r="K26">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L26">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="M26">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="N26">
-        <v>0.57575757599999999</v>
+        <v>0.89743589700000004</v>
       </c>
       <c r="O26" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>9996</v>
+        <v>10038</v>
       </c>
       <c r="B27">
-        <v>321</v>
+        <v>503</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D27" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E27" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F27">
-        <v>20153</v>
+        <v>200150</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>10000</v>
+        <v>10027</v>
       </c>
       <c r="B28">
-        <v>327</v>
-      </c>
-      <c r="C28">
-        <v>327</v>
+        <v>212</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
       </c>
       <c r="D28" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="E28" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F28">
-        <v>200150</v>
+        <v>20057</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J28">
+        <v>0.85714285700000004</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="N28">
+        <v>0.85714285700000004</v>
       </c>
       <c r="O28" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>9942</v>
+        <v>9984</v>
       </c>
       <c r="B29">
-        <v>205</v>
+        <v>307</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="D29" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E29" s="1">
         <v>46206</v>
       </c>
-      <c r="E29" s="1">
-        <v>46205</v>
-      </c>
       <c r="F29">
-        <v>20043</v>
+        <v>11215</v>
       </c>
       <c r="G29">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H29">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="I29">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="J29">
-        <v>0.92156862699999997</v>
+        <v>0.57575757599999999</v>
       </c>
       <c r="K29">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="L29">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="M29">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="N29">
-        <v>0.92156862699999997</v>
+        <v>0.57575757599999999</v>
       </c>
       <c r="O29" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>9943</v>
+        <v>10034</v>
       </c>
       <c r="B30">
-        <v>206</v>
-      </c>
-      <c r="C30" t="s">
-        <v>72</v>
+        <v>237</v>
+      </c>
+      <c r="C30">
+        <v>237</v>
       </c>
       <c r="D30" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="E30" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F30">
-        <v>20106</v>
+        <v>20003</v>
       </c>
       <c r="G30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H30">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I30">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="J30">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="K30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L30">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M30">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="N30">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="O30" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9946</v>
+        <v>10037</v>
       </c>
       <c r="B31">
-        <v>212</v>
-      </c>
-      <c r="C31" t="s">
-        <v>73</v>
+        <v>240</v>
+      </c>
+      <c r="C31">
+        <v>240</v>
       </c>
       <c r="D31" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="E31" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F31">
-        <v>20153</v>
+        <v>20006</v>
       </c>
       <c r="G31">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="I31">
-        <v>-35</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>0.222222222</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K31">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="L31">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="M31">
-        <v>-35</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>0.222222222</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O31" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>9950</v>
+        <v>10029</v>
       </c>
       <c r="B32">
-        <v>216</v>
-      </c>
-      <c r="C32" t="s">
-        <v>74</v>
+        <v>232</v>
+      </c>
+      <c r="C32">
+        <v>232</v>
       </c>
       <c r="D32" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="E32" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F32">
-        <v>20095</v>
+        <v>20130</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
       <c r="K32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>0</v>
       </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
       <c r="O32" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>10002</v>
+        <v>9996</v>
       </c>
       <c r="B33">
-        <v>326</v>
-      </c>
-      <c r="C33">
-        <v>326</v>
+        <v>321</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
       </c>
       <c r="D33" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="E33" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="F33">
-        <v>20076</v>
+        <v>20153</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
+        <v>2</v>
+      </c>
+      <c r="K33">
         <v>1</v>
       </c>
-      <c r="K33">
-        <v>4</v>
-      </c>
       <c r="L33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>10003</v>
+        <v>9942</v>
       </c>
       <c r="B34">
-        <v>328</v>
-      </c>
-      <c r="C34">
-        <v>328</v>
+        <v>205</v>
+      </c>
+      <c r="C34" t="s">
+        <v>71</v>
       </c>
       <c r="D34" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="E34" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="F34">
-        <v>20095</v>
+        <v>20043</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J34">
+        <v>0.92156862699999997</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N34">
+        <v>0.92156862699999997</v>
       </c>
       <c r="O34" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>9951</v>
+        <v>9943</v>
       </c>
       <c r="B35">
-        <v>231</v>
-      </c>
-      <c r="C35">
-        <v>231</v>
+        <v>206</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
       </c>
       <c r="D35" s="1">
         <v>46206</v>
@@ -2241,45 +2253,45 @@
         <v>46205</v>
       </c>
       <c r="F35">
-        <v>20005</v>
+        <v>20106</v>
       </c>
       <c r="G35">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H35">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I35">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="J35">
-        <v>0.67441860499999995</v>
+        <v>0.6</v>
       </c>
       <c r="K35">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="L35">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="M35">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="N35">
-        <v>0.67441860499999995</v>
+        <v>0.6</v>
       </c>
       <c r="O35" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>9952</v>
+        <v>9946</v>
       </c>
       <c r="B36">
-        <v>232</v>
-      </c>
-      <c r="C36">
-        <v>232</v>
+        <v>212</v>
+      </c>
+      <c r="C36" t="s">
+        <v>73</v>
       </c>
       <c r="D36" s="1">
         <v>46206</v>
@@ -2288,45 +2300,45 @@
         <v>46205</v>
       </c>
       <c r="F36">
-        <v>20130</v>
+        <v>20153</v>
       </c>
       <c r="G36">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-39</v>
+        <v>-35</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>0.222222222</v>
       </c>
       <c r="K36">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-39</v>
+        <v>-35</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>0.222222222</v>
       </c>
       <c r="O36" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>9953</v>
+        <v>9950</v>
       </c>
       <c r="B37">
-        <v>233</v>
-      </c>
-      <c r="C37">
-        <v>233</v>
+        <v>216</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
       </c>
       <c r="D37" s="1">
         <v>46206</v>
@@ -2335,95 +2347,95 @@
         <v>46205</v>
       </c>
       <c r="F37">
-        <v>200158</v>
+        <v>20095</v>
       </c>
       <c r="G37">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
       <c r="K37">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L37">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M37">
         <v>0</v>
       </c>
-      <c r="N37">
-        <v>1</v>
-      </c>
       <c r="O37" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>10004</v>
+        <v>10002</v>
       </c>
       <c r="B38">
-        <v>131</v>
+        <v>326</v>
       </c>
       <c r="C38">
-        <v>131</v>
+        <v>326</v>
       </c>
       <c r="D38" s="1">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E38" s="1">
         <v>46207</v>
       </c>
       <c r="F38">
-        <v>20005</v>
+        <v>20076</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
       <c r="K38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M38">
         <v>0</v>
       </c>
+      <c r="N38">
+        <v>1</v>
+      </c>
       <c r="O38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>10006</v>
+        <v>10003</v>
       </c>
       <c r="B39">
-        <v>134</v>
+        <v>328</v>
       </c>
       <c r="C39">
-        <v>134</v>
+        <v>328</v>
       </c>
       <c r="D39" s="1">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E39" s="1">
         <v>46207</v>
       </c>
       <c r="F39">
-        <v>20112</v>
+        <v>20095</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2444,59 +2456,65 @@
         <v>0</v>
       </c>
       <c r="O39" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>10012</v>
+        <v>9951</v>
       </c>
       <c r="B40">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="C40">
-        <v>140</v>
+        <v>231</v>
       </c>
       <c r="D40" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="E40" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="F40">
-        <v>20006</v>
+        <v>20005</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="J40">
+        <v>0.67441860499999995</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="N40">
+        <v>0.67441860499999995</v>
       </c>
       <c r="O40" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>9955</v>
+        <v>9952</v>
       </c>
       <c r="B41">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C41">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D41" s="1">
         <v>46206</v>
@@ -2505,101 +2523,101 @@
         <v>46205</v>
       </c>
       <c r="F41">
-        <v>20113</v>
+        <v>20130</v>
       </c>
       <c r="G41">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H41">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>-6</v>
+        <v>-39</v>
       </c>
       <c r="J41">
-        <v>0.76923076899999998</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="L41">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>-6</v>
+        <v>-39</v>
       </c>
       <c r="N41">
-        <v>0.76923076899999998</v>
+        <v>0</v>
       </c>
       <c r="O41" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>9976</v>
+        <v>9953</v>
       </c>
       <c r="B42">
-        <v>339</v>
+        <v>233</v>
       </c>
       <c r="C42">
-        <v>339</v>
+        <v>233</v>
       </c>
       <c r="D42" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="E42" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F42">
-        <v>20008</v>
+        <v>200158</v>
       </c>
       <c r="G42">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H42">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I42">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>0.73333333300000003</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L42">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M42">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>0.73333333300000003</v>
+        <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>10013</v>
+        <v>10006</v>
       </c>
       <c r="B43">
-        <v>501</v>
-      </c>
-      <c r="C43" t="s">
-        <v>65</v>
+        <v>134</v>
+      </c>
+      <c r="C43">
+        <v>134</v>
       </c>
       <c r="D43" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="E43" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="F43">
-        <v>20095</v>
+        <v>20112</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -2620,18 +2638,18 @@
         <v>0</v>
       </c>
       <c r="O43" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>9959</v>
+        <v>9955</v>
       </c>
       <c r="B44">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C44">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D44" s="1">
         <v>46206</v>
@@ -2640,45 +2658,45 @@
         <v>46205</v>
       </c>
       <c r="F44">
-        <v>20008</v>
+        <v>20113</v>
       </c>
       <c r="G44">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H44">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I44">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="J44">
-        <v>0.75</v>
+        <v>0.76923076899999998</v>
       </c>
       <c r="K44">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="L44">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M44">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="N44">
-        <v>0.75</v>
+        <v>0.76923076899999998</v>
       </c>
       <c r="O44" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>9999</v>
+        <v>9976</v>
       </c>
       <c r="B45">
-        <v>325</v>
-      </c>
-      <c r="C45" t="s">
-        <v>95</v>
+        <v>339</v>
+      </c>
+      <c r="C45">
+        <v>339</v>
       </c>
       <c r="D45" s="1">
         <v>46207</v>
@@ -2687,139 +2705,133 @@
         <v>46206</v>
       </c>
       <c r="F45">
-        <v>20095</v>
+        <v>20008</v>
       </c>
       <c r="G45">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H45">
+        <v>22</v>
+      </c>
+      <c r="I45">
+        <v>-8</v>
+      </c>
+      <c r="J45">
+        <v>0.73333333300000003</v>
+      </c>
+      <c r="K45">
+        <v>30</v>
+      </c>
+      <c r="L45">
+        <v>22</v>
+      </c>
+      <c r="M45">
+        <v>-8</v>
+      </c>
+      <c r="N45">
+        <v>0.73333333300000003</v>
+      </c>
+      <c r="O45" t="s">
         <v>15</v>
-      </c>
-      <c r="I45">
-        <v>-3</v>
-      </c>
-      <c r="J45">
-        <v>0.83333333300000001</v>
-      </c>
-      <c r="K45">
-        <v>18</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>-18</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>9998</v>
+        <v>10013</v>
       </c>
       <c r="B46">
-        <v>324</v>
+        <v>501</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D46" s="1">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E46" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F46">
-        <v>20105</v>
+        <v>20095</v>
       </c>
       <c r="G46">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>-4</v>
-      </c>
-      <c r="J46">
-        <v>0.80952380999999995</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>-4</v>
-      </c>
-      <c r="N46">
-        <v>0.80952380999999995</v>
+        <v>0</v>
       </c>
       <c r="O46" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>9978</v>
+        <v>9959</v>
       </c>
       <c r="B47">
-        <v>301</v>
-      </c>
-      <c r="C47" t="s">
-        <v>88</v>
+        <v>239</v>
+      </c>
+      <c r="C47">
+        <v>239</v>
       </c>
       <c r="D47" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="E47" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F47">
-        <v>20155</v>
+        <v>20008</v>
       </c>
       <c r="G47">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H47">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I47">
         <v>-4</v>
       </c>
       <c r="J47">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="K47">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M47">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="O47" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>9988</v>
+        <v>9999</v>
       </c>
       <c r="B48">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="D48" s="1">
         <v>46207</v>
@@ -2828,45 +2840,45 @@
         <v>46206</v>
       </c>
       <c r="F48">
-        <v>20106</v>
+        <v>20095</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H48">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I48">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="J48">
-        <v>0.6</v>
+        <v>0.83333333300000001</v>
       </c>
       <c r="K48">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L48">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>-4</v>
+        <v>-18</v>
       </c>
       <c r="N48">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O48" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>9993</v>
+        <v>9998</v>
       </c>
       <c r="B49">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C49" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D49" s="1">
         <v>46207</v>
@@ -2875,45 +2887,45 @@
         <v>46206</v>
       </c>
       <c r="F49">
-        <v>20058</v>
+        <v>20105</v>
       </c>
       <c r="G49">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H49">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I49">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="J49">
-        <v>0.75</v>
+        <v>0.80952380999999995</v>
       </c>
       <c r="K49">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M49">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>0.80952380999999995</v>
       </c>
       <c r="O49" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>9968</v>
+        <v>9978</v>
       </c>
       <c r="B50">
-        <v>331</v>
-      </c>
-      <c r="C50">
-        <v>331</v>
+        <v>301</v>
+      </c>
+      <c r="C50" t="s">
+        <v>88</v>
       </c>
       <c r="D50" s="1">
         <v>46207</v>
@@ -2922,45 +2934,45 @@
         <v>46206</v>
       </c>
       <c r="F50">
-        <v>20006</v>
+        <v>20155</v>
       </c>
       <c r="G50">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H50">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I50">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="J50">
-        <v>0.85714285700000004</v>
+        <v>0.8</v>
       </c>
       <c r="K50">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="N50">
         <v>0</v>
       </c>
       <c r="O50" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>9973</v>
+        <v>9988</v>
       </c>
       <c r="B51">
-        <v>336</v>
-      </c>
-      <c r="C51">
-        <v>336</v>
+        <v>313</v>
+      </c>
+      <c r="C51" t="s">
+        <v>56</v>
       </c>
       <c r="D51" s="1">
         <v>46207</v>
@@ -2969,45 +2981,45 @@
         <v>46206</v>
       </c>
       <c r="F51">
-        <v>20111</v>
+        <v>20106</v>
       </c>
       <c r="G51">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H51">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I51">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="J51">
-        <v>0.6875</v>
+        <v>0.6</v>
       </c>
       <c r="K51">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M51">
-        <v>-32</v>
+        <v>-4</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="O51" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>9991</v>
+        <v>9993</v>
       </c>
       <c r="B52">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D52" s="1">
         <v>46207</v>
@@ -3016,19 +3028,19 @@
         <v>46206</v>
       </c>
       <c r="F52">
-        <v>20066</v>
+        <v>20058</v>
       </c>
       <c r="G52">
         <v>20</v>
       </c>
       <c r="H52">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I52">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J52">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="K52">
         <v>20</v>
@@ -3043,18 +3055,18 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>9989</v>
+        <v>9968</v>
       </c>
       <c r="B53">
-        <v>315</v>
-      </c>
-      <c r="C53" t="s">
-        <v>58</v>
+        <v>331</v>
+      </c>
+      <c r="C53">
+        <v>331</v>
       </c>
       <c r="D53" s="1">
         <v>46207</v>
@@ -3063,139 +3075,133 @@
         <v>46206</v>
       </c>
       <c r="F53">
-        <v>20153</v>
+        <v>20006</v>
       </c>
       <c r="G53">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H53">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>0.85714285700000004</v>
       </c>
       <c r="K53">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="N53">
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>9958</v>
+        <v>9973</v>
       </c>
       <c r="B54">
-        <v>238</v>
+        <v>336</v>
       </c>
       <c r="C54">
-        <v>238</v>
+        <v>336</v>
       </c>
       <c r="D54" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E54" s="1">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F54">
-        <v>20007</v>
+        <v>20111</v>
       </c>
       <c r="G54">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H54">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I54">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="J54">
-        <v>0.70370370400000004</v>
+        <v>0.6875</v>
       </c>
       <c r="K54">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54">
-        <v>-27</v>
+        <v>-32</v>
       </c>
       <c r="N54">
         <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>9975</v>
+        <v>10039</v>
       </c>
       <c r="B55">
-        <v>338</v>
-      </c>
-      <c r="C55">
-        <v>338</v>
+        <v>800</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
       </c>
       <c r="D55" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E55" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F55">
-        <v>20112</v>
+        <v>200150</v>
       </c>
       <c r="G55">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
-      <c r="J55">
-        <v>1</v>
-      </c>
       <c r="K55">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L55">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M55">
         <v>0</v>
       </c>
-      <c r="N55">
-        <v>1</v>
-      </c>
       <c r="O55" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>9979</v>
+        <v>9991</v>
       </c>
       <c r="B56">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="C56" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D56" s="1">
         <v>46207</v>
@@ -3204,212 +3210,236 @@
         <v>46206</v>
       </c>
       <c r="F56">
-        <v>20058</v>
+        <v>20066</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>-2</v>
+      </c>
+      <c r="J56">
+        <v>0.9</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56">
-        <v>1</v>
+        <v>-20</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
       </c>
       <c r="O56" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>10024</v>
+        <v>9989</v>
       </c>
       <c r="B57">
-        <v>209</v>
+        <v>315</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="D57" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="E57" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="F57">
-        <v>20105</v>
+        <v>20153</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
       <c r="K57">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57">
+        <v>-14</v>
+      </c>
+      <c r="N57">
         <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10025</v>
+        <v>9958</v>
       </c>
       <c r="B58">
-        <v>210</v>
-      </c>
-      <c r="C58" t="s">
-        <v>97</v>
+        <v>238</v>
+      </c>
+      <c r="C58">
+        <v>238</v>
       </c>
       <c r="D58" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="E58" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="F58">
-        <v>20066</v>
+        <v>20007</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J58">
+        <v>0.70370370400000004</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
       <c r="M58">
+        <v>-27</v>
+      </c>
+      <c r="N58">
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>10026</v>
+        <v>9975</v>
       </c>
       <c r="B59">
-        <v>211</v>
-      </c>
-      <c r="C59" t="s">
-        <v>98</v>
+        <v>338</v>
+      </c>
+      <c r="C59">
+        <v>338</v>
       </c>
       <c r="D59" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="E59" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="F59">
-        <v>20058</v>
+        <v>20112</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I59">
         <v>0</v>
       </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
       <c r="K59">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M59">
         <v>0</v>
       </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
       <c r="O59" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>10027</v>
+        <v>9979</v>
       </c>
       <c r="B60">
-        <v>212</v>
+        <v>302</v>
       </c>
       <c r="C60" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D60" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="E60" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="F60">
-        <v>20057</v>
+        <v>20058</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>10028</v>
+        <v>10040</v>
       </c>
       <c r="B61">
-        <v>231</v>
-      </c>
-      <c r="C61">
-        <v>231</v>
+        <v>302</v>
+      </c>
+      <c r="C61" t="s">
+        <v>75</v>
       </c>
       <c r="D61" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E61" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F61">
-        <v>20005</v>
+        <v>20058</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -3430,27 +3460,27 @@
         <v>0</v>
       </c>
       <c r="O61" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>10029</v>
+        <v>10041</v>
       </c>
       <c r="B62">
-        <v>232</v>
-      </c>
-      <c r="C62">
-        <v>232</v>
+        <v>303</v>
+      </c>
+      <c r="C62" t="s">
+        <v>66</v>
       </c>
       <c r="D62" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E62" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F62">
-        <v>20130</v>
+        <v>11215</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -3471,27 +3501,27 @@
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>10030</v>
+        <v>10042</v>
       </c>
       <c r="B63">
-        <v>233</v>
-      </c>
-      <c r="C63">
-        <v>233</v>
+        <v>304</v>
+      </c>
+      <c r="C63" t="s">
+        <v>53</v>
       </c>
       <c r="D63" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E63" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F63">
-        <v>200158</v>
+        <v>20086</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -3512,27 +3542,27 @@
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>10031</v>
+        <v>10043</v>
       </c>
       <c r="B64">
-        <v>234</v>
-      </c>
-      <c r="C64">
-        <v>234</v>
+        <v>305</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
       </c>
       <c r="D64" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E64" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F64">
-        <v>20112</v>
+        <v>20066</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3553,27 +3583,27 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>10032</v>
+        <v>10044</v>
       </c>
       <c r="B65">
-        <v>235</v>
-      </c>
-      <c r="C65">
-        <v>235</v>
+        <v>307</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
       </c>
       <c r="D65" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E65" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F65">
-        <v>20113</v>
+        <v>20105</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -3594,27 +3624,27 @@
         <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>10033</v>
+        <v>10045</v>
       </c>
       <c r="B66">
-        <v>236</v>
-      </c>
-      <c r="C66">
-        <v>236</v>
+        <v>308</v>
+      </c>
+      <c r="C66" t="s">
+        <v>99</v>
       </c>
       <c r="D66" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E66" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F66">
-        <v>20111</v>
+        <v>20057</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3635,27 +3665,27 @@
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>10034</v>
+        <v>10046</v>
       </c>
       <c r="B67">
-        <v>237</v>
-      </c>
-      <c r="C67">
-        <v>237</v>
+        <v>311</v>
+      </c>
+      <c r="C67" t="s">
+        <v>55</v>
       </c>
       <c r="D67" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E67" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F67">
-        <v>20003</v>
+        <v>20106</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -3676,27 +3706,27 @@
         <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10035</v>
+        <v>10047</v>
       </c>
       <c r="B68">
-        <v>238</v>
-      </c>
-      <c r="C68">
-        <v>238</v>
+        <v>312</v>
+      </c>
+      <c r="C68" t="s">
+        <v>52</v>
       </c>
       <c r="D68" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E68" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F68">
-        <v>20007</v>
+        <v>20095</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -3717,27 +3747,27 @@
         <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10036</v>
+        <v>10048</v>
       </c>
       <c r="B69">
-        <v>239</v>
-      </c>
-      <c r="C69">
-        <v>239</v>
+        <v>313</v>
+      </c>
+      <c r="C69" t="s">
+        <v>56</v>
       </c>
       <c r="D69" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E69" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F69">
-        <v>20008</v>
+        <v>20076</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -3758,27 +3788,27 @@
         <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>10037</v>
+        <v>10049</v>
       </c>
       <c r="B70">
-        <v>240</v>
-      </c>
-      <c r="C70">
-        <v>240</v>
+        <v>314</v>
+      </c>
+      <c r="C70" t="s">
+        <v>57</v>
       </c>
       <c r="D70" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E70" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F70">
-        <v>20006</v>
+        <v>20153</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -3799,27 +3829,27 @@
         <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10038</v>
+        <v>10050</v>
       </c>
       <c r="B71">
-        <v>503</v>
+        <v>315</v>
       </c>
       <c r="C71" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D71" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E71" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F71">
-        <v>200150</v>
+        <v>20043</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -3840,27 +3870,27 @@
         <v>0</v>
       </c>
       <c r="O71" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>10016</v>
+        <v>10051</v>
       </c>
       <c r="B72">
-        <v>201</v>
+        <v>316</v>
       </c>
       <c r="C72" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D72" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E72" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F72">
-        <v>20153</v>
+        <v>200150</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -3881,27 +3911,27 @@
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>10017</v>
+        <v>10052</v>
       </c>
       <c r="B73">
-        <v>202</v>
+        <v>321</v>
       </c>
       <c r="C73" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D73" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E73" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F73">
-        <v>20086</v>
+        <v>20006</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -3922,27 +3952,27 @@
         <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>10018</v>
+        <v>10053</v>
       </c>
       <c r="B74">
-        <v>203</v>
+        <v>322</v>
       </c>
       <c r="C74" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="D74" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F74">
-        <v>20155</v>
+        <v>20130</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -3963,27 +3993,27 @@
         <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>10019</v>
+        <v>10054</v>
       </c>
       <c r="B75">
-        <v>204</v>
+        <v>323</v>
       </c>
       <c r="C75" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D75" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E75" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F75">
-        <v>20095</v>
+        <v>200158</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -4004,27 +4034,27 @@
         <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>10020</v>
+        <v>10055</v>
       </c>
       <c r="B76">
-        <v>205</v>
+        <v>324</v>
       </c>
       <c r="C76" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D76" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E76" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F76">
-        <v>20043</v>
+        <v>20112</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -4045,27 +4075,27 @@
         <v>0</v>
       </c>
       <c r="O76" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>10021</v>
+        <v>10056</v>
       </c>
       <c r="B77">
-        <v>206</v>
+        <v>325</v>
       </c>
       <c r="C77" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D77" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E77" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F77">
-        <v>20076</v>
+        <v>20113</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -4086,27 +4116,27 @@
         <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>10022</v>
+        <v>10057</v>
       </c>
       <c r="B78">
-        <v>207</v>
-      </c>
-      <c r="C78" t="s">
-        <v>84</v>
+        <v>326</v>
+      </c>
+      <c r="C78">
+        <v>326</v>
       </c>
       <c r="D78" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E78" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F78">
-        <v>20106</v>
+        <v>20111</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -4127,27 +4157,27 @@
         <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>10023</v>
+        <v>10058</v>
       </c>
       <c r="B79">
-        <v>208</v>
-      </c>
-      <c r="C79" t="s">
-        <v>85</v>
+        <v>327</v>
+      </c>
+      <c r="C79">
+        <v>327</v>
       </c>
       <c r="D79" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E79" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F79">
-        <v>11215</v>
+        <v>20003</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -4168,27 +4198,27 @@
         <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>10015</v>
+        <v>10059</v>
       </c>
       <c r="B80">
-        <v>502</v>
-      </c>
-      <c r="C80" t="s">
-        <v>77</v>
+        <v>328</v>
+      </c>
+      <c r="C80">
+        <v>328</v>
       </c>
       <c r="D80" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E80" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F80">
-        <v>20043</v>
+        <v>20007</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -4209,773 +4239,725 @@
         <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>9980</v>
+        <v>10060</v>
       </c>
       <c r="B81">
-        <v>303</v>
-      </c>
-      <c r="C81" t="s">
-        <v>66</v>
+        <v>329</v>
+      </c>
+      <c r="C81">
+        <v>329</v>
       </c>
       <c r="D81" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E81" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F81">
-        <v>20043</v>
+        <v>20008</v>
       </c>
       <c r="G81">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I81">
-        <v>-11</v>
-      </c>
-      <c r="J81">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K81">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L81">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M81">
-        <v>-11</v>
-      </c>
-      <c r="N81">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>10005</v>
+        <v>10061</v>
       </c>
       <c r="B82">
-        <v>133</v>
+        <v>330</v>
       </c>
       <c r="C82">
-        <v>133</v>
+        <v>330</v>
       </c>
       <c r="D82" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E82" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="F82">
-        <v>200158</v>
+        <v>20005</v>
       </c>
       <c r="G82">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I82">
         <v>0</v>
       </c>
-      <c r="J82">
-        <v>1</v>
-      </c>
       <c r="K82">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L82">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M82">
         <v>0</v>
       </c>
-      <c r="N82">
-        <v>1</v>
-      </c>
       <c r="O82" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>10007</v>
+        <v>10062</v>
       </c>
       <c r="B83">
-        <v>135</v>
-      </c>
-      <c r="C83">
-        <v>135</v>
+        <v>502</v>
+      </c>
+      <c r="C83" t="s">
+        <v>77</v>
       </c>
       <c r="D83" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E83" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="F83">
-        <v>20113</v>
+        <v>200150</v>
       </c>
       <c r="G83">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I83">
-        <v>-5</v>
-      </c>
-      <c r="J83">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K83">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L83">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>-5</v>
-      </c>
-      <c r="N83">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>9972</v>
+        <v>10063</v>
       </c>
       <c r="B84">
-        <v>335</v>
-      </c>
-      <c r="C84">
-        <v>335</v>
+        <v>503</v>
+      </c>
+      <c r="C84" t="s">
+        <v>63</v>
       </c>
       <c r="D84" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E84" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F84">
-        <v>20113</v>
+        <v>200150</v>
       </c>
       <c r="G84">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I84">
-        <v>-4</v>
-      </c>
-      <c r="J84">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K84">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L84">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>-4</v>
-      </c>
-      <c r="N84">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>10011</v>
+        <v>10064</v>
       </c>
       <c r="B85">
-        <v>139</v>
-      </c>
-      <c r="C85">
-        <v>139</v>
+        <v>304</v>
+      </c>
+      <c r="C85" t="s">
+        <v>53</v>
       </c>
       <c r="D85" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E85" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="F85">
-        <v>20008</v>
+        <v>20086</v>
       </c>
       <c r="G85">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>1</v>
-      </c>
-      <c r="J85">
-        <v>1.0476190480000001</v>
+        <v>0</v>
       </c>
       <c r="K85">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L85">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>1</v>
-      </c>
-      <c r="N85">
-        <v>1.0476190480000001</v>
+        <v>0</v>
       </c>
       <c r="O85" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>10009</v>
+        <v>10017</v>
       </c>
       <c r="B86">
-        <v>137</v>
-      </c>
-      <c r="C86">
-        <v>137</v>
+        <v>202</v>
+      </c>
+      <c r="C86" t="s">
+        <v>81</v>
       </c>
       <c r="D86" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E86" s="1">
         <v>46209</v>
       </c>
-      <c r="E86" s="1">
-        <v>46207</v>
-      </c>
       <c r="F86">
-        <v>20003</v>
+        <v>20086</v>
       </c>
       <c r="G86">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H86">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J86">
-        <v>1</v>
+        <v>0.86666666699999995</v>
       </c>
       <c r="K86">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L86">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>0.86666666699999995</v>
       </c>
       <c r="O86" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>9974</v>
+        <v>10021</v>
       </c>
       <c r="B87">
-        <v>337</v>
-      </c>
-      <c r="C87">
-        <v>337</v>
+        <v>206</v>
+      </c>
+      <c r="C87" t="s">
+        <v>72</v>
       </c>
       <c r="D87" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E87" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F87">
-        <v>20003</v>
+        <v>20076</v>
       </c>
       <c r="G87">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H87">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I87">
-        <v>17</v>
+        <v>-11</v>
       </c>
       <c r="J87">
-        <v>1.653846154</v>
+        <v>0.67647058800000004</v>
       </c>
       <c r="K87">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L87">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="M87">
-        <v>17</v>
+        <v>-11</v>
       </c>
       <c r="N87">
-        <v>1.653846154</v>
+        <v>0.67647058800000004</v>
       </c>
       <c r="O87" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>9982</v>
+        <v>10020</v>
       </c>
       <c r="B88">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="C88" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="D88" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E88" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F88">
-        <v>20106</v>
+        <v>20043</v>
       </c>
       <c r="G88">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="H88">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I88">
-        <v>-4</v>
+        <v>-27</v>
       </c>
       <c r="J88">
-        <v>0.84615384599999999</v>
+        <v>0.47058823500000002</v>
       </c>
       <c r="K88">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="L88">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M88">
-        <v>-4</v>
+        <v>-27</v>
       </c>
       <c r="N88">
-        <v>0.84615384599999999</v>
+        <v>0.47058823500000002</v>
       </c>
       <c r="O88" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>9983</v>
+        <v>10022</v>
       </c>
       <c r="B89">
-        <v>306</v>
+        <v>207</v>
       </c>
       <c r="C89" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D89" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E89" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F89">
-        <v>20105</v>
+        <v>20106</v>
       </c>
       <c r="G89">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H89">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="I89">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="J89">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="K89">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="L89">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="M89">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="N89">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="O89" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>9985</v>
+        <v>10004</v>
       </c>
       <c r="B90">
-        <v>310</v>
-      </c>
-      <c r="C90" t="s">
-        <v>68</v>
+        <v>131</v>
+      </c>
+      <c r="C90">
+        <v>131</v>
       </c>
       <c r="D90" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E90" s="1">
         <v>46207</v>
       </c>
-      <c r="E90" s="1">
-        <v>46206</v>
-      </c>
       <c r="F90">
-        <v>20155</v>
+        <v>20008</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H90">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>-7</v>
+      </c>
+      <c r="J90">
+        <v>0.53333333299999997</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L90">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M90">
-        <v>1</v>
+        <v>-7</v>
+      </c>
+      <c r="N90">
+        <v>0.53333333299999997</v>
       </c>
       <c r="O90" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>9986</v>
+        <v>10028</v>
       </c>
       <c r="B91">
-        <v>311</v>
-      </c>
-      <c r="C91" t="s">
-        <v>55</v>
+        <v>231</v>
+      </c>
+      <c r="C91">
+        <v>231</v>
       </c>
       <c r="D91" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E91" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F91">
-        <v>20057</v>
+        <v>20005</v>
       </c>
       <c r="G91">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H91">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I91">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="J91">
-        <v>0.94545454500000004</v>
+        <v>0.74285714300000005</v>
       </c>
       <c r="K91">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L91">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="M91">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="N91">
-        <v>0.94545454500000004</v>
+        <v>0.74285714300000005</v>
       </c>
       <c r="O91" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>9995</v>
+        <v>10033</v>
       </c>
       <c r="B92">
-        <v>320</v>
-      </c>
-      <c r="C92" t="s">
-        <v>69</v>
+        <v>236</v>
+      </c>
+      <c r="C92">
+        <v>236</v>
       </c>
       <c r="D92" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E92" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F92">
-        <v>20066</v>
+        <v>20111</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J92">
-        <v>1</v>
+        <v>0.909090909</v>
       </c>
       <c r="K92">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L92">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N92">
-        <v>1</v>
+        <v>0.909090909</v>
       </c>
       <c r="O92" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>10008</v>
+        <v>10030</v>
       </c>
       <c r="B93">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="C93">
-        <v>136</v>
+        <v>233</v>
       </c>
       <c r="D93" s="1">
         <v>46209</v>
       </c>
       <c r="E93" s="1">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="F93">
-        <v>20111</v>
+        <v>200158</v>
       </c>
       <c r="G93">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I93">
-        <v>-17</v>
-      </c>
-      <c r="J93">
-        <v>0.54054054100000004</v>
+        <v>0</v>
       </c>
       <c r="K93">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L93">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M93">
-        <v>-17</v>
-      </c>
-      <c r="N93">
-        <v>0.54054054100000004</v>
+        <v>0</v>
       </c>
       <c r="O93" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>9898</v>
+        <v>10031</v>
       </c>
       <c r="B94">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="C94">
-        <v>332</v>
+        <v>234</v>
       </c>
       <c r="D94" s="1">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E94" s="1">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="F94">
-        <v>20130</v>
+        <v>20112</v>
       </c>
       <c r="G94">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H94">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I94">
-        <v>-5</v>
-      </c>
-      <c r="J94">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K94">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L94">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>-5</v>
-      </c>
-      <c r="N94">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O94" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>9910</v>
+        <v>10032</v>
       </c>
       <c r="B95">
-        <v>103</v>
-      </c>
-      <c r="C95" t="s">
-        <v>29</v>
+        <v>235</v>
+      </c>
+      <c r="C95">
+        <v>235</v>
       </c>
       <c r="D95" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E95" s="1">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="F95">
-        <v>20153</v>
+        <v>20113</v>
       </c>
       <c r="G95">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I95">
-        <v>-19</v>
-      </c>
-      <c r="J95">
-        <v>0.58695652200000004</v>
+        <v>0</v>
       </c>
       <c r="K95">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L95">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M95">
-        <v>-19</v>
-      </c>
-      <c r="N95">
-        <v>0.58695652200000004</v>
+        <v>0</v>
       </c>
       <c r="O95" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>9933</v>
+        <v>10035</v>
       </c>
       <c r="B96">
-        <v>800</v>
-      </c>
-      <c r="C96" t="s">
-        <v>62</v>
+        <v>238</v>
+      </c>
+      <c r="C96">
+        <v>238</v>
       </c>
       <c r="D96" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E96" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F96">
-        <v>200150</v>
+        <v>20007</v>
       </c>
       <c r="G96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96">
         <v>0</v>
       </c>
       <c r="I96">
-        <v>-1</v>
-      </c>
-      <c r="J96">
         <v>0</v>
       </c>
       <c r="K96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96">
         <v>0</v>
       </c>
       <c r="M96">
-        <v>-1</v>
-      </c>
-      <c r="N96">
         <v>0</v>
       </c>
       <c r="O96" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>9936</v>
+        <v>10036</v>
       </c>
       <c r="B97">
-        <v>800</v>
-      </c>
-      <c r="C97" t="s">
-        <v>62</v>
+        <v>239</v>
+      </c>
+      <c r="C97">
+        <v>239</v>
       </c>
       <c r="D97" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E97" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F97">
-        <v>200150</v>
+        <v>20008</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -4996,27 +4978,27 @@
         <v>0</v>
       </c>
       <c r="O97" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>9937</v>
+        <v>10015</v>
       </c>
       <c r="B98">
-        <v>800</v>
+        <v>502</v>
       </c>
       <c r="C98" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D98" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E98" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F98">
-        <v>200150</v>
+        <v>20043</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -5037,380 +5019,380 @@
         <v>0</v>
       </c>
       <c r="O98" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>9921</v>
+        <v>9980</v>
       </c>
       <c r="B99">
-        <v>114</v>
+        <v>303</v>
       </c>
       <c r="C99" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D99" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E99" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F99">
-        <v>20048</v>
+        <v>20043</v>
       </c>
       <c r="G99">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I99">
-        <v>-28</v>
+        <v>-11</v>
       </c>
       <c r="J99">
-        <v>0</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K99">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M99">
-        <v>-28</v>
+        <v>-11</v>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O99" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>9911</v>
+        <v>10005</v>
       </c>
       <c r="B100">
-        <v>104</v>
-      </c>
-      <c r="C100" t="s">
-        <v>31</v>
+        <v>133</v>
+      </c>
+      <c r="C100">
+        <v>133</v>
       </c>
       <c r="D100" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E100" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F100">
-        <v>20105</v>
+        <v>200158</v>
       </c>
       <c r="G100">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="H100">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I100">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="J100">
-        <v>0.68518518500000003</v>
+        <v>1</v>
       </c>
       <c r="K100">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="L100">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="M100">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="N100">
-        <v>0.68518518500000003</v>
+        <v>1</v>
       </c>
       <c r="O100" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>9912</v>
+        <v>10007</v>
       </c>
       <c r="B101">
-        <v>105</v>
-      </c>
-      <c r="C101" t="s">
-        <v>33</v>
+        <v>135</v>
+      </c>
+      <c r="C101">
+        <v>135</v>
       </c>
       <c r="D101" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E101" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F101">
-        <v>20058</v>
+        <v>20113</v>
       </c>
       <c r="G101">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="H101">
         <v>20</v>
       </c>
       <c r="I101">
-        <v>-28</v>
+        <v>-5</v>
       </c>
       <c r="J101">
-        <v>0.41666666699999999</v>
+        <v>0.8</v>
       </c>
       <c r="K101">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="L101">
         <v>20</v>
       </c>
       <c r="M101">
-        <v>-28</v>
+        <v>-5</v>
       </c>
       <c r="N101">
-        <v>0.41666666699999999</v>
+        <v>0.8</v>
       </c>
       <c r="O101" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>9914</v>
+        <v>9972</v>
       </c>
       <c r="B102">
-        <v>107</v>
-      </c>
-      <c r="C102" t="s">
-        <v>37</v>
+        <v>335</v>
+      </c>
+      <c r="C102">
+        <v>335</v>
       </c>
       <c r="D102" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E102" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F102">
-        <v>20155</v>
+        <v>20113</v>
       </c>
       <c r="G102">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="J102">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K102">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L102">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M102">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N102">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O102" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>9915</v>
+        <v>10011</v>
       </c>
       <c r="B103">
-        <v>108</v>
-      </c>
-      <c r="C103" t="s">
-        <v>39</v>
+        <v>139</v>
+      </c>
+      <c r="C103">
+        <v>139</v>
       </c>
       <c r="D103" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E103" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F103">
-        <v>20057</v>
+        <v>20008</v>
       </c>
       <c r="G103">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="H103">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="I103">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="J103">
-        <v>0.87323943699999995</v>
+        <v>1.0476190480000001</v>
       </c>
       <c r="K103">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="L103">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="M103">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="N103">
-        <v>0.87323943699999995</v>
+        <v>1.0476190480000001</v>
       </c>
       <c r="O103" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>9916</v>
+        <v>10009</v>
       </c>
       <c r="B104">
-        <v>109</v>
-      </c>
-      <c r="C104" t="s">
-        <v>41</v>
+        <v>137</v>
+      </c>
+      <c r="C104">
+        <v>137</v>
       </c>
       <c r="D104" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E104" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F104">
-        <v>20112</v>
+        <v>20003</v>
       </c>
       <c r="G104">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="H104">
         <v>12</v>
       </c>
       <c r="I104">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="J104">
-        <v>0.38709677399999998</v>
+        <v>1</v>
       </c>
       <c r="K104">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="L104">
         <v>12</v>
       </c>
       <c r="M104">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="N104">
-        <v>0.38709677399999998</v>
+        <v>1</v>
       </c>
       <c r="O104" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>9917</v>
+        <v>9974</v>
       </c>
       <c r="B105">
-        <v>110</v>
-      </c>
-      <c r="C105" t="s">
+        <v>337</v>
+      </c>
+      <c r="C105">
+        <v>337</v>
+      </c>
+      <c r="D105" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E105" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F105">
+        <v>20003</v>
+      </c>
+      <c r="G105">
+        <v>26</v>
+      </c>
+      <c r="H105">
         <v>43</v>
       </c>
-      <c r="D105" s="1">
-        <v>46205</v>
-      </c>
-      <c r="E105" s="1">
-        <v>46204</v>
-      </c>
-      <c r="F105">
-        <v>20066</v>
-      </c>
-      <c r="G105">
-        <v>46</v>
-      </c>
-      <c r="H105">
-        <v>28</v>
-      </c>
       <c r="I105">
-        <v>-18</v>
+        <v>17</v>
       </c>
       <c r="J105">
-        <v>0.60869565199999998</v>
+        <v>1.653846154</v>
       </c>
       <c r="K105">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="L105">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="M105">
-        <v>-18</v>
+        <v>17</v>
       </c>
       <c r="N105">
-        <v>0.60869565199999998</v>
+        <v>1.653846154</v>
       </c>
       <c r="O105" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>9919</v>
+        <v>9982</v>
       </c>
       <c r="B106">
-        <v>112</v>
+        <v>305</v>
       </c>
       <c r="C106" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D106" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E106" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F106">
         <v>20106</v>
       </c>
       <c r="G106">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="H106">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I106">
-        <v>-37</v>
+        <v>-4</v>
       </c>
       <c r="J106">
-        <v>0.26</v>
+        <v>0.84615384599999999</v>
       </c>
       <c r="K106">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="L106">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M106">
-        <v>-37</v>
+        <v>-4</v>
       </c>
       <c r="N106">
-        <v>0.26</v>
+        <v>0.84615384599999999</v>
       </c>
       <c r="O106" t="s">
         <v>47</v>
@@ -5418,289 +5400,289 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>9924</v>
+        <v>9983</v>
       </c>
       <c r="B107">
-        <v>133</v>
-      </c>
-      <c r="C107">
-        <v>133</v>
+        <v>306</v>
+      </c>
+      <c r="C107" t="s">
+        <v>67</v>
       </c>
       <c r="D107" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E107" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F107">
-        <v>200158</v>
+        <v>20105</v>
       </c>
       <c r="G107">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="H107">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="K107">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L107">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M107">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="N107">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="O107" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>9927</v>
+        <v>9985</v>
       </c>
       <c r="B108">
-        <v>137</v>
-      </c>
-      <c r="C108">
-        <v>137</v>
+        <v>310</v>
+      </c>
+      <c r="C108" t="s">
+        <v>68</v>
       </c>
       <c r="D108" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E108" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F108">
-        <v>20003</v>
+        <v>20155</v>
       </c>
       <c r="G108">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H108">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I108">
-        <v>-5</v>
-      </c>
-      <c r="J108">
-        <v>0.70588235300000002</v>
+        <v>1</v>
       </c>
       <c r="K108">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L108">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M108">
-        <v>-5</v>
-      </c>
-      <c r="N108">
-        <v>0.70588235300000002</v>
+        <v>1</v>
       </c>
       <c r="O108" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>9928</v>
+        <v>9986</v>
       </c>
       <c r="B109">
-        <v>138</v>
-      </c>
-      <c r="C109">
-        <v>138</v>
+        <v>311</v>
+      </c>
+      <c r="C109" t="s">
+        <v>55</v>
       </c>
       <c r="D109" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E109" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F109">
-        <v>20007</v>
+        <v>20057</v>
       </c>
       <c r="G109">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="H109">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="I109">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="J109">
-        <v>0.70967741900000003</v>
+        <v>0.94545454500000004</v>
       </c>
       <c r="K109">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="L109">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="M109">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="N109">
-        <v>0.70967741900000003</v>
+        <v>0.94545454500000004</v>
       </c>
       <c r="O109" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>9929</v>
+        <v>9995</v>
       </c>
       <c r="B110">
-        <v>139</v>
-      </c>
-      <c r="C110">
-        <v>139</v>
+        <v>320</v>
+      </c>
+      <c r="C110" t="s">
+        <v>69</v>
       </c>
       <c r="D110" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E110" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F110">
-        <v>20008</v>
+        <v>20066</v>
       </c>
       <c r="G110">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H110">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I110">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="J110">
-        <v>0.66666666699999999</v>
+        <v>1</v>
       </c>
       <c r="K110">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L110">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M110">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="N110">
-        <v>0.66666666699999999</v>
+        <v>1</v>
       </c>
       <c r="O110" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>9923</v>
+        <v>10008</v>
       </c>
       <c r="B111">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C111">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D111" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E111" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F111">
-        <v>20130</v>
+        <v>20111</v>
       </c>
       <c r="G111">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="H111">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I111">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="J111">
-        <v>0.8</v>
+        <v>0.54054054100000004</v>
       </c>
       <c r="K111">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="L111">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="M111">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="N111">
-        <v>0.8</v>
+        <v>0.54054054100000004</v>
       </c>
       <c r="O111" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>9935</v>
+        <v>9898</v>
       </c>
       <c r="B112">
-        <v>502</v>
-      </c>
-      <c r="C112" t="s">
-        <v>77</v>
+        <v>332</v>
+      </c>
+      <c r="C112">
+        <v>332</v>
       </c>
       <c r="D112" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E112" s="1">
-        <v>46205</v>
+        <v>46203</v>
       </c>
       <c r="F112">
-        <v>20043</v>
+        <v>20130</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J112">
+        <v>0.8</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N112">
+        <v>0.8</v>
       </c>
       <c r="O112" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>9920</v>
+        <v>9910</v>
       </c>
       <c r="B113">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C113" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D113" s="1">
         <v>46205</v>
@@ -5709,139 +5691,133 @@
         <v>46204</v>
       </c>
       <c r="F113">
-        <v>20095</v>
+        <v>20153</v>
       </c>
       <c r="G113">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H113">
+        <v>27</v>
+      </c>
+      <c r="I113">
+        <v>-19</v>
+      </c>
+      <c r="J113">
+        <v>0.58695652200000004</v>
+      </c>
+      <c r="K113">
+        <v>46</v>
+      </c>
+      <c r="L113">
+        <v>27</v>
+      </c>
+      <c r="M113">
+        <v>-19</v>
+      </c>
+      <c r="N113">
+        <v>0.58695652200000004</v>
+      </c>
+      <c r="O113" t="s">
         <v>30</v>
-      </c>
-      <c r="I113">
-        <v>-14</v>
-      </c>
-      <c r="J113">
-        <v>0.68181818199999999</v>
-      </c>
-      <c r="K113">
-        <v>44</v>
-      </c>
-      <c r="L113">
-        <v>30</v>
-      </c>
-      <c r="M113">
-        <v>-14</v>
-      </c>
-      <c r="N113">
-        <v>0.68181818199999999</v>
-      </c>
-      <c r="O113" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>9909</v>
+        <v>9933</v>
       </c>
       <c r="B114">
-        <v>102</v>
+        <v>800</v>
       </c>
       <c r="C114" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D114" s="1">
         <v>46205</v>
       </c>
       <c r="E114" s="1">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="F114">
-        <v>20086</v>
+        <v>200150</v>
       </c>
       <c r="G114">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="H114">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I114">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="J114">
-        <v>0.87272727299999997</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="L114">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M114">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="N114">
-        <v>0.87272727299999997</v>
+        <v>0</v>
       </c>
       <c r="O114" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>9922</v>
+        <v>9936</v>
       </c>
       <c r="B115">
-        <v>131</v>
-      </c>
-      <c r="C115">
-        <v>131</v>
+        <v>800</v>
+      </c>
+      <c r="C115" t="s">
+        <v>62</v>
       </c>
       <c r="D115" s="1">
         <v>46205</v>
       </c>
       <c r="E115" s="1">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="F115">
-        <v>20005</v>
+        <v>200150</v>
       </c>
       <c r="G115">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I115">
-        <v>-5</v>
-      </c>
-      <c r="J115">
-        <v>0.76190476200000001</v>
+        <v>0</v>
       </c>
       <c r="K115">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L115">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M115">
-        <v>-5</v>
-      </c>
-      <c r="N115">
-        <v>0.76190476200000001</v>
+        <v>0</v>
       </c>
       <c r="O115" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>9934</v>
+        <v>9937</v>
       </c>
       <c r="B116">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="C116" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D116" s="1">
         <v>46205</v>
@@ -5850,7 +5826,7 @@
         <v>46205</v>
       </c>
       <c r="F116">
-        <v>20006</v>
+        <v>200150</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -5871,18 +5847,18 @@
         <v>0</v>
       </c>
       <c r="O116" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>9930</v>
+        <v>9921</v>
       </c>
       <c r="B117">
-        <v>140</v>
-      </c>
-      <c r="C117">
-        <v>140</v>
+        <v>114</v>
+      </c>
+      <c r="C117" t="s">
+        <v>50</v>
       </c>
       <c r="D117" s="1">
         <v>46205</v>
@@ -5891,45 +5867,45 @@
         <v>46204</v>
       </c>
       <c r="F117">
-        <v>20006</v>
+        <v>20048</v>
       </c>
       <c r="G117">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H117">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I117">
-        <v>-1</v>
+        <v>-28</v>
       </c>
       <c r="J117">
-        <v>0.96774193500000005</v>
+        <v>0</v>
       </c>
       <c r="K117">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="L117">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M117">
-        <v>-1</v>
+        <v>-28</v>
       </c>
       <c r="N117">
-        <v>0.96774193500000005</v>
+        <v>0</v>
       </c>
       <c r="O117" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>9908</v>
+        <v>9911</v>
       </c>
       <c r="B118">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C118" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D118" s="1">
         <v>46205</v>
@@ -5938,45 +5914,45 @@
         <v>46204</v>
       </c>
       <c r="F118">
-        <v>20076</v>
+        <v>20105</v>
       </c>
       <c r="G118">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="H118">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I118">
-        <v>-6</v>
+        <v>-17</v>
       </c>
       <c r="J118">
-        <v>0.85</v>
+        <v>0.68518518500000003</v>
       </c>
       <c r="K118">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="L118">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M118">
-        <v>-6</v>
+        <v>-17</v>
       </c>
       <c r="N118">
-        <v>0.85</v>
+        <v>0.68518518500000003</v>
       </c>
       <c r="O118" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>9913</v>
+        <v>9912</v>
       </c>
       <c r="B119">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C119" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D119" s="1">
         <v>46205</v>
@@ -5985,221 +5961,233 @@
         <v>46204</v>
       </c>
       <c r="F119">
-        <v>11215</v>
+        <v>20058</v>
       </c>
       <c r="G119">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H119">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I119">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="J119">
-        <v>0.52459016400000003</v>
+        <v>0.41666666699999999</v>
       </c>
       <c r="K119">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="L119">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="M119">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="N119">
-        <v>0.52459016400000003</v>
+        <v>0.41666666699999999</v>
       </c>
       <c r="O119" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>9902</v>
+        <v>9914</v>
       </c>
       <c r="B120">
-        <v>336</v>
-      </c>
-      <c r="C120">
-        <v>336</v>
+        <v>107</v>
+      </c>
+      <c r="C120" t="s">
+        <v>37</v>
       </c>
       <c r="D120" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E120" s="1">
         <v>46204</v>
       </c>
-      <c r="E120" s="1">
-        <v>46203</v>
-      </c>
       <c r="F120">
-        <v>20111</v>
+        <v>20155</v>
       </c>
       <c r="G120">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H120">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I120">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J120">
-        <v>0.73684210500000002</v>
+        <v>1</v>
       </c>
       <c r="K120">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L120">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M120">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="N120">
-        <v>0.73684210500000002</v>
+        <v>1</v>
       </c>
       <c r="O120" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>9904</v>
+        <v>9915</v>
       </c>
       <c r="B121">
-        <v>338</v>
-      </c>
-      <c r="C121">
-        <v>338</v>
+        <v>108</v>
+      </c>
+      <c r="C121" t="s">
+        <v>39</v>
       </c>
       <c r="D121" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E121" s="1">
         <v>46204</v>
       </c>
-      <c r="E121" s="1">
-        <v>46203</v>
-      </c>
       <c r="F121">
-        <v>20007</v>
+        <v>20057</v>
       </c>
       <c r="G121">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="H121">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="I121">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="J121">
-        <v>0.68181818199999999</v>
+        <v>0.87323943699999995</v>
       </c>
       <c r="K121">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="L121">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="M121">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="N121">
-        <v>0.68181818199999999</v>
+        <v>0.87323943699999995</v>
       </c>
       <c r="O121" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>9949</v>
+        <v>9916</v>
       </c>
       <c r="B122">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="C122" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="D122" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E122" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F122">
-        <v>200150</v>
+        <v>20112</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I122">
-        <v>0</v>
+        <v>-19</v>
+      </c>
+      <c r="J122">
+        <v>0.38709677399999998</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>-19</v>
+      </c>
+      <c r="N122">
+        <v>0.38709677399999998</v>
       </c>
       <c r="O122" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>9965</v>
+        <v>9917</v>
       </c>
       <c r="B123">
-        <v>502</v>
+        <v>110</v>
       </c>
       <c r="C123" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="D123" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E123" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F123">
-        <v>20086</v>
+        <v>20066</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I123">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="J123">
+        <v>0.60869565199999998</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L123">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M123">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="N123">
+        <v>0.60869565199999998</v>
       </c>
       <c r="O123" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>9925</v>
+        <v>9919</v>
       </c>
       <c r="B124">
-        <v>135</v>
-      </c>
-      <c r="C124">
-        <v>135</v>
+        <v>112</v>
+      </c>
+      <c r="C124" t="s">
+        <v>46</v>
       </c>
       <c r="D124" s="1">
         <v>46205</v>
@@ -6208,750 +6196,744 @@
         <v>46204</v>
       </c>
       <c r="F124">
-        <v>20113</v>
+        <v>20106</v>
       </c>
       <c r="G124">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="H124">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I124">
-        <v>-4</v>
+        <v>-37</v>
       </c>
       <c r="J124">
-        <v>0.75</v>
+        <v>0.26</v>
       </c>
       <c r="K124">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="L124">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M124">
-        <v>-4</v>
+        <v>-37</v>
       </c>
       <c r="N124">
-        <v>0.75</v>
+        <v>0.26</v>
       </c>
       <c r="O124" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>9938</v>
+        <v>9924</v>
       </c>
       <c r="B125">
-        <v>201</v>
-      </c>
-      <c r="C125" t="s">
-        <v>80</v>
+        <v>133</v>
+      </c>
+      <c r="C125">
+        <v>133</v>
       </c>
       <c r="D125" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E125" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F125">
-        <v>20155</v>
+        <v>200158</v>
       </c>
       <c r="G125">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H125">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I125">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="J125">
-        <v>0.89473684200000003</v>
+        <v>1</v>
       </c>
       <c r="K125">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L125">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M125">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="N125">
-        <v>0.89473684200000003</v>
+        <v>1</v>
       </c>
       <c r="O125" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>9939</v>
+        <v>9927</v>
       </c>
       <c r="B126">
-        <v>202</v>
-      </c>
-      <c r="C126" t="s">
-        <v>81</v>
+        <v>137</v>
+      </c>
+      <c r="C126">
+        <v>137</v>
       </c>
       <c r="D126" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E126" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F126">
-        <v>20057</v>
+        <v>20003</v>
       </c>
       <c r="G126">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H126">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="I126">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J126">
-        <v>0.95454545499999999</v>
+        <v>0.70588235300000002</v>
       </c>
       <c r="K126">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L126">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="M126">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="N126">
-        <v>0.95454545499999999</v>
+        <v>0.70588235300000002</v>
       </c>
       <c r="O126" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>9940</v>
+        <v>9928</v>
       </c>
       <c r="B127">
-        <v>203</v>
-      </c>
-      <c r="C127" t="s">
-        <v>82</v>
+        <v>138</v>
+      </c>
+      <c r="C127">
+        <v>138</v>
       </c>
       <c r="D127" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E127" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F127">
-        <v>20086</v>
+        <v>20007</v>
       </c>
       <c r="G127">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H127">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I127">
         <v>-9</v>
       </c>
       <c r="J127">
-        <v>0.76315789499999998</v>
+        <v>0.70967741900000003</v>
       </c>
       <c r="K127">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L127">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M127">
         <v>-9</v>
       </c>
       <c r="N127">
-        <v>0.76315789499999998</v>
+        <v>0.70967741900000003</v>
       </c>
       <c r="O127" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>9941</v>
+        <v>9929</v>
       </c>
       <c r="B128">
-        <v>204</v>
-      </c>
-      <c r="C128" t="s">
-        <v>83</v>
+        <v>139</v>
+      </c>
+      <c r="C128">
+        <v>139</v>
       </c>
       <c r="D128" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E128" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F128">
-        <v>20058</v>
+        <v>20008</v>
       </c>
       <c r="G128">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="H128">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I128">
-        <v>-39</v>
+        <v>-6</v>
       </c>
       <c r="J128">
-        <v>0.409090909</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K128">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="L128">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="M128">
-        <v>-39</v>
+        <v>-6</v>
       </c>
       <c r="N128">
-        <v>0.409090909</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O128" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>9987</v>
+        <v>9923</v>
       </c>
       <c r="B129">
-        <v>312</v>
-      </c>
-      <c r="C129" t="s">
-        <v>52</v>
+        <v>132</v>
+      </c>
+      <c r="C129">
+        <v>132</v>
       </c>
       <c r="D129" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E129" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F129">
-        <v>20086</v>
+        <v>20130</v>
       </c>
       <c r="G129">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H129">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I129">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="J129">
-        <v>1.095238095</v>
+        <v>0.8</v>
       </c>
       <c r="K129">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L129">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M129">
-        <v>-21</v>
+        <v>-2</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O129" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>9944</v>
+        <v>9935</v>
       </c>
       <c r="B130">
-        <v>207</v>
+        <v>502</v>
       </c>
       <c r="C130" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D130" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E130" s="1">
         <v>46205</v>
       </c>
       <c r="F130">
-        <v>20105</v>
+        <v>20043</v>
       </c>
       <c r="G130">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I130">
-        <v>-1</v>
-      </c>
-      <c r="J130">
-        <v>0.96969696999999999</v>
+        <v>0</v>
       </c>
       <c r="K130">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L130">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M130">
-        <v>-1</v>
-      </c>
-      <c r="N130">
-        <v>0.96969696999999999</v>
+        <v>0</v>
       </c>
       <c r="O130" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>9945</v>
+        <v>9920</v>
       </c>
       <c r="B131">
-        <v>208</v>
+        <v>113</v>
       </c>
       <c r="C131" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="D131" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E131" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F131">
-        <v>20076</v>
+        <v>20095</v>
       </c>
       <c r="G131">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H131">
         <v>30</v>
       </c>
       <c r="I131">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="J131">
-        <v>0.76923076899999998</v>
+        <v>0.68181818199999999</v>
       </c>
       <c r="K131">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L131">
         <v>30</v>
       </c>
       <c r="M131">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="N131">
-        <v>0.76923076899999998</v>
+        <v>0.68181818199999999</v>
       </c>
       <c r="O131" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>9947</v>
+        <v>9909</v>
       </c>
       <c r="B132">
-        <v>213</v>
+        <v>102</v>
       </c>
       <c r="C132" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="D132" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E132" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F132">
-        <v>20066</v>
+        <v>20086</v>
       </c>
       <c r="G132">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H132">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I132">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="J132">
-        <v>0.75</v>
+        <v>0.87272727299999997</v>
       </c>
       <c r="K132">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="L132">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M132">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="N132">
-        <v>0.75</v>
+        <v>0.87272727299999997</v>
       </c>
       <c r="O132" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>9960</v>
+        <v>9922</v>
       </c>
       <c r="B133">
-        <v>240</v>
+        <v>131</v>
       </c>
       <c r="C133">
-        <v>240</v>
+        <v>131</v>
       </c>
       <c r="D133" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E133" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F133">
-        <v>20006</v>
+        <v>20005</v>
       </c>
       <c r="G133">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H133">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I133">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J133">
-        <v>0.92592592600000001</v>
+        <v>0.76190476200000001</v>
       </c>
       <c r="K133">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L133">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M133">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="N133">
-        <v>0.92592592600000001</v>
+        <v>0.76190476200000001</v>
       </c>
       <c r="O133" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>9957</v>
+        <v>9934</v>
       </c>
       <c r="B134">
-        <v>237</v>
-      </c>
-      <c r="C134">
-        <v>237</v>
+        <v>500</v>
+      </c>
+      <c r="C134" t="s">
+        <v>78</v>
       </c>
       <c r="D134" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E134" s="1">
         <v>46205</v>
       </c>
       <c r="F134">
-        <v>20003</v>
+        <v>20006</v>
       </c>
       <c r="G134">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H134">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I134">
-        <v>-17</v>
-      </c>
-      <c r="J134">
-        <v>0.59523809500000002</v>
+        <v>0</v>
       </c>
       <c r="K134">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L134">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M134">
-        <v>-17</v>
-      </c>
-      <c r="N134">
-        <v>0.59523809500000002</v>
+        <v>0</v>
       </c>
       <c r="O134" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>9994</v>
+        <v>9930</v>
       </c>
       <c r="B135">
-        <v>319</v>
-      </c>
-      <c r="C135" t="s">
-        <v>92</v>
+        <v>140</v>
+      </c>
+      <c r="C135">
+        <v>140</v>
       </c>
       <c r="D135" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="E135" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F135">
-        <v>11215</v>
+        <v>20006</v>
       </c>
       <c r="G135">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H135">
+        <v>30</v>
+      </c>
+      <c r="I135">
+        <v>-1</v>
+      </c>
+      <c r="J135">
+        <v>0.96774193500000005</v>
+      </c>
+      <c r="K135">
+        <v>31</v>
+      </c>
+      <c r="L135">
+        <v>30</v>
+      </c>
+      <c r="M135">
+        <v>-1</v>
+      </c>
+      <c r="N135">
+        <v>0.96774193500000005</v>
+      </c>
+      <c r="O135" t="s">
         <v>16</v>
-      </c>
-      <c r="I135">
-        <v>-5</v>
-      </c>
-      <c r="J135">
-        <v>0.76190476200000001</v>
-      </c>
-      <c r="K135">
-        <v>21</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>-21</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>9992</v>
+        <v>9908</v>
       </c>
       <c r="B136">
-        <v>317</v>
+        <v>101</v>
       </c>
       <c r="C136" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="D136" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="E136" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F136">
-        <v>20043</v>
+        <v>20076</v>
       </c>
       <c r="G136">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H136">
+        <v>34</v>
+      </c>
+      <c r="I136">
+        <v>-6</v>
+      </c>
+      <c r="J136">
+        <v>0.85</v>
+      </c>
+      <c r="K136">
+        <v>40</v>
+      </c>
+      <c r="L136">
+        <v>34</v>
+      </c>
+      <c r="M136">
+        <v>-6</v>
+      </c>
+      <c r="N136">
+        <v>0.85</v>
+      </c>
+      <c r="O136" t="s">
         <v>20</v>
-      </c>
-      <c r="I136">
-        <v>-1</v>
-      </c>
-      <c r="J136">
-        <v>0.95238095199999995</v>
-      </c>
-      <c r="K136">
-        <v>21</v>
-      </c>
-      <c r="L136">
-        <v>20</v>
-      </c>
-      <c r="M136">
-        <v>-1</v>
-      </c>
-      <c r="N136">
-        <v>0.95238095199999995</v>
-      </c>
-      <c r="O136" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>9969</v>
+        <v>9913</v>
       </c>
       <c r="B137">
-        <v>332</v>
-      </c>
-      <c r="C137">
-        <v>332</v>
+        <v>106</v>
+      </c>
+      <c r="C137" t="s">
+        <v>35</v>
       </c>
       <c r="D137" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="E137" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F137">
-        <v>20130</v>
+        <v>11215</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I137">
-        <v>0</v>
+        <v>-29</v>
+      </c>
+      <c r="J137">
+        <v>0.52459016400000003</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L137">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M137">
-        <v>0</v>
+        <v>-29</v>
+      </c>
+      <c r="N137">
+        <v>0.52459016400000003</v>
       </c>
       <c r="O137" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>9977</v>
+        <v>9902</v>
       </c>
       <c r="B138">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C138">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D138" s="1">
-        <v>46207</v>
+        <v>46204</v>
       </c>
       <c r="E138" s="1">
-        <v>46206</v>
+        <v>46203</v>
       </c>
       <c r="F138">
-        <v>20005</v>
+        <v>20111</v>
       </c>
       <c r="G138">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H138">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I138">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="J138">
-        <v>1.043478261</v>
+        <v>0.73684210500000002</v>
       </c>
       <c r="K138">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L138">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="M138">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="N138">
-        <v>1.043478261</v>
+        <v>0.73684210500000002</v>
       </c>
       <c r="O138" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>9997</v>
+        <v>9904</v>
       </c>
       <c r="B139">
-        <v>323</v>
-      </c>
-      <c r="C139" t="s">
-        <v>93</v>
+        <v>338</v>
+      </c>
+      <c r="C139">
+        <v>338</v>
       </c>
       <c r="D139" s="1">
-        <v>46207</v>
+        <v>46204</v>
       </c>
       <c r="E139" s="1">
-        <v>46206</v>
+        <v>46203</v>
       </c>
       <c r="F139">
-        <v>20076</v>
+        <v>20007</v>
       </c>
       <c r="G139">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H139">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="J139">
-        <v>1</v>
+        <v>0.68181818199999999</v>
       </c>
       <c r="K139">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="L139">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="M139">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="N139">
-        <v>1</v>
+        <v>0.68181818199999999</v>
       </c>
       <c r="O139" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>10014</v>
+        <v>9949</v>
       </c>
       <c r="B140">
-        <v>800</v>
+        <v>215</v>
       </c>
       <c r="C140" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D140" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="E140" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="F140">
         <v>200150</v>
@@ -6980,101 +6962,101 @@
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>10010</v>
+        <v>9965</v>
       </c>
       <c r="B141">
-        <v>138</v>
-      </c>
-      <c r="C141">
-        <v>138</v>
+        <v>502</v>
+      </c>
+      <c r="C141" t="s">
+        <v>77</v>
       </c>
       <c r="D141" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="E141" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="F141">
-        <v>20007</v>
+        <v>20086</v>
       </c>
       <c r="G141">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H141">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I141">
-        <v>-10</v>
-      </c>
-      <c r="J141">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="K141">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L141">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M141">
-        <v>-10</v>
-      </c>
-      <c r="N141">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="O141" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>9962</v>
+        <v>9925</v>
       </c>
       <c r="B142">
-        <v>504</v>
-      </c>
-      <c r="C142" t="s">
-        <v>76</v>
+        <v>135</v>
+      </c>
+      <c r="C142">
+        <v>135</v>
       </c>
       <c r="D142" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E142" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F142">
-        <v>200150</v>
+        <v>20113</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I142">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J142">
+        <v>0.75</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L142">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M142">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N142">
+        <v>0.75</v>
       </c>
       <c r="O142" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>9956</v>
+        <v>9938</v>
       </c>
       <c r="B143">
-        <v>236</v>
-      </c>
-      <c r="C143">
-        <v>236</v>
+        <v>201</v>
+      </c>
+      <c r="C143" t="s">
+        <v>80</v>
       </c>
       <c r="D143" s="1">
         <v>46206</v>
@@ -7083,45 +7065,45 @@
         <v>46205</v>
       </c>
       <c r="F143">
-        <v>20111</v>
+        <v>20155</v>
       </c>
       <c r="G143">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H143">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I143">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="J143">
-        <v>0.72413793100000001</v>
+        <v>0.89473684200000003</v>
       </c>
       <c r="K143">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L143">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="M143">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="N143">
-        <v>0.72413793100000001</v>
+        <v>0.89473684200000003</v>
       </c>
       <c r="O143" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>9954</v>
+        <v>9939</v>
       </c>
       <c r="B144">
-        <v>234</v>
-      </c>
-      <c r="C144">
-        <v>234</v>
+        <v>202</v>
+      </c>
+      <c r="C144" t="s">
+        <v>81</v>
       </c>
       <c r="D144" s="1">
         <v>46206</v>
@@ -7130,45 +7112,45 @@
         <v>46205</v>
       </c>
       <c r="F144">
-        <v>20112</v>
+        <v>20057</v>
       </c>
       <c r="G144">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H144">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I144">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="J144">
-        <v>0.71428571399999996</v>
+        <v>0.95454545499999999</v>
       </c>
       <c r="K144">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L144">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="M144">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="N144">
-        <v>0.71428571399999996</v>
+        <v>0.95454545499999999</v>
       </c>
       <c r="O144" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>9948</v>
+        <v>9940</v>
       </c>
       <c r="B145">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="C145" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D145" s="1">
         <v>46206</v>
@@ -7177,80 +7159,92 @@
         <v>46205</v>
       </c>
       <c r="F145">
-        <v>11215</v>
+        <v>20086</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H145">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="I145">
-        <v>1</v>
+        <v>-9</v>
+      </c>
+      <c r="J145">
+        <v>0.76315789499999998</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L145">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M145">
-        <v>1</v>
+        <v>-9</v>
+      </c>
+      <c r="N145">
+        <v>0.76315789499999998</v>
       </c>
       <c r="O145" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>9970</v>
+        <v>9941</v>
       </c>
       <c r="B146">
-        <v>333</v>
-      </c>
-      <c r="C146">
-        <v>333</v>
+        <v>204</v>
+      </c>
+      <c r="C146" t="s">
+        <v>83</v>
       </c>
       <c r="D146" s="1">
         <v>46206</v>
       </c>
       <c r="E146" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F146">
-        <v>200158</v>
+        <v>20058</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>-39</v>
+      </c>
+      <c r="J146">
+        <v>0.409090909</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L146">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M146">
-        <v>0</v>
+        <v>-39</v>
+      </c>
+      <c r="N146">
+        <v>0.409090909</v>
       </c>
       <c r="O146" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>9971</v>
+        <v>9987</v>
       </c>
       <c r="B147">
-        <v>334</v>
-      </c>
-      <c r="C147">
-        <v>334</v>
+        <v>312</v>
+      </c>
+      <c r="C147" t="s">
+        <v>52</v>
       </c>
       <c r="D147" s="1">
         <v>46206</v>
@@ -7259,180 +7253,1268 @@
         <v>46206</v>
       </c>
       <c r="F147">
-        <v>20007</v>
+        <v>20086</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I147">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J147">
+        <v>1.095238095</v>
       </c>
       <c r="K147">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L147">
         <v>0</v>
       </c>
       <c r="M147">
+        <v>-21</v>
+      </c>
+      <c r="N147">
         <v>0</v>
       </c>
       <c r="O147" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>10001</v>
+        <v>9944</v>
       </c>
       <c r="B148">
-        <v>500</v>
+        <v>207</v>
       </c>
       <c r="C148" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D148" s="1">
         <v>46206</v>
       </c>
       <c r="E148" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F148">
+        <v>20105</v>
+      </c>
+      <c r="G148">
+        <v>33</v>
+      </c>
+      <c r="H148">
+        <v>32</v>
+      </c>
+      <c r="I148">
+        <v>-1</v>
+      </c>
+      <c r="J148">
+        <v>0.96969696999999999</v>
+      </c>
+      <c r="K148">
+        <v>33</v>
+      </c>
+      <c r="L148">
+        <v>32</v>
+      </c>
+      <c r="M148">
+        <v>-1</v>
+      </c>
+      <c r="N148">
+        <v>0.96969696999999999</v>
+      </c>
+      <c r="O148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>9945</v>
+      </c>
+      <c r="B149">
+        <v>208</v>
+      </c>
+      <c r="C149" t="s">
+        <v>85</v>
+      </c>
+      <c r="D149" s="1">
         <v>46206</v>
       </c>
-      <c r="F148">
+      <c r="E149" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F149">
+        <v>20076</v>
+      </c>
+      <c r="G149">
+        <v>39</v>
+      </c>
+      <c r="H149">
+        <v>30</v>
+      </c>
+      <c r="I149">
+        <v>-9</v>
+      </c>
+      <c r="J149">
+        <v>0.76923076899999998</v>
+      </c>
+      <c r="K149">
+        <v>39</v>
+      </c>
+      <c r="L149">
+        <v>30</v>
+      </c>
+      <c r="M149">
+        <v>-9</v>
+      </c>
+      <c r="N149">
+        <v>0.76923076899999998</v>
+      </c>
+      <c r="O149" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>9947</v>
+      </c>
+      <c r="B150">
+        <v>213</v>
+      </c>
+      <c r="C150" t="s">
+        <v>86</v>
+      </c>
+      <c r="D150" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E150" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F150">
+        <v>20066</v>
+      </c>
+      <c r="G150">
+        <v>60</v>
+      </c>
+      <c r="H150">
+        <v>45</v>
+      </c>
+      <c r="I150">
+        <v>-15</v>
+      </c>
+      <c r="J150">
+        <v>0.75</v>
+      </c>
+      <c r="K150">
+        <v>60</v>
+      </c>
+      <c r="L150">
+        <v>45</v>
+      </c>
+      <c r="M150">
+        <v>-15</v>
+      </c>
+      <c r="N150">
+        <v>0.75</v>
+      </c>
+      <c r="O150" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>9960</v>
+      </c>
+      <c r="B151">
+        <v>240</v>
+      </c>
+      <c r="C151">
+        <v>240</v>
+      </c>
+      <c r="D151" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E151" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F151">
+        <v>20006</v>
+      </c>
+      <c r="G151">
+        <v>27</v>
+      </c>
+      <c r="H151">
+        <v>25</v>
+      </c>
+      <c r="I151">
+        <v>-2</v>
+      </c>
+      <c r="J151">
+        <v>0.92592592600000001</v>
+      </c>
+      <c r="K151">
+        <v>27</v>
+      </c>
+      <c r="L151">
+        <v>25</v>
+      </c>
+      <c r="M151">
+        <v>-2</v>
+      </c>
+      <c r="N151">
+        <v>0.92592592600000001</v>
+      </c>
+      <c r="O151" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>9957</v>
+      </c>
+      <c r="B152">
+        <v>237</v>
+      </c>
+      <c r="C152">
+        <v>237</v>
+      </c>
+      <c r="D152" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E152" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F152">
+        <v>20003</v>
+      </c>
+      <c r="G152">
+        <v>42</v>
+      </c>
+      <c r="H152">
+        <v>25</v>
+      </c>
+      <c r="I152">
+        <v>-17</v>
+      </c>
+      <c r="J152">
+        <v>0.59523809500000002</v>
+      </c>
+      <c r="K152">
+        <v>42</v>
+      </c>
+      <c r="L152">
+        <v>25</v>
+      </c>
+      <c r="M152">
+        <v>-17</v>
+      </c>
+      <c r="N152">
+        <v>0.59523809500000002</v>
+      </c>
+      <c r="O152" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>9994</v>
+      </c>
+      <c r="B153">
+        <v>319</v>
+      </c>
+      <c r="C153" t="s">
+        <v>92</v>
+      </c>
+      <c r="D153" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E153" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F153">
+        <v>11215</v>
+      </c>
+      <c r="G153">
+        <v>21</v>
+      </c>
+      <c r="H153">
+        <v>16</v>
+      </c>
+      <c r="I153">
+        <v>-5</v>
+      </c>
+      <c r="J153">
+        <v>0.76190476200000001</v>
+      </c>
+      <c r="K153">
+        <v>21</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>-21</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>9992</v>
+      </c>
+      <c r="B154">
+        <v>317</v>
+      </c>
+      <c r="C154" t="s">
+        <v>90</v>
+      </c>
+      <c r="D154" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E154" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F154">
+        <v>20043</v>
+      </c>
+      <c r="G154">
+        <v>21</v>
+      </c>
+      <c r="H154">
+        <v>20</v>
+      </c>
+      <c r="I154">
+        <v>-1</v>
+      </c>
+      <c r="J154">
+        <v>0.95238095199999995</v>
+      </c>
+      <c r="K154">
+        <v>21</v>
+      </c>
+      <c r="L154">
+        <v>20</v>
+      </c>
+      <c r="M154">
+        <v>-1</v>
+      </c>
+      <c r="N154">
+        <v>0.95238095199999995</v>
+      </c>
+      <c r="O154" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>9969</v>
+      </c>
+      <c r="B155">
+        <v>332</v>
+      </c>
+      <c r="C155">
+        <v>332</v>
+      </c>
+      <c r="D155" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E155" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F155">
+        <v>20130</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="O155" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>9977</v>
+      </c>
+      <c r="B156">
+        <v>340</v>
+      </c>
+      <c r="C156">
+        <v>340</v>
+      </c>
+      <c r="D156" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E156" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F156">
+        <v>20005</v>
+      </c>
+      <c r="G156">
+        <v>23</v>
+      </c>
+      <c r="H156">
+        <v>24</v>
+      </c>
+      <c r="I156">
+        <v>1</v>
+      </c>
+      <c r="J156">
+        <v>1.043478261</v>
+      </c>
+      <c r="K156">
+        <v>23</v>
+      </c>
+      <c r="L156">
+        <v>24</v>
+      </c>
+      <c r="M156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>1.043478261</v>
+      </c>
+      <c r="O156" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>9997</v>
+      </c>
+      <c r="B157">
+        <v>323</v>
+      </c>
+      <c r="C157" t="s">
+        <v>93</v>
+      </c>
+      <c r="D157" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E157" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F157">
+        <v>20076</v>
+      </c>
+      <c r="G157">
+        <v>32</v>
+      </c>
+      <c r="H157">
+        <v>32</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>32</v>
+      </c>
+      <c r="L157">
+        <v>32</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>1</v>
+      </c>
+      <c r="O157" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>10014</v>
+      </c>
+      <c r="B158">
+        <v>800</v>
+      </c>
+      <c r="C158" t="s">
+        <v>62</v>
+      </c>
+      <c r="D158" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E158" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F158">
+        <v>200150</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="O158" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>10010</v>
+      </c>
+      <c r="B159">
+        <v>138</v>
+      </c>
+      <c r="C159">
+        <v>138</v>
+      </c>
+      <c r="D159" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E159" s="1">
+        <v>46207</v>
+      </c>
+      <c r="F159">
+        <v>20007</v>
+      </c>
+      <c r="G159">
+        <v>32</v>
+      </c>
+      <c r="H159">
+        <v>22</v>
+      </c>
+      <c r="I159">
+        <v>-10</v>
+      </c>
+      <c r="J159">
+        <v>0.6875</v>
+      </c>
+      <c r="K159">
+        <v>32</v>
+      </c>
+      <c r="L159">
+        <v>22</v>
+      </c>
+      <c r="M159">
+        <v>-10</v>
+      </c>
+      <c r="N159">
+        <v>0.6875</v>
+      </c>
+      <c r="O159" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>9962</v>
+      </c>
+      <c r="B160">
+        <v>504</v>
+      </c>
+      <c r="C160" t="s">
+        <v>76</v>
+      </c>
+      <c r="D160" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E160" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F160">
+        <v>200150</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="O160" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>9956</v>
+      </c>
+      <c r="B161">
+        <v>236</v>
+      </c>
+      <c r="C161">
+        <v>236</v>
+      </c>
+      <c r="D161" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E161" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F161">
         <v>20111</v>
       </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
-        <v>0</v>
-      </c>
-      <c r="I148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148">
-        <v>0</v>
-      </c>
-      <c r="O148" t="s">
+      <c r="G161">
+        <v>29</v>
+      </c>
+      <c r="H161">
+        <v>21</v>
+      </c>
+      <c r="I161">
+        <v>-8</v>
+      </c>
+      <c r="J161">
+        <v>0.72413793100000001</v>
+      </c>
+      <c r="K161">
+        <v>29</v>
+      </c>
+      <c r="L161">
+        <v>21</v>
+      </c>
+      <c r="M161">
+        <v>-8</v>
+      </c>
+      <c r="N161">
+        <v>0.72413793100000001</v>
+      </c>
+      <c r="O161" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D149" s="1"/>
-      <c r="E149" s="1"/>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D150" s="1"/>
-      <c r="E150" s="1"/>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D151" s="1"/>
-      <c r="E151" s="1"/>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D152" s="1"/>
-      <c r="E152" s="1"/>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D153" s="1"/>
-      <c r="E153" s="1"/>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D154" s="1"/>
-      <c r="E154" s="1"/>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D155" s="1"/>
-      <c r="E155" s="1"/>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D156" s="1"/>
-      <c r="E156" s="1"/>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D157" s="1"/>
-      <c r="E157" s="1"/>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D158" s="1"/>
-      <c r="E158" s="1"/>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D159" s="1"/>
-      <c r="E159" s="1"/>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D160" s="1"/>
-      <c r="E160" s="1"/>
-    </row>
-    <row r="161" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D161" s="1"/>
-      <c r="E161" s="1"/>
-    </row>
-    <row r="162" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D162" s="1"/>
-      <c r="E162" s="1"/>
-    </row>
-    <row r="163" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D163" s="1"/>
-      <c r="E163" s="1"/>
-    </row>
-    <row r="164" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D164" s="1"/>
-      <c r="E164" s="1"/>
-    </row>
-    <row r="165" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D165" s="1"/>
-      <c r="E165" s="1"/>
-    </row>
-    <row r="166" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D166" s="1"/>
-      <c r="E166" s="1"/>
-    </row>
-    <row r="167" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D167" s="1"/>
-      <c r="E167" s="1"/>
-    </row>
-    <row r="168" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D168" s="1"/>
-      <c r="E168" s="1"/>
-    </row>
-    <row r="169" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D169" s="1"/>
-      <c r="E169" s="1"/>
-    </row>
-    <row r="170" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D170" s="1"/>
-      <c r="E170" s="1"/>
-    </row>
-    <row r="171" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D171" s="1"/>
-      <c r="E171" s="1"/>
-    </row>
-    <row r="172" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D172" s="1"/>
-      <c r="E172" s="1"/>
-    </row>
-    <row r="173" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D173" s="1"/>
-      <c r="E173" s="1"/>
-    </row>
-    <row r="174" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D174" s="1"/>
-      <c r="E174" s="1"/>
-    </row>
-    <row r="175" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>9954</v>
+      </c>
+      <c r="B162">
+        <v>234</v>
+      </c>
+      <c r="C162">
+        <v>234</v>
+      </c>
+      <c r="D162" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E162" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F162">
+        <v>20112</v>
+      </c>
+      <c r="G162">
+        <v>28</v>
+      </c>
+      <c r="H162">
+        <v>20</v>
+      </c>
+      <c r="I162">
+        <v>-8</v>
+      </c>
+      <c r="J162">
+        <v>0.71428571399999996</v>
+      </c>
+      <c r="K162">
+        <v>28</v>
+      </c>
+      <c r="L162">
+        <v>20</v>
+      </c>
+      <c r="M162">
+        <v>-8</v>
+      </c>
+      <c r="N162">
+        <v>0.71428571399999996</v>
+      </c>
+      <c r="O162" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>9948</v>
+      </c>
+      <c r="B163">
+        <v>214</v>
+      </c>
+      <c r="C163" t="s">
+        <v>87</v>
+      </c>
+      <c r="D163" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E163" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F163">
+        <v>11215</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>1</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="O163" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>10012</v>
+      </c>
+      <c r="B164">
+        <v>140</v>
+      </c>
+      <c r="C164">
+        <v>140</v>
+      </c>
+      <c r="D164" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E164" s="1">
+        <v>46207</v>
+      </c>
+      <c r="F164">
+        <v>20006</v>
+      </c>
+      <c r="G164">
+        <v>14</v>
+      </c>
+      <c r="H164">
+        <v>11</v>
+      </c>
+      <c r="I164">
+        <v>-3</v>
+      </c>
+      <c r="J164">
+        <v>0.78571428600000004</v>
+      </c>
+      <c r="K164">
+        <v>14</v>
+      </c>
+      <c r="L164">
+        <v>11</v>
+      </c>
+      <c r="M164">
+        <v>-3</v>
+      </c>
+      <c r="N164">
+        <v>0.78571428600000004</v>
+      </c>
+      <c r="O164" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>10016</v>
+      </c>
+      <c r="B165">
+        <v>201</v>
+      </c>
+      <c r="C165" t="s">
+        <v>80</v>
+      </c>
+      <c r="D165" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E165" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F165">
+        <v>20153</v>
+      </c>
+      <c r="G165">
+        <v>51</v>
+      </c>
+      <c r="H165">
+        <v>36</v>
+      </c>
+      <c r="I165">
+        <v>-15</v>
+      </c>
+      <c r="J165">
+        <v>0.70588235300000002</v>
+      </c>
+      <c r="K165">
+        <v>51</v>
+      </c>
+      <c r="L165">
+        <v>36</v>
+      </c>
+      <c r="M165">
+        <v>-15</v>
+      </c>
+      <c r="N165">
+        <v>0.70588235300000002</v>
+      </c>
+      <c r="O165" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>10018</v>
+      </c>
+      <c r="B166">
+        <v>203</v>
+      </c>
+      <c r="C166" t="s">
+        <v>82</v>
+      </c>
+      <c r="D166" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E166" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F166">
+        <v>20155</v>
+      </c>
+      <c r="G166">
+        <v>26</v>
+      </c>
+      <c r="H166">
+        <v>15</v>
+      </c>
+      <c r="I166">
+        <v>-11</v>
+      </c>
+      <c r="J166">
+        <v>0.57692307700000001</v>
+      </c>
+      <c r="K166">
+        <v>26</v>
+      </c>
+      <c r="L166">
+        <v>15</v>
+      </c>
+      <c r="M166">
+        <v>-11</v>
+      </c>
+      <c r="N166">
+        <v>0.57692307700000001</v>
+      </c>
+      <c r="O166" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>10019</v>
+      </c>
+      <c r="B167">
+        <v>204</v>
+      </c>
+      <c r="C167" t="s">
+        <v>83</v>
+      </c>
+      <c r="D167" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E167" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F167">
+        <v>20095</v>
+      </c>
+      <c r="G167">
+        <v>58</v>
+      </c>
+      <c r="H167">
+        <v>37</v>
+      </c>
+      <c r="I167">
+        <v>-21</v>
+      </c>
+      <c r="J167">
+        <v>0.63793103399999995</v>
+      </c>
+      <c r="K167">
+        <v>58</v>
+      </c>
+      <c r="L167">
+        <v>37</v>
+      </c>
+      <c r="M167">
+        <v>-21</v>
+      </c>
+      <c r="N167">
+        <v>0.63793103399999995</v>
+      </c>
+      <c r="O167" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>10023</v>
+      </c>
+      <c r="B168">
+        <v>208</v>
+      </c>
+      <c r="C168" t="s">
+        <v>85</v>
+      </c>
+      <c r="D168" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E168" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F168">
+        <v>11215</v>
+      </c>
+      <c r="G168">
+        <v>46</v>
+      </c>
+      <c r="H168">
+        <v>34</v>
+      </c>
+      <c r="I168">
+        <v>-12</v>
+      </c>
+      <c r="J168">
+        <v>0.73913043499999997</v>
+      </c>
+      <c r="K168">
+        <v>46</v>
+      </c>
+      <c r="L168">
+        <v>34</v>
+      </c>
+      <c r="M168">
+        <v>-12</v>
+      </c>
+      <c r="N168">
+        <v>0.73913043499999997</v>
+      </c>
+      <c r="O168" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>10025</v>
+      </c>
+      <c r="B169">
+        <v>210</v>
+      </c>
+      <c r="C169" t="s">
+        <v>97</v>
+      </c>
+      <c r="D169" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E169" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F169">
+        <v>20066</v>
+      </c>
+      <c r="G169">
+        <v>25</v>
+      </c>
+      <c r="H169">
+        <v>13</v>
+      </c>
+      <c r="I169">
+        <v>-12</v>
+      </c>
+      <c r="J169">
+        <v>0.52</v>
+      </c>
+      <c r="K169">
+        <v>25</v>
+      </c>
+      <c r="L169">
+        <v>13</v>
+      </c>
+      <c r="M169">
+        <v>-12</v>
+      </c>
+      <c r="N169">
+        <v>0.52</v>
+      </c>
+      <c r="O169" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>10024</v>
+      </c>
+      <c r="B170">
+        <v>209</v>
+      </c>
+      <c r="C170" t="s">
+        <v>96</v>
+      </c>
+      <c r="D170" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E170" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F170">
+        <v>20105</v>
+      </c>
+      <c r="G170">
+        <v>42</v>
+      </c>
+      <c r="H170">
+        <v>35</v>
+      </c>
+      <c r="I170">
+        <v>-7</v>
+      </c>
+      <c r="J170">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K170">
+        <v>42</v>
+      </c>
+      <c r="L170">
+        <v>35</v>
+      </c>
+      <c r="M170">
+        <v>-7</v>
+      </c>
+      <c r="N170">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O170" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>10026</v>
+      </c>
+      <c r="B171">
+        <v>211</v>
+      </c>
+      <c r="C171" t="s">
+        <v>98</v>
+      </c>
+      <c r="D171" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E171" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F171">
+        <v>20058</v>
+      </c>
+      <c r="G171">
+        <v>62</v>
+      </c>
+      <c r="H171">
+        <v>23</v>
+      </c>
+      <c r="I171">
+        <v>-39</v>
+      </c>
+      <c r="J171">
+        <v>0.37096774199999999</v>
+      </c>
+      <c r="K171">
+        <v>62</v>
+      </c>
+      <c r="L171">
+        <v>23</v>
+      </c>
+      <c r="M171">
+        <v>-39</v>
+      </c>
+      <c r="N171">
+        <v>0.37096774199999999</v>
+      </c>
+      <c r="O171" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>9970</v>
+      </c>
+      <c r="B172">
+        <v>333</v>
+      </c>
+      <c r="C172">
+        <v>333</v>
+      </c>
+      <c r="D172" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E172" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F172">
+        <v>200158</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="O172" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>9971</v>
+      </c>
+      <c r="B173">
+        <v>334</v>
+      </c>
+      <c r="C173">
+        <v>334</v>
+      </c>
+      <c r="D173" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E173" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F173">
+        <v>20007</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="O173" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>10001</v>
+      </c>
+      <c r="B174">
+        <v>500</v>
+      </c>
+      <c r="C174" t="s">
+        <v>78</v>
+      </c>
+      <c r="D174" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E174" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F174">
+        <v>20111</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>0</v>
+      </c>
+      <c r="O174" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
     </row>
-    <row r="176" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
     </row>

--- a/data/cartones.xlsx
+++ b/data/cartones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFB8BEC-5219-420E-88F7-464BA5C9A6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EC6B20-10C3-4AD8-B9ED-50AA47C2986A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF2EE928-F73E-4AAC-BA22-2F9F659AC8B2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="106">
   <si>
     <t>codigo</t>
   </si>
@@ -337,6 +337,21 @@
   </si>
   <si>
     <t>322 CAM 22 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>221 CAM 21 MARTES</t>
+  </si>
+  <si>
+    <t>222 CAM 22 MARTES</t>
+  </si>
+  <si>
+    <t>223 CAM 23 MARTES</t>
+  </si>
+  <si>
+    <t>224 CAM 24 MARTES</t>
+  </si>
+  <si>
+    <t>225 CAM 25 MARTES</t>
   </si>
 </sst>
 </file>
@@ -2191,60 +2206,60 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>9942</v>
+        <v>10031</v>
       </c>
       <c r="B34">
-        <v>205</v>
-      </c>
-      <c r="C34" t="s">
-        <v>71</v>
+        <v>234</v>
+      </c>
+      <c r="C34">
+        <v>234</v>
       </c>
       <c r="D34" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="E34" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F34">
-        <v>20043</v>
+        <v>20112</v>
       </c>
       <c r="G34">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="H34">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J34">
-        <v>0.92156862699999997</v>
+        <v>0.64285714299999996</v>
       </c>
       <c r="K34">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="L34">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="N34">
-        <v>0.92156862699999997</v>
+        <v>0.64285714299999996</v>
       </c>
       <c r="O34" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>9943</v>
+        <v>9942</v>
       </c>
       <c r="B35">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D35" s="1">
         <v>46206</v>
@@ -2253,45 +2268,45 @@
         <v>46205</v>
       </c>
       <c r="F35">
-        <v>20106</v>
+        <v>20043</v>
       </c>
       <c r="G35">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="H35">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="I35">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="J35">
-        <v>0.6</v>
+        <v>0.92156862699999997</v>
       </c>
       <c r="K35">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L35">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="M35">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="N35">
-        <v>0.6</v>
+        <v>0.92156862699999997</v>
       </c>
       <c r="O35" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>9946</v>
+        <v>9943</v>
       </c>
       <c r="B36">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D36" s="1">
         <v>46206</v>
@@ -2300,45 +2315,45 @@
         <v>46205</v>
       </c>
       <c r="F36">
-        <v>20153</v>
+        <v>20106</v>
       </c>
       <c r="G36">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H36">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I36">
-        <v>-35</v>
+        <v>-10</v>
       </c>
       <c r="J36">
-        <v>0.222222222</v>
+        <v>0.6</v>
       </c>
       <c r="K36">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="L36">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M36">
-        <v>-35</v>
+        <v>-10</v>
       </c>
       <c r="N36">
-        <v>0.222222222</v>
+        <v>0.6</v>
       </c>
       <c r="O36" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>9950</v>
+        <v>9946</v>
       </c>
       <c r="B37">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="1">
         <v>46206</v>
@@ -2347,86 +2362,86 @@
         <v>46205</v>
       </c>
       <c r="F37">
-        <v>20095</v>
+        <v>20153</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>-35</v>
+      </c>
+      <c r="J37">
+        <v>0.222222222</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>-35</v>
+      </c>
+      <c r="N37">
+        <v>0.222222222</v>
       </c>
       <c r="O37" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>10002</v>
+        <v>9950</v>
       </c>
       <c r="B38">
-        <v>326</v>
-      </c>
-      <c r="C38">
-        <v>326</v>
+        <v>216</v>
+      </c>
+      <c r="C38" t="s">
+        <v>74</v>
       </c>
       <c r="D38" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="E38" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="F38">
-        <v>20076</v>
+        <v>20095</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
       <c r="K38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M38">
         <v>0</v>
       </c>
-      <c r="N38">
-        <v>1</v>
-      </c>
       <c r="O38" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="B39">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C39">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D39" s="1">
         <v>46209</v>
@@ -2435,86 +2450,86 @@
         <v>46207</v>
       </c>
       <c r="F39">
-        <v>20095</v>
+        <v>20076</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
       <c r="K39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M39">
         <v>0</v>
       </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
       <c r="O39" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>9951</v>
+        <v>10003</v>
       </c>
       <c r="B40">
-        <v>231</v>
+        <v>328</v>
       </c>
       <c r="C40">
-        <v>231</v>
+        <v>328</v>
       </c>
       <c r="D40" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="E40" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="F40">
-        <v>20005</v>
+        <v>20095</v>
       </c>
       <c r="G40">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>-14</v>
-      </c>
-      <c r="J40">
-        <v>0.67441860499999995</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L40">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M40">
-        <v>-14</v>
-      </c>
-      <c r="N40">
-        <v>0.67441860499999995</v>
+        <v>0</v>
       </c>
       <c r="O40" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>9952</v>
+        <v>9951</v>
       </c>
       <c r="B41">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D41" s="1">
         <v>46206</v>
@@ -2523,45 +2538,45 @@
         <v>46205</v>
       </c>
       <c r="F41">
-        <v>20130</v>
+        <v>20005</v>
       </c>
       <c r="G41">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I41">
-        <v>-39</v>
+        <v>-14</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>0.67441860499999995</v>
       </c>
       <c r="K41">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M41">
-        <v>-39</v>
+        <v>-14</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>0.67441860499999995</v>
       </c>
       <c r="O41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>9953</v>
+        <v>9952</v>
       </c>
       <c r="B42">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C42">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D42" s="1">
         <v>46206</v>
@@ -2570,268 +2585,274 @@
         <v>46205</v>
       </c>
       <c r="F42">
-        <v>200158</v>
+        <v>20130</v>
       </c>
       <c r="G42">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H42">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L42">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="N42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>10006</v>
+        <v>9953</v>
       </c>
       <c r="B43">
-        <v>134</v>
+        <v>233</v>
       </c>
       <c r="C43">
-        <v>134</v>
+        <v>233</v>
       </c>
       <c r="D43" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="E43" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="F43">
-        <v>20112</v>
+        <v>200158</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
       <c r="K43">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M43">
         <v>0</v>
       </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
       <c r="O43" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>9955</v>
+        <v>10035</v>
       </c>
       <c r="B44">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C44">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D44" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="E44" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F44">
-        <v>20113</v>
+        <v>20007</v>
       </c>
       <c r="G44">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H44">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I44">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="J44">
-        <v>0.76923076899999998</v>
+        <v>0.7</v>
       </c>
       <c r="K44">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L44">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M44">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="N44">
-        <v>0.76923076899999998</v>
+        <v>0.7</v>
       </c>
       <c r="O44" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>9976</v>
+        <v>10051</v>
       </c>
       <c r="B45">
-        <v>339</v>
-      </c>
-      <c r="C45">
-        <v>339</v>
+        <v>316</v>
+      </c>
+      <c r="C45" t="s">
+        <v>89</v>
       </c>
       <c r="D45" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E45" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F45">
-        <v>20008</v>
+        <v>200150</v>
       </c>
       <c r="G45">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>-8</v>
-      </c>
-      <c r="J45">
-        <v>0.73333333300000003</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>-8</v>
-      </c>
-      <c r="N45">
-        <v>0.73333333300000003</v>
+        <v>0</v>
       </c>
       <c r="O45" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>10013</v>
+        <v>10006</v>
       </c>
       <c r="B46">
-        <v>501</v>
-      </c>
-      <c r="C46" t="s">
-        <v>65</v>
+        <v>134</v>
+      </c>
+      <c r="C46">
+        <v>134</v>
       </c>
       <c r="D46" s="1">
         <v>46209</v>
       </c>
       <c r="E46" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="F46">
-        <v>20095</v>
+        <v>20112</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J46">
+        <v>0.571428571</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N46">
+        <v>0.571428571</v>
       </c>
       <c r="O46" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>9959</v>
+        <v>10020</v>
       </c>
       <c r="B47">
-        <v>239</v>
-      </c>
-      <c r="C47">
-        <v>239</v>
+        <v>205</v>
+      </c>
+      <c r="C47" t="s">
+        <v>71</v>
       </c>
       <c r="D47" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="E47" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F47">
-        <v>20008</v>
+        <v>20043</v>
       </c>
       <c r="G47">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="H47">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I47">
-        <v>-4</v>
+        <v>-27</v>
       </c>
       <c r="J47">
-        <v>0.75</v>
+        <v>0.47058823500000002</v>
       </c>
       <c r="K47">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="L47">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M47">
-        <v>-4</v>
+        <v>-27</v>
       </c>
       <c r="N47">
-        <v>0.75</v>
+        <v>0.47058823500000002</v>
       </c>
       <c r="O47" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>9999</v>
+        <v>9974</v>
       </c>
       <c r="B48">
-        <v>325</v>
-      </c>
-      <c r="C48" t="s">
-        <v>95</v>
+        <v>337</v>
+      </c>
+      <c r="C48">
+        <v>337</v>
       </c>
       <c r="D48" s="1">
         <v>46207</v>
@@ -2840,280 +2861,280 @@
         <v>46206</v>
       </c>
       <c r="F48">
-        <v>20095</v>
+        <v>20003</v>
       </c>
       <c r="G48">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H48">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="I48">
-        <v>-3</v>
+        <v>17</v>
       </c>
       <c r="J48">
-        <v>0.83333333300000001</v>
+        <v>1.653846154</v>
       </c>
       <c r="K48">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M48">
-        <v>-18</v>
+        <v>17</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.653846154</v>
       </c>
       <c r="O48" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>9998</v>
+        <v>10040</v>
       </c>
       <c r="B49">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D49" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E49" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F49">
-        <v>20105</v>
+        <v>20058</v>
       </c>
       <c r="G49">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="H49">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I49">
-        <v>-4</v>
+        <v>-32</v>
       </c>
       <c r="J49">
-        <v>0.80952380999999995</v>
+        <v>0.46666666699999998</v>
       </c>
       <c r="K49">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="L49">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="M49">
-        <v>-4</v>
+        <v>-32</v>
       </c>
       <c r="N49">
-        <v>0.80952380999999995</v>
+        <v>0.46666666699999998</v>
       </c>
       <c r="O49" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>9978</v>
+        <v>10048</v>
       </c>
       <c r="B50">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="D50" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E50" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F50">
-        <v>20155</v>
+        <v>20076</v>
       </c>
       <c r="G50">
+        <v>32</v>
+      </c>
+      <c r="H50">
+        <v>23</v>
+      </c>
+      <c r="I50">
+        <v>-9</v>
+      </c>
+      <c r="J50">
+        <v>0.71875</v>
+      </c>
+      <c r="K50">
+        <v>32</v>
+      </c>
+      <c r="L50">
+        <v>23</v>
+      </c>
+      <c r="M50">
+        <v>-9</v>
+      </c>
+      <c r="N50">
+        <v>0.71875</v>
+      </c>
+      <c r="O50" t="s">
         <v>20</v>
-      </c>
-      <c r="H50">
-        <v>16</v>
-      </c>
-      <c r="I50">
-        <v>-4</v>
-      </c>
-      <c r="J50">
-        <v>0.8</v>
-      </c>
-      <c r="K50">
-        <v>20</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>-20</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>9988</v>
+        <v>10050</v>
       </c>
       <c r="B51">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D51" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E51" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F51">
-        <v>20106</v>
+        <v>20043</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H51">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I51">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="J51">
-        <v>0.6</v>
+        <v>0.84375</v>
       </c>
       <c r="K51">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="M51">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="N51">
-        <v>0.6</v>
+        <v>0.84375</v>
       </c>
       <c r="O51" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>9993</v>
+        <v>10043</v>
       </c>
       <c r="B52">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="C52" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="D52" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E52" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F52">
-        <v>20058</v>
+        <v>20066</v>
       </c>
       <c r="G52">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H52">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I52">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J52">
-        <v>0.75</v>
+        <v>0.80645161300000001</v>
       </c>
       <c r="K52">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M52">
-        <v>-20</v>
+        <v>-6</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>0.80645161300000001</v>
       </c>
       <c r="O52" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>9968</v>
+        <v>9955</v>
       </c>
       <c r="B53">
-        <v>331</v>
+        <v>235</v>
       </c>
       <c r="C53">
-        <v>331</v>
+        <v>235</v>
       </c>
       <c r="D53" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="E53" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F53">
-        <v>20006</v>
+        <v>20113</v>
       </c>
       <c r="G53">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H53">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I53">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="J53">
-        <v>0.85714285700000004</v>
+        <v>0.76923076899999998</v>
       </c>
       <c r="K53">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M53">
-        <v>-21</v>
+        <v>-6</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>0.76923076899999998</v>
       </c>
       <c r="O53" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>9973</v>
+        <v>9976</v>
       </c>
       <c r="B54">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C54">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D54" s="1">
         <v>46207</v>
@@ -3122,54 +3143,54 @@
         <v>46206</v>
       </c>
       <c r="F54">
-        <v>20111</v>
+        <v>20008</v>
       </c>
       <c r="G54">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H54">
         <v>22</v>
       </c>
       <c r="I54">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="J54">
-        <v>0.6875</v>
+        <v>0.73333333300000003</v>
       </c>
       <c r="K54">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M54">
-        <v>-32</v>
+        <v>-8</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>0.73333333300000003</v>
       </c>
       <c r="O54" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10039</v>
+        <v>10013</v>
       </c>
       <c r="B55">
-        <v>800</v>
+        <v>501</v>
       </c>
       <c r="C55" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D55" s="1">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="E55" s="1">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="F55">
-        <v>200150</v>
+        <v>20095</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -3190,65 +3211,65 @@
         <v>0</v>
       </c>
       <c r="O55" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>9991</v>
+        <v>9959</v>
       </c>
       <c r="B56">
-        <v>316</v>
-      </c>
-      <c r="C56" t="s">
-        <v>89</v>
+        <v>239</v>
+      </c>
+      <c r="C56">
+        <v>239</v>
       </c>
       <c r="D56" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="E56" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F56">
-        <v>20066</v>
+        <v>20008</v>
       </c>
       <c r="G56">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H56">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I56">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="J56">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="K56">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M56">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="O56" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>9989</v>
+        <v>9999</v>
       </c>
       <c r="B57">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="D57" s="1">
         <v>46207</v>
@@ -3257,92 +3278,92 @@
         <v>46206</v>
       </c>
       <c r="F57">
-        <v>20153</v>
+        <v>20095</v>
       </c>
       <c r="G57">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H57">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>0.83333333300000001</v>
       </c>
       <c r="K57">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57">
-        <v>-14</v>
+        <v>-18</v>
       </c>
       <c r="N57">
         <v>0</v>
       </c>
       <c r="O57" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>9958</v>
+        <v>9998</v>
       </c>
       <c r="B58">
-        <v>238</v>
-      </c>
-      <c r="C58">
-        <v>238</v>
+        <v>324</v>
+      </c>
+      <c r="C58" t="s">
+        <v>94</v>
       </c>
       <c r="D58" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E58" s="1">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F58">
-        <v>20007</v>
+        <v>20105</v>
       </c>
       <c r="G58">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H58">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I58">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="J58">
-        <v>0.70370370400000004</v>
+        <v>0.80952380999999995</v>
       </c>
       <c r="K58">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M58">
-        <v>-27</v>
+        <v>-4</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>0.80952380999999995</v>
       </c>
       <c r="O58" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>9975</v>
+        <v>9978</v>
       </c>
       <c r="B59">
-        <v>338</v>
-      </c>
-      <c r="C59">
-        <v>338</v>
+        <v>301</v>
+      </c>
+      <c r="C59" t="s">
+        <v>88</v>
       </c>
       <c r="D59" s="1">
         <v>46207</v>
@@ -3351,45 +3372,45 @@
         <v>46206</v>
       </c>
       <c r="F59">
-        <v>20112</v>
+        <v>20155</v>
       </c>
       <c r="G59">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H59">
         <v>16</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K59">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L59">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>9979</v>
+        <v>9988</v>
       </c>
       <c r="B60">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C60" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D60" s="1">
         <v>46207</v>
@@ -3398,65 +3419,77 @@
         <v>46206</v>
       </c>
       <c r="F60">
-        <v>20058</v>
+        <v>20106</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>-4</v>
+      </c>
+      <c r="J60">
+        <v>0.6</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M60">
-        <v>1</v>
+        <v>-4</v>
+      </c>
+      <c r="N60">
+        <v>0.6</v>
       </c>
       <c r="O60" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>10040</v>
+        <v>9993</v>
       </c>
       <c r="B61">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="C61" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D61" s="1">
-        <v>46210</v>
+        <v>46207</v>
       </c>
       <c r="E61" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="F61">
         <v>20058</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J61">
+        <v>0.75</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
       <c r="M61">
+        <v>-20</v>
+      </c>
+      <c r="N61">
         <v>0</v>
       </c>
       <c r="O61" t="s">
@@ -3465,95 +3498,107 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>10041</v>
+        <v>9968</v>
       </c>
       <c r="B62">
-        <v>303</v>
-      </c>
-      <c r="C62" t="s">
-        <v>66</v>
+        <v>331</v>
+      </c>
+      <c r="C62">
+        <v>331</v>
       </c>
       <c r="D62" s="1">
-        <v>46210</v>
+        <v>46207</v>
       </c>
       <c r="E62" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="F62">
-        <v>11215</v>
+        <v>20006</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J62">
+        <v>0.85714285700000004</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
       <c r="M62">
+        <v>-21</v>
+      </c>
+      <c r="N62">
         <v>0</v>
       </c>
       <c r="O62" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>10042</v>
+        <v>9973</v>
       </c>
       <c r="B63">
-        <v>304</v>
-      </c>
-      <c r="C63" t="s">
-        <v>53</v>
+        <v>336</v>
+      </c>
+      <c r="C63">
+        <v>336</v>
       </c>
       <c r="D63" s="1">
-        <v>46210</v>
+        <v>46207</v>
       </c>
       <c r="E63" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="F63">
-        <v>20086</v>
+        <v>20111</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J63">
+        <v>0.6875</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63">
+        <v>-32</v>
+      </c>
+      <c r="N63">
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>10043</v>
+        <v>10039</v>
       </c>
       <c r="B64">
-        <v>305</v>
+        <v>800</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="D64" s="1">
         <v>46210</v>
@@ -3562,7 +3607,7 @@
         <v>46210</v>
       </c>
       <c r="F64">
-        <v>20066</v>
+        <v>200150</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3583,232 +3628,256 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>10044</v>
+        <v>9991</v>
       </c>
       <c r="B65">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C65" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="D65" s="1">
-        <v>46210</v>
+        <v>46207</v>
       </c>
       <c r="E65" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="F65">
-        <v>20105</v>
+        <v>20066</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J65">
+        <v>0.9</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65">
+        <v>-20</v>
+      </c>
+      <c r="N65">
         <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>10045</v>
+        <v>9989</v>
       </c>
       <c r="B66">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="D66" s="1">
-        <v>46210</v>
+        <v>46207</v>
       </c>
       <c r="E66" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="F66">
-        <v>20057</v>
+        <v>20153</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I66">
         <v>0</v>
       </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
       <c r="K66">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="M66">
+        <v>-14</v>
+      </c>
+      <c r="N66">
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>10046</v>
+        <v>9958</v>
       </c>
       <c r="B67">
-        <v>311</v>
-      </c>
-      <c r="C67" t="s">
-        <v>55</v>
+        <v>238</v>
+      </c>
+      <c r="C67">
+        <v>238</v>
       </c>
       <c r="D67" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E67" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="F67">
-        <v>20106</v>
+        <v>20007</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J67">
+        <v>0.70370370400000004</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67">
+        <v>-27</v>
+      </c>
+      <c r="N67">
         <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10047</v>
+        <v>9975</v>
       </c>
       <c r="B68">
-        <v>312</v>
-      </c>
-      <c r="C68" t="s">
-        <v>52</v>
+        <v>338</v>
+      </c>
+      <c r="C68">
+        <v>338</v>
       </c>
       <c r="D68" s="1">
-        <v>46210</v>
+        <v>46207</v>
       </c>
       <c r="E68" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="F68">
-        <v>20095</v>
+        <v>20112</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
       <c r="K68">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M68">
         <v>0</v>
       </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
       <c r="O68" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10048</v>
+        <v>9979</v>
       </c>
       <c r="B69">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="C69" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D69" s="1">
-        <v>46210</v>
+        <v>46207</v>
       </c>
       <c r="E69" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="F69">
-        <v>20076</v>
+        <v>20058</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69">
         <v>0</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>10049</v>
+        <v>10086</v>
       </c>
       <c r="B70">
-        <v>314</v>
-      </c>
-      <c r="C70" t="s">
-        <v>57</v>
+        <v>227</v>
+      </c>
+      <c r="C70">
+        <v>227</v>
       </c>
       <c r="D70" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E70" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="F70">
-        <v>20153</v>
+        <v>20003</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -3829,59 +3898,65 @@
         <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10050</v>
+        <v>10041</v>
       </c>
       <c r="B71">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="C71" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D71" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E71" s="1">
         <v>46210</v>
       </c>
       <c r="F71">
-        <v>20043</v>
+        <v>11215</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="J71">
+        <v>0.6</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="N71">
+        <v>0.6</v>
       </c>
       <c r="O71" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>10051</v>
+        <v>10042</v>
       </c>
       <c r="B72">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C72" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="D72" s="1">
         <v>46210</v>
@@ -3890,7 +3965,7 @@
         <v>46210</v>
       </c>
       <c r="F72">
-        <v>200150</v>
+        <v>20086</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -3911,27 +3986,27 @@
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>10052</v>
+        <v>10087</v>
       </c>
       <c r="B73">
-        <v>321</v>
-      </c>
-      <c r="C73" t="s">
-        <v>70</v>
+        <v>228</v>
+      </c>
+      <c r="C73">
+        <v>228</v>
       </c>
       <c r="D73" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E73" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="F73">
-        <v>20006</v>
+        <v>20007</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -3952,191 +4027,215 @@
         <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>10053</v>
+        <v>10044</v>
       </c>
       <c r="B74">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="C74" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="D74" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E74" s="1">
         <v>46210</v>
       </c>
       <c r="F74">
-        <v>20130</v>
+        <v>20105</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="J74">
+        <v>1.1290322580000001</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="N74">
+        <v>1.1290322580000001</v>
       </c>
       <c r="O74" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>10054</v>
+        <v>10045</v>
       </c>
       <c r="B75">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="C75" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D75" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E75" s="1">
         <v>46210</v>
       </c>
       <c r="F75">
-        <v>200158</v>
+        <v>20057</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J75">
+        <v>0.89830508499999995</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N75">
+        <v>0.89830508499999995</v>
       </c>
       <c r="O75" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>10055</v>
+        <v>10046</v>
       </c>
       <c r="B76">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="D76" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E76" s="1">
         <v>46210</v>
       </c>
       <c r="F76">
-        <v>20112</v>
+        <v>20106</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I76">
         <v>0</v>
       </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
       <c r="K76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M76">
         <v>0</v>
       </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
       <c r="O76" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>10056</v>
+        <v>10047</v>
       </c>
       <c r="B77">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="D77" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E77" s="1">
         <v>46210</v>
       </c>
       <c r="F77">
-        <v>20113</v>
+        <v>20095</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J77">
+        <v>0.85</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N77">
+        <v>0.85</v>
       </c>
       <c r="O77" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>10057</v>
+        <v>10088</v>
       </c>
       <c r="B78">
-        <v>326</v>
+        <v>229</v>
       </c>
       <c r="C78">
-        <v>326</v>
+        <v>229</v>
       </c>
       <c r="D78" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E78" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="F78">
-        <v>20111</v>
+        <v>20008</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -4157,68 +4256,74 @@
         <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>10058</v>
+        <v>10049</v>
       </c>
       <c r="B79">
-        <v>327</v>
-      </c>
-      <c r="C79">
-        <v>327</v>
+        <v>314</v>
+      </c>
+      <c r="C79" t="s">
+        <v>57</v>
       </c>
       <c r="D79" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E79" s="1">
         <v>46210</v>
       </c>
       <c r="F79">
-        <v>20003</v>
+        <v>20153</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="J79">
+        <v>0.71428571399999996</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="N79">
+        <v>0.71428571399999996</v>
       </c>
       <c r="O79" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>10059</v>
+        <v>10089</v>
       </c>
       <c r="B80">
-        <v>328</v>
+        <v>230</v>
       </c>
       <c r="C80">
-        <v>328</v>
+        <v>230</v>
       </c>
       <c r="D80" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E80" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="F80">
-        <v>20007</v>
+        <v>20006</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -4239,59 +4344,65 @@
         <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>10060</v>
+        <v>10064</v>
       </c>
       <c r="B81">
-        <v>329</v>
-      </c>
-      <c r="C81">
-        <v>329</v>
+        <v>304</v>
+      </c>
+      <c r="C81" t="s">
+        <v>53</v>
       </c>
       <c r="D81" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E81" s="1">
         <v>46210</v>
       </c>
       <c r="F81">
-        <v>20008</v>
+        <v>20086</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="J81">
+        <v>0.73076923100000002</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="N81">
+        <v>0.73076923100000002</v>
       </c>
       <c r="O81" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>10061</v>
+        <v>10052</v>
       </c>
       <c r="B82">
-        <v>330</v>
-      </c>
-      <c r="C82">
-        <v>330</v>
+        <v>321</v>
+      </c>
+      <c r="C82" t="s">
+        <v>70</v>
       </c>
       <c r="D82" s="1">
         <v>46210</v>
@@ -4300,7 +4411,7 @@
         <v>46210</v>
       </c>
       <c r="F82">
-        <v>20005</v>
+        <v>20006</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -4321,18 +4432,18 @@
         <v>0</v>
       </c>
       <c r="O82" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>10062</v>
+        <v>10053</v>
       </c>
       <c r="B83">
-        <v>502</v>
+        <v>322</v>
       </c>
       <c r="C83" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D83" s="1">
         <v>46210</v>
@@ -4341,7 +4452,7 @@
         <v>46210</v>
       </c>
       <c r="F83">
-        <v>200150</v>
+        <v>20130</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -4362,18 +4473,18 @@
         <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>10063</v>
+        <v>10054</v>
       </c>
       <c r="B84">
-        <v>503</v>
+        <v>323</v>
       </c>
       <c r="C84" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="D84" s="1">
         <v>46210</v>
@@ -4382,7 +4493,7 @@
         <v>46210</v>
       </c>
       <c r="F84">
-        <v>200150</v>
+        <v>200158</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -4403,280 +4514,274 @@
         <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>10064</v>
+        <v>10055</v>
       </c>
       <c r="B85">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="C85" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="D85" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E85" s="1">
         <v>46210</v>
       </c>
       <c r="F85">
-        <v>20086</v>
+        <v>20112</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J85">
+        <v>0.70833333300000001</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N85">
+        <v>0.70833333300000001</v>
       </c>
       <c r="O85" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>10017</v>
+        <v>10056</v>
       </c>
       <c r="B86">
-        <v>202</v>
+        <v>325</v>
       </c>
       <c r="C86" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D86" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E86" s="1">
         <v>46210</v>
       </c>
-      <c r="E86" s="1">
-        <v>46209</v>
-      </c>
       <c r="F86">
-        <v>20086</v>
+        <v>20113</v>
       </c>
       <c r="G86">
         <v>15</v>
       </c>
       <c r="H86">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I86">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="J86">
-        <v>0.86666666699999995</v>
+        <v>0.8</v>
       </c>
       <c r="K86">
         <v>15</v>
       </c>
       <c r="L86">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M86">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="N86">
-        <v>0.86666666699999995</v>
+        <v>0.8</v>
       </c>
       <c r="O86" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>10021</v>
+        <v>10057</v>
       </c>
       <c r="B87">
-        <v>206</v>
-      </c>
-      <c r="C87" t="s">
-        <v>72</v>
+        <v>326</v>
+      </c>
+      <c r="C87">
+        <v>326</v>
       </c>
       <c r="D87" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E87" s="1">
         <v>46210</v>
       </c>
-      <c r="E87" s="1">
-        <v>46209</v>
-      </c>
       <c r="F87">
-        <v>20076</v>
+        <v>20111</v>
       </c>
       <c r="G87">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H87">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I87">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="J87">
-        <v>0.67647058800000004</v>
+        <v>0.7</v>
       </c>
       <c r="K87">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L87">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M87">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="N87">
-        <v>0.67647058800000004</v>
+        <v>0.7</v>
       </c>
       <c r="O87" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>10020</v>
+        <v>10058</v>
       </c>
       <c r="B88">
-        <v>205</v>
-      </c>
-      <c r="C88" t="s">
-        <v>71</v>
+        <v>327</v>
+      </c>
+      <c r="C88">
+        <v>327</v>
       </c>
       <c r="D88" s="1">
         <v>46210</v>
       </c>
       <c r="E88" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F88">
-        <v>20043</v>
+        <v>20003</v>
       </c>
       <c r="G88">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I88">
-        <v>-27</v>
-      </c>
-      <c r="J88">
-        <v>0.47058823500000002</v>
+        <v>0</v>
       </c>
       <c r="K88">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L88">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M88">
-        <v>-27</v>
-      </c>
-      <c r="N88">
-        <v>0.47058823500000002</v>
+        <v>0</v>
       </c>
       <c r="O88" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>10022</v>
+        <v>10059</v>
       </c>
       <c r="B89">
-        <v>207</v>
-      </c>
-      <c r="C89" t="s">
-        <v>84</v>
+        <v>328</v>
+      </c>
+      <c r="C89">
+        <v>328</v>
       </c>
       <c r="D89" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E89" s="1">
         <v>46210</v>
       </c>
-      <c r="E89" s="1">
-        <v>46209</v>
-      </c>
       <c r="F89">
-        <v>20106</v>
+        <v>20007</v>
       </c>
       <c r="G89">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H89">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I89">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="J89">
-        <v>0.4</v>
+        <v>0.70833333300000001</v>
       </c>
       <c r="K89">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L89">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M89">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="N89">
-        <v>0.4</v>
+        <v>0.70833333300000001</v>
       </c>
       <c r="O89" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>10004</v>
+        <v>10060</v>
       </c>
       <c r="B90">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="C90">
-        <v>131</v>
+        <v>329</v>
       </c>
       <c r="D90" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E90" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="F90">
         <v>20008</v>
       </c>
       <c r="G90">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I90">
-        <v>-7</v>
-      </c>
-      <c r="J90">
-        <v>0.53333333299999997</v>
+        <v>0</v>
       </c>
       <c r="K90">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L90">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>-7</v>
-      </c>
-      <c r="N90">
-        <v>0.53333333299999997</v>
+        <v>0</v>
       </c>
       <c r="O90" t="s">
         <v>15</v>
@@ -4684,46 +4789,46 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>10028</v>
+        <v>10061</v>
       </c>
       <c r="B91">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="C91">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="D91" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E91" s="1">
         <v>46210</v>
-      </c>
-      <c r="E91" s="1">
-        <v>46209</v>
       </c>
       <c r="F91">
         <v>20005</v>
       </c>
       <c r="G91">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H91">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I91">
         <v>-9</v>
       </c>
       <c r="J91">
-        <v>0.74285714300000005</v>
+        <v>0.735294118</v>
       </c>
       <c r="K91">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L91">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M91">
         <v>-9</v>
       </c>
       <c r="N91">
-        <v>0.74285714300000005</v>
+        <v>0.735294118</v>
       </c>
       <c r="O91" t="s">
         <v>21</v>
@@ -4731,69 +4836,63 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>10033</v>
+        <v>10062</v>
       </c>
       <c r="B92">
-        <v>236</v>
-      </c>
-      <c r="C92">
-        <v>236</v>
+        <v>502</v>
+      </c>
+      <c r="C92" t="s">
+        <v>77</v>
       </c>
       <c r="D92" s="1">
         <v>46210</v>
       </c>
       <c r="E92" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F92">
-        <v>20111</v>
+        <v>200150</v>
       </c>
       <c r="G92">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H92">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I92">
-        <v>-2</v>
-      </c>
-      <c r="J92">
-        <v>0.909090909</v>
+        <v>0</v>
       </c>
       <c r="K92">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L92">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M92">
-        <v>-2</v>
-      </c>
-      <c r="N92">
-        <v>0.909090909</v>
+        <v>0</v>
       </c>
       <c r="O92" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>10030</v>
+        <v>10063</v>
       </c>
       <c r="B93">
-        <v>233</v>
-      </c>
-      <c r="C93">
-        <v>233</v>
+        <v>503</v>
+      </c>
+      <c r="C93" t="s">
+        <v>63</v>
       </c>
       <c r="D93" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E93" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F93">
-        <v>200158</v>
+        <v>200150</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -4814,168 +4913,192 @@
         <v>0</v>
       </c>
       <c r="O93" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>10031</v>
+        <v>10017</v>
       </c>
       <c r="B94">
-        <v>234</v>
-      </c>
-      <c r="C94">
-        <v>234</v>
+        <v>202</v>
+      </c>
+      <c r="C94" t="s">
+        <v>81</v>
       </c>
       <c r="D94" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E94" s="1">
         <v>46209</v>
       </c>
       <c r="F94">
-        <v>20112</v>
+        <v>20086</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J94">
+        <v>0.86666666699999995</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="N94">
+        <v>0.86666666699999995</v>
       </c>
       <c r="O94" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>10032</v>
+        <v>10021</v>
       </c>
       <c r="B95">
-        <v>235</v>
-      </c>
-      <c r="C95">
-        <v>235</v>
+        <v>206</v>
+      </c>
+      <c r="C95" t="s">
+        <v>72</v>
       </c>
       <c r="D95" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E95" s="1">
         <v>46209</v>
       </c>
       <c r="F95">
-        <v>20113</v>
+        <v>20076</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="J95">
+        <v>0.67647058800000004</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L95">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="N95">
+        <v>0.67647058800000004</v>
       </c>
       <c r="O95" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>10035</v>
+        <v>10022</v>
       </c>
       <c r="B96">
-        <v>238</v>
-      </c>
-      <c r="C96">
-        <v>238</v>
+        <v>207</v>
+      </c>
+      <c r="C96" t="s">
+        <v>84</v>
       </c>
       <c r="D96" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E96" s="1">
         <v>46209</v>
       </c>
       <c r="F96">
-        <v>20007</v>
+        <v>20106</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="J96">
+        <v>0.4</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M96">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="N96">
+        <v>0.4</v>
       </c>
       <c r="O96" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>10036</v>
+        <v>10004</v>
       </c>
       <c r="B97">
-        <v>239</v>
+        <v>131</v>
       </c>
       <c r="C97">
-        <v>239</v>
+        <v>131</v>
       </c>
       <c r="D97" s="1">
         <v>46209</v>
       </c>
       <c r="E97" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="F97">
         <v>20008</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I97">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J97">
+        <v>0.53333333299999997</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N97">
+        <v>0.53333333299999997</v>
       </c>
       <c r="O97" t="s">
         <v>15</v>
@@ -4983,551 +5106,503 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>10015</v>
+        <v>10028</v>
       </c>
       <c r="B98">
-        <v>502</v>
-      </c>
-      <c r="C98" t="s">
-        <v>77</v>
+        <v>231</v>
+      </c>
+      <c r="C98">
+        <v>231</v>
       </c>
       <c r="D98" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E98" s="1">
         <v>46209</v>
       </c>
       <c r="F98">
-        <v>20043</v>
+        <v>20005</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I98">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="J98">
+        <v>0.74285714300000005</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L98">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="N98">
+        <v>0.74285714300000005</v>
       </c>
       <c r="O98" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>9980</v>
+        <v>10033</v>
       </c>
       <c r="B99">
-        <v>303</v>
-      </c>
-      <c r="C99" t="s">
-        <v>66</v>
+        <v>236</v>
+      </c>
+      <c r="C99">
+        <v>236</v>
       </c>
       <c r="D99" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E99" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F99">
-        <v>20043</v>
+        <v>20111</v>
       </c>
       <c r="G99">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="H99">
+        <v>20</v>
+      </c>
+      <c r="I99">
+        <v>-2</v>
+      </c>
+      <c r="J99">
+        <v>0.909090909</v>
+      </c>
+      <c r="K99">
         <v>22</v>
       </c>
-      <c r="I99">
-        <v>-11</v>
-      </c>
-      <c r="J99">
-        <v>0.66666666699999999</v>
-      </c>
-      <c r="K99">
-        <v>33</v>
-      </c>
       <c r="L99">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M99">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="N99">
-        <v>0.66666666699999999</v>
+        <v>0.909090909</v>
       </c>
       <c r="O99" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>10005</v>
+        <v>10065</v>
       </c>
       <c r="B100">
-        <v>133</v>
-      </c>
-      <c r="C100">
-        <v>133</v>
+        <v>201</v>
+      </c>
+      <c r="C100" t="s">
+        <v>80</v>
       </c>
       <c r="D100" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E100" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="F100">
-        <v>200158</v>
+        <v>20076</v>
       </c>
       <c r="G100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I100">
         <v>0</v>
       </c>
-      <c r="J100">
-        <v>1</v>
-      </c>
       <c r="K100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L100">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M100">
         <v>0</v>
       </c>
-      <c r="N100">
-        <v>1</v>
-      </c>
       <c r="O100" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>10007</v>
+        <v>10066</v>
       </c>
       <c r="B101">
-        <v>135</v>
-      </c>
-      <c r="C101">
-        <v>135</v>
+        <v>202</v>
+      </c>
+      <c r="C101" t="s">
+        <v>81</v>
       </c>
       <c r="D101" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E101" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="F101">
-        <v>20113</v>
+        <v>20086</v>
       </c>
       <c r="G101">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I101">
-        <v>-5</v>
-      </c>
-      <c r="J101">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K101">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L101">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M101">
-        <v>-5</v>
-      </c>
-      <c r="N101">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O101" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>9972</v>
+        <v>10067</v>
       </c>
       <c r="B102">
-        <v>335</v>
-      </c>
-      <c r="C102">
-        <v>335</v>
+        <v>203</v>
+      </c>
+      <c r="C102" t="s">
+        <v>82</v>
       </c>
       <c r="D102" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E102" s="1">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="F102">
-        <v>20113</v>
+        <v>20153</v>
       </c>
       <c r="G102">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H102">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I102">
-        <v>-4</v>
-      </c>
-      <c r="J102">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K102">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L102">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M102">
-        <v>-4</v>
-      </c>
-      <c r="N102">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O102" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>10011</v>
+        <v>10068</v>
       </c>
       <c r="B103">
-        <v>139</v>
-      </c>
-      <c r="C103">
-        <v>139</v>
+        <v>204</v>
+      </c>
+      <c r="C103" t="s">
+        <v>83</v>
       </c>
       <c r="D103" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E103" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="F103">
-        <v>20008</v>
+        <v>20095</v>
       </c>
       <c r="G103">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H103">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I103">
-        <v>1</v>
-      </c>
-      <c r="J103">
-        <v>1.0476190480000001</v>
+        <v>0</v>
       </c>
       <c r="K103">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L103">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M103">
-        <v>1</v>
-      </c>
-      <c r="N103">
-        <v>1.0476190480000001</v>
+        <v>0</v>
       </c>
       <c r="O103" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>10009</v>
+        <v>10069</v>
       </c>
       <c r="B104">
-        <v>137</v>
-      </c>
-      <c r="C104">
-        <v>137</v>
+        <v>205</v>
+      </c>
+      <c r="C104" t="s">
+        <v>71</v>
       </c>
       <c r="D104" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E104" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="F104">
-        <v>20003</v>
+        <v>20058</v>
       </c>
       <c r="G104">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H104">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I104">
         <v>0</v>
       </c>
-      <c r="J104">
-        <v>1</v>
-      </c>
       <c r="K104">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L104">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M104">
         <v>0</v>
       </c>
-      <c r="N104">
-        <v>1</v>
-      </c>
       <c r="O104" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>9974</v>
+        <v>10070</v>
       </c>
       <c r="B105">
-        <v>337</v>
-      </c>
-      <c r="C105">
-        <v>337</v>
+        <v>206</v>
+      </c>
+      <c r="C105" t="s">
+        <v>72</v>
       </c>
       <c r="D105" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E105" s="1">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="F105">
-        <v>20003</v>
+        <v>20057</v>
       </c>
       <c r="G105">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I105">
-        <v>17</v>
-      </c>
-      <c r="J105">
-        <v>1.653846154</v>
+        <v>0</v>
       </c>
       <c r="K105">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L105">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M105">
-        <v>17</v>
-      </c>
-      <c r="N105">
-        <v>1.653846154</v>
+        <v>0</v>
       </c>
       <c r="O105" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>9982</v>
+        <v>10030</v>
       </c>
       <c r="B106">
-        <v>305</v>
-      </c>
-      <c r="C106" t="s">
-        <v>17</v>
+        <v>233</v>
+      </c>
+      <c r="C106">
+        <v>233</v>
       </c>
       <c r="D106" s="1">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E106" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F106">
-        <v>20106</v>
+        <v>200158</v>
       </c>
       <c r="G106">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H106">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I106">
-        <v>-4</v>
-      </c>
-      <c r="J106">
-        <v>0.84615384599999999</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L106">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M106">
-        <v>-4</v>
-      </c>
-      <c r="N106">
-        <v>0.84615384599999999</v>
+        <v>0</v>
       </c>
       <c r="O106" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>9983</v>
+        <v>10071</v>
       </c>
       <c r="B107">
-        <v>306</v>
+        <v>207</v>
       </c>
       <c r="C107" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D107" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E107" s="1">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="F107">
-        <v>20105</v>
+        <v>20155</v>
       </c>
       <c r="G107">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I107">
-        <v>-14</v>
-      </c>
-      <c r="J107">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="K107">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L107">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M107">
-        <v>-14</v>
-      </c>
-      <c r="N107">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="O107" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>9985</v>
+        <v>10032</v>
       </c>
       <c r="B108">
-        <v>310</v>
-      </c>
-      <c r="C108" t="s">
-        <v>68</v>
+        <v>235</v>
+      </c>
+      <c r="C108">
+        <v>235</v>
       </c>
       <c r="D108" s="1">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E108" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F108">
-        <v>20155</v>
+        <v>20113</v>
       </c>
       <c r="G108">
         <v>0</v>
       </c>
       <c r="H108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K108">
         <v>0</v>
       </c>
       <c r="L108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>9986</v>
+        <v>10072</v>
       </c>
       <c r="B109">
-        <v>311</v>
+        <v>208</v>
       </c>
       <c r="C109" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="D109" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E109" s="1">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="F109">
         <v>20057</v>
       </c>
       <c r="G109">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I109">
-        <v>-3</v>
-      </c>
-      <c r="J109">
-        <v>0.94545454500000004</v>
+        <v>0</v>
       </c>
       <c r="K109">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L109">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M109">
-        <v>-3</v>
-      </c>
-      <c r="N109">
-        <v>0.94545454500000004</v>
+        <v>0</v>
       </c>
       <c r="O109" t="s">
         <v>40</v>
@@ -5535,257 +5610,227 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>9995</v>
+        <v>10073</v>
       </c>
       <c r="B110">
-        <v>320</v>
+        <v>209</v>
       </c>
       <c r="C110" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D110" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="E110" s="1">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="F110">
-        <v>20066</v>
+        <v>20105</v>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110">
         <v>0</v>
       </c>
-      <c r="J110">
-        <v>1</v>
-      </c>
       <c r="K110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110">
         <v>0</v>
       </c>
-      <c r="N110">
-        <v>1</v>
-      </c>
       <c r="O110" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>10008</v>
+        <v>10074</v>
       </c>
       <c r="B111">
-        <v>136</v>
-      </c>
-      <c r="C111">
-        <v>136</v>
+        <v>210</v>
+      </c>
+      <c r="C111" t="s">
+        <v>97</v>
       </c>
       <c r="D111" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E111" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="F111">
-        <v>20111</v>
+        <v>20066</v>
       </c>
       <c r="G111">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H111">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I111">
-        <v>-17</v>
-      </c>
-      <c r="J111">
-        <v>0.54054054100000004</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L111">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M111">
-        <v>-17</v>
-      </c>
-      <c r="N111">
-        <v>0.54054054100000004</v>
+        <v>0</v>
       </c>
       <c r="O111" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>9898</v>
+        <v>10036</v>
       </c>
       <c r="B112">
-        <v>332</v>
+        <v>239</v>
       </c>
       <c r="C112">
-        <v>332</v>
+        <v>239</v>
       </c>
       <c r="D112" s="1">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="E112" s="1">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="F112">
-        <v>20130</v>
+        <v>20008</v>
       </c>
       <c r="G112">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I112">
-        <v>-5</v>
-      </c>
-      <c r="J112">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K112">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L112">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M112">
-        <v>-5</v>
-      </c>
-      <c r="N112">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O112" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>9910</v>
+        <v>10075</v>
       </c>
       <c r="B113">
-        <v>103</v>
+        <v>211</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="D113" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E113" s="1">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F113">
-        <v>20153</v>
+        <v>20043</v>
       </c>
       <c r="G113">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I113">
-        <v>-19</v>
-      </c>
-      <c r="J113">
-        <v>0.58695652200000004</v>
+        <v>0</v>
       </c>
       <c r="K113">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L113">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M113">
-        <v>-19</v>
-      </c>
-      <c r="N113">
-        <v>0.58695652200000004</v>
+        <v>0</v>
       </c>
       <c r="O113" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>9933</v>
+        <v>10076</v>
       </c>
       <c r="B114">
-        <v>800</v>
+        <v>212</v>
       </c>
       <c r="C114" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D114" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E114" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="F114">
-        <v>200150</v>
+        <v>20106</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
-        <v>-1</v>
-      </c>
-      <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114">
         <v>0</v>
       </c>
       <c r="M114">
-        <v>-1</v>
-      </c>
-      <c r="N114">
         <v>0</v>
       </c>
       <c r="O114" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>9936</v>
+        <v>10077</v>
       </c>
       <c r="B115">
-        <v>800</v>
+        <v>214</v>
       </c>
       <c r="C115" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="D115" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E115" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="F115">
-        <v>200150</v>
+        <v>20043</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -5806,27 +5851,27 @@
         <v>0</v>
       </c>
       <c r="O115" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>9937</v>
+        <v>10078</v>
       </c>
       <c r="B116">
-        <v>800</v>
+        <v>215</v>
       </c>
       <c r="C116" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D116" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E116" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="F116">
-        <v>200150</v>
+        <v>11215</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -5847,50 +5892,44 @@
         <v>0</v>
       </c>
       <c r="O116" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>9921</v>
+        <v>10079</v>
       </c>
       <c r="B117">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="C117" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D117" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E117" s="1">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F117">
         <v>20048</v>
       </c>
       <c r="G117">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H117">
         <v>0</v>
       </c>
       <c r="I117">
-        <v>-28</v>
-      </c>
-      <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
       <c r="M117">
-        <v>-28</v>
-      </c>
-      <c r="N117">
         <v>0</v>
       </c>
       <c r="O117" t="s">
@@ -5899,336 +5938,300 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>9911</v>
+        <v>10080</v>
       </c>
       <c r="B118">
-        <v>104</v>
+        <v>221</v>
       </c>
       <c r="C118" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
       <c r="D118" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E118" s="1">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F118">
-        <v>20105</v>
+        <v>20005</v>
       </c>
       <c r="G118">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I118">
-        <v>-17</v>
-      </c>
-      <c r="J118">
-        <v>0.68518518500000003</v>
+        <v>0</v>
       </c>
       <c r="K118">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L118">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M118">
-        <v>-17</v>
-      </c>
-      <c r="N118">
-        <v>0.68518518500000003</v>
+        <v>0</v>
       </c>
       <c r="O118" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>9912</v>
+        <v>10081</v>
       </c>
       <c r="B119">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="C119" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D119" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E119" s="1">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F119">
-        <v>20058</v>
+        <v>20130</v>
       </c>
       <c r="G119">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I119">
-        <v>-28</v>
-      </c>
-      <c r="J119">
-        <v>0.41666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K119">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L119">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M119">
-        <v>-28</v>
-      </c>
-      <c r="N119">
-        <v>0.41666666699999999</v>
+        <v>0</v>
       </c>
       <c r="O119" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>9914</v>
+        <v>10082</v>
       </c>
       <c r="B120">
-        <v>107</v>
+        <v>223</v>
       </c>
       <c r="C120" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="D120" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E120" s="1">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F120">
-        <v>20155</v>
+        <v>200158</v>
       </c>
       <c r="G120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120">
         <v>0</v>
       </c>
-      <c r="J120">
-        <v>1</v>
-      </c>
       <c r="K120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120">
         <v>0</v>
       </c>
-      <c r="N120">
-        <v>1</v>
-      </c>
       <c r="O120" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>9915</v>
+        <v>10083</v>
       </c>
       <c r="B121">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c r="C121" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="D121" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E121" s="1">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F121">
-        <v>20057</v>
+        <v>20112</v>
       </c>
       <c r="G121">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I121">
-        <v>-9</v>
-      </c>
-      <c r="J121">
-        <v>0.87323943699999995</v>
+        <v>0</v>
       </c>
       <c r="K121">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L121">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M121">
-        <v>-9</v>
-      </c>
-      <c r="N121">
-        <v>0.87323943699999995</v>
+        <v>0</v>
       </c>
       <c r="O121" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>9916</v>
+        <v>10084</v>
       </c>
       <c r="B122">
-        <v>109</v>
+        <v>225</v>
       </c>
       <c r="C122" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="D122" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E122" s="1">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="F122">
-        <v>20112</v>
+        <v>20113</v>
       </c>
       <c r="G122">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I122">
-        <v>-19</v>
-      </c>
-      <c r="J122">
-        <v>0.38709677399999998</v>
+        <v>0</v>
       </c>
       <c r="K122">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L122">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M122">
-        <v>-19</v>
-      </c>
-      <c r="N122">
-        <v>0.38709677399999998</v>
+        <v>0</v>
       </c>
       <c r="O122" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>9917</v>
+        <v>10015</v>
       </c>
       <c r="B123">
-        <v>110</v>
+        <v>502</v>
       </c>
       <c r="C123" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="D123" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E123" s="1">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="F123">
-        <v>20066</v>
+        <v>20043</v>
       </c>
       <c r="G123">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I123">
-        <v>-18</v>
-      </c>
-      <c r="J123">
-        <v>0.60869565199999998</v>
+        <v>0</v>
       </c>
       <c r="K123">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L123">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M123">
-        <v>-18</v>
-      </c>
-      <c r="N123">
-        <v>0.60869565199999998</v>
+        <v>0</v>
       </c>
       <c r="O123" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>9919</v>
+        <v>9980</v>
       </c>
       <c r="B124">
-        <v>112</v>
+        <v>303</v>
       </c>
       <c r="C124" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D124" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E124" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F124">
-        <v>20106</v>
+        <v>20043</v>
       </c>
       <c r="G124">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="H124">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I124">
-        <v>-37</v>
+        <v>-11</v>
       </c>
       <c r="J124">
-        <v>0.26</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K124">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="L124">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="M124">
-        <v>-37</v>
+        <v>-11</v>
       </c>
       <c r="N124">
-        <v>0.26</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O124" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>9924</v>
+        <v>10005</v>
       </c>
       <c r="B125">
         <v>133</v>
@@ -6237,19 +6240,19 @@
         <v>133</v>
       </c>
       <c r="D125" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E125" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F125">
         <v>200158</v>
       </c>
       <c r="G125">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H125">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -6258,10 +6261,10 @@
         <v>1</v>
       </c>
       <c r="K125">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L125">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M125">
         <v>0</v>
@@ -6275,101 +6278,101 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>9927</v>
+        <v>10007</v>
       </c>
       <c r="B126">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C126">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D126" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E126" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F126">
-        <v>20003</v>
+        <v>20113</v>
       </c>
       <c r="G126">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H126">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I126">
         <v>-5</v>
       </c>
       <c r="J126">
-        <v>0.70588235300000002</v>
+        <v>0.8</v>
       </c>
       <c r="K126">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L126">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M126">
         <v>-5</v>
       </c>
       <c r="N126">
-        <v>0.70588235300000002</v>
+        <v>0.8</v>
       </c>
       <c r="O126" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>9928</v>
+        <v>9972</v>
       </c>
       <c r="B127">
-        <v>138</v>
+        <v>335</v>
       </c>
       <c r="C127">
-        <v>138</v>
+        <v>335</v>
       </c>
       <c r="D127" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E127" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F127">
-        <v>20007</v>
+        <v>20113</v>
       </c>
       <c r="G127">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H127">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I127">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="J127">
-        <v>0.70967741900000003</v>
+        <v>0.8</v>
       </c>
       <c r="K127">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="L127">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M127">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="N127">
-        <v>0.70967741900000003</v>
+        <v>0.8</v>
       </c>
       <c r="O127" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>9929</v>
+        <v>10011</v>
       </c>
       <c r="B128">
         <v>139</v>
@@ -6378,37 +6381,37 @@
         <v>139</v>
       </c>
       <c r="D128" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E128" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F128">
         <v>20008</v>
       </c>
       <c r="G128">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H128">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I128">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="J128">
-        <v>0.66666666699999999</v>
+        <v>1.0476190480000001</v>
       </c>
       <c r="K128">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L128">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M128">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="N128">
-        <v>0.66666666699999999</v>
+        <v>1.0476190480000001</v>
       </c>
       <c r="O128" t="s">
         <v>15</v>
@@ -6416,69 +6419,69 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>9923</v>
+        <v>10009</v>
       </c>
       <c r="B129">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C129">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D129" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E129" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F129">
-        <v>20130</v>
+        <v>20003</v>
       </c>
       <c r="G129">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H129">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I129">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J129">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K129">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L129">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M129">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="N129">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O129" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>9935</v>
+        <v>10085</v>
       </c>
       <c r="B130">
-        <v>502</v>
-      </c>
-      <c r="C130" t="s">
-        <v>77</v>
+        <v>226</v>
+      </c>
+      <c r="C130">
+        <v>226</v>
       </c>
       <c r="D130" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="E130" s="1">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="F130">
-        <v>20043</v>
+        <v>20111</v>
       </c>
       <c r="G130">
         <v>0</v>
@@ -6499,438 +6502,438 @@
         <v>0</v>
       </c>
       <c r="O130" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>9920</v>
+        <v>9982</v>
       </c>
       <c r="B131">
-        <v>113</v>
+        <v>305</v>
       </c>
       <c r="C131" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="D131" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E131" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F131">
-        <v>20095</v>
+        <v>20106</v>
       </c>
       <c r="G131">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H131">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="I131">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="J131">
-        <v>0.68181818199999999</v>
+        <v>0.84615384599999999</v>
       </c>
       <c r="K131">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="L131">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M131">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="N131">
-        <v>0.68181818199999999</v>
+        <v>0.84615384599999999</v>
       </c>
       <c r="O131" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>9909</v>
+        <v>9983</v>
       </c>
       <c r="B132">
-        <v>102</v>
+        <v>306</v>
       </c>
       <c r="C132" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D132" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E132" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F132">
-        <v>20086</v>
+        <v>20105</v>
       </c>
       <c r="G132">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="H132">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I132">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="J132">
-        <v>0.87272727299999997</v>
+        <v>0.65</v>
       </c>
       <c r="K132">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L132">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="M132">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="N132">
-        <v>0.87272727299999997</v>
+        <v>0.65</v>
       </c>
       <c r="O132" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>9922</v>
+        <v>9985</v>
       </c>
       <c r="B133">
-        <v>131</v>
-      </c>
-      <c r="C133">
-        <v>131</v>
+        <v>310</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
       </c>
       <c r="D133" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E133" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F133">
-        <v>20005</v>
+        <v>20155</v>
       </c>
       <c r="G133">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H133">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I133">
-        <v>-5</v>
-      </c>
-      <c r="J133">
-        <v>0.76190476200000001</v>
+        <v>1</v>
       </c>
       <c r="K133">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L133">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M133">
-        <v>-5</v>
-      </c>
-      <c r="N133">
-        <v>0.76190476200000001</v>
+        <v>1</v>
       </c>
       <c r="O133" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>9934</v>
+        <v>9986</v>
       </c>
       <c r="B134">
-        <v>500</v>
+        <v>311</v>
       </c>
       <c r="C134" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="D134" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E134" s="1">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F134">
-        <v>20006</v>
+        <v>20057</v>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H134">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I134">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J134">
+        <v>0.94545454500000004</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L134">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M134">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N134">
+        <v>0.94545454500000004</v>
       </c>
       <c r="O134" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>9930</v>
+        <v>9995</v>
       </c>
       <c r="B135">
-        <v>140</v>
-      </c>
-      <c r="C135">
-        <v>140</v>
+        <v>320</v>
+      </c>
+      <c r="C135" t="s">
+        <v>69</v>
       </c>
       <c r="D135" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E135" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F135">
-        <v>20006</v>
+        <v>20066</v>
       </c>
       <c r="G135">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I135">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J135">
-        <v>0.96774193500000005</v>
+        <v>1</v>
       </c>
       <c r="K135">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="L135">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="M135">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N135">
-        <v>0.96774193500000005</v>
+        <v>1</v>
       </c>
       <c r="O135" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>9908</v>
+        <v>10008</v>
       </c>
       <c r="B136">
-        <v>101</v>
-      </c>
-      <c r="C136" t="s">
-        <v>28</v>
+        <v>136</v>
+      </c>
+      <c r="C136">
+        <v>136</v>
       </c>
       <c r="D136" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E136" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="F136">
-        <v>20076</v>
+        <v>20111</v>
       </c>
       <c r="G136">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H136">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I136">
-        <v>-6</v>
+        <v>-17</v>
       </c>
       <c r="J136">
-        <v>0.85</v>
+        <v>0.54054054100000004</v>
       </c>
       <c r="K136">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L136">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="M136">
-        <v>-6</v>
+        <v>-17</v>
       </c>
       <c r="N136">
-        <v>0.85</v>
+        <v>0.54054054100000004</v>
       </c>
       <c r="O136" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>9913</v>
+        <v>9898</v>
       </c>
       <c r="B137">
-        <v>106</v>
-      </c>
-      <c r="C137" t="s">
-        <v>35</v>
+        <v>332</v>
+      </c>
+      <c r="C137">
+        <v>332</v>
       </c>
       <c r="D137" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E137" s="1">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="F137">
-        <v>11215</v>
+        <v>20130</v>
       </c>
       <c r="G137">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="H137">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I137">
-        <v>-29</v>
+        <v>-5</v>
       </c>
       <c r="J137">
-        <v>0.52459016400000003</v>
+        <v>0.8</v>
       </c>
       <c r="K137">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="L137">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="M137">
-        <v>-29</v>
+        <v>-5</v>
       </c>
       <c r="N137">
-        <v>0.52459016400000003</v>
+        <v>0.8</v>
       </c>
       <c r="O137" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>9902</v>
+        <v>9910</v>
       </c>
       <c r="B138">
-        <v>336</v>
-      </c>
-      <c r="C138">
-        <v>336</v>
+        <v>103</v>
+      </c>
+      <c r="C138" t="s">
+        <v>29</v>
       </c>
       <c r="D138" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E138" s="1">
         <v>46204</v>
       </c>
-      <c r="E138" s="1">
-        <v>46203</v>
-      </c>
       <c r="F138">
-        <v>20111</v>
+        <v>20153</v>
       </c>
       <c r="G138">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="H138">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I138">
-        <v>-5</v>
+        <v>-19</v>
       </c>
       <c r="J138">
-        <v>0.73684210500000002</v>
+        <v>0.58695652200000004</v>
       </c>
       <c r="K138">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="L138">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="M138">
-        <v>-5</v>
+        <v>-19</v>
       </c>
       <c r="N138">
-        <v>0.73684210500000002</v>
+        <v>0.58695652200000004</v>
       </c>
       <c r="O138" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>9904</v>
+        <v>9933</v>
       </c>
       <c r="B139">
-        <v>338</v>
-      </c>
-      <c r="C139">
-        <v>338</v>
+        <v>800</v>
+      </c>
+      <c r="C139" t="s">
+        <v>62</v>
       </c>
       <c r="D139" s="1">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="E139" s="1">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="F139">
-        <v>20007</v>
+        <v>200150</v>
       </c>
       <c r="G139">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H139">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I139">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="J139">
-        <v>0.68181818199999999</v>
+        <v>0</v>
       </c>
       <c r="K139">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="L139">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M139">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="N139">
-        <v>0.68181818199999999</v>
+        <v>0</v>
       </c>
       <c r="O139" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>9949</v>
+        <v>9936</v>
       </c>
       <c r="B140">
-        <v>215</v>
+        <v>800</v>
       </c>
       <c r="C140" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D140" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E140" s="1">
         <v>46205</v>
@@ -6962,22 +6965,22 @@
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>9965</v>
+        <v>9937</v>
       </c>
       <c r="B141">
-        <v>502</v>
+        <v>800</v>
       </c>
       <c r="C141" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D141" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E141" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F141">
-        <v>20086</v>
+        <v>200150</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -6998,18 +7001,18 @@
         <v>0</v>
       </c>
       <c r="O141" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>9925</v>
+        <v>9921</v>
       </c>
       <c r="B142">
-        <v>135</v>
-      </c>
-      <c r="C142">
-        <v>135</v>
+        <v>114</v>
+      </c>
+      <c r="C142" t="s">
+        <v>50</v>
       </c>
       <c r="D142" s="1">
         <v>46205</v>
@@ -7018,609 +7021,609 @@
         <v>46204</v>
       </c>
       <c r="F142">
-        <v>20113</v>
+        <v>20048</v>
       </c>
       <c r="G142">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H142">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I142">
-        <v>-4</v>
+        <v>-28</v>
       </c>
       <c r="J142">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="K142">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L142">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M142">
-        <v>-4</v>
+        <v>-28</v>
       </c>
       <c r="N142">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="O142" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>9938</v>
+        <v>9911</v>
       </c>
       <c r="B143">
-        <v>201</v>
+        <v>104</v>
       </c>
       <c r="C143" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="D143" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E143" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F143">
-        <v>20155</v>
+        <v>20105</v>
       </c>
       <c r="G143">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="H143">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I143">
-        <v>-4</v>
+        <v>-17</v>
       </c>
       <c r="J143">
-        <v>0.89473684200000003</v>
+        <v>0.68518518500000003</v>
       </c>
       <c r="K143">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="L143">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="M143">
-        <v>-4</v>
+        <v>-17</v>
       </c>
       <c r="N143">
-        <v>0.89473684200000003</v>
+        <v>0.68518518500000003</v>
       </c>
       <c r="O143" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>9939</v>
+        <v>9912</v>
       </c>
       <c r="B144">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="C144" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="D144" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E144" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F144">
-        <v>20057</v>
+        <v>20058</v>
       </c>
       <c r="G144">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H144">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I144">
-        <v>-2</v>
+        <v>-28</v>
       </c>
       <c r="J144">
-        <v>0.95454545499999999</v>
+        <v>0.41666666699999999</v>
       </c>
       <c r="K144">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L144">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M144">
-        <v>-2</v>
+        <v>-28</v>
       </c>
       <c r="N144">
-        <v>0.95454545499999999</v>
+        <v>0.41666666699999999</v>
       </c>
       <c r="O144" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>9940</v>
+        <v>9914</v>
       </c>
       <c r="B145">
-        <v>203</v>
+        <v>107</v>
       </c>
       <c r="C145" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="D145" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E145" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F145">
-        <v>20086</v>
+        <v>20155</v>
       </c>
       <c r="G145">
+        <v>1</v>
+      </c>
+      <c r="H145">
+        <v>1</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>1</v>
+      </c>
+      <c r="K145">
+        <v>1</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
         <v>38</v>
-      </c>
-      <c r="H145">
-        <v>29</v>
-      </c>
-      <c r="I145">
-        <v>-9</v>
-      </c>
-      <c r="J145">
-        <v>0.76315789499999998</v>
-      </c>
-      <c r="K145">
-        <v>38</v>
-      </c>
-      <c r="L145">
-        <v>29</v>
-      </c>
-      <c r="M145">
-        <v>-9</v>
-      </c>
-      <c r="N145">
-        <v>0.76315789499999998</v>
-      </c>
-      <c r="O145" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>9941</v>
+        <v>9915</v>
       </c>
       <c r="B146">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="C146" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="D146" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E146" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F146">
-        <v>20058</v>
+        <v>20057</v>
       </c>
       <c r="G146">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H146">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="I146">
-        <v>-39</v>
+        <v>-9</v>
       </c>
       <c r="J146">
-        <v>0.409090909</v>
+        <v>0.87323943699999995</v>
       </c>
       <c r="K146">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L146">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M146">
-        <v>-39</v>
+        <v>-9</v>
       </c>
       <c r="N146">
-        <v>0.409090909</v>
+        <v>0.87323943699999995</v>
       </c>
       <c r="O146" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>9987</v>
+        <v>9916</v>
       </c>
       <c r="B147">
-        <v>312</v>
+        <v>109</v>
       </c>
       <c r="C147" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D147" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E147" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F147">
-        <v>20086</v>
+        <v>20112</v>
       </c>
       <c r="G147">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H147">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I147">
-        <v>2</v>
+        <v>-19</v>
       </c>
       <c r="J147">
-        <v>1.095238095</v>
+        <v>0.38709677399999998</v>
       </c>
       <c r="K147">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L147">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M147">
-        <v>-21</v>
+        <v>-19</v>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>0.38709677399999998</v>
       </c>
       <c r="O147" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>9944</v>
+        <v>9917</v>
       </c>
       <c r="B148">
-        <v>207</v>
+        <v>110</v>
       </c>
       <c r="C148" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="D148" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E148" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F148">
-        <v>20105</v>
+        <v>20066</v>
       </c>
       <c r="G148">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H148">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I148">
-        <v>-1</v>
+        <v>-18</v>
       </c>
       <c r="J148">
-        <v>0.96969696999999999</v>
+        <v>0.60869565199999998</v>
       </c>
       <c r="K148">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="L148">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M148">
-        <v>-1</v>
+        <v>-18</v>
       </c>
       <c r="N148">
-        <v>0.96969696999999999</v>
+        <v>0.60869565199999998</v>
       </c>
       <c r="O148" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>9945</v>
+        <v>9919</v>
       </c>
       <c r="B149">
-        <v>208</v>
+        <v>112</v>
       </c>
       <c r="C149" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D149" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E149" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F149">
-        <v>20076</v>
+        <v>20106</v>
       </c>
       <c r="G149">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H149">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I149">
-        <v>-9</v>
+        <v>-37</v>
       </c>
       <c r="J149">
-        <v>0.76923076899999998</v>
+        <v>0.26</v>
       </c>
       <c r="K149">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L149">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="M149">
-        <v>-9</v>
+        <v>-37</v>
       </c>
       <c r="N149">
-        <v>0.76923076899999998</v>
+        <v>0.26</v>
       </c>
       <c r="O149" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>9947</v>
+        <v>9924</v>
       </c>
       <c r="B150">
-        <v>213</v>
-      </c>
-      <c r="C150" t="s">
-        <v>86</v>
+        <v>133</v>
+      </c>
+      <c r="C150">
+        <v>133</v>
       </c>
       <c r="D150" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E150" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F150">
-        <v>20066</v>
+        <v>200158</v>
       </c>
       <c r="G150">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="H150">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I150">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="J150">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="K150">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="L150">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="M150">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="N150">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O150" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>9960</v>
+        <v>9927</v>
       </c>
       <c r="B151">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="C151">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="D151" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E151" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F151">
-        <v>20006</v>
+        <v>20003</v>
       </c>
       <c r="G151">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H151">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I151">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="J151">
-        <v>0.92592592600000001</v>
+        <v>0.70588235300000002</v>
       </c>
       <c r="K151">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L151">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M151">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="N151">
-        <v>0.92592592600000001</v>
+        <v>0.70588235300000002</v>
       </c>
       <c r="O151" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>9957</v>
+        <v>9928</v>
       </c>
       <c r="B152">
-        <v>237</v>
+        <v>138</v>
       </c>
       <c r="C152">
-        <v>237</v>
+        <v>138</v>
       </c>
       <c r="D152" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E152" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F152">
-        <v>20003</v>
+        <v>20007</v>
       </c>
       <c r="G152">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H152">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I152">
-        <v>-17</v>
+        <v>-9</v>
       </c>
       <c r="J152">
-        <v>0.59523809500000002</v>
+        <v>0.70967741900000003</v>
       </c>
       <c r="K152">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L152">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M152">
-        <v>-17</v>
+        <v>-9</v>
       </c>
       <c r="N152">
-        <v>0.59523809500000002</v>
+        <v>0.70967741900000003</v>
       </c>
       <c r="O152" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>9994</v>
+        <v>9929</v>
       </c>
       <c r="B153">
-        <v>319</v>
-      </c>
-      <c r="C153" t="s">
-        <v>92</v>
+        <v>139</v>
+      </c>
+      <c r="C153">
+        <v>139</v>
       </c>
       <c r="D153" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="E153" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F153">
-        <v>11215</v>
+        <v>20008</v>
       </c>
       <c r="G153">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H153">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I153">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J153">
-        <v>0.76190476200000001</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K153">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L153">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M153">
-        <v>-21</v>
+        <v>-6</v>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O153" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>9992</v>
+        <v>9923</v>
       </c>
       <c r="B154">
-        <v>317</v>
-      </c>
-      <c r="C154" t="s">
-        <v>90</v>
+        <v>132</v>
+      </c>
+      <c r="C154">
+        <v>132</v>
       </c>
       <c r="D154" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="E154" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F154">
-        <v>20043</v>
+        <v>20130</v>
       </c>
       <c r="G154">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H154">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I154">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="J154">
-        <v>0.95238095199999995</v>
+        <v>0.8</v>
       </c>
       <c r="K154">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="L154">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="M154">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N154">
-        <v>0.95238095199999995</v>
+        <v>0.8</v>
       </c>
       <c r="O154" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>9969</v>
+        <v>10001</v>
       </c>
       <c r="B155">
-        <v>332</v>
-      </c>
-      <c r="C155">
-        <v>332</v>
+        <v>500</v>
+      </c>
+      <c r="C155" t="s">
+        <v>78</v>
       </c>
       <c r="D155" s="1">
         <v>46207</v>
@@ -7629,7 +7632,7 @@
         <v>46206</v>
       </c>
       <c r="F155">
-        <v>20130</v>
+        <v>20111</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -7650,209 +7653,209 @@
         <v>0</v>
       </c>
       <c r="O155" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>9977</v>
+        <v>9935</v>
       </c>
       <c r="B156">
-        <v>340</v>
-      </c>
-      <c r="C156">
-        <v>340</v>
+        <v>502</v>
+      </c>
+      <c r="C156" t="s">
+        <v>77</v>
       </c>
       <c r="D156" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="E156" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F156">
-        <v>20005</v>
+        <v>20043</v>
       </c>
       <c r="G156">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I156">
-        <v>1</v>
-      </c>
-      <c r="J156">
-        <v>1.043478261</v>
+        <v>0</v>
       </c>
       <c r="K156">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L156">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M156">
-        <v>1</v>
-      </c>
-      <c r="N156">
-        <v>1.043478261</v>
+        <v>0</v>
       </c>
       <c r="O156" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>9997</v>
+        <v>9920</v>
       </c>
       <c r="B157">
-        <v>323</v>
+        <v>113</v>
       </c>
       <c r="C157" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="D157" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="E157" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F157">
-        <v>20076</v>
+        <v>20095</v>
       </c>
       <c r="G157">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="H157">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I157">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="J157">
-        <v>1</v>
+        <v>0.68181818199999999</v>
       </c>
       <c r="K157">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="L157">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="M157">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="N157">
-        <v>1</v>
+        <v>0.68181818199999999</v>
       </c>
       <c r="O157" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>10014</v>
+        <v>9909</v>
       </c>
       <c r="B158">
-        <v>800</v>
+        <v>102</v>
       </c>
       <c r="C158" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D158" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="E158" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F158">
-        <v>200150</v>
+        <v>20086</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I158">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J158">
+        <v>0.87272727299999997</v>
       </c>
       <c r="K158">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L158">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M158">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N158">
+        <v>0.87272727299999997</v>
       </c>
       <c r="O158" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>10010</v>
+        <v>9922</v>
       </c>
       <c r="B159">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C159">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D159" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="E159" s="1">
-        <v>46207</v>
+        <v>46204</v>
       </c>
       <c r="F159">
-        <v>20007</v>
+        <v>20005</v>
       </c>
       <c r="G159">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H159">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I159">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="J159">
-        <v>0.6875</v>
+        <v>0.76190476200000001</v>
       </c>
       <c r="K159">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L159">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M159">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="N159">
-        <v>0.6875</v>
+        <v>0.76190476200000001</v>
       </c>
       <c r="O159" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>9962</v>
+        <v>9934</v>
       </c>
       <c r="B160">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C160" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D160" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E160" s="1">
         <v>46205</v>
       </c>
       <c r="F160">
-        <v>200150</v>
+        <v>20006</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -7873,139 +7876,145 @@
         <v>0</v>
       </c>
       <c r="O160" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>9956</v>
+        <v>9930</v>
       </c>
       <c r="B161">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="C161">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="D161" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E161" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F161">
-        <v>20111</v>
+        <v>20006</v>
       </c>
       <c r="G161">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H161">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I161">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="J161">
-        <v>0.72413793100000001</v>
+        <v>0.96774193500000005</v>
       </c>
       <c r="K161">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L161">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M161">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="N161">
-        <v>0.72413793100000001</v>
+        <v>0.96774193500000005</v>
       </c>
       <c r="O161" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>9954</v>
+        <v>9908</v>
       </c>
       <c r="B162">
-        <v>234</v>
-      </c>
-      <c r="C162">
-        <v>234</v>
+        <v>101</v>
+      </c>
+      <c r="C162" t="s">
+        <v>28</v>
       </c>
       <c r="D162" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E162" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F162">
-        <v>20112</v>
+        <v>20076</v>
       </c>
       <c r="G162">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="H162">
+        <v>34</v>
+      </c>
+      <c r="I162">
+        <v>-6</v>
+      </c>
+      <c r="J162">
+        <v>0.85</v>
+      </c>
+      <c r="K162">
+        <v>40</v>
+      </c>
+      <c r="L162">
+        <v>34</v>
+      </c>
+      <c r="M162">
+        <v>-6</v>
+      </c>
+      <c r="N162">
+        <v>0.85</v>
+      </c>
+      <c r="O162" t="s">
         <v>20</v>
-      </c>
-      <c r="I162">
-        <v>-8</v>
-      </c>
-      <c r="J162">
-        <v>0.71428571399999996</v>
-      </c>
-      <c r="K162">
-        <v>28</v>
-      </c>
-      <c r="L162">
-        <v>20</v>
-      </c>
-      <c r="M162">
-        <v>-8</v>
-      </c>
-      <c r="N162">
-        <v>0.71428571399999996</v>
-      </c>
-      <c r="O162" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>9948</v>
+        <v>9913</v>
       </c>
       <c r="B163">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="C163" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="D163" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E163" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F163">
         <v>11215</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H163">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="I163">
-        <v>1</v>
+        <v>-29</v>
+      </c>
+      <c r="J163">
+        <v>0.52459016400000003</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L163">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="M163">
-        <v>1</v>
+        <v>-29</v>
+      </c>
+      <c r="N163">
+        <v>0.52459016400000003</v>
       </c>
       <c r="O163" t="s">
         <v>36</v>
@@ -8013,430 +8022,424 @@
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>10012</v>
+        <v>9902</v>
       </c>
       <c r="B164">
-        <v>140</v>
+        <v>336</v>
       </c>
       <c r="C164">
-        <v>140</v>
+        <v>336</v>
       </c>
       <c r="D164" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="E164" s="1">
-        <v>46207</v>
+        <v>46203</v>
       </c>
       <c r="F164">
-        <v>20006</v>
+        <v>20111</v>
       </c>
       <c r="G164">
+        <v>19</v>
+      </c>
+      <c r="H164">
         <v>14</v>
       </c>
-      <c r="H164">
-        <v>11</v>
-      </c>
       <c r="I164">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="J164">
-        <v>0.78571428600000004</v>
+        <v>0.73684210500000002</v>
       </c>
       <c r="K164">
+        <v>19</v>
+      </c>
+      <c r="L164">
         <v>14</v>
       </c>
-      <c r="L164">
-        <v>11</v>
-      </c>
       <c r="M164">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="N164">
-        <v>0.78571428600000004</v>
+        <v>0.73684210500000002</v>
       </c>
       <c r="O164" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>10016</v>
+        <v>9904</v>
       </c>
       <c r="B165">
-        <v>201</v>
-      </c>
-      <c r="C165" t="s">
-        <v>80</v>
+        <v>338</v>
+      </c>
+      <c r="C165">
+        <v>338</v>
       </c>
       <c r="D165" s="1">
-        <v>46210</v>
+        <v>46204</v>
       </c>
       <c r="E165" s="1">
-        <v>46209</v>
+        <v>46203</v>
       </c>
       <c r="F165">
-        <v>20153</v>
+        <v>20007</v>
       </c>
       <c r="G165">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="H165">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="I165">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="J165">
-        <v>0.70588235300000002</v>
+        <v>0.68181818199999999</v>
       </c>
       <c r="K165">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="L165">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="M165">
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="N165">
-        <v>0.70588235300000002</v>
+        <v>0.68181818199999999</v>
       </c>
       <c r="O165" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>10018</v>
+        <v>9949</v>
       </c>
       <c r="B166">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C166" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D166" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="E166" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="F166">
-        <v>20155</v>
+        <v>200150</v>
       </c>
       <c r="G166">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I166">
-        <v>-11</v>
-      </c>
-      <c r="J166">
-        <v>0.57692307700000001</v>
+        <v>0</v>
       </c>
       <c r="K166">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L166">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M166">
-        <v>-11</v>
-      </c>
-      <c r="N166">
-        <v>0.57692307700000001</v>
+        <v>0</v>
       </c>
       <c r="O166" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>10019</v>
+        <v>9965</v>
       </c>
       <c r="B167">
-        <v>204</v>
+        <v>502</v>
       </c>
       <c r="C167" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D167" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="E167" s="1">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="F167">
-        <v>20095</v>
+        <v>20086</v>
       </c>
       <c r="G167">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I167">
-        <v>-21</v>
-      </c>
-      <c r="J167">
-        <v>0.63793103399999995</v>
+        <v>0</v>
       </c>
       <c r="K167">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L167">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M167">
-        <v>-21</v>
-      </c>
-      <c r="N167">
-        <v>0.63793103399999995</v>
+        <v>0</v>
       </c>
       <c r="O167" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>10023</v>
+        <v>9925</v>
       </c>
       <c r="B168">
-        <v>208</v>
-      </c>
-      <c r="C168" t="s">
-        <v>85</v>
+        <v>135</v>
+      </c>
+      <c r="C168">
+        <v>135</v>
       </c>
       <c r="D168" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E168" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F168">
-        <v>11215</v>
+        <v>20113</v>
       </c>
       <c r="G168">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H168">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I168">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="J168">
-        <v>0.73913043499999997</v>
+        <v>0.75</v>
       </c>
       <c r="K168">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="L168">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="M168">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="N168">
-        <v>0.73913043499999997</v>
+        <v>0.75</v>
       </c>
       <c r="O168" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>10025</v>
+        <v>9938</v>
       </c>
       <c r="B169">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C169" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D169" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="E169" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="F169">
-        <v>20066</v>
+        <v>20155</v>
       </c>
       <c r="G169">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H169">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="I169">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="J169">
-        <v>0.52</v>
+        <v>0.89473684200000003</v>
       </c>
       <c r="K169">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L169">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="M169">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="N169">
-        <v>0.52</v>
+        <v>0.89473684200000003</v>
       </c>
       <c r="O169" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>10024</v>
+        <v>9939</v>
       </c>
       <c r="B170">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C170" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="D170" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="E170" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="F170">
-        <v>20105</v>
+        <v>20057</v>
       </c>
       <c r="G170">
+        <v>44</v>
+      </c>
+      <c r="H170">
         <v>42</v>
       </c>
-      <c r="H170">
-        <v>35</v>
-      </c>
       <c r="I170">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="J170">
-        <v>0.83333333300000001</v>
+        <v>0.95454545499999999</v>
       </c>
       <c r="K170">
+        <v>44</v>
+      </c>
+      <c r="L170">
         <v>42</v>
       </c>
-      <c r="L170">
-        <v>35</v>
-      </c>
       <c r="M170">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="N170">
-        <v>0.83333333300000001</v>
+        <v>0.95454545499999999</v>
       </c>
       <c r="O170" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>10026</v>
+        <v>9940</v>
       </c>
       <c r="B171">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C171" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="D171" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="E171" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="F171">
-        <v>20058</v>
+        <v>20086</v>
       </c>
       <c r="G171">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="H171">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I171">
-        <v>-39</v>
+        <v>-9</v>
       </c>
       <c r="J171">
-        <v>0.37096774199999999</v>
+        <v>0.76315789499999998</v>
       </c>
       <c r="K171">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L171">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M171">
-        <v>-39</v>
+        <v>-9</v>
       </c>
       <c r="N171">
-        <v>0.37096774199999999</v>
+        <v>0.76315789499999998</v>
       </c>
       <c r="O171" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>9970</v>
+        <v>9941</v>
       </c>
       <c r="B172">
-        <v>333</v>
-      </c>
-      <c r="C172">
-        <v>333</v>
+        <v>204</v>
+      </c>
+      <c r="C172" t="s">
+        <v>83</v>
       </c>
       <c r="D172" s="1">
         <v>46206</v>
       </c>
       <c r="E172" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F172">
-        <v>200158</v>
+        <v>20058</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I172">
-        <v>0</v>
+        <v>-39</v>
+      </c>
+      <c r="J172">
+        <v>0.409090909</v>
       </c>
       <c r="K172">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L172">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M172">
-        <v>0</v>
+        <v>-39</v>
+      </c>
+      <c r="N172">
+        <v>0.409090909</v>
       </c>
       <c r="O172" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>9971</v>
+        <v>9987</v>
       </c>
       <c r="B173">
-        <v>334</v>
-      </c>
-      <c r="C173">
-        <v>334</v>
+        <v>312</v>
+      </c>
+      <c r="C173" t="s">
+        <v>52</v>
       </c>
       <c r="D173" s="1">
         <v>46206</v>
@@ -8445,204 +8448,1255 @@
         <v>46206</v>
       </c>
       <c r="F173">
-        <v>20007</v>
+        <v>20086</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I173">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J173">
+        <v>1.095238095</v>
       </c>
       <c r="K173">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L173">
         <v>0</v>
       </c>
       <c r="M173">
+        <v>-21</v>
+      </c>
+      <c r="N173">
         <v>0</v>
       </c>
       <c r="O173" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>10001</v>
+        <v>9944</v>
       </c>
       <c r="B174">
-        <v>500</v>
+        <v>207</v>
       </c>
       <c r="C174" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D174" s="1">
         <v>46206</v>
       </c>
       <c r="E174" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F174">
+        <v>20105</v>
+      </c>
+      <c r="G174">
+        <v>33</v>
+      </c>
+      <c r="H174">
+        <v>32</v>
+      </c>
+      <c r="I174">
+        <v>-1</v>
+      </c>
+      <c r="J174">
+        <v>0.96969696999999999</v>
+      </c>
+      <c r="K174">
+        <v>33</v>
+      </c>
+      <c r="L174">
+        <v>32</v>
+      </c>
+      <c r="M174">
+        <v>-1</v>
+      </c>
+      <c r="N174">
+        <v>0.96969696999999999</v>
+      </c>
+      <c r="O174" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>9945</v>
+      </c>
+      <c r="B175">
+        <v>208</v>
+      </c>
+      <c r="C175" t="s">
+        <v>85</v>
+      </c>
+      <c r="D175" s="1">
         <v>46206</v>
       </c>
-      <c r="F174">
+      <c r="E175" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F175">
+        <v>20076</v>
+      </c>
+      <c r="G175">
+        <v>39</v>
+      </c>
+      <c r="H175">
+        <v>30</v>
+      </c>
+      <c r="I175">
+        <v>-9</v>
+      </c>
+      <c r="J175">
+        <v>0.76923076899999998</v>
+      </c>
+      <c r="K175">
+        <v>39</v>
+      </c>
+      <c r="L175">
+        <v>30</v>
+      </c>
+      <c r="M175">
+        <v>-9</v>
+      </c>
+      <c r="N175">
+        <v>0.76923076899999998</v>
+      </c>
+      <c r="O175" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>9947</v>
+      </c>
+      <c r="B176">
+        <v>213</v>
+      </c>
+      <c r="C176" t="s">
+        <v>86</v>
+      </c>
+      <c r="D176" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E176" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F176">
+        <v>20066</v>
+      </c>
+      <c r="G176">
+        <v>60</v>
+      </c>
+      <c r="H176">
+        <v>45</v>
+      </c>
+      <c r="I176">
+        <v>-15</v>
+      </c>
+      <c r="J176">
+        <v>0.75</v>
+      </c>
+      <c r="K176">
+        <v>60</v>
+      </c>
+      <c r="L176">
+        <v>45</v>
+      </c>
+      <c r="M176">
+        <v>-15</v>
+      </c>
+      <c r="N176">
+        <v>0.75</v>
+      </c>
+      <c r="O176" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>9960</v>
+      </c>
+      <c r="B177">
+        <v>240</v>
+      </c>
+      <c r="C177">
+        <v>240</v>
+      </c>
+      <c r="D177" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E177" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F177">
+        <v>20006</v>
+      </c>
+      <c r="G177">
+        <v>27</v>
+      </c>
+      <c r="H177">
+        <v>25</v>
+      </c>
+      <c r="I177">
+        <v>-2</v>
+      </c>
+      <c r="J177">
+        <v>0.92592592600000001</v>
+      </c>
+      <c r="K177">
+        <v>27</v>
+      </c>
+      <c r="L177">
+        <v>25</v>
+      </c>
+      <c r="M177">
+        <v>-2</v>
+      </c>
+      <c r="N177">
+        <v>0.92592592600000001</v>
+      </c>
+      <c r="O177" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>9957</v>
+      </c>
+      <c r="B178">
+        <v>237</v>
+      </c>
+      <c r="C178">
+        <v>237</v>
+      </c>
+      <c r="D178" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E178" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F178">
+        <v>20003</v>
+      </c>
+      <c r="G178">
+        <v>42</v>
+      </c>
+      <c r="H178">
+        <v>25</v>
+      </c>
+      <c r="I178">
+        <v>-17</v>
+      </c>
+      <c r="J178">
+        <v>0.59523809500000002</v>
+      </c>
+      <c r="K178">
+        <v>42</v>
+      </c>
+      <c r="L178">
+        <v>25</v>
+      </c>
+      <c r="M178">
+        <v>-17</v>
+      </c>
+      <c r="N178">
+        <v>0.59523809500000002</v>
+      </c>
+      <c r="O178" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>9994</v>
+      </c>
+      <c r="B179">
+        <v>319</v>
+      </c>
+      <c r="C179" t="s">
+        <v>92</v>
+      </c>
+      <c r="D179" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E179" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F179">
+        <v>11215</v>
+      </c>
+      <c r="G179">
+        <v>21</v>
+      </c>
+      <c r="H179">
+        <v>16</v>
+      </c>
+      <c r="I179">
+        <v>-5</v>
+      </c>
+      <c r="J179">
+        <v>0.76190476200000001</v>
+      </c>
+      <c r="K179">
+        <v>21</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>-21</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>9992</v>
+      </c>
+      <c r="B180">
+        <v>317</v>
+      </c>
+      <c r="C180" t="s">
+        <v>90</v>
+      </c>
+      <c r="D180" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E180" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F180">
+        <v>20043</v>
+      </c>
+      <c r="G180">
+        <v>21</v>
+      </c>
+      <c r="H180">
+        <v>20</v>
+      </c>
+      <c r="I180">
+        <v>-1</v>
+      </c>
+      <c r="J180">
+        <v>0.95238095199999995</v>
+      </c>
+      <c r="K180">
+        <v>21</v>
+      </c>
+      <c r="L180">
+        <v>20</v>
+      </c>
+      <c r="M180">
+        <v>-1</v>
+      </c>
+      <c r="N180">
+        <v>0.95238095199999995</v>
+      </c>
+      <c r="O180" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>9969</v>
+      </c>
+      <c r="B181">
+        <v>332</v>
+      </c>
+      <c r="C181">
+        <v>332</v>
+      </c>
+      <c r="D181" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E181" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F181">
+        <v>20130</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+      <c r="O181" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>9977</v>
+      </c>
+      <c r="B182">
+        <v>340</v>
+      </c>
+      <c r="C182">
+        <v>340</v>
+      </c>
+      <c r="D182" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E182" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F182">
+        <v>20005</v>
+      </c>
+      <c r="G182">
+        <v>23</v>
+      </c>
+      <c r="H182">
+        <v>24</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="J182">
+        <v>1.043478261</v>
+      </c>
+      <c r="K182">
+        <v>23</v>
+      </c>
+      <c r="L182">
+        <v>24</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>1.043478261</v>
+      </c>
+      <c r="O182" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>9997</v>
+      </c>
+      <c r="B183">
+        <v>323</v>
+      </c>
+      <c r="C183" t="s">
+        <v>93</v>
+      </c>
+      <c r="D183" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E183" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F183">
+        <v>20076</v>
+      </c>
+      <c r="G183">
+        <v>32</v>
+      </c>
+      <c r="H183">
+        <v>32</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>1</v>
+      </c>
+      <c r="K183">
+        <v>32</v>
+      </c>
+      <c r="L183">
+        <v>32</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+      <c r="N183">
+        <v>1</v>
+      </c>
+      <c r="O183" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>10014</v>
+      </c>
+      <c r="B184">
+        <v>800</v>
+      </c>
+      <c r="C184" t="s">
+        <v>62</v>
+      </c>
+      <c r="D184" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E184" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F184">
+        <v>200150</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="O184" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>10010</v>
+      </c>
+      <c r="B185">
+        <v>138</v>
+      </c>
+      <c r="C185">
+        <v>138</v>
+      </c>
+      <c r="D185" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E185" s="1">
+        <v>46207</v>
+      </c>
+      <c r="F185">
+        <v>20007</v>
+      </c>
+      <c r="G185">
+        <v>32</v>
+      </c>
+      <c r="H185">
+        <v>22</v>
+      </c>
+      <c r="I185">
+        <v>-10</v>
+      </c>
+      <c r="J185">
+        <v>0.6875</v>
+      </c>
+      <c r="K185">
+        <v>32</v>
+      </c>
+      <c r="L185">
+        <v>22</v>
+      </c>
+      <c r="M185">
+        <v>-10</v>
+      </c>
+      <c r="N185">
+        <v>0.6875</v>
+      </c>
+      <c r="O185" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>9962</v>
+      </c>
+      <c r="B186">
+        <v>504</v>
+      </c>
+      <c r="C186" t="s">
+        <v>76</v>
+      </c>
+      <c r="D186" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E186" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F186">
+        <v>200150</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="O186" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>9956</v>
+      </c>
+      <c r="B187">
+        <v>236</v>
+      </c>
+      <c r="C187">
+        <v>236</v>
+      </c>
+      <c r="D187" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E187" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F187">
         <v>20111</v>
       </c>
-      <c r="G174">
-        <v>0</v>
-      </c>
-      <c r="H174">
-        <v>0</v>
-      </c>
-      <c r="I174">
-        <v>0</v>
-      </c>
-      <c r="K174">
-        <v>0</v>
-      </c>
-      <c r="L174">
-        <v>0</v>
-      </c>
-      <c r="M174">
-        <v>0</v>
-      </c>
-      <c r="O174" t="s">
+      <c r="G187">
+        <v>29</v>
+      </c>
+      <c r="H187">
+        <v>21</v>
+      </c>
+      <c r="I187">
+        <v>-8</v>
+      </c>
+      <c r="J187">
+        <v>0.72413793100000001</v>
+      </c>
+      <c r="K187">
+        <v>29</v>
+      </c>
+      <c r="L187">
+        <v>21</v>
+      </c>
+      <c r="M187">
+        <v>-8</v>
+      </c>
+      <c r="N187">
+        <v>0.72413793100000001</v>
+      </c>
+      <c r="O187" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D175" s="1"/>
-      <c r="E175" s="1"/>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D176" s="1"/>
-      <c r="E176" s="1"/>
-    </row>
-    <row r="177" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D177" s="1"/>
-      <c r="E177" s="1"/>
-    </row>
-    <row r="178" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D178" s="1"/>
-      <c r="E178" s="1"/>
-    </row>
-    <row r="179" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D179" s="1"/>
-      <c r="E179" s="1"/>
-    </row>
-    <row r="180" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D180" s="1"/>
-      <c r="E180" s="1"/>
-    </row>
-    <row r="181" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D181" s="1"/>
-      <c r="E181" s="1"/>
-    </row>
-    <row r="182" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D182" s="1"/>
-      <c r="E182" s="1"/>
-    </row>
-    <row r="183" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D183" s="1"/>
-      <c r="E183" s="1"/>
-    </row>
-    <row r="184" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D184" s="1"/>
-      <c r="E184" s="1"/>
-    </row>
-    <row r="185" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D185" s="1"/>
-      <c r="E185" s="1"/>
-    </row>
-    <row r="186" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D186" s="1"/>
-      <c r="E186" s="1"/>
-    </row>
-    <row r="187" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D187" s="1"/>
-      <c r="E187" s="1"/>
-    </row>
-    <row r="188" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D188" s="1"/>
-      <c r="E188" s="1"/>
-    </row>
-    <row r="189" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D189" s="1"/>
-      <c r="E189" s="1"/>
-    </row>
-    <row r="190" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D190" s="1"/>
-      <c r="E190" s="1"/>
-    </row>
-    <row r="191" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D191" s="1"/>
-      <c r="E191" s="1"/>
-    </row>
-    <row r="192" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D192" s="1"/>
-      <c r="E192" s="1"/>
-    </row>
-    <row r="193" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D193" s="1"/>
-      <c r="E193" s="1"/>
-    </row>
-    <row r="194" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D194" s="1"/>
-      <c r="E194" s="1"/>
-    </row>
-    <row r="195" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D195" s="1"/>
-      <c r="E195" s="1"/>
-    </row>
-    <row r="196" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D196" s="1"/>
-      <c r="E196" s="1"/>
-    </row>
-    <row r="197" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D197" s="1"/>
-      <c r="E197" s="1"/>
-    </row>
-    <row r="198" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D198" s="1"/>
-      <c r="E198" s="1"/>
-    </row>
-    <row r="199" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D199" s="1"/>
-      <c r="E199" s="1"/>
-    </row>
-    <row r="200" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>9954</v>
+      </c>
+      <c r="B188">
+        <v>234</v>
+      </c>
+      <c r="C188">
+        <v>234</v>
+      </c>
+      <c r="D188" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E188" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F188">
+        <v>20112</v>
+      </c>
+      <c r="G188">
+        <v>28</v>
+      </c>
+      <c r="H188">
+        <v>20</v>
+      </c>
+      <c r="I188">
+        <v>-8</v>
+      </c>
+      <c r="J188">
+        <v>0.71428571399999996</v>
+      </c>
+      <c r="K188">
+        <v>28</v>
+      </c>
+      <c r="L188">
+        <v>20</v>
+      </c>
+      <c r="M188">
+        <v>-8</v>
+      </c>
+      <c r="N188">
+        <v>0.71428571399999996</v>
+      </c>
+      <c r="O188" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>9948</v>
+      </c>
+      <c r="B189">
+        <v>214</v>
+      </c>
+      <c r="C189" t="s">
+        <v>87</v>
+      </c>
+      <c r="D189" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E189" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F189">
+        <v>11215</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>1</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>1</v>
+      </c>
+      <c r="O189" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>10012</v>
+      </c>
+      <c r="B190">
+        <v>140</v>
+      </c>
+      <c r="C190">
+        <v>140</v>
+      </c>
+      <c r="D190" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E190" s="1">
+        <v>46207</v>
+      </c>
+      <c r="F190">
+        <v>20006</v>
+      </c>
+      <c r="G190">
+        <v>14</v>
+      </c>
+      <c r="H190">
+        <v>11</v>
+      </c>
+      <c r="I190">
+        <v>-3</v>
+      </c>
+      <c r="J190">
+        <v>0.78571428600000004</v>
+      </c>
+      <c r="K190">
+        <v>14</v>
+      </c>
+      <c r="L190">
+        <v>11</v>
+      </c>
+      <c r="M190">
+        <v>-3</v>
+      </c>
+      <c r="N190">
+        <v>0.78571428600000004</v>
+      </c>
+      <c r="O190" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>10016</v>
+      </c>
+      <c r="B191">
+        <v>201</v>
+      </c>
+      <c r="C191" t="s">
+        <v>80</v>
+      </c>
+      <c r="D191" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E191" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F191">
+        <v>20153</v>
+      </c>
+      <c r="G191">
+        <v>51</v>
+      </c>
+      <c r="H191">
+        <v>36</v>
+      </c>
+      <c r="I191">
+        <v>-15</v>
+      </c>
+      <c r="J191">
+        <v>0.70588235300000002</v>
+      </c>
+      <c r="K191">
+        <v>51</v>
+      </c>
+      <c r="L191">
+        <v>36</v>
+      </c>
+      <c r="M191">
+        <v>-15</v>
+      </c>
+      <c r="N191">
+        <v>0.70588235300000002</v>
+      </c>
+      <c r="O191" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>10018</v>
+      </c>
+      <c r="B192">
+        <v>203</v>
+      </c>
+      <c r="C192" t="s">
+        <v>82</v>
+      </c>
+      <c r="D192" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E192" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F192">
+        <v>20155</v>
+      </c>
+      <c r="G192">
+        <v>26</v>
+      </c>
+      <c r="H192">
+        <v>15</v>
+      </c>
+      <c r="I192">
+        <v>-11</v>
+      </c>
+      <c r="J192">
+        <v>0.57692307700000001</v>
+      </c>
+      <c r="K192">
+        <v>26</v>
+      </c>
+      <c r="L192">
+        <v>15</v>
+      </c>
+      <c r="M192">
+        <v>-11</v>
+      </c>
+      <c r="N192">
+        <v>0.57692307700000001</v>
+      </c>
+      <c r="O192" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>10019</v>
+      </c>
+      <c r="B193">
+        <v>204</v>
+      </c>
+      <c r="C193" t="s">
+        <v>83</v>
+      </c>
+      <c r="D193" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E193" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F193">
+        <v>20095</v>
+      </c>
+      <c r="G193">
+        <v>58</v>
+      </c>
+      <c r="H193">
+        <v>37</v>
+      </c>
+      <c r="I193">
+        <v>-21</v>
+      </c>
+      <c r="J193">
+        <v>0.63793103399999995</v>
+      </c>
+      <c r="K193">
+        <v>58</v>
+      </c>
+      <c r="L193">
+        <v>37</v>
+      </c>
+      <c r="M193">
+        <v>-21</v>
+      </c>
+      <c r="N193">
+        <v>0.63793103399999995</v>
+      </c>
+      <c r="O193" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>10023</v>
+      </c>
+      <c r="B194">
+        <v>208</v>
+      </c>
+      <c r="C194" t="s">
+        <v>85</v>
+      </c>
+      <c r="D194" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E194" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F194">
+        <v>11215</v>
+      </c>
+      <c r="G194">
+        <v>46</v>
+      </c>
+      <c r="H194">
+        <v>34</v>
+      </c>
+      <c r="I194">
+        <v>-12</v>
+      </c>
+      <c r="J194">
+        <v>0.73913043499999997</v>
+      </c>
+      <c r="K194">
+        <v>46</v>
+      </c>
+      <c r="L194">
+        <v>34</v>
+      </c>
+      <c r="M194">
+        <v>-12</v>
+      </c>
+      <c r="N194">
+        <v>0.73913043499999997</v>
+      </c>
+      <c r="O194" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>10025</v>
+      </c>
+      <c r="B195">
+        <v>210</v>
+      </c>
+      <c r="C195" t="s">
+        <v>97</v>
+      </c>
+      <c r="D195" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E195" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F195">
+        <v>20066</v>
+      </c>
+      <c r="G195">
+        <v>25</v>
+      </c>
+      <c r="H195">
+        <v>13</v>
+      </c>
+      <c r="I195">
+        <v>-12</v>
+      </c>
+      <c r="J195">
+        <v>0.52</v>
+      </c>
+      <c r="K195">
+        <v>25</v>
+      </c>
+      <c r="L195">
+        <v>13</v>
+      </c>
+      <c r="M195">
+        <v>-12</v>
+      </c>
+      <c r="N195">
+        <v>0.52</v>
+      </c>
+      <c r="O195" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>10024</v>
+      </c>
+      <c r="B196">
+        <v>209</v>
+      </c>
+      <c r="C196" t="s">
+        <v>96</v>
+      </c>
+      <c r="D196" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E196" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F196">
+        <v>20105</v>
+      </c>
+      <c r="G196">
+        <v>42</v>
+      </c>
+      <c r="H196">
+        <v>35</v>
+      </c>
+      <c r="I196">
+        <v>-7</v>
+      </c>
+      <c r="J196">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K196">
+        <v>42</v>
+      </c>
+      <c r="L196">
+        <v>35</v>
+      </c>
+      <c r="M196">
+        <v>-7</v>
+      </c>
+      <c r="N196">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O196" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>10026</v>
+      </c>
+      <c r="B197">
+        <v>211</v>
+      </c>
+      <c r="C197" t="s">
+        <v>98</v>
+      </c>
+      <c r="D197" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E197" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F197">
+        <v>20058</v>
+      </c>
+      <c r="G197">
+        <v>62</v>
+      </c>
+      <c r="H197">
+        <v>23</v>
+      </c>
+      <c r="I197">
+        <v>-39</v>
+      </c>
+      <c r="J197">
+        <v>0.37096774199999999</v>
+      </c>
+      <c r="K197">
+        <v>62</v>
+      </c>
+      <c r="L197">
+        <v>23</v>
+      </c>
+      <c r="M197">
+        <v>-39</v>
+      </c>
+      <c r="N197">
+        <v>0.37096774199999999</v>
+      </c>
+      <c r="O197" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>9970</v>
+      </c>
+      <c r="B198">
+        <v>333</v>
+      </c>
+      <c r="C198">
+        <v>333</v>
+      </c>
+      <c r="D198" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E198" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F198">
+        <v>200158</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="O198" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>9971</v>
+      </c>
+      <c r="B199">
+        <v>334</v>
+      </c>
+      <c r="C199">
+        <v>334</v>
+      </c>
+      <c r="D199" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E199" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F199">
+        <v>20007</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="O199" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
     </row>
-    <row r="201" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
     </row>
-    <row r="202" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
     </row>
-    <row r="203" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
     </row>
-    <row r="204" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
     </row>
-    <row r="205" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
     </row>
-    <row r="206" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
     </row>
-    <row r="207" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
     </row>
-    <row r="208" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
     </row>

--- a/data/cartones.xlsx
+++ b/data/cartones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EC6B20-10C3-4AD8-B9ED-50AA47C2986A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD358975-8ED1-49B7-810D-6461B0B4C0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DF2EE928-F73E-4AAC-BA22-2F9F659AC8B2}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="130">
   <si>
     <t>codigo</t>
   </si>
@@ -352,6 +352,78 @@
   </si>
   <si>
     <t>225 CAM 25 MARTES</t>
+  </si>
+  <si>
+    <t>404 CAM 4 JUEVES</t>
+  </si>
+  <si>
+    <t>412 CAM 12 JUEVES</t>
+  </si>
+  <si>
+    <t>413 CAM 13 JUEVES</t>
+  </si>
+  <si>
+    <t>415 CAM 15 JUEVES</t>
+  </si>
+  <si>
+    <t>416 CAM 16 JUEVES</t>
+  </si>
+  <si>
+    <t>417 CAM 17 JUEVES</t>
+  </si>
+  <si>
+    <t>418 CAM 18 JUEVES</t>
+  </si>
+  <si>
+    <t>419 CAM 19 JUEVES</t>
+  </si>
+  <si>
+    <t>423 CAM 23 JUEVES</t>
+  </si>
+  <si>
+    <t>424 CAM 24 JUEVES</t>
+  </si>
+  <si>
+    <t>425 CAM 25 JUEVES</t>
+  </si>
+  <si>
+    <t>506 Deposito clientes esp</t>
+  </si>
+  <si>
+    <t>402 CAM 2 JUEVES</t>
+  </si>
+  <si>
+    <t>403 CAM 3 JUEVES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> JOSE RICAPA</t>
+  </si>
+  <si>
+    <t>405 CAM 5 JUEVES</t>
+  </si>
+  <si>
+    <t>406 CAM 6 JUEVES</t>
+  </si>
+  <si>
+    <t>407 CAM 7 JUEVES</t>
+  </si>
+  <si>
+    <t>409 CAM 9 JUEVES</t>
+  </si>
+  <si>
+    <t>410 CAM 10 JUEVES</t>
+  </si>
+  <si>
+    <t>411 CAM 11 JUEVES</t>
+  </si>
+  <si>
+    <t>420 CAM 20 JUEVES</t>
+  </si>
+  <si>
+    <t>421 CAM 21 JUEVES</t>
+  </si>
+  <si>
+    <t>422 CAM 22 JUEVES</t>
   </si>
 </sst>
 </file>
@@ -3633,154 +3705,154 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>9991</v>
+        <v>10052</v>
       </c>
       <c r="B65">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="D65" s="1">
-        <v>46207</v>
+        <v>46210</v>
       </c>
       <c r="E65" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F65">
-        <v>20066</v>
+        <v>20006</v>
       </c>
       <c r="G65">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H65">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I65">
         <v>-2</v>
       </c>
       <c r="J65">
-        <v>0.9</v>
+        <v>0.94594594600000004</v>
       </c>
       <c r="K65">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65">
-        <v>-20</v>
+        <v>-37</v>
       </c>
       <c r="N65">
         <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>9989</v>
+        <v>10053</v>
       </c>
       <c r="B66">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C66" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="D66" s="1">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="E66" s="1">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="F66">
-        <v>20153</v>
+        <v>20130</v>
       </c>
       <c r="G66">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="H66">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>0.6875</v>
       </c>
       <c r="K66">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="M66">
-        <v>-14</v>
+        <v>-64</v>
       </c>
       <c r="N66">
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>9958</v>
+        <v>9991</v>
       </c>
       <c r="B67">
-        <v>238</v>
-      </c>
-      <c r="C67">
-        <v>238</v>
+        <v>316</v>
+      </c>
+      <c r="C67" t="s">
+        <v>89</v>
       </c>
       <c r="D67" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E67" s="1">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F67">
-        <v>20007</v>
+        <v>20066</v>
       </c>
       <c r="G67">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H67">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I67">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="J67">
-        <v>0.70370370400000004</v>
+        <v>0.9</v>
       </c>
       <c r="K67">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67">
-        <v>-27</v>
+        <v>-20</v>
       </c>
       <c r="N67">
         <v>0</v>
       </c>
       <c r="O67" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>9975</v>
+        <v>9989</v>
       </c>
       <c r="B68">
-        <v>338</v>
-      </c>
-      <c r="C68">
-        <v>338</v>
+        <v>315</v>
+      </c>
+      <c r="C68" t="s">
+        <v>58</v>
       </c>
       <c r="D68" s="1">
         <v>46207</v>
@@ -3789,13 +3861,13 @@
         <v>46206</v>
       </c>
       <c r="F68">
-        <v>20112</v>
+        <v>20153</v>
       </c>
       <c r="G68">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H68">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3804,168 +3876,174 @@
         <v>1</v>
       </c>
       <c r="K68">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L68">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>9979</v>
+        <v>9958</v>
       </c>
       <c r="B69">
-        <v>302</v>
-      </c>
-      <c r="C69" t="s">
-        <v>75</v>
+        <v>238</v>
+      </c>
+      <c r="C69">
+        <v>238</v>
       </c>
       <c r="D69" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="E69" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F69">
-        <v>20058</v>
+        <v>20007</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>-8</v>
+      </c>
+      <c r="J69">
+        <v>0.70370370400000004</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69">
-        <v>1</v>
+        <v>-27</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>10086</v>
+        <v>9975</v>
       </c>
       <c r="B70">
-        <v>227</v>
+        <v>338</v>
       </c>
       <c r="C70">
-        <v>227</v>
+        <v>338</v>
       </c>
       <c r="D70" s="1">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="E70" s="1">
-        <v>46211</v>
+        <v>46206</v>
       </c>
       <c r="F70">
-        <v>20003</v>
+        <v>20112</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I70">
         <v>0</v>
       </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
       <c r="K70">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M70">
         <v>0</v>
       </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
       <c r="O70" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10041</v>
+        <v>9979</v>
       </c>
       <c r="B71">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D71" s="1">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="E71" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="F71">
-        <v>11215</v>
+        <v>20058</v>
       </c>
       <c r="G71">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I71">
-        <v>-12</v>
-      </c>
-      <c r="J71">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K71">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L71">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M71">
-        <v>-12</v>
-      </c>
-      <c r="N71">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O71" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>10042</v>
+        <v>10086</v>
       </c>
       <c r="B72">
-        <v>304</v>
-      </c>
-      <c r="C72" t="s">
-        <v>53</v>
+        <v>227</v>
+      </c>
+      <c r="C72">
+        <v>227</v>
       </c>
       <c r="D72" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E72" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="F72">
-        <v>20086</v>
+        <v>20003</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -3986,153 +4064,147 @@
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>10087</v>
+        <v>10041</v>
       </c>
       <c r="B73">
-        <v>228</v>
-      </c>
-      <c r="C73">
-        <v>228</v>
+        <v>303</v>
+      </c>
+      <c r="C73" t="s">
+        <v>66</v>
       </c>
       <c r="D73" s="1">
         <v>46211</v>
       </c>
       <c r="E73" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="F73">
-        <v>20007</v>
+        <v>11215</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="J73">
+        <v>0.6</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="N73">
+        <v>0.6</v>
       </c>
       <c r="O73" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>10044</v>
+        <v>10042</v>
       </c>
       <c r="B74">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C74" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="D74" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1">
         <v>46210</v>
       </c>
       <c r="F74">
-        <v>20105</v>
+        <v>20086</v>
       </c>
       <c r="G74">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I74">
-        <v>4</v>
-      </c>
-      <c r="J74">
-        <v>1.1290322580000001</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L74">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M74">
-        <v>4</v>
-      </c>
-      <c r="N74">
-        <v>1.1290322580000001</v>
+        <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>10045</v>
+        <v>10087</v>
       </c>
       <c r="B75">
-        <v>308</v>
-      </c>
-      <c r="C75" t="s">
-        <v>99</v>
+        <v>228</v>
+      </c>
+      <c r="C75">
+        <v>228</v>
       </c>
       <c r="D75" s="1">
         <v>46211</v>
       </c>
       <c r="E75" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="F75">
-        <v>20057</v>
+        <v>20007</v>
       </c>
       <c r="G75">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I75">
-        <v>-6</v>
-      </c>
-      <c r="J75">
-        <v>0.89830508499999995</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L75">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M75">
-        <v>-6</v>
-      </c>
-      <c r="N75">
-        <v>0.89830508499999995</v>
+        <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>10046</v>
+        <v>10044</v>
       </c>
       <c r="B76">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C76" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="D76" s="1">
         <v>46211</v>
@@ -4141,45 +4213,45 @@
         <v>46210</v>
       </c>
       <c r="F76">
-        <v>20106</v>
+        <v>20105</v>
       </c>
       <c r="G76">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H76">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>1.1290322580000001</v>
       </c>
       <c r="K76">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="L76">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N76">
-        <v>1</v>
+        <v>1.1290322580000001</v>
       </c>
       <c r="O76" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>10047</v>
+        <v>10045</v>
       </c>
       <c r="B77">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C77" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="D77" s="1">
         <v>46211</v>
@@ -4188,86 +4260,92 @@
         <v>46210</v>
       </c>
       <c r="F77">
-        <v>20095</v>
+        <v>20057</v>
       </c>
       <c r="G77">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="H77">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I77">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="J77">
-        <v>0.85</v>
+        <v>0.89830508499999995</v>
       </c>
       <c r="K77">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="L77">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="M77">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="N77">
-        <v>0.85</v>
+        <v>0.89830508499999995</v>
       </c>
       <c r="O77" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>10088</v>
+        <v>10046</v>
       </c>
       <c r="B78">
-        <v>229</v>
-      </c>
-      <c r="C78">
-        <v>229</v>
+        <v>311</v>
+      </c>
+      <c r="C78" t="s">
+        <v>55</v>
       </c>
       <c r="D78" s="1">
         <v>46211</v>
       </c>
       <c r="E78" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="F78">
-        <v>20008</v>
+        <v>20106</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I78">
         <v>0</v>
       </c>
+      <c r="J78">
+        <v>1</v>
+      </c>
       <c r="K78">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M78">
         <v>0</v>
       </c>
+      <c r="N78">
+        <v>1</v>
+      </c>
       <c r="O78" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>10049</v>
+        <v>10047</v>
       </c>
       <c r="B79">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C79" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D79" s="1">
         <v>46211</v>
@@ -4276,45 +4354,45 @@
         <v>46210</v>
       </c>
       <c r="F79">
-        <v>20153</v>
+        <v>20095</v>
       </c>
       <c r="G79">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H79">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I79">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="J79">
-        <v>0.71428571399999996</v>
+        <v>0.85</v>
       </c>
       <c r="K79">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="L79">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="M79">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="N79">
-        <v>0.71428571399999996</v>
+        <v>0.85</v>
       </c>
       <c r="O79" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>10089</v>
+        <v>10088</v>
       </c>
       <c r="B80">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C80">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D80" s="1">
         <v>46211</v>
@@ -4323,7 +4401,7 @@
         <v>46211</v>
       </c>
       <c r="F80">
-        <v>20006</v>
+        <v>20008</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -4344,18 +4422,18 @@
         <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>10064</v>
+        <v>10049</v>
       </c>
       <c r="B81">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C81" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D81" s="1">
         <v>46211</v>
@@ -4364,72 +4442,78 @@
         <v>46210</v>
       </c>
       <c r="F81">
-        <v>20086</v>
+        <v>20153</v>
       </c>
       <c r="G81">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="H81">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I81">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="J81">
-        <v>0.73076923100000002</v>
+        <v>0.71428571399999996</v>
       </c>
       <c r="K81">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="L81">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="M81">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="N81">
-        <v>0.73076923100000002</v>
+        <v>0.71428571399999996</v>
       </c>
       <c r="O81" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>10052</v>
+        <v>10089</v>
       </c>
       <c r="B82">
-        <v>321</v>
-      </c>
-      <c r="C82" t="s">
-        <v>70</v>
+        <v>230</v>
+      </c>
+      <c r="C82">
+        <v>230</v>
       </c>
       <c r="D82" s="1">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="E82" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="F82">
         <v>20006</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J82">
+        <v>1.095238095</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="N82">
+        <v>1.095238095</v>
       </c>
       <c r="O82" t="s">
         <v>16</v>
@@ -4437,43 +4521,49 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>10053</v>
+        <v>10064</v>
       </c>
       <c r="B83">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="C83" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="D83" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E83" s="1">
         <v>46210</v>
       </c>
       <c r="F83">
-        <v>20130</v>
+        <v>20086</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="J83">
+        <v>0.73076923100000002</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="N83">
+        <v>0.73076923100000002</v>
       </c>
       <c r="O83" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
@@ -4487,7 +4577,7 @@
         <v>93</v>
       </c>
       <c r="D84" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E84" s="1">
         <v>46210</v>
@@ -4496,22 +4586,28 @@
         <v>200158</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I84">
         <v>0</v>
       </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
       <c r="K84">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M84">
         <v>0</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
       </c>
       <c r="O84" t="s">
         <v>23</v>
@@ -4519,13 +4615,13 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>10055</v>
+        <v>10058</v>
       </c>
       <c r="B85">
-        <v>324</v>
-      </c>
-      <c r="C85" t="s">
-        <v>94</v>
+        <v>327</v>
+      </c>
+      <c r="C85">
+        <v>327</v>
       </c>
       <c r="D85" s="1">
         <v>46211</v>
@@ -4534,45 +4630,45 @@
         <v>46210</v>
       </c>
       <c r="F85">
-        <v>20112</v>
+        <v>20003</v>
       </c>
       <c r="G85">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H85">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I85">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="J85">
-        <v>0.70833333300000001</v>
+        <v>0.696969697</v>
       </c>
       <c r="K85">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L85">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M85">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="N85">
-        <v>0.70833333300000001</v>
+        <v>0.696969697</v>
       </c>
       <c r="O85" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>10056</v>
+        <v>10060</v>
       </c>
       <c r="B86">
-        <v>325</v>
-      </c>
-      <c r="C86" t="s">
-        <v>95</v>
+        <v>329</v>
+      </c>
+      <c r="C86">
+        <v>329</v>
       </c>
       <c r="D86" s="1">
         <v>46211</v>
@@ -4581,45 +4677,45 @@
         <v>46210</v>
       </c>
       <c r="F86">
-        <v>20113</v>
+        <v>20008</v>
       </c>
       <c r="G86">
+        <v>26</v>
+      </c>
+      <c r="H86">
+        <v>18</v>
+      </c>
+      <c r="I86">
+        <v>-8</v>
+      </c>
+      <c r="J86">
+        <v>0.69230769199999997</v>
+      </c>
+      <c r="K86">
+        <v>26</v>
+      </c>
+      <c r="L86">
+        <v>18</v>
+      </c>
+      <c r="M86">
+        <v>-8</v>
+      </c>
+      <c r="N86">
+        <v>0.69230769199999997</v>
+      </c>
+      <c r="O86" t="s">
         <v>15</v>
-      </c>
-      <c r="H86">
-        <v>12</v>
-      </c>
-      <c r="I86">
-        <v>-3</v>
-      </c>
-      <c r="J86">
-        <v>0.8</v>
-      </c>
-      <c r="K86">
-        <v>15</v>
-      </c>
-      <c r="L86">
-        <v>12</v>
-      </c>
-      <c r="M86">
-        <v>-3</v>
-      </c>
-      <c r="N86">
-        <v>0.8</v>
-      </c>
-      <c r="O86" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>10057</v>
+        <v>10055</v>
       </c>
       <c r="B87">
-        <v>326</v>
-      </c>
-      <c r="C87">
-        <v>326</v>
+        <v>324</v>
+      </c>
+      <c r="C87" t="s">
+        <v>94</v>
       </c>
       <c r="D87" s="1">
         <v>46211</v>
@@ -4628,86 +4724,92 @@
         <v>46210</v>
       </c>
       <c r="F87">
-        <v>20111</v>
+        <v>20112</v>
       </c>
       <c r="G87">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H87">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I87">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="J87">
-        <v>0.7</v>
+        <v>0.70833333300000001</v>
       </c>
       <c r="K87">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L87">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M87">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="N87">
-        <v>0.7</v>
+        <v>0.70833333300000001</v>
       </c>
       <c r="O87" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>10058</v>
+        <v>10056</v>
       </c>
       <c r="B88">
-        <v>327</v>
-      </c>
-      <c r="C88">
-        <v>327</v>
+        <v>325</v>
+      </c>
+      <c r="C88" t="s">
+        <v>95</v>
       </c>
       <c r="D88" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E88" s="1">
         <v>46210</v>
       </c>
       <c r="F88">
-        <v>20003</v>
+        <v>20113</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J88">
+        <v>0.8</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N88">
+        <v>0.8</v>
       </c>
       <c r="O88" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>10059</v>
+        <v>10057</v>
       </c>
       <c r="B89">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C89">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D89" s="1">
         <v>46211</v>
@@ -4716,86 +4818,92 @@
         <v>46210</v>
       </c>
       <c r="F89">
-        <v>20007</v>
+        <v>20111</v>
       </c>
       <c r="G89">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H89">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I89">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="J89">
-        <v>0.70833333300000001</v>
+        <v>0.7</v>
       </c>
       <c r="K89">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L89">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M89">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="N89">
-        <v>0.70833333300000001</v>
+        <v>0.7</v>
       </c>
       <c r="O89" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>10060</v>
+        <v>9971</v>
       </c>
       <c r="B90">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C90">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D90" s="1">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="E90" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="F90">
-        <v>20008</v>
+        <v>20007</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J90">
+        <v>0.66666666699999999</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N90">
+        <v>0.66666666699999999</v>
       </c>
       <c r="O90" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>10061</v>
+        <v>10059</v>
       </c>
       <c r="B91">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C91">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D91" s="1">
         <v>46211</v>
@@ -4804,51 +4912,51 @@
         <v>46210</v>
       </c>
       <c r="F91">
-        <v>20005</v>
+        <v>20007</v>
       </c>
       <c r="G91">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H91">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I91">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="J91">
-        <v>0.735294118</v>
+        <v>0.70833333300000001</v>
       </c>
       <c r="K91">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="L91">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M91">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="N91">
-        <v>0.735294118</v>
+        <v>0.70833333300000001</v>
       </c>
       <c r="O91" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>10062</v>
+        <v>10090</v>
       </c>
       <c r="B92">
-        <v>502</v>
+        <v>800</v>
       </c>
       <c r="C92" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D92" s="1">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="E92" s="1">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="F92">
         <v>200150</v>
@@ -4877,242 +4985,230 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>10063</v>
+        <v>10061</v>
       </c>
       <c r="B93">
-        <v>503</v>
-      </c>
-      <c r="C93" t="s">
-        <v>63</v>
+        <v>330</v>
+      </c>
+      <c r="C93">
+        <v>330</v>
       </c>
       <c r="D93" s="1">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="E93" s="1">
         <v>46210</v>
       </c>
       <c r="F93">
-        <v>200150</v>
+        <v>20005</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="J93">
+        <v>0.735294118</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L93">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="N93">
+        <v>0.735294118</v>
       </c>
       <c r="O93" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>10017</v>
+        <v>10062</v>
       </c>
       <c r="B94">
-        <v>202</v>
+        <v>502</v>
       </c>
       <c r="C94" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D94" s="1">
         <v>46210</v>
       </c>
       <c r="E94" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="F94">
-        <v>20086</v>
+        <v>200150</v>
       </c>
       <c r="G94">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H94">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I94">
-        <v>-2</v>
-      </c>
-      <c r="J94">
-        <v>0.86666666699999995</v>
+        <v>0</v>
       </c>
       <c r="K94">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L94">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>-2</v>
-      </c>
-      <c r="N94">
-        <v>0.86666666699999995</v>
+        <v>0</v>
       </c>
       <c r="O94" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>10021</v>
+        <v>10063</v>
       </c>
       <c r="B95">
-        <v>206</v>
+        <v>503</v>
       </c>
       <c r="C95" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D95" s="1">
+        <v>46211</v>
+      </c>
+      <c r="E95" s="1">
         <v>46210</v>
       </c>
-      <c r="E95" s="1">
-        <v>46209</v>
-      </c>
       <c r="F95">
-        <v>20076</v>
+        <v>200150</v>
       </c>
       <c r="G95">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H95">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I95">
-        <v>-11</v>
-      </c>
-      <c r="J95">
-        <v>0.67647058800000004</v>
+        <v>0</v>
       </c>
       <c r="K95">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L95">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M95">
-        <v>-11</v>
-      </c>
-      <c r="N95">
-        <v>0.67647058800000004</v>
+        <v>0</v>
       </c>
       <c r="O95" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>10022</v>
+        <v>10091</v>
       </c>
       <c r="B96">
-        <v>207</v>
+        <v>800</v>
       </c>
       <c r="C96" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="D96" s="1">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="E96" s="1">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="F96">
-        <v>20106</v>
+        <v>200150</v>
       </c>
       <c r="G96">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I96">
-        <v>-15</v>
-      </c>
-      <c r="J96">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="K96">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L96">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M96">
-        <v>-15</v>
-      </c>
-      <c r="N96">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O96" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>10004</v>
+        <v>10017</v>
       </c>
       <c r="B97">
-        <v>131</v>
-      </c>
-      <c r="C97">
-        <v>131</v>
+        <v>202</v>
+      </c>
+      <c r="C97" t="s">
+        <v>81</v>
       </c>
       <c r="D97" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E97" s="1">
         <v>46209</v>
       </c>
-      <c r="E97" s="1">
-        <v>46207</v>
-      </c>
       <c r="F97">
-        <v>20008</v>
+        <v>20086</v>
       </c>
       <c r="G97">
         <v>15</v>
       </c>
       <c r="H97">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I97">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="J97">
-        <v>0.53333333299999997</v>
+        <v>0.86666666699999995</v>
       </c>
       <c r="K97">
         <v>15</v>
       </c>
       <c r="L97">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M97">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="N97">
-        <v>0.53333333299999997</v>
+        <v>0.86666666699999995</v>
       </c>
       <c r="O97" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>10028</v>
+        <v>10021</v>
       </c>
       <c r="B98">
-        <v>231</v>
-      </c>
-      <c r="C98">
-        <v>231</v>
+        <v>206</v>
+      </c>
+      <c r="C98" t="s">
+        <v>72</v>
       </c>
       <c r="D98" s="1">
         <v>46210</v>
@@ -5121,256 +5217,274 @@
         <v>46209</v>
       </c>
       <c r="F98">
-        <v>20005</v>
+        <v>20076</v>
       </c>
       <c r="G98">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H98">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I98">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="J98">
-        <v>0.74285714300000005</v>
+        <v>0.67647058800000004</v>
       </c>
       <c r="K98">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L98">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M98">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="N98">
-        <v>0.74285714300000005</v>
+        <v>0.67647058800000004</v>
       </c>
       <c r="O98" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>10033</v>
+        <v>10092</v>
       </c>
       <c r="B99">
-        <v>236</v>
-      </c>
-      <c r="C99">
-        <v>236</v>
+        <v>800</v>
+      </c>
+      <c r="C99" t="s">
+        <v>62</v>
       </c>
       <c r="D99" s="1">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="E99" s="1">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="F99">
-        <v>20111</v>
+        <v>200150</v>
       </c>
       <c r="G99">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I99">
-        <v>-2</v>
-      </c>
-      <c r="J99">
-        <v>0.909090909</v>
+        <v>0</v>
       </c>
       <c r="K99">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L99">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M99">
-        <v>-2</v>
-      </c>
-      <c r="N99">
-        <v>0.909090909</v>
+        <v>0</v>
       </c>
       <c r="O99" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>10065</v>
+        <v>10022</v>
       </c>
       <c r="B100">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C100" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D100" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="E100" s="1">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="F100">
-        <v>20076</v>
+        <v>20106</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="J100">
+        <v>0.4</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L100">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M100">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="N100">
+        <v>0.4</v>
       </c>
       <c r="O100" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>10066</v>
+        <v>10004</v>
       </c>
       <c r="B101">
-        <v>202</v>
-      </c>
-      <c r="C101" t="s">
-        <v>81</v>
+        <v>131</v>
+      </c>
+      <c r="C101">
+        <v>131</v>
       </c>
       <c r="D101" s="1">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="E101" s="1">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="F101">
-        <v>20086</v>
+        <v>20008</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I101">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J101">
+        <v>0.53333333299999997</v>
       </c>
       <c r="K101">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N101">
+        <v>0.53333333299999997</v>
       </c>
       <c r="O101" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>10067</v>
+        <v>10028</v>
       </c>
       <c r="B102">
-        <v>203</v>
-      </c>
-      <c r="C102" t="s">
-        <v>82</v>
+        <v>231</v>
+      </c>
+      <c r="C102">
+        <v>231</v>
       </c>
       <c r="D102" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="E102" s="1">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="F102">
-        <v>20153</v>
+        <v>20005</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="J102">
+        <v>0.74285714300000005</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L102">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M102">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="N102">
+        <v>0.74285714300000005</v>
       </c>
       <c r="O102" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>10068</v>
+        <v>10033</v>
       </c>
       <c r="B103">
-        <v>204</v>
-      </c>
-      <c r="C103" t="s">
-        <v>83</v>
+        <v>236</v>
+      </c>
+      <c r="C103">
+        <v>236</v>
       </c>
       <c r="D103" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="E103" s="1">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="F103">
-        <v>20095</v>
+        <v>20111</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I103">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J103">
+        <v>0.909090909</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L103">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M103">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="N103">
+        <v>0.909090909</v>
       </c>
       <c r="O103" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>10069</v>
+        <v>10065</v>
       </c>
       <c r="B104">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C104" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D104" s="1">
         <v>46211</v>
@@ -5379,7 +5493,7 @@
         <v>46211</v>
       </c>
       <c r="F104">
-        <v>20058</v>
+        <v>20076</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -5400,18 +5514,18 @@
         <v>0</v>
       </c>
       <c r="O104" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>10070</v>
+        <v>10066</v>
       </c>
       <c r="B105">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C105" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D105" s="1">
         <v>46211</v>
@@ -5420,7 +5534,7 @@
         <v>46211</v>
       </c>
       <c r="F105">
-        <v>20057</v>
+        <v>20086</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -5441,27 +5555,27 @@
         <v>0</v>
       </c>
       <c r="O105" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>10030</v>
+        <v>10067</v>
       </c>
       <c r="B106">
-        <v>233</v>
-      </c>
-      <c r="C106">
-        <v>233</v>
+        <v>203</v>
+      </c>
+      <c r="C106" t="s">
+        <v>82</v>
       </c>
       <c r="D106" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E106" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="F106">
-        <v>200158</v>
+        <v>20153</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -5482,18 +5596,18 @@
         <v>0</v>
       </c>
       <c r="O106" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>10071</v>
+        <v>10068</v>
       </c>
       <c r="B107">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C107" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D107" s="1">
         <v>46211</v>
@@ -5502,7 +5616,7 @@
         <v>46211</v>
       </c>
       <c r="F107">
-        <v>20155</v>
+        <v>20095</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -5523,27 +5637,27 @@
         <v>0</v>
       </c>
       <c r="O107" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>10032</v>
+        <v>10069</v>
       </c>
       <c r="B108">
-        <v>235</v>
-      </c>
-      <c r="C108">
-        <v>235</v>
+        <v>205</v>
+      </c>
+      <c r="C108" t="s">
+        <v>71</v>
       </c>
       <c r="D108" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E108" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="F108">
-        <v>20113</v>
+        <v>20058</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -5564,18 +5678,18 @@
         <v>0</v>
       </c>
       <c r="O108" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>10072</v>
+        <v>10070</v>
       </c>
       <c r="B109">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C109" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="D109" s="1">
         <v>46211</v>
@@ -5610,54 +5724,60 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>10073</v>
+        <v>10030</v>
       </c>
       <c r="B110">
-        <v>209</v>
-      </c>
-      <c r="C110" t="s">
-        <v>96</v>
+        <v>233</v>
+      </c>
+      <c r="C110">
+        <v>233</v>
       </c>
       <c r="D110" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="E110" s="1">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="F110">
-        <v>20105</v>
+        <v>200158</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I110">
         <v>0</v>
       </c>
+      <c r="J110">
+        <v>1</v>
+      </c>
       <c r="K110">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="L110">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M110">
         <v>0</v>
       </c>
+      <c r="N110">
+        <v>1</v>
+      </c>
       <c r="O110" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>10074</v>
+        <v>10071</v>
       </c>
       <c r="B111">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C111" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D111" s="1">
         <v>46211</v>
@@ -5666,7 +5786,7 @@
         <v>46211</v>
       </c>
       <c r="F111">
-        <v>20066</v>
+        <v>20155</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -5687,100 +5807,112 @@
         <v>0</v>
       </c>
       <c r="O111" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>10036</v>
+        <v>10032</v>
       </c>
       <c r="B112">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C112">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D112" s="1">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="E112" s="1">
         <v>46209</v>
       </c>
       <c r="F112">
-        <v>20008</v>
+        <v>20113</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J112">
+        <v>0.79166666699999999</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N112">
+        <v>0.79166666699999999</v>
       </c>
       <c r="O112" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>10075</v>
+        <v>10072</v>
       </c>
       <c r="B113">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C113" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D113" s="1">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="E113" s="1">
         <v>46211</v>
       </c>
       <c r="F113">
-        <v>20043</v>
+        <v>20057</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I113">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J113">
+        <v>0.91176470600000004</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M113">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N113">
+        <v>0.91176470600000004</v>
       </c>
       <c r="O113" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>10076</v>
+        <v>10073</v>
       </c>
       <c r="B114">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C114" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D114" s="1">
         <v>46211</v>
@@ -5789,7 +5921,7 @@
         <v>46211</v>
       </c>
       <c r="F114">
-        <v>20106</v>
+        <v>20105</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -5810,273 +5942,303 @@
         <v>0</v>
       </c>
       <c r="O114" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>10077</v>
+        <v>10074</v>
       </c>
       <c r="B115">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C115" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D115" s="1">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="E115" s="1">
         <v>46211</v>
       </c>
       <c r="F115">
-        <v>20043</v>
+        <v>20066</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J115">
+        <v>0.803921569</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M115">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="N115">
+        <v>0.803921569</v>
       </c>
       <c r="O115" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>10078</v>
+        <v>10036</v>
       </c>
       <c r="B116">
-        <v>215</v>
-      </c>
-      <c r="C116" t="s">
-        <v>79</v>
+        <v>239</v>
+      </c>
+      <c r="C116">
+        <v>239</v>
       </c>
       <c r="D116" s="1">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="E116" s="1">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="F116">
-        <v>11215</v>
+        <v>20008</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>-16</v>
+      </c>
+      <c r="J116">
+        <v>0.54285714299999999</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L116">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M116">
-        <v>0</v>
+        <v>-16</v>
+      </c>
+      <c r="N116">
+        <v>0.54285714299999999</v>
       </c>
       <c r="O116" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>10079</v>
+        <v>10075</v>
       </c>
       <c r="B117">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C117" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D117" s="1">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="E117" s="1">
         <v>46211</v>
       </c>
       <c r="F117">
-        <v>20048</v>
+        <v>20043</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J117">
+        <v>0.91803278700000002</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="L117">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M117">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N117">
+        <v>0.91803278700000002</v>
       </c>
       <c r="O117" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>10080</v>
+        <v>10076</v>
       </c>
       <c r="B118">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C118" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="D118" s="1">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="E118" s="1">
         <v>46211</v>
       </c>
       <c r="F118">
-        <v>20005</v>
+        <v>20106</v>
       </c>
       <c r="G118">
         <v>0</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118">
         <v>0</v>
       </c>
       <c r="L118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O118" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>10081</v>
+        <v>10077</v>
       </c>
       <c r="B119">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C119" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="D119" s="1">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="E119" s="1">
         <v>46211</v>
       </c>
       <c r="F119">
-        <v>20130</v>
+        <v>20043</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>-34</v>
+      </c>
+      <c r="J119">
+        <v>2.8571428999999999E-2</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119">
-        <v>0</v>
+        <v>-34</v>
+      </c>
+      <c r="N119">
+        <v>2.8571428999999999E-2</v>
       </c>
       <c r="O119" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>10082</v>
+        <v>10078</v>
       </c>
       <c r="B120">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C120" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D120" s="1">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="E120" s="1">
         <v>46211</v>
       </c>
       <c r="F120">
-        <v>200158</v>
+        <v>11215</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I120">
-        <v>0</v>
+        <v>-22</v>
+      </c>
+      <c r="J120">
+        <v>0.6</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L120">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M120">
-        <v>0</v>
+        <v>-22</v>
+      </c>
+      <c r="N120">
+        <v>0.6</v>
       </c>
       <c r="O120" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>10083</v>
+        <v>10079</v>
       </c>
       <c r="B121">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C121" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D121" s="1">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="E121" s="1">
         <v>46211</v>
       </c>
       <c r="F121">
-        <v>20112</v>
+        <v>20048</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -6097,68 +6259,74 @@
         <v>0</v>
       </c>
       <c r="O121" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>10084</v>
+        <v>10080</v>
       </c>
       <c r="B122">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C122" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D122" s="1">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="E122" s="1">
         <v>46211</v>
       </c>
       <c r="F122">
-        <v>20113</v>
+        <v>20005</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I122">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="J122">
+        <v>0.78461538500000005</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="N122">
+        <v>0.78461538500000005</v>
       </c>
       <c r="O122" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>10015</v>
+        <v>10081</v>
       </c>
       <c r="B123">
-        <v>502</v>
+        <v>222</v>
       </c>
       <c r="C123" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D123" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E123" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="F123">
-        <v>20043</v>
+        <v>20130</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -6179,145 +6347,139 @@
         <v>0</v>
       </c>
       <c r="O123" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>9980</v>
+        <v>10082</v>
       </c>
       <c r="B124">
-        <v>303</v>
+        <v>223</v>
       </c>
       <c r="C124" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="D124" s="1">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="E124" s="1">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="F124">
-        <v>20043</v>
+        <v>200158</v>
       </c>
       <c r="G124">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H124">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="I124">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="J124">
-        <v>0.66666666699999999</v>
+        <v>1</v>
       </c>
       <c r="K124">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L124">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="M124">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="N124">
-        <v>0.66666666699999999</v>
+        <v>1</v>
       </c>
       <c r="O124" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>10005</v>
+        <v>10083</v>
       </c>
       <c r="B125">
-        <v>133</v>
-      </c>
-      <c r="C125">
-        <v>133</v>
+        <v>224</v>
+      </c>
+      <c r="C125" t="s">
+        <v>104</v>
       </c>
       <c r="D125" s="1">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="E125" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="F125">
-        <v>200158</v>
+        <v>20112</v>
       </c>
       <c r="G125">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H125">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I125">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="J125">
-        <v>1</v>
+        <v>0.58823529399999996</v>
       </c>
       <c r="K125">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L125">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="M125">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="N125">
-        <v>1</v>
+        <v>0.58823529399999996</v>
       </c>
       <c r="O125" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>10007</v>
+        <v>10084</v>
       </c>
       <c r="B126">
-        <v>135</v>
-      </c>
-      <c r="C126">
-        <v>135</v>
+        <v>225</v>
+      </c>
+      <c r="C126" t="s">
+        <v>105</v>
       </c>
       <c r="D126" s="1">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E126" s="1">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="F126">
         <v>20113</v>
       </c>
       <c r="G126">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I126">
-        <v>-5</v>
-      </c>
-      <c r="J126">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K126">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L126">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M126">
-        <v>-5</v>
-      </c>
-      <c r="N126">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O126" t="s">
         <v>24</v>
@@ -6325,107 +6487,101 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>9972</v>
+        <v>10015</v>
       </c>
       <c r="B127">
-        <v>335</v>
-      </c>
-      <c r="C127">
-        <v>335</v>
+        <v>502</v>
+      </c>
+      <c r="C127" t="s">
+        <v>77</v>
       </c>
       <c r="D127" s="1">
-        <v>46207</v>
+        <v>46209</v>
       </c>
       <c r="E127" s="1">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="F127">
-        <v>20113</v>
+        <v>20043</v>
       </c>
       <c r="G127">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I127">
-        <v>-4</v>
-      </c>
-      <c r="J127">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K127">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L127">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M127">
-        <v>-4</v>
-      </c>
-      <c r="N127">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O127" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>10011</v>
+        <v>9980</v>
       </c>
       <c r="B128">
-        <v>139</v>
-      </c>
-      <c r="C128">
-        <v>139</v>
+        <v>303</v>
+      </c>
+      <c r="C128" t="s">
+        <v>66</v>
       </c>
       <c r="D128" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="E128" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="F128">
-        <v>20008</v>
+        <v>20043</v>
       </c>
       <c r="G128">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H128">
         <v>22</v>
       </c>
       <c r="I128">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="J128">
-        <v>1.0476190480000001</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K128">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="L128">
         <v>22</v>
       </c>
       <c r="M128">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="N128">
-        <v>1.0476190480000001</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O128" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>10009</v>
+        <v>10005</v>
       </c>
       <c r="B129">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C129">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D129" s="1">
         <v>46209</v>
@@ -6434,13 +6590,13 @@
         <v>46207</v>
       </c>
       <c r="F129">
-        <v>20003</v>
+        <v>200158</v>
       </c>
       <c r="G129">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H129">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -6449,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="K129">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="L129">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M129">
         <v>0</v>
@@ -6461,59 +6617,65 @@
         <v>1</v>
       </c>
       <c r="O129" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>10085</v>
+        <v>10007</v>
       </c>
       <c r="B130">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="C130">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="D130" s="1">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="E130" s="1">
-        <v>46211</v>
+        <v>46207</v>
       </c>
       <c r="F130">
-        <v>20111</v>
+        <v>20113</v>
       </c>
       <c r="G130">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J130">
+        <v>0.8</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L130">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M130">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N130">
+        <v>0.8</v>
       </c>
       <c r="O130" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>9982</v>
+        <v>9972</v>
       </c>
       <c r="B131">
-        <v>305</v>
-      </c>
-      <c r="C131" t="s">
-        <v>17</v>
+        <v>335</v>
+      </c>
+      <c r="C131">
+        <v>335</v>
       </c>
       <c r="D131" s="1">
         <v>46207</v>
@@ -6522,180 +6684,186 @@
         <v>46206</v>
       </c>
       <c r="F131">
-        <v>20106</v>
+        <v>20113</v>
       </c>
       <c r="G131">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H131">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I131">
         <v>-4</v>
       </c>
       <c r="J131">
-        <v>0.84615384599999999</v>
+        <v>0.8</v>
       </c>
       <c r="K131">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L131">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="M131">
         <v>-4</v>
       </c>
       <c r="N131">
-        <v>0.84615384599999999</v>
+        <v>0.8</v>
       </c>
       <c r="O131" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>9983</v>
+        <v>10011</v>
       </c>
       <c r="B132">
-        <v>306</v>
-      </c>
-      <c r="C132" t="s">
-        <v>67</v>
+        <v>139</v>
+      </c>
+      <c r="C132">
+        <v>139</v>
       </c>
       <c r="D132" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E132" s="1">
         <v>46207</v>
       </c>
-      <c r="E132" s="1">
-        <v>46206</v>
-      </c>
       <c r="F132">
-        <v>20105</v>
+        <v>20008</v>
       </c>
       <c r="G132">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H132">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I132">
-        <v>-14</v>
+        <v>1</v>
       </c>
       <c r="J132">
-        <v>0.65</v>
+        <v>1.0476190480000001</v>
       </c>
       <c r="K132">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L132">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M132">
-        <v>-14</v>
+        <v>1</v>
       </c>
       <c r="N132">
-        <v>0.65</v>
+        <v>1.0476190480000001</v>
       </c>
       <c r="O132" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>9985</v>
+        <v>10009</v>
       </c>
       <c r="B133">
-        <v>310</v>
-      </c>
-      <c r="C133" t="s">
-        <v>68</v>
+        <v>137</v>
+      </c>
+      <c r="C133">
+        <v>137</v>
       </c>
       <c r="D133" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E133" s="1">
         <v>46207</v>
       </c>
-      <c r="E133" s="1">
-        <v>46206</v>
-      </c>
       <c r="F133">
-        <v>20155</v>
+        <v>20003</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H133">
+        <v>12</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
         <v>1</v>
       </c>
-      <c r="I133">
+      <c r="K133">
+        <v>12</v>
+      </c>
+      <c r="L133">
+        <v>12</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
         <v>1</v>
       </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>1</v>
-      </c>
-      <c r="M133">
-        <v>1</v>
-      </c>
       <c r="O133" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>9986</v>
+        <v>10085</v>
       </c>
       <c r="B134">
-        <v>311</v>
-      </c>
-      <c r="C134" t="s">
-        <v>55</v>
+        <v>226</v>
+      </c>
+      <c r="C134">
+        <v>226</v>
       </c>
       <c r="D134" s="1">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="E134" s="1">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="F134">
-        <v>20057</v>
+        <v>20111</v>
       </c>
       <c r="G134">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="H134">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="I134">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="J134">
-        <v>0.94545454500000004</v>
+        <v>0.69230769199999997</v>
       </c>
       <c r="K134">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="L134">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="M134">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="N134">
-        <v>0.94545454500000004</v>
+        <v>0.69230769199999997</v>
       </c>
       <c r="O134" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>9995</v>
+        <v>9982</v>
       </c>
       <c r="B135">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="C135" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="D135" s="1">
         <v>46207</v>
@@ -6704,283 +6872,283 @@
         <v>46206</v>
       </c>
       <c r="F135">
-        <v>20066</v>
+        <v>20106</v>
       </c>
       <c r="G135">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H135">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I135">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="J135">
-        <v>1</v>
+        <v>0.84615384599999999</v>
       </c>
       <c r="K135">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L135">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="M135">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N135">
-        <v>1</v>
+        <v>0.84615384599999999</v>
       </c>
       <c r="O135" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>10008</v>
+        <v>9983</v>
       </c>
       <c r="B136">
-        <v>136</v>
-      </c>
-      <c r="C136">
-        <v>136</v>
+        <v>306</v>
+      </c>
+      <c r="C136" t="s">
+        <v>67</v>
       </c>
       <c r="D136" s="1">
-        <v>46209</v>
+        <v>46207</v>
       </c>
       <c r="E136" s="1">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="F136">
-        <v>20111</v>
+        <v>20105</v>
       </c>
       <c r="G136">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H136">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I136">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="J136">
-        <v>0.54054054100000004</v>
+        <v>0.65</v>
       </c>
       <c r="K136">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L136">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M136">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="N136">
-        <v>0.54054054100000004</v>
+        <v>0.65</v>
       </c>
       <c r="O136" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>9898</v>
+        <v>9985</v>
       </c>
       <c r="B137">
-        <v>332</v>
-      </c>
-      <c r="C137">
-        <v>332</v>
+        <v>310</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
       </c>
       <c r="D137" s="1">
-        <v>46204</v>
+        <v>46207</v>
       </c>
       <c r="E137" s="1">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="F137">
-        <v>20130</v>
+        <v>20155</v>
       </c>
       <c r="G137">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H137">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I137">
-        <v>-5</v>
-      </c>
-      <c r="J137">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K137">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L137">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M137">
-        <v>-5</v>
-      </c>
-      <c r="N137">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O137" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>9910</v>
+        <v>9986</v>
       </c>
       <c r="B138">
-        <v>103</v>
+        <v>311</v>
       </c>
       <c r="C138" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="D138" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E138" s="1">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="F138">
-        <v>20153</v>
+        <v>20057</v>
       </c>
       <c r="G138">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H138">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="I138">
-        <v>-19</v>
+        <v>-3</v>
       </c>
       <c r="J138">
-        <v>0.58695652200000004</v>
+        <v>0.94545454500000004</v>
       </c>
       <c r="K138">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="L138">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="M138">
-        <v>-19</v>
+        <v>-3</v>
       </c>
       <c r="N138">
-        <v>0.58695652200000004</v>
+        <v>0.94545454500000004</v>
       </c>
       <c r="O138" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>9933</v>
+        <v>9995</v>
       </c>
       <c r="B139">
-        <v>800</v>
+        <v>320</v>
       </c>
       <c r="C139" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="D139" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="E139" s="1">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F139">
-        <v>200150</v>
+        <v>20066</v>
       </c>
       <c r="G139">
         <v>1</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I139">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K139">
         <v>1</v>
       </c>
       <c r="L139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>9936</v>
+        <v>10008</v>
       </c>
       <c r="B140">
-        <v>800</v>
-      </c>
-      <c r="C140" t="s">
-        <v>62</v>
+        <v>136</v>
+      </c>
+      <c r="C140">
+        <v>136</v>
       </c>
       <c r="D140" s="1">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="E140" s="1">
-        <v>46205</v>
+        <v>46207</v>
       </c>
       <c r="F140">
-        <v>200150</v>
+        <v>20111</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I140">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="J140">
+        <v>0.54054054100000004</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L140">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M140">
-        <v>0</v>
+        <v>-17</v>
+      </c>
+      <c r="N140">
+        <v>0.54054054100000004</v>
       </c>
       <c r="O140" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>9937</v>
+        <v>10093</v>
       </c>
       <c r="B141">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="C141" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D141" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E141" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F141">
-        <v>200150</v>
+        <v>20048</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -7001,427 +7169,373 @@
         <v>0</v>
       </c>
       <c r="O141" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>9921</v>
+        <v>10096</v>
       </c>
       <c r="B142">
-        <v>114</v>
+        <v>404</v>
       </c>
       <c r="C142" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="D142" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E142" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F142">
-        <v>20048</v>
+        <v>20086</v>
       </c>
       <c r="G142">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H142">
         <v>0</v>
       </c>
       <c r="I142">
-        <v>-28</v>
-      </c>
-      <c r="J142">
         <v>0</v>
       </c>
       <c r="K142">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
       <c r="M142">
-        <v>-28</v>
-      </c>
-      <c r="N142">
         <v>0</v>
       </c>
       <c r="O142" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>9911</v>
+        <v>10103</v>
       </c>
       <c r="B143">
-        <v>104</v>
+        <v>412</v>
       </c>
       <c r="C143" t="s">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="D143" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E143" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F143">
-        <v>20105</v>
+        <v>20086</v>
       </c>
       <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="O143" t="s">
         <v>54</v>
-      </c>
-      <c r="H143">
-        <v>37</v>
-      </c>
-      <c r="I143">
-        <v>-17</v>
-      </c>
-      <c r="J143">
-        <v>0.68518518500000003</v>
-      </c>
-      <c r="K143">
-        <v>54</v>
-      </c>
-      <c r="L143">
-        <v>37</v>
-      </c>
-      <c r="M143">
-        <v>-17</v>
-      </c>
-      <c r="N143">
-        <v>0.68518518500000003</v>
-      </c>
-      <c r="O143" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>9912</v>
+        <v>10129</v>
       </c>
       <c r="B144">
-        <v>105</v>
-      </c>
-      <c r="C144" t="s">
-        <v>33</v>
+        <v>329</v>
+      </c>
+      <c r="C144">
+        <v>329</v>
       </c>
       <c r="D144" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E144" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F144">
-        <v>20058</v>
+        <v>20008</v>
       </c>
       <c r="G144">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H144">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I144">
-        <v>-28</v>
-      </c>
-      <c r="J144">
-        <v>0.41666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K144">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L144">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M144">
-        <v>-28</v>
-      </c>
-      <c r="N144">
-        <v>0.41666666699999999</v>
+        <v>0</v>
       </c>
       <c r="O144" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>9914</v>
+        <v>10130</v>
       </c>
       <c r="B145">
-        <v>107</v>
-      </c>
-      <c r="C145" t="s">
-        <v>37</v>
+        <v>330</v>
+      </c>
+      <c r="C145">
+        <v>330</v>
       </c>
       <c r="D145" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E145" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F145">
-        <v>20155</v>
+        <v>20005</v>
       </c>
       <c r="G145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145">
         <v>0</v>
       </c>
-      <c r="J145">
-        <v>1</v>
-      </c>
       <c r="K145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145">
         <v>0</v>
       </c>
-      <c r="N145">
-        <v>1</v>
-      </c>
       <c r="O145" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>9915</v>
+        <v>10131</v>
       </c>
       <c r="B146">
-        <v>108</v>
+        <v>412</v>
       </c>
       <c r="C146" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="D146" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E146" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F146">
-        <v>20057</v>
+        <v>20086</v>
       </c>
       <c r="G146">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I146">
-        <v>-9</v>
-      </c>
-      <c r="J146">
-        <v>0.87323943699999995</v>
+        <v>0</v>
       </c>
       <c r="K146">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L146">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M146">
-        <v>-9</v>
-      </c>
-      <c r="N146">
-        <v>0.87323943699999995</v>
+        <v>0</v>
       </c>
       <c r="O146" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>9916</v>
+        <v>10132</v>
       </c>
       <c r="B147">
-        <v>109</v>
+        <v>404</v>
       </c>
       <c r="C147" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="D147" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E147" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F147">
-        <v>20112</v>
+        <v>20086</v>
       </c>
       <c r="G147">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I147">
-        <v>-19</v>
-      </c>
-      <c r="J147">
-        <v>0.38709677399999998</v>
+        <v>0</v>
       </c>
       <c r="K147">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L147">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M147">
-        <v>-19</v>
-      </c>
-      <c r="N147">
-        <v>0.38709677399999998</v>
+        <v>0</v>
       </c>
       <c r="O147" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>9917</v>
+        <v>10121</v>
       </c>
       <c r="B148">
-        <v>110</v>
+        <v>321</v>
       </c>
       <c r="C148" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="D148" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E148" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F148">
-        <v>20066</v>
+        <v>20006</v>
       </c>
       <c r="G148">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H148">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I148">
-        <v>-18</v>
-      </c>
-      <c r="J148">
-        <v>0.60869565199999998</v>
+        <v>0</v>
       </c>
       <c r="K148">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L148">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M148">
-        <v>-18</v>
-      </c>
-      <c r="N148">
-        <v>0.60869565199999998</v>
+        <v>0</v>
       </c>
       <c r="O148" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>9919</v>
+        <v>10122</v>
       </c>
       <c r="B149">
-        <v>112</v>
+        <v>322</v>
       </c>
       <c r="C149" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="D149" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E149" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F149">
-        <v>20106</v>
+        <v>20130</v>
       </c>
       <c r="G149">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I149">
-        <v>-37</v>
-      </c>
-      <c r="J149">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="K149">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L149">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M149">
-        <v>-37</v>
-      </c>
-      <c r="N149">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="O149" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>9924</v>
+        <v>10123</v>
       </c>
       <c r="B150">
-        <v>133</v>
-      </c>
-      <c r="C150">
-        <v>133</v>
+        <v>323</v>
+      </c>
+      <c r="C150" t="s">
+        <v>93</v>
       </c>
       <c r="D150" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E150" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F150">
         <v>200158</v>
       </c>
       <c r="G150">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H150">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I150">
         <v>0</v>
       </c>
-      <c r="J150">
-        <v>1</v>
-      </c>
       <c r="K150">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L150">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M150">
         <v>0</v>
-      </c>
-      <c r="N150">
-        <v>1</v>
       </c>
       <c r="O150" t="s">
         <v>23</v>
@@ -7429,210 +7543,186 @@
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>9927</v>
+        <v>10124</v>
       </c>
       <c r="B151">
-        <v>137</v>
-      </c>
-      <c r="C151">
-        <v>137</v>
+        <v>324</v>
+      </c>
+      <c r="C151" t="s">
+        <v>94</v>
       </c>
       <c r="D151" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E151" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F151">
-        <v>20003</v>
+        <v>20007</v>
       </c>
       <c r="G151">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H151">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I151">
-        <v>-5</v>
-      </c>
-      <c r="J151">
-        <v>0.70588235300000002</v>
+        <v>0</v>
       </c>
       <c r="K151">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L151">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M151">
-        <v>-5</v>
-      </c>
-      <c r="N151">
-        <v>0.70588235300000002</v>
+        <v>0</v>
       </c>
       <c r="O151" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>9928</v>
+        <v>10125</v>
       </c>
       <c r="B152">
-        <v>138</v>
-      </c>
-      <c r="C152">
-        <v>138</v>
+        <v>325</v>
+      </c>
+      <c r="C152" t="s">
+        <v>95</v>
       </c>
       <c r="D152" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E152" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F152">
-        <v>20007</v>
+        <v>20113</v>
       </c>
       <c r="G152">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H152">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I152">
-        <v>-9</v>
-      </c>
-      <c r="J152">
-        <v>0.70967741900000003</v>
+        <v>0</v>
       </c>
       <c r="K152">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L152">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M152">
-        <v>-9</v>
-      </c>
-      <c r="N152">
-        <v>0.70967741900000003</v>
+        <v>0</v>
       </c>
       <c r="O152" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>9929</v>
+        <v>10126</v>
       </c>
       <c r="B153">
-        <v>139</v>
+        <v>326</v>
       </c>
       <c r="C153">
-        <v>139</v>
+        <v>326</v>
       </c>
       <c r="D153" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E153" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F153">
-        <v>20008</v>
+        <v>20111</v>
       </c>
       <c r="G153">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I153">
-        <v>-6</v>
-      </c>
-      <c r="J153">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K153">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L153">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M153">
-        <v>-6</v>
-      </c>
-      <c r="N153">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="O153" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>9923</v>
+        <v>10127</v>
       </c>
       <c r="B154">
-        <v>132</v>
+        <v>327</v>
       </c>
       <c r="C154">
-        <v>132</v>
+        <v>327</v>
       </c>
       <c r="D154" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E154" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F154">
-        <v>20130</v>
+        <v>20003</v>
       </c>
       <c r="G154">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I154">
-        <v>-2</v>
-      </c>
-      <c r="J154">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K154">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L154">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M154">
-        <v>-2</v>
-      </c>
-      <c r="N154">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O154" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>10001</v>
+        <v>10128</v>
       </c>
       <c r="B155">
-        <v>500</v>
-      </c>
-      <c r="C155" t="s">
-        <v>78</v>
+        <v>328</v>
+      </c>
+      <c r="C155">
+        <v>328</v>
       </c>
       <c r="D155" s="1">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="E155" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="F155">
-        <v>20111</v>
+        <v>20112</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -7653,27 +7743,27 @@
         <v>0</v>
       </c>
       <c r="O155" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>9935</v>
+        <v>10104</v>
       </c>
       <c r="B156">
-        <v>502</v>
+        <v>413</v>
       </c>
       <c r="C156" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D156" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E156" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F156">
-        <v>20043</v>
+        <v>20106</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -7694,168 +7784,150 @@
         <v>0</v>
       </c>
       <c r="O156" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>9920</v>
+        <v>10105</v>
       </c>
       <c r="B157">
-        <v>113</v>
+        <v>415</v>
       </c>
       <c r="C157" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="D157" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E157" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F157">
-        <v>20095</v>
+        <v>20153</v>
       </c>
       <c r="G157">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="O157" t="s">
         <v>30</v>
-      </c>
-      <c r="I157">
-        <v>-14</v>
-      </c>
-      <c r="J157">
-        <v>0.68181818199999999</v>
-      </c>
-      <c r="K157">
-        <v>44</v>
-      </c>
-      <c r="L157">
-        <v>30</v>
-      </c>
-      <c r="M157">
-        <v>-14</v>
-      </c>
-      <c r="N157">
-        <v>0.68181818199999999</v>
-      </c>
-      <c r="O157" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>9909</v>
+        <v>10106</v>
       </c>
       <c r="B158">
-        <v>102</v>
+        <v>416</v>
       </c>
       <c r="C158" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="D158" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E158" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F158">
-        <v>20086</v>
+        <v>20095</v>
       </c>
       <c r="G158">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I158">
-        <v>-7</v>
-      </c>
-      <c r="J158">
-        <v>0.87272727299999997</v>
+        <v>0</v>
       </c>
       <c r="K158">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L158">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M158">
-        <v>-7</v>
-      </c>
-      <c r="N158">
-        <v>0.87272727299999997</v>
+        <v>0</v>
       </c>
       <c r="O158" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>9922</v>
+        <v>10107</v>
       </c>
       <c r="B159">
-        <v>131</v>
-      </c>
-      <c r="C159">
-        <v>131</v>
+        <v>417</v>
+      </c>
+      <c r="C159" t="s">
+        <v>111</v>
       </c>
       <c r="D159" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E159" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F159">
-        <v>20005</v>
+        <v>20043</v>
       </c>
       <c r="G159">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I159">
-        <v>-5</v>
-      </c>
-      <c r="J159">
-        <v>0.76190476200000001</v>
+        <v>0</v>
       </c>
       <c r="K159">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L159">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M159">
-        <v>-5</v>
-      </c>
-      <c r="N159">
-        <v>0.76190476200000001</v>
+        <v>0</v>
       </c>
       <c r="O159" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>9934</v>
+        <v>10108</v>
       </c>
       <c r="B160">
-        <v>500</v>
+        <v>418</v>
       </c>
       <c r="C160" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D160" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E160" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F160">
-        <v>20006</v>
+        <v>20058</v>
       </c>
       <c r="G160">
         <v>0</v>
@@ -7876,98 +7948,86 @@
         <v>0</v>
       </c>
       <c r="O160" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>9930</v>
+        <v>10109</v>
       </c>
       <c r="B161">
-        <v>140</v>
-      </c>
-      <c r="C161">
-        <v>140</v>
+        <v>419</v>
+      </c>
+      <c r="C161" t="s">
+        <v>113</v>
       </c>
       <c r="D161" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E161" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F161">
-        <v>20006</v>
+        <v>11215</v>
       </c>
       <c r="G161">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I161">
-        <v>-1</v>
-      </c>
-      <c r="J161">
-        <v>0.96774193500000005</v>
+        <v>0</v>
       </c>
       <c r="K161">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L161">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M161">
-        <v>-1</v>
-      </c>
-      <c r="N161">
-        <v>0.96774193500000005</v>
+        <v>0</v>
       </c>
       <c r="O161" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>9908</v>
+        <v>10113</v>
       </c>
       <c r="B162">
-        <v>101</v>
+        <v>423</v>
       </c>
       <c r="C162" t="s">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="D162" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E162" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F162">
         <v>20076</v>
       </c>
       <c r="G162">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I162">
-        <v>-6</v>
-      </c>
-      <c r="J162">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K162">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L162">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M162">
-        <v>-6</v>
-      </c>
-      <c r="N162">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="O162" t="s">
         <v>20</v>
@@ -7975,160 +8035,142 @@
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>9913</v>
+        <v>10114</v>
       </c>
       <c r="B163">
-        <v>106</v>
+        <v>424</v>
       </c>
       <c r="C163" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="D163" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E163" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F163">
-        <v>11215</v>
+        <v>20105</v>
       </c>
       <c r="G163">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="O163" t="s">
         <v>32</v>
-      </c>
-      <c r="I163">
-        <v>-29</v>
-      </c>
-      <c r="J163">
-        <v>0.52459016400000003</v>
-      </c>
-      <c r="K163">
-        <v>61</v>
-      </c>
-      <c r="L163">
-        <v>32</v>
-      </c>
-      <c r="M163">
-        <v>-29</v>
-      </c>
-      <c r="N163">
-        <v>0.52459016400000003</v>
-      </c>
-      <c r="O163" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>9902</v>
+        <v>10115</v>
       </c>
       <c r="B164">
-        <v>336</v>
-      </c>
-      <c r="C164">
-        <v>336</v>
+        <v>425</v>
+      </c>
+      <c r="C164" t="s">
+        <v>116</v>
       </c>
       <c r="D164" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="E164" s="1">
-        <v>46203</v>
+        <v>46213</v>
       </c>
       <c r="F164">
-        <v>20111</v>
+        <v>20155</v>
       </c>
       <c r="G164">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I164">
-        <v>-5</v>
-      </c>
-      <c r="J164">
-        <v>0.73684210500000002</v>
+        <v>0</v>
       </c>
       <c r="K164">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L164">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M164">
-        <v>-5</v>
-      </c>
-      <c r="N164">
-        <v>0.73684210500000002</v>
+        <v>0</v>
       </c>
       <c r="O164" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>9904</v>
+        <v>10116</v>
       </c>
       <c r="B165">
-        <v>338</v>
+        <v>426</v>
       </c>
       <c r="C165">
-        <v>338</v>
+        <v>426</v>
       </c>
       <c r="D165" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="E165" s="1">
-        <v>46203</v>
+        <v>46213</v>
       </c>
       <c r="F165">
-        <v>20007</v>
+        <v>20066</v>
       </c>
       <c r="G165">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I165">
-        <v>-7</v>
-      </c>
-      <c r="J165">
-        <v>0.68181818199999999</v>
+        <v>0</v>
       </c>
       <c r="K165">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L165">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M165">
-        <v>-7</v>
-      </c>
-      <c r="N165">
-        <v>0.68181818199999999</v>
+        <v>0</v>
       </c>
       <c r="O165" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>9949</v>
+        <v>10117</v>
       </c>
       <c r="B166">
-        <v>215</v>
+        <v>503</v>
       </c>
       <c r="C166" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D166" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E166" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F166">
         <v>200150</v>
@@ -8157,22 +8199,22 @@
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>9965</v>
+        <v>10118</v>
       </c>
       <c r="B167">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C167" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D167" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E167" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="F167">
-        <v>20086</v>
+        <v>200150</v>
       </c>
       <c r="G167">
         <v>0</v>
@@ -8193,623 +8235,545 @@
         <v>0</v>
       </c>
       <c r="O167" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>9925</v>
+        <v>10119</v>
       </c>
       <c r="B168">
-        <v>135</v>
-      </c>
-      <c r="C168">
-        <v>135</v>
+        <v>505</v>
+      </c>
+      <c r="C168" t="s">
+        <v>64</v>
       </c>
       <c r="D168" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E168" s="1">
-        <v>46204</v>
+        <v>46213</v>
       </c>
       <c r="F168">
-        <v>20113</v>
+        <v>200150</v>
       </c>
       <c r="G168">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I168">
-        <v>-4</v>
-      </c>
-      <c r="J168">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="K168">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L168">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M168">
-        <v>-4</v>
-      </c>
-      <c r="N168">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="O168" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>9938</v>
+        <v>10120</v>
       </c>
       <c r="B169">
-        <v>201</v>
+        <v>506</v>
       </c>
       <c r="C169" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="D169" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E169" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F169">
-        <v>20155</v>
+        <v>200150</v>
       </c>
       <c r="G169">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I169">
-        <v>-4</v>
-      </c>
-      <c r="J169">
-        <v>0.89473684200000003</v>
+        <v>0</v>
       </c>
       <c r="K169">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L169">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M169">
-        <v>-4</v>
-      </c>
-      <c r="N169">
-        <v>0.89473684200000003</v>
+        <v>0</v>
       </c>
       <c r="O169" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>9939</v>
+        <v>10094</v>
       </c>
       <c r="B170">
-        <v>202</v>
+        <v>402</v>
       </c>
       <c r="C170" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D170" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E170" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F170">
-        <v>20057</v>
+        <v>20058</v>
       </c>
       <c r="G170">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I170">
-        <v>-2</v>
-      </c>
-      <c r="J170">
-        <v>0.95454545499999999</v>
+        <v>0</v>
       </c>
       <c r="K170">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L170">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M170">
-        <v>-2</v>
-      </c>
-      <c r="N170">
-        <v>0.95454545499999999</v>
+        <v>0</v>
       </c>
       <c r="O170" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>9940</v>
+        <v>10095</v>
       </c>
       <c r="B171">
-        <v>203</v>
+        <v>403</v>
       </c>
       <c r="C171" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="D171" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E171" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F171">
-        <v>20086</v>
+        <v>20047</v>
       </c>
       <c r="G171">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I171">
-        <v>-9</v>
-      </c>
-      <c r="J171">
-        <v>0.76315789499999998</v>
+        <v>0</v>
       </c>
       <c r="K171">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L171">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M171">
-        <v>-9</v>
-      </c>
-      <c r="N171">
-        <v>0.76315789499999998</v>
+        <v>0</v>
       </c>
       <c r="O171" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>9941</v>
+        <v>10097</v>
       </c>
       <c r="B172">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="C172" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="D172" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E172" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F172">
-        <v>20058</v>
+        <v>20106</v>
       </c>
       <c r="G172">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I172">
-        <v>-39</v>
-      </c>
-      <c r="J172">
-        <v>0.409090909</v>
+        <v>0</v>
       </c>
       <c r="K172">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L172">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M172">
-        <v>-39</v>
-      </c>
-      <c r="N172">
-        <v>0.409090909</v>
+        <v>0</v>
       </c>
       <c r="O172" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>9987</v>
+        <v>10098</v>
       </c>
       <c r="B173">
-        <v>312</v>
+        <v>406</v>
       </c>
       <c r="C173" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="D173" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E173" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="F173">
-        <v>20086</v>
+        <v>20105</v>
       </c>
       <c r="G173">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I173">
-        <v>2</v>
-      </c>
-      <c r="J173">
-        <v>1.095238095</v>
+        <v>0</v>
       </c>
       <c r="K173">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L173">
         <v>0</v>
       </c>
       <c r="M173">
-        <v>-21</v>
-      </c>
-      <c r="N173">
         <v>0</v>
       </c>
       <c r="O173" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>9944</v>
+        <v>10099</v>
       </c>
       <c r="B174">
-        <v>207</v>
+        <v>407</v>
       </c>
       <c r="C174" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D174" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E174" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F174">
-        <v>20105</v>
+        <v>11215</v>
       </c>
       <c r="G174">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H174">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I174">
-        <v>-1</v>
-      </c>
-      <c r="J174">
-        <v>0.96969696999999999</v>
+        <v>0</v>
       </c>
       <c r="K174">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L174">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M174">
-        <v>-1</v>
-      </c>
-      <c r="N174">
-        <v>0.96969696999999999</v>
+        <v>0</v>
       </c>
       <c r="O174" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>9945</v>
+        <v>10100</v>
       </c>
       <c r="B175">
-        <v>208</v>
+        <v>409</v>
       </c>
       <c r="C175" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="D175" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E175" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F175">
-        <v>20076</v>
+        <v>20043</v>
       </c>
       <c r="G175">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I175">
-        <v>-9</v>
-      </c>
-      <c r="J175">
-        <v>0.76923076899999998</v>
+        <v>0</v>
       </c>
       <c r="K175">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L175">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M175">
-        <v>-9</v>
-      </c>
-      <c r="N175">
-        <v>0.76923076899999998</v>
+        <v>0</v>
       </c>
       <c r="O175" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>9947</v>
+        <v>10101</v>
       </c>
       <c r="B176">
-        <v>213</v>
+        <v>410</v>
       </c>
       <c r="C176" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="D176" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E176" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F176">
-        <v>20066</v>
+        <v>20155</v>
       </c>
       <c r="G176">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H176">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I176">
-        <v>-15</v>
-      </c>
-      <c r="J176">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="K176">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L176">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M176">
-        <v>-15</v>
-      </c>
-      <c r="N176">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="O176" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>9960</v>
+        <v>10102</v>
       </c>
       <c r="B177">
-        <v>240</v>
-      </c>
-      <c r="C177">
-        <v>240</v>
+        <v>411</v>
+      </c>
+      <c r="C177" t="s">
+        <v>126</v>
       </c>
       <c r="D177" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E177" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F177">
-        <v>20006</v>
+        <v>20057</v>
       </c>
       <c r="G177">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I177">
-        <v>-2</v>
-      </c>
-      <c r="J177">
-        <v>0.92592592600000001</v>
+        <v>0</v>
       </c>
       <c r="K177">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L177">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M177">
-        <v>-2</v>
-      </c>
-      <c r="N177">
-        <v>0.92592592600000001</v>
+        <v>0</v>
       </c>
       <c r="O177" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>9957</v>
+        <v>10110</v>
       </c>
       <c r="B178">
-        <v>237</v>
-      </c>
-      <c r="C178">
-        <v>237</v>
+        <v>420</v>
+      </c>
+      <c r="C178" t="s">
+        <v>127</v>
       </c>
       <c r="D178" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E178" s="1">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F178">
-        <v>20003</v>
+        <v>20066</v>
       </c>
       <c r="G178">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I178">
-        <v>-17</v>
-      </c>
-      <c r="J178">
-        <v>0.59523809500000002</v>
+        <v>0</v>
       </c>
       <c r="K178">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L178">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M178">
-        <v>-17</v>
-      </c>
-      <c r="N178">
-        <v>0.59523809500000002</v>
+        <v>0</v>
       </c>
       <c r="O178" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>9994</v>
+        <v>10111</v>
       </c>
       <c r="B179">
-        <v>319</v>
+        <v>421</v>
       </c>
       <c r="C179" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="D179" s="1">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="E179" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="F179">
-        <v>11215</v>
+        <v>20153</v>
       </c>
       <c r="G179">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H179">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I179">
-        <v>-5</v>
-      </c>
-      <c r="J179">
-        <v>0.76190476200000001</v>
+        <v>0</v>
       </c>
       <c r="K179">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L179">
         <v>0</v>
       </c>
       <c r="M179">
-        <v>-21</v>
-      </c>
-      <c r="N179">
         <v>0</v>
       </c>
       <c r="O179" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>9992</v>
+        <v>10112</v>
       </c>
       <c r="B180">
-        <v>317</v>
+        <v>422</v>
       </c>
       <c r="C180" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="D180" s="1">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="E180" s="1">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="F180">
-        <v>20043</v>
+        <v>20048</v>
       </c>
       <c r="G180">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H180">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I180">
-        <v>-1</v>
-      </c>
-      <c r="J180">
-        <v>0.95238095199999995</v>
+        <v>0</v>
       </c>
       <c r="K180">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L180">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M180">
-        <v>-1</v>
-      </c>
-      <c r="N180">
-        <v>0.95238095199999995</v>
+        <v>0</v>
       </c>
       <c r="O180" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>9969</v>
+        <v>9898</v>
       </c>
       <c r="B181">
         <v>332</v>
@@ -8818,31 +8782,37 @@
         <v>332</v>
       </c>
       <c r="D181" s="1">
-        <v>46207</v>
+        <v>46204</v>
       </c>
       <c r="E181" s="1">
-        <v>46206</v>
+        <v>46203</v>
       </c>
       <c r="F181">
         <v>20130</v>
       </c>
       <c r="G181">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I181">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J181">
+        <v>0.8</v>
       </c>
       <c r="K181">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L181">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M181">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N181">
+        <v>0.8</v>
       </c>
       <c r="O181" t="s">
         <v>22</v>
@@ -8850,101 +8820,101 @@
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>9977</v>
+        <v>9910</v>
       </c>
       <c r="B182">
-        <v>340</v>
-      </c>
-      <c r="C182">
-        <v>340</v>
+        <v>103</v>
+      </c>
+      <c r="C182" t="s">
+        <v>29</v>
       </c>
       <c r="D182" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="E182" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F182">
-        <v>20005</v>
+        <v>20153</v>
       </c>
       <c r="G182">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H182">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I182">
-        <v>1</v>
+        <v>-19</v>
       </c>
       <c r="J182">
-        <v>1.043478261</v>
+        <v>0.58695652200000004</v>
       </c>
       <c r="K182">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="L182">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M182">
-        <v>1</v>
+        <v>-19</v>
       </c>
       <c r="N182">
-        <v>1.043478261</v>
+        <v>0.58695652200000004</v>
       </c>
       <c r="O182" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>9997</v>
+        <v>9933</v>
       </c>
       <c r="B183">
-        <v>323</v>
+        <v>800</v>
       </c>
       <c r="C183" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="D183" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="E183" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="F183">
-        <v>20076</v>
+        <v>200150</v>
       </c>
       <c r="G183">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H183">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I183">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
         <v>1</v>
       </c>
-      <c r="K183">
-        <v>32</v>
-      </c>
       <c r="L183">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M183">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O183" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>10014</v>
+        <v>9936</v>
       </c>
       <c r="B184">
         <v>800</v>
@@ -8953,10 +8923,10 @@
         <v>62</v>
       </c>
       <c r="D184" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="E184" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="F184">
         <v>200150</v>
@@ -8985,910 +8955,2717 @@
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>10010</v>
+        <v>9937</v>
       </c>
       <c r="B185">
-        <v>138</v>
-      </c>
-      <c r="C185">
-        <v>138</v>
+        <v>800</v>
+      </c>
+      <c r="C185" t="s">
+        <v>62</v>
       </c>
       <c r="D185" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="E185" s="1">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="F185">
-        <v>20007</v>
+        <v>200150</v>
       </c>
       <c r="G185">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I185">
-        <v>-10</v>
-      </c>
-      <c r="J185">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="K185">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L185">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M185">
-        <v>-10</v>
-      </c>
-      <c r="N185">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="O185" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>9962</v>
+        <v>9921</v>
       </c>
       <c r="B186">
-        <v>504</v>
+        <v>114</v>
       </c>
       <c r="C186" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D186" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E186" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F186">
-        <v>200150</v>
+        <v>20048</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H186">
         <v>0</v>
       </c>
       <c r="I186">
+        <v>-28</v>
+      </c>
+      <c r="J186">
         <v>0</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L186">
         <v>0</v>
       </c>
       <c r="M186">
+        <v>-28</v>
+      </c>
+      <c r="N186">
         <v>0</v>
       </c>
       <c r="O186" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>9956</v>
+        <v>9911</v>
       </c>
       <c r="B187">
-        <v>236</v>
-      </c>
-      <c r="C187">
-        <v>236</v>
+        <v>104</v>
+      </c>
+      <c r="C187" t="s">
+        <v>31</v>
       </c>
       <c r="D187" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E187" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F187">
-        <v>20111</v>
+        <v>20105</v>
       </c>
       <c r="G187">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H187">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I187">
-        <v>-8</v>
+        <v>-17</v>
       </c>
       <c r="J187">
-        <v>0.72413793100000001</v>
+        <v>0.68518518500000003</v>
       </c>
       <c r="K187">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="L187">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M187">
-        <v>-8</v>
+        <v>-17</v>
       </c>
       <c r="N187">
-        <v>0.72413793100000001</v>
+        <v>0.68518518500000003</v>
       </c>
       <c r="O187" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>9954</v>
+        <v>9912</v>
       </c>
       <c r="B188">
-        <v>234</v>
-      </c>
-      <c r="C188">
-        <v>234</v>
+        <v>105</v>
+      </c>
+      <c r="C188" t="s">
+        <v>33</v>
       </c>
       <c r="D188" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E188" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F188">
-        <v>20112</v>
+        <v>20058</v>
       </c>
       <c r="G188">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H188">
         <v>20</v>
       </c>
       <c r="I188">
-        <v>-8</v>
+        <v>-28</v>
       </c>
       <c r="J188">
-        <v>0.71428571399999996</v>
+        <v>0.41666666699999999</v>
       </c>
       <c r="K188">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L188">
         <v>20</v>
       </c>
       <c r="M188">
-        <v>-8</v>
+        <v>-28</v>
       </c>
       <c r="N188">
-        <v>0.71428571399999996</v>
+        <v>0.41666666699999999</v>
       </c>
       <c r="O188" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>9948</v>
+        <v>9914</v>
       </c>
       <c r="B189">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="C189" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="D189" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E189" s="1">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="F189">
-        <v>11215</v>
+        <v>20155</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189">
         <v>1</v>
       </c>
       <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
         <v>1</v>
       </c>
       <c r="K189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L189">
         <v>1</v>
       </c>
       <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
         <v>1</v>
       </c>
       <c r="O189" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>10012</v>
+        <v>9915</v>
       </c>
       <c r="B190">
-        <v>140</v>
-      </c>
-      <c r="C190">
-        <v>140</v>
+        <v>108</v>
+      </c>
+      <c r="C190" t="s">
+        <v>39</v>
       </c>
       <c r="D190" s="1">
-        <v>46209</v>
+        <v>46205</v>
       </c>
       <c r="E190" s="1">
-        <v>46207</v>
+        <v>46204</v>
       </c>
       <c r="F190">
-        <v>20006</v>
+        <v>20057</v>
       </c>
       <c r="G190">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="H190">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="I190">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="J190">
-        <v>0.78571428600000004</v>
+        <v>0.87323943699999995</v>
       </c>
       <c r="K190">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="L190">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="M190">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="N190">
-        <v>0.78571428600000004</v>
+        <v>0.87323943699999995</v>
       </c>
       <c r="O190" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>10016</v>
+        <v>9916</v>
       </c>
       <c r="B191">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="C191" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="D191" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E191" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F191">
-        <v>20153</v>
+        <v>20112</v>
       </c>
       <c r="G191">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="H191">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="I191">
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="J191">
-        <v>0.70588235300000002</v>
+        <v>0.38709677399999998</v>
       </c>
       <c r="K191">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="L191">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="M191">
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="N191">
-        <v>0.70588235300000002</v>
+        <v>0.38709677399999998</v>
       </c>
       <c r="O191" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>10018</v>
+        <v>9917</v>
       </c>
       <c r="B192">
-        <v>203</v>
+        <v>110</v>
       </c>
       <c r="C192" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="D192" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E192" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F192">
-        <v>20155</v>
+        <v>20066</v>
       </c>
       <c r="G192">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="H192">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I192">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="J192">
-        <v>0.57692307700000001</v>
+        <v>0.60869565199999998</v>
       </c>
       <c r="K192">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="L192">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M192">
-        <v>-11</v>
+        <v>-18</v>
       </c>
       <c r="N192">
-        <v>0.57692307700000001</v>
+        <v>0.60869565199999998</v>
       </c>
       <c r="O192" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>10019</v>
+        <v>9919</v>
       </c>
       <c r="B193">
-        <v>204</v>
+        <v>112</v>
       </c>
       <c r="C193" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D193" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E193" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F193">
-        <v>20095</v>
+        <v>20106</v>
       </c>
       <c r="G193">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="H193">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="I193">
-        <v>-21</v>
+        <v>-37</v>
       </c>
       <c r="J193">
-        <v>0.63793103399999995</v>
+        <v>0.26</v>
       </c>
       <c r="K193">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="L193">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="M193">
-        <v>-21</v>
+        <v>-37</v>
       </c>
       <c r="N193">
-        <v>0.63793103399999995</v>
+        <v>0.26</v>
       </c>
       <c r="O193" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>10023</v>
+        <v>9924</v>
       </c>
       <c r="B194">
-        <v>208</v>
-      </c>
-      <c r="C194" t="s">
-        <v>85</v>
+        <v>133</v>
+      </c>
+      <c r="C194">
+        <v>133</v>
       </c>
       <c r="D194" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E194" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F194">
-        <v>11215</v>
+        <v>200158</v>
       </c>
       <c r="G194">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H194">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I194">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="J194">
-        <v>0.73913043499999997</v>
+        <v>1</v>
       </c>
       <c r="K194">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="L194">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="M194">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="N194">
-        <v>0.73913043499999997</v>
+        <v>1</v>
       </c>
       <c r="O194" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>10025</v>
+        <v>9927</v>
       </c>
       <c r="B195">
-        <v>210</v>
-      </c>
-      <c r="C195" t="s">
-        <v>97</v>
+        <v>137</v>
+      </c>
+      <c r="C195">
+        <v>137</v>
       </c>
       <c r="D195" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E195" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F195">
-        <v>20066</v>
+        <v>20003</v>
       </c>
       <c r="G195">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H195">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I195">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="J195">
-        <v>0.52</v>
+        <v>0.70588235300000002</v>
       </c>
       <c r="K195">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L195">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M195">
-        <v>-12</v>
+        <v>-5</v>
       </c>
       <c r="N195">
-        <v>0.52</v>
+        <v>0.70588235300000002</v>
       </c>
       <c r="O195" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>10024</v>
+        <v>9928</v>
       </c>
       <c r="B196">
-        <v>209</v>
-      </c>
-      <c r="C196" t="s">
-        <v>96</v>
+        <v>138</v>
+      </c>
+      <c r="C196">
+        <v>138</v>
       </c>
       <c r="D196" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E196" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F196">
-        <v>20105</v>
+        <v>20007</v>
       </c>
       <c r="G196">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H196">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I196">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="J196">
-        <v>0.83333333300000001</v>
+        <v>0.70967741900000003</v>
       </c>
       <c r="K196">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="L196">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M196">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="N196">
-        <v>0.83333333300000001</v>
+        <v>0.70967741900000003</v>
       </c>
       <c r="O196" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>10026</v>
+        <v>9929</v>
       </c>
       <c r="B197">
-        <v>211</v>
-      </c>
-      <c r="C197" t="s">
-        <v>98</v>
+        <v>139</v>
+      </c>
+      <c r="C197">
+        <v>139</v>
       </c>
       <c r="D197" s="1">
-        <v>46210</v>
+        <v>46205</v>
       </c>
       <c r="E197" s="1">
-        <v>46209</v>
+        <v>46204</v>
       </c>
       <c r="F197">
-        <v>20058</v>
+        <v>20008</v>
       </c>
       <c r="G197">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="H197">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I197">
-        <v>-39</v>
+        <v>-6</v>
       </c>
       <c r="J197">
-        <v>0.37096774199999999</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K197">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="L197">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M197">
-        <v>-39</v>
+        <v>-6</v>
       </c>
       <c r="N197">
-        <v>0.37096774199999999</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O197" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>9970</v>
+        <v>9923</v>
       </c>
       <c r="B198">
-        <v>333</v>
+        <v>132</v>
       </c>
       <c r="C198">
-        <v>333</v>
+        <v>132</v>
       </c>
       <c r="D198" s="1">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="E198" s="1">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="F198">
-        <v>200158</v>
+        <v>20130</v>
       </c>
       <c r="G198">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H198">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I198">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J198">
+        <v>0.8</v>
       </c>
       <c r="K198">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L198">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M198">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="N198">
+        <v>0.8</v>
       </c>
       <c r="O198" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>9971</v>
+        <v>10001</v>
       </c>
       <c r="B199">
-        <v>334</v>
-      </c>
-      <c r="C199">
-        <v>334</v>
+        <v>500</v>
+      </c>
+      <c r="C199" t="s">
+        <v>78</v>
       </c>
       <c r="D199" s="1">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="E199" s="1">
         <v>46206</v>
       </c>
       <c r="F199">
+        <v>20111</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
+      </c>
+      <c r="O199" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>9935</v>
+      </c>
+      <c r="B200">
+        <v>502</v>
+      </c>
+      <c r="C200" t="s">
+        <v>77</v>
+      </c>
+      <c r="D200" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E200" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F200">
+        <v>20043</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
+      </c>
+      <c r="O200" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>9920</v>
+      </c>
+      <c r="B201">
+        <v>113</v>
+      </c>
+      <c r="C201" t="s">
+        <v>48</v>
+      </c>
+      <c r="D201" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E201" s="1">
+        <v>46204</v>
+      </c>
+      <c r="F201">
+        <v>20095</v>
+      </c>
+      <c r="G201">
+        <v>44</v>
+      </c>
+      <c r="H201">
+        <v>30</v>
+      </c>
+      <c r="I201">
+        <v>-14</v>
+      </c>
+      <c r="J201">
+        <v>0.68181818199999999</v>
+      </c>
+      <c r="K201">
+        <v>44</v>
+      </c>
+      <c r="L201">
+        <v>30</v>
+      </c>
+      <c r="M201">
+        <v>-14</v>
+      </c>
+      <c r="N201">
+        <v>0.68181818199999999</v>
+      </c>
+      <c r="O201" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>9909</v>
+      </c>
+      <c r="B202">
+        <v>102</v>
+      </c>
+      <c r="C202" t="s">
+        <v>61</v>
+      </c>
+      <c r="D202" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E202" s="1">
+        <v>46204</v>
+      </c>
+      <c r="F202">
+        <v>20086</v>
+      </c>
+      <c r="G202">
+        <v>55</v>
+      </c>
+      <c r="H202">
+        <v>48</v>
+      </c>
+      <c r="I202">
+        <v>-7</v>
+      </c>
+      <c r="J202">
+        <v>0.87272727299999997</v>
+      </c>
+      <c r="K202">
+        <v>55</v>
+      </c>
+      <c r="L202">
+        <v>48</v>
+      </c>
+      <c r="M202">
+        <v>-7</v>
+      </c>
+      <c r="N202">
+        <v>0.87272727299999997</v>
+      </c>
+      <c r="O202" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>9922</v>
+      </c>
+      <c r="B203">
+        <v>131</v>
+      </c>
+      <c r="C203">
+        <v>131</v>
+      </c>
+      <c r="D203" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E203" s="1">
+        <v>46204</v>
+      </c>
+      <c r="F203">
+        <v>20005</v>
+      </c>
+      <c r="G203">
+        <v>21</v>
+      </c>
+      <c r="H203">
+        <v>16</v>
+      </c>
+      <c r="I203">
+        <v>-5</v>
+      </c>
+      <c r="J203">
+        <v>0.76190476200000001</v>
+      </c>
+      <c r="K203">
+        <v>21</v>
+      </c>
+      <c r="L203">
+        <v>16</v>
+      </c>
+      <c r="M203">
+        <v>-5</v>
+      </c>
+      <c r="N203">
+        <v>0.76190476200000001</v>
+      </c>
+      <c r="O203" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>9934</v>
+      </c>
+      <c r="B204">
+        <v>500</v>
+      </c>
+      <c r="C204" t="s">
+        <v>78</v>
+      </c>
+      <c r="D204" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E204" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F204">
+        <v>20006</v>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="O204" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>9930</v>
+      </c>
+      <c r="B205">
+        <v>140</v>
+      </c>
+      <c r="C205">
+        <v>140</v>
+      </c>
+      <c r="D205" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E205" s="1">
+        <v>46204</v>
+      </c>
+      <c r="F205">
+        <v>20006</v>
+      </c>
+      <c r="G205">
+        <v>31</v>
+      </c>
+      <c r="H205">
+        <v>30</v>
+      </c>
+      <c r="I205">
+        <v>-1</v>
+      </c>
+      <c r="J205">
+        <v>0.96774193500000005</v>
+      </c>
+      <c r="K205">
+        <v>31</v>
+      </c>
+      <c r="L205">
+        <v>30</v>
+      </c>
+      <c r="M205">
+        <v>-1</v>
+      </c>
+      <c r="N205">
+        <v>0.96774193500000005</v>
+      </c>
+      <c r="O205" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>9908</v>
+      </c>
+      <c r="B206">
+        <v>101</v>
+      </c>
+      <c r="C206" t="s">
+        <v>28</v>
+      </c>
+      <c r="D206" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E206" s="1">
+        <v>46204</v>
+      </c>
+      <c r="F206">
+        <v>20076</v>
+      </c>
+      <c r="G206">
+        <v>40</v>
+      </c>
+      <c r="H206">
+        <v>34</v>
+      </c>
+      <c r="I206">
+        <v>-6</v>
+      </c>
+      <c r="J206">
+        <v>0.85</v>
+      </c>
+      <c r="K206">
+        <v>40</v>
+      </c>
+      <c r="L206">
+        <v>34</v>
+      </c>
+      <c r="M206">
+        <v>-6</v>
+      </c>
+      <c r="N206">
+        <v>0.85</v>
+      </c>
+      <c r="O206" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>9913</v>
+      </c>
+      <c r="B207">
+        <v>106</v>
+      </c>
+      <c r="C207" t="s">
+        <v>35</v>
+      </c>
+      <c r="D207" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E207" s="1">
+        <v>46204</v>
+      </c>
+      <c r="F207">
+        <v>11215</v>
+      </c>
+      <c r="G207">
+        <v>61</v>
+      </c>
+      <c r="H207">
+        <v>32</v>
+      </c>
+      <c r="I207">
+        <v>-29</v>
+      </c>
+      <c r="J207">
+        <v>0.52459016400000003</v>
+      </c>
+      <c r="K207">
+        <v>61</v>
+      </c>
+      <c r="L207">
+        <v>32</v>
+      </c>
+      <c r="M207">
+        <v>-29</v>
+      </c>
+      <c r="N207">
+        <v>0.52459016400000003</v>
+      </c>
+      <c r="O207" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>9902</v>
+      </c>
+      <c r="B208">
+        <v>336</v>
+      </c>
+      <c r="C208">
+        <v>336</v>
+      </c>
+      <c r="D208" s="1">
+        <v>46204</v>
+      </c>
+      <c r="E208" s="1">
+        <v>46203</v>
+      </c>
+      <c r="F208">
+        <v>20111</v>
+      </c>
+      <c r="G208">
+        <v>19</v>
+      </c>
+      <c r="H208">
+        <v>14</v>
+      </c>
+      <c r="I208">
+        <v>-5</v>
+      </c>
+      <c r="J208">
+        <v>0.73684210500000002</v>
+      </c>
+      <c r="K208">
+        <v>19</v>
+      </c>
+      <c r="L208">
+        <v>14</v>
+      </c>
+      <c r="M208">
+        <v>-5</v>
+      </c>
+      <c r="N208">
+        <v>0.73684210500000002</v>
+      </c>
+      <c r="O208" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>9904</v>
+      </c>
+      <c r="B209">
+        <v>338</v>
+      </c>
+      <c r="C209">
+        <v>338</v>
+      </c>
+      <c r="D209" s="1">
+        <v>46204</v>
+      </c>
+      <c r="E209" s="1">
+        <v>46203</v>
+      </c>
+      <c r="F209">
         <v>20007</v>
       </c>
-      <c r="G199">
-        <v>0</v>
-      </c>
-      <c r="H199">
-        <v>0</v>
-      </c>
-      <c r="I199">
-        <v>0</v>
-      </c>
-      <c r="K199">
-        <v>0</v>
-      </c>
-      <c r="L199">
-        <v>0</v>
-      </c>
-      <c r="M199">
-        <v>0</v>
-      </c>
-      <c r="O199" t="s">
+      <c r="G209">
+        <v>22</v>
+      </c>
+      <c r="H209">
+        <v>15</v>
+      </c>
+      <c r="I209">
+        <v>-7</v>
+      </c>
+      <c r="J209">
+        <v>0.68181818199999999</v>
+      </c>
+      <c r="K209">
+        <v>22</v>
+      </c>
+      <c r="L209">
+        <v>15</v>
+      </c>
+      <c r="M209">
+        <v>-7</v>
+      </c>
+      <c r="N209">
+        <v>0.68181818199999999</v>
+      </c>
+      <c r="O209" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D200" s="1"/>
-      <c r="E200" s="1"/>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D201" s="1"/>
-      <c r="E201" s="1"/>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D202" s="1"/>
-      <c r="E202" s="1"/>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D203" s="1"/>
-      <c r="E203" s="1"/>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D204" s="1"/>
-      <c r="E204" s="1"/>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D205" s="1"/>
-      <c r="E205" s="1"/>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D206" s="1"/>
-      <c r="E206" s="1"/>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D207" s="1"/>
-      <c r="E207" s="1"/>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D208" s="1"/>
-      <c r="E208" s="1"/>
-    </row>
-    <row r="209" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D209" s="1"/>
-      <c r="E209" s="1"/>
-    </row>
-    <row r="210" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D210" s="1"/>
-      <c r="E210" s="1"/>
-    </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D211" s="1"/>
-      <c r="E211" s="1"/>
-    </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D212" s="1"/>
-      <c r="E212" s="1"/>
-    </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D213" s="1"/>
-      <c r="E213" s="1"/>
-    </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D214" s="1"/>
-      <c r="E214" s="1"/>
-    </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D215" s="1"/>
-      <c r="E215" s="1"/>
-    </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D216" s="1"/>
-      <c r="E216" s="1"/>
-    </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D217" s="1"/>
-      <c r="E217" s="1"/>
-    </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D218" s="1"/>
-      <c r="E218" s="1"/>
-    </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D219" s="1"/>
-      <c r="E219" s="1"/>
-    </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D220" s="1"/>
-      <c r="E220" s="1"/>
-    </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D221" s="1"/>
-      <c r="E221" s="1"/>
-    </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D222" s="1"/>
-      <c r="E222" s="1"/>
-    </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D223" s="1"/>
-      <c r="E223" s="1"/>
-    </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D224" s="1"/>
-      <c r="E224" s="1"/>
-    </row>
-    <row r="225" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D225" s="1"/>
-      <c r="E225" s="1"/>
-    </row>
-    <row r="226" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D226" s="1"/>
-      <c r="E226" s="1"/>
-    </row>
-    <row r="227" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D227" s="1"/>
-      <c r="E227" s="1"/>
-    </row>
-    <row r="228" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D228" s="1"/>
-      <c r="E228" s="1"/>
-    </row>
-    <row r="229" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D229" s="1"/>
-      <c r="E229" s="1"/>
-    </row>
-    <row r="230" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D230" s="1"/>
-      <c r="E230" s="1"/>
-    </row>
-    <row r="231" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D231" s="1"/>
-      <c r="E231" s="1"/>
-    </row>
-    <row r="232" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D232" s="1"/>
-      <c r="E232" s="1"/>
-    </row>
-    <row r="233" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D233" s="1"/>
-      <c r="E233" s="1"/>
-    </row>
-    <row r="234" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D234" s="1"/>
-      <c r="E234" s="1"/>
-    </row>
-    <row r="235" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D235" s="1"/>
-      <c r="E235" s="1"/>
-    </row>
-    <row r="236" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D236" s="1"/>
-      <c r="E236" s="1"/>
-    </row>
-    <row r="237" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D237" s="1"/>
-      <c r="E237" s="1"/>
-    </row>
-    <row r="238" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D238" s="1"/>
-      <c r="E238" s="1"/>
-    </row>
-    <row r="239" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D239" s="1"/>
-      <c r="E239" s="1"/>
-    </row>
-    <row r="240" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D240" s="1"/>
-      <c r="E240" s="1"/>
-    </row>
-    <row r="241" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D241" s="1"/>
-      <c r="E241" s="1"/>
-    </row>
-    <row r="242" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D242" s="1"/>
-      <c r="E242" s="1"/>
-    </row>
-    <row r="243" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>9949</v>
+      </c>
+      <c r="B210">
+        <v>215</v>
+      </c>
+      <c r="C210" t="s">
+        <v>79</v>
+      </c>
+      <c r="D210" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E210" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F210">
+        <v>200150</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+      <c r="M210">
+        <v>0</v>
+      </c>
+      <c r="O210" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>9965</v>
+      </c>
+      <c r="B211">
+        <v>502</v>
+      </c>
+      <c r="C211" t="s">
+        <v>77</v>
+      </c>
+      <c r="D211" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E211" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F211">
+        <v>20086</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="O211" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>9925</v>
+      </c>
+      <c r="B212">
+        <v>135</v>
+      </c>
+      <c r="C212">
+        <v>135</v>
+      </c>
+      <c r="D212" s="1">
+        <v>46205</v>
+      </c>
+      <c r="E212" s="1">
+        <v>46204</v>
+      </c>
+      <c r="F212">
+        <v>20113</v>
+      </c>
+      <c r="G212">
+        <v>16</v>
+      </c>
+      <c r="H212">
+        <v>12</v>
+      </c>
+      <c r="I212">
+        <v>-4</v>
+      </c>
+      <c r="J212">
+        <v>0.75</v>
+      </c>
+      <c r="K212">
+        <v>16</v>
+      </c>
+      <c r="L212">
+        <v>12</v>
+      </c>
+      <c r="M212">
+        <v>-4</v>
+      </c>
+      <c r="N212">
+        <v>0.75</v>
+      </c>
+      <c r="O212" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>9938</v>
+      </c>
+      <c r="B213">
+        <v>201</v>
+      </c>
+      <c r="C213" t="s">
+        <v>80</v>
+      </c>
+      <c r="D213" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E213" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F213">
+        <v>20155</v>
+      </c>
+      <c r="G213">
+        <v>38</v>
+      </c>
+      <c r="H213">
+        <v>34</v>
+      </c>
+      <c r="I213">
+        <v>-4</v>
+      </c>
+      <c r="J213">
+        <v>0.89473684200000003</v>
+      </c>
+      <c r="K213">
+        <v>38</v>
+      </c>
+      <c r="L213">
+        <v>34</v>
+      </c>
+      <c r="M213">
+        <v>-4</v>
+      </c>
+      <c r="N213">
+        <v>0.89473684200000003</v>
+      </c>
+      <c r="O213" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>9939</v>
+      </c>
+      <c r="B214">
+        <v>202</v>
+      </c>
+      <c r="C214" t="s">
+        <v>81</v>
+      </c>
+      <c r="D214" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E214" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F214">
+        <v>20057</v>
+      </c>
+      <c r="G214">
+        <v>44</v>
+      </c>
+      <c r="H214">
+        <v>42</v>
+      </c>
+      <c r="I214">
+        <v>-2</v>
+      </c>
+      <c r="J214">
+        <v>0.95454545499999999</v>
+      </c>
+      <c r="K214">
+        <v>44</v>
+      </c>
+      <c r="L214">
+        <v>42</v>
+      </c>
+      <c r="M214">
+        <v>-2</v>
+      </c>
+      <c r="N214">
+        <v>0.95454545499999999</v>
+      </c>
+      <c r="O214" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>9940</v>
+      </c>
+      <c r="B215">
+        <v>203</v>
+      </c>
+      <c r="C215" t="s">
+        <v>82</v>
+      </c>
+      <c r="D215" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E215" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F215">
+        <v>20086</v>
+      </c>
+      <c r="G215">
+        <v>38</v>
+      </c>
+      <c r="H215">
+        <v>29</v>
+      </c>
+      <c r="I215">
+        <v>-9</v>
+      </c>
+      <c r="J215">
+        <v>0.76315789499999998</v>
+      </c>
+      <c r="K215">
+        <v>38</v>
+      </c>
+      <c r="L215">
+        <v>29</v>
+      </c>
+      <c r="M215">
+        <v>-9</v>
+      </c>
+      <c r="N215">
+        <v>0.76315789499999998</v>
+      </c>
+      <c r="O215" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>9941</v>
+      </c>
+      <c r="B216">
+        <v>204</v>
+      </c>
+      <c r="C216" t="s">
+        <v>83</v>
+      </c>
+      <c r="D216" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E216" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F216">
+        <v>20058</v>
+      </c>
+      <c r="G216">
+        <v>66</v>
+      </c>
+      <c r="H216">
+        <v>27</v>
+      </c>
+      <c r="I216">
+        <v>-39</v>
+      </c>
+      <c r="J216">
+        <v>0.409090909</v>
+      </c>
+      <c r="K216">
+        <v>66</v>
+      </c>
+      <c r="L216">
+        <v>27</v>
+      </c>
+      <c r="M216">
+        <v>-39</v>
+      </c>
+      <c r="N216">
+        <v>0.409090909</v>
+      </c>
+      <c r="O216" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>9987</v>
+      </c>
+      <c r="B217">
+        <v>312</v>
+      </c>
+      <c r="C217" t="s">
+        <v>52</v>
+      </c>
+      <c r="D217" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E217" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F217">
+        <v>20086</v>
+      </c>
+      <c r="G217">
+        <v>21</v>
+      </c>
+      <c r="H217">
+        <v>23</v>
+      </c>
+      <c r="I217">
+        <v>2</v>
+      </c>
+      <c r="J217">
+        <v>1.095238095</v>
+      </c>
+      <c r="K217">
+        <v>21</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>-21</v>
+      </c>
+      <c r="N217">
+        <v>0</v>
+      </c>
+      <c r="O217" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>9944</v>
+      </c>
+      <c r="B218">
+        <v>207</v>
+      </c>
+      <c r="C218" t="s">
+        <v>84</v>
+      </c>
+      <c r="D218" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E218" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F218">
+        <v>20105</v>
+      </c>
+      <c r="G218">
+        <v>33</v>
+      </c>
+      <c r="H218">
+        <v>32</v>
+      </c>
+      <c r="I218">
+        <v>-1</v>
+      </c>
+      <c r="J218">
+        <v>0.96969696999999999</v>
+      </c>
+      <c r="K218">
+        <v>33</v>
+      </c>
+      <c r="L218">
+        <v>32</v>
+      </c>
+      <c r="M218">
+        <v>-1</v>
+      </c>
+      <c r="N218">
+        <v>0.96969696999999999</v>
+      </c>
+      <c r="O218" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>9945</v>
+      </c>
+      <c r="B219">
+        <v>208</v>
+      </c>
+      <c r="C219" t="s">
+        <v>85</v>
+      </c>
+      <c r="D219" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E219" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F219">
+        <v>20076</v>
+      </c>
+      <c r="G219">
+        <v>39</v>
+      </c>
+      <c r="H219">
+        <v>30</v>
+      </c>
+      <c r="I219">
+        <v>-9</v>
+      </c>
+      <c r="J219">
+        <v>0.76923076899999998</v>
+      </c>
+      <c r="K219">
+        <v>39</v>
+      </c>
+      <c r="L219">
+        <v>30</v>
+      </c>
+      <c r="M219">
+        <v>-9</v>
+      </c>
+      <c r="N219">
+        <v>0.76923076899999998</v>
+      </c>
+      <c r="O219" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>9947</v>
+      </c>
+      <c r="B220">
+        <v>213</v>
+      </c>
+      <c r="C220" t="s">
+        <v>86</v>
+      </c>
+      <c r="D220" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E220" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F220">
+        <v>20066</v>
+      </c>
+      <c r="G220">
+        <v>60</v>
+      </c>
+      <c r="H220">
+        <v>45</v>
+      </c>
+      <c r="I220">
+        <v>-15</v>
+      </c>
+      <c r="J220">
+        <v>0.75</v>
+      </c>
+      <c r="K220">
+        <v>60</v>
+      </c>
+      <c r="L220">
+        <v>45</v>
+      </c>
+      <c r="M220">
+        <v>-15</v>
+      </c>
+      <c r="N220">
+        <v>0.75</v>
+      </c>
+      <c r="O220" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>9960</v>
+      </c>
+      <c r="B221">
+        <v>240</v>
+      </c>
+      <c r="C221">
+        <v>240</v>
+      </c>
+      <c r="D221" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E221" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F221">
+        <v>20006</v>
+      </c>
+      <c r="G221">
+        <v>27</v>
+      </c>
+      <c r="H221">
+        <v>25</v>
+      </c>
+      <c r="I221">
+        <v>-2</v>
+      </c>
+      <c r="J221">
+        <v>0.92592592600000001</v>
+      </c>
+      <c r="K221">
+        <v>27</v>
+      </c>
+      <c r="L221">
+        <v>25</v>
+      </c>
+      <c r="M221">
+        <v>-2</v>
+      </c>
+      <c r="N221">
+        <v>0.92592592600000001</v>
+      </c>
+      <c r="O221" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>9957</v>
+      </c>
+      <c r="B222">
+        <v>237</v>
+      </c>
+      <c r="C222">
+        <v>237</v>
+      </c>
+      <c r="D222" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E222" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F222">
+        <v>20003</v>
+      </c>
+      <c r="G222">
+        <v>42</v>
+      </c>
+      <c r="H222">
+        <v>25</v>
+      </c>
+      <c r="I222">
+        <v>-17</v>
+      </c>
+      <c r="J222">
+        <v>0.59523809500000002</v>
+      </c>
+      <c r="K222">
+        <v>42</v>
+      </c>
+      <c r="L222">
+        <v>25</v>
+      </c>
+      <c r="M222">
+        <v>-17</v>
+      </c>
+      <c r="N222">
+        <v>0.59523809500000002</v>
+      </c>
+      <c r="O222" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>9994</v>
+      </c>
+      <c r="B223">
+        <v>319</v>
+      </c>
+      <c r="C223" t="s">
+        <v>92</v>
+      </c>
+      <c r="D223" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E223" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F223">
+        <v>11215</v>
+      </c>
+      <c r="G223">
+        <v>21</v>
+      </c>
+      <c r="H223">
+        <v>16</v>
+      </c>
+      <c r="I223">
+        <v>-5</v>
+      </c>
+      <c r="J223">
+        <v>0.76190476200000001</v>
+      </c>
+      <c r="K223">
+        <v>21</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+      <c r="M223">
+        <v>-21</v>
+      </c>
+      <c r="N223">
+        <v>0</v>
+      </c>
+      <c r="O223" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>9992</v>
+      </c>
+      <c r="B224">
+        <v>317</v>
+      </c>
+      <c r="C224" t="s">
+        <v>90</v>
+      </c>
+      <c r="D224" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E224" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F224">
+        <v>20043</v>
+      </c>
+      <c r="G224">
+        <v>21</v>
+      </c>
+      <c r="H224">
+        <v>20</v>
+      </c>
+      <c r="I224">
+        <v>-1</v>
+      </c>
+      <c r="J224">
+        <v>0.95238095199999995</v>
+      </c>
+      <c r="K224">
+        <v>21</v>
+      </c>
+      <c r="L224">
+        <v>20</v>
+      </c>
+      <c r="M224">
+        <v>-1</v>
+      </c>
+      <c r="N224">
+        <v>0.95238095199999995</v>
+      </c>
+      <c r="O224" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>9969</v>
+      </c>
+      <c r="B225">
+        <v>332</v>
+      </c>
+      <c r="C225">
+        <v>332</v>
+      </c>
+      <c r="D225" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E225" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F225">
+        <v>20130</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="O225" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>9977</v>
+      </c>
+      <c r="B226">
+        <v>340</v>
+      </c>
+      <c r="C226">
+        <v>340</v>
+      </c>
+      <c r="D226" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E226" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F226">
+        <v>20005</v>
+      </c>
+      <c r="G226">
+        <v>23</v>
+      </c>
+      <c r="H226">
+        <v>24</v>
+      </c>
+      <c r="I226">
+        <v>1</v>
+      </c>
+      <c r="J226">
+        <v>1.043478261</v>
+      </c>
+      <c r="K226">
+        <v>23</v>
+      </c>
+      <c r="L226">
+        <v>24</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>1.043478261</v>
+      </c>
+      <c r="O226" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>9997</v>
+      </c>
+      <c r="B227">
+        <v>323</v>
+      </c>
+      <c r="C227" t="s">
+        <v>93</v>
+      </c>
+      <c r="D227" s="1">
+        <v>46207</v>
+      </c>
+      <c r="E227" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F227">
+        <v>20076</v>
+      </c>
+      <c r="G227">
+        <v>32</v>
+      </c>
+      <c r="H227">
+        <v>32</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>32</v>
+      </c>
+      <c r="L227">
+        <v>32</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
+      </c>
+      <c r="N227">
+        <v>1</v>
+      </c>
+      <c r="O227" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>10014</v>
+      </c>
+      <c r="B228">
+        <v>800</v>
+      </c>
+      <c r="C228" t="s">
+        <v>62</v>
+      </c>
+      <c r="D228" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E228" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F228">
+        <v>200150</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
+      </c>
+      <c r="O228" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>10010</v>
+      </c>
+      <c r="B229">
+        <v>138</v>
+      </c>
+      <c r="C229">
+        <v>138</v>
+      </c>
+      <c r="D229" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E229" s="1">
+        <v>46207</v>
+      </c>
+      <c r="F229">
+        <v>20007</v>
+      </c>
+      <c r="G229">
+        <v>32</v>
+      </c>
+      <c r="H229">
+        <v>22</v>
+      </c>
+      <c r="I229">
+        <v>-10</v>
+      </c>
+      <c r="J229">
+        <v>0.6875</v>
+      </c>
+      <c r="K229">
+        <v>32</v>
+      </c>
+      <c r="L229">
+        <v>22</v>
+      </c>
+      <c r="M229">
+        <v>-10</v>
+      </c>
+      <c r="N229">
+        <v>0.6875</v>
+      </c>
+      <c r="O229" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>9962</v>
+      </c>
+      <c r="B230">
+        <v>504</v>
+      </c>
+      <c r="C230" t="s">
+        <v>76</v>
+      </c>
+      <c r="D230" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E230" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F230">
+        <v>200150</v>
+      </c>
+      <c r="G230">
+        <v>0</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="O230" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>9956</v>
+      </c>
+      <c r="B231">
+        <v>236</v>
+      </c>
+      <c r="C231">
+        <v>236</v>
+      </c>
+      <c r="D231" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E231" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F231">
+        <v>20111</v>
+      </c>
+      <c r="G231">
+        <v>29</v>
+      </c>
+      <c r="H231">
+        <v>21</v>
+      </c>
+      <c r="I231">
+        <v>-8</v>
+      </c>
+      <c r="J231">
+        <v>0.72413793100000001</v>
+      </c>
+      <c r="K231">
+        <v>29</v>
+      </c>
+      <c r="L231">
+        <v>21</v>
+      </c>
+      <c r="M231">
+        <v>-8</v>
+      </c>
+      <c r="N231">
+        <v>0.72413793100000001</v>
+      </c>
+      <c r="O231" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>9954</v>
+      </c>
+      <c r="B232">
+        <v>234</v>
+      </c>
+      <c r="C232">
+        <v>234</v>
+      </c>
+      <c r="D232" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E232" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F232">
+        <v>20112</v>
+      </c>
+      <c r="G232">
+        <v>28</v>
+      </c>
+      <c r="H232">
+        <v>20</v>
+      </c>
+      <c r="I232">
+        <v>-8</v>
+      </c>
+      <c r="J232">
+        <v>0.71428571399999996</v>
+      </c>
+      <c r="K232">
+        <v>28</v>
+      </c>
+      <c r="L232">
+        <v>20</v>
+      </c>
+      <c r="M232">
+        <v>-8</v>
+      </c>
+      <c r="N232">
+        <v>0.71428571399999996</v>
+      </c>
+      <c r="O232" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>9948</v>
+      </c>
+      <c r="B233">
+        <v>214</v>
+      </c>
+      <c r="C233" t="s">
+        <v>87</v>
+      </c>
+      <c r="D233" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E233" s="1">
+        <v>46205</v>
+      </c>
+      <c r="F233">
+        <v>11215</v>
+      </c>
+      <c r="G233">
+        <v>0</v>
+      </c>
+      <c r="H233">
+        <v>1</v>
+      </c>
+      <c r="I233">
+        <v>1</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>1</v>
+      </c>
+      <c r="M233">
+        <v>1</v>
+      </c>
+      <c r="O233" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>10012</v>
+      </c>
+      <c r="B234">
+        <v>140</v>
+      </c>
+      <c r="C234">
+        <v>140</v>
+      </c>
+      <c r="D234" s="1">
+        <v>46209</v>
+      </c>
+      <c r="E234" s="1">
+        <v>46207</v>
+      </c>
+      <c r="F234">
+        <v>20006</v>
+      </c>
+      <c r="G234">
+        <v>14</v>
+      </c>
+      <c r="H234">
+        <v>11</v>
+      </c>
+      <c r="I234">
+        <v>-3</v>
+      </c>
+      <c r="J234">
+        <v>0.78571428600000004</v>
+      </c>
+      <c r="K234">
+        <v>14</v>
+      </c>
+      <c r="L234">
+        <v>11</v>
+      </c>
+      <c r="M234">
+        <v>-3</v>
+      </c>
+      <c r="N234">
+        <v>0.78571428600000004</v>
+      </c>
+      <c r="O234" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>10016</v>
+      </c>
+      <c r="B235">
+        <v>201</v>
+      </c>
+      <c r="C235" t="s">
+        <v>80</v>
+      </c>
+      <c r="D235" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E235" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F235">
+        <v>20153</v>
+      </c>
+      <c r="G235">
+        <v>51</v>
+      </c>
+      <c r="H235">
+        <v>36</v>
+      </c>
+      <c r="I235">
+        <v>-15</v>
+      </c>
+      <c r="J235">
+        <v>0.70588235300000002</v>
+      </c>
+      <c r="K235">
+        <v>51</v>
+      </c>
+      <c r="L235">
+        <v>36</v>
+      </c>
+      <c r="M235">
+        <v>-15</v>
+      </c>
+      <c r="N235">
+        <v>0.70588235300000002</v>
+      </c>
+      <c r="O235" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>10018</v>
+      </c>
+      <c r="B236">
+        <v>203</v>
+      </c>
+      <c r="C236" t="s">
+        <v>82</v>
+      </c>
+      <c r="D236" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E236" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F236">
+        <v>20155</v>
+      </c>
+      <c r="G236">
+        <v>26</v>
+      </c>
+      <c r="H236">
+        <v>15</v>
+      </c>
+      <c r="I236">
+        <v>-11</v>
+      </c>
+      <c r="J236">
+        <v>0.57692307700000001</v>
+      </c>
+      <c r="K236">
+        <v>26</v>
+      </c>
+      <c r="L236">
+        <v>15</v>
+      </c>
+      <c r="M236">
+        <v>-11</v>
+      </c>
+      <c r="N236">
+        <v>0.57692307700000001</v>
+      </c>
+      <c r="O236" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>10019</v>
+      </c>
+      <c r="B237">
+        <v>204</v>
+      </c>
+      <c r="C237" t="s">
+        <v>83</v>
+      </c>
+      <c r="D237" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E237" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F237">
+        <v>20095</v>
+      </c>
+      <c r="G237">
+        <v>58</v>
+      </c>
+      <c r="H237">
+        <v>37</v>
+      </c>
+      <c r="I237">
+        <v>-21</v>
+      </c>
+      <c r="J237">
+        <v>0.63793103399999995</v>
+      </c>
+      <c r="K237">
+        <v>58</v>
+      </c>
+      <c r="L237">
+        <v>37</v>
+      </c>
+      <c r="M237">
+        <v>-21</v>
+      </c>
+      <c r="N237">
+        <v>0.63793103399999995</v>
+      </c>
+      <c r="O237" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>10023</v>
+      </c>
+      <c r="B238">
+        <v>208</v>
+      </c>
+      <c r="C238" t="s">
+        <v>85</v>
+      </c>
+      <c r="D238" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E238" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F238">
+        <v>11215</v>
+      </c>
+      <c r="G238">
+        <v>46</v>
+      </c>
+      <c r="H238">
+        <v>34</v>
+      </c>
+      <c r="I238">
+        <v>-12</v>
+      </c>
+      <c r="J238">
+        <v>0.73913043499999997</v>
+      </c>
+      <c r="K238">
+        <v>46</v>
+      </c>
+      <c r="L238">
+        <v>34</v>
+      </c>
+      <c r="M238">
+        <v>-12</v>
+      </c>
+      <c r="N238">
+        <v>0.73913043499999997</v>
+      </c>
+      <c r="O238" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>10025</v>
+      </c>
+      <c r="B239">
+        <v>210</v>
+      </c>
+      <c r="C239" t="s">
+        <v>97</v>
+      </c>
+      <c r="D239" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E239" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F239">
+        <v>20066</v>
+      </c>
+      <c r="G239">
+        <v>25</v>
+      </c>
+      <c r="H239">
+        <v>13</v>
+      </c>
+      <c r="I239">
+        <v>-12</v>
+      </c>
+      <c r="J239">
+        <v>0.52</v>
+      </c>
+      <c r="K239">
+        <v>25</v>
+      </c>
+      <c r="L239">
+        <v>13</v>
+      </c>
+      <c r="M239">
+        <v>-12</v>
+      </c>
+      <c r="N239">
+        <v>0.52</v>
+      </c>
+      <c r="O239" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>10024</v>
+      </c>
+      <c r="B240">
+        <v>209</v>
+      </c>
+      <c r="C240" t="s">
+        <v>96</v>
+      </c>
+      <c r="D240" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E240" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F240">
+        <v>20105</v>
+      </c>
+      <c r="G240">
+        <v>42</v>
+      </c>
+      <c r="H240">
+        <v>35</v>
+      </c>
+      <c r="I240">
+        <v>-7</v>
+      </c>
+      <c r="J240">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K240">
+        <v>42</v>
+      </c>
+      <c r="L240">
+        <v>35</v>
+      </c>
+      <c r="M240">
+        <v>-7</v>
+      </c>
+      <c r="N240">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O240" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>10026</v>
+      </c>
+      <c r="B241">
+        <v>211</v>
+      </c>
+      <c r="C241" t="s">
+        <v>98</v>
+      </c>
+      <c r="D241" s="1">
+        <v>46210</v>
+      </c>
+      <c r="E241" s="1">
+        <v>46209</v>
+      </c>
+      <c r="F241">
+        <v>20058</v>
+      </c>
+      <c r="G241">
+        <v>62</v>
+      </c>
+      <c r="H241">
+        <v>23</v>
+      </c>
+      <c r="I241">
+        <v>-39</v>
+      </c>
+      <c r="J241">
+        <v>0.37096774199999999</v>
+      </c>
+      <c r="K241">
+        <v>62</v>
+      </c>
+      <c r="L241">
+        <v>23</v>
+      </c>
+      <c r="M241">
+        <v>-39</v>
+      </c>
+      <c r="N241">
+        <v>0.37096774199999999</v>
+      </c>
+      <c r="O241" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>9970</v>
+      </c>
+      <c r="B242">
+        <v>333</v>
+      </c>
+      <c r="C242">
+        <v>333</v>
+      </c>
+      <c r="D242" s="1">
+        <v>46206</v>
+      </c>
+      <c r="E242" s="1">
+        <v>46206</v>
+      </c>
+      <c r="F242">
+        <v>200158</v>
+      </c>
+      <c r="G242">
+        <v>0</v>
+      </c>
+      <c r="H242">
+        <v>0</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="O242" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
     </row>
-    <row r="244" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
     </row>
-    <row r="245" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
     </row>
-    <row r="246" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
     </row>
-    <row r="247" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
     </row>
-    <row r="248" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
     </row>
-    <row r="249" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
     </row>
-    <row r="250" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
     </row>
-    <row r="251" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
     </row>
-    <row r="252" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
     </row>
-    <row r="253" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
     </row>
-    <row r="254" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
     </row>
-    <row r="255" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
     </row>
-    <row r="256" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
     </row>

--- a/data/cartones.xlsx
+++ b/data/cartones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos julio 2026 - copia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos agosto 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5021E22D-F446-4C9F-BAD7-79666558F181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D5BC11-48EC-4CF1-8F99-556D35105847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EE42AFD4-3D44-431D-BF0C-DB1E709F72DE}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="94">
   <si>
     <t>codigo</t>
   </si>
@@ -268,6 +268,54 @@
   </si>
   <si>
     <t>400 CAM 400 AUXILIAR</t>
+  </si>
+  <si>
+    <t>214 CAM 14 MARTES</t>
+  </si>
+  <si>
+    <t>215 CAM 15 MARTES</t>
+  </si>
+  <si>
+    <t>102 CAM 2 LUNES</t>
+  </si>
+  <si>
+    <t>111 CAM 11 LUNES</t>
+  </si>
+  <si>
+    <t>110 CAM 10 LUNES</t>
+  </si>
+  <si>
+    <t>113 CAM 13 LUNES</t>
+  </si>
+  <si>
+    <t>318 CAM 18 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>101 CAM 1 LUNES</t>
+  </si>
+  <si>
+    <t>104 CAM 4 LUNES</t>
+  </si>
+  <si>
+    <t>105 CAM 5 LUNES</t>
+  </si>
+  <si>
+    <t>108 CAM 8 LUNES</t>
+  </si>
+  <si>
+    <t>112 CAM 12 LUNES</t>
+  </si>
+  <si>
+    <t>109 CAM 9 LUNES</t>
+  </si>
+  <si>
+    <t>103 CAM 3 LUNES</t>
+  </si>
+  <si>
+    <t>106 CAM 6 LUNES</t>
+  </si>
+  <si>
+    <t>107 CAM 7 LUNES</t>
   </si>
 </sst>
 </file>
@@ -620,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74F70945-99D5-4C4A-8C8A-BA7E0A7AEEC0}">
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -672,13 +720,13 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>10631</v>
+        <v>10630</v>
       </c>
       <c r="B2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D2" s="1">
         <v>46235</v>
@@ -687,45 +735,45 @@
         <v>46234</v>
       </c>
       <c r="F2">
-        <v>20112</v>
+        <v>20130</v>
       </c>
       <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <v>10</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
         <v>17</v>
-      </c>
-      <c r="H2">
-        <v>15</v>
-      </c>
-      <c r="I2">
-        <v>-2</v>
-      </c>
-      <c r="J2">
-        <v>0.88235294099999995</v>
-      </c>
-      <c r="K2">
-        <v>17</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>-17</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>10635</v>
+        <v>10631</v>
       </c>
       <c r="B3">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C3">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D3" s="1">
         <v>46235</v>
@@ -740,25 +788,25 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="J3">
-        <v>0.58823529399999996</v>
+        <v>0.88235294099999995</v>
       </c>
       <c r="K3">
         <v>17</v>
       </c>
       <c r="L3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="N3">
-        <v>0.58823529399999996</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>31</v>
@@ -766,69 +814,63 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>10611</v>
+        <v>10678</v>
       </c>
       <c r="B4">
-        <v>304</v>
+        <v>800</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E4" s="1">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="F4">
-        <v>20086</v>
+        <v>200150</v>
       </c>
       <c r="G4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-4</v>
-      </c>
-      <c r="J4">
-        <v>0.90697674399999995</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>-4</v>
-      </c>
-      <c r="N4">
-        <v>0.90697674399999995</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>10615</v>
+        <v>10649</v>
       </c>
       <c r="B5">
-        <v>308</v>
+        <v>500</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="D5" s="1">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="E5" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F5">
-        <v>20095</v>
+        <v>20043</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -849,18 +891,18 @@
         <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>10613</v>
+        <v>10635</v>
       </c>
       <c r="B6">
-        <v>306</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
+        <v>338</v>
+      </c>
+      <c r="C6">
+        <v>338</v>
       </c>
       <c r="D6" s="1">
         <v>46235</v>
@@ -869,677 +911,677 @@
         <v>46234</v>
       </c>
       <c r="F6">
-        <v>11215</v>
+        <v>20112</v>
       </c>
       <c r="G6">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-30</v>
+        <v>-7</v>
       </c>
       <c r="J6">
-        <v>0.31818181800000001</v>
+        <v>0.58823529399999996</v>
       </c>
       <c r="K6">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-30</v>
+        <v>-7</v>
       </c>
       <c r="N6">
-        <v>0.31818181800000001</v>
+        <v>0.58823529399999996</v>
       </c>
       <c r="O6" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10608</v>
+        <v>10681</v>
       </c>
       <c r="B7">
-        <v>301</v>
+        <v>800</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E7" s="1">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="F7">
-        <v>20066</v>
+        <v>200150</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>4</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>4</v>
-      </c>
-      <c r="N7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>10616</v>
+        <v>10656</v>
       </c>
       <c r="B8">
-        <v>310</v>
+        <v>204</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E8" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F8">
-        <v>20155</v>
+        <v>20095</v>
       </c>
       <c r="G8">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="H8">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0.81481481499999997</v>
       </c>
       <c r="K8">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="L8">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0.81481481499999997</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>10620</v>
+        <v>10658</v>
       </c>
       <c r="B9">
-        <v>314</v>
+        <v>206</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D9" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E9" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F9">
-        <v>20047</v>
+        <v>20076</v>
       </c>
       <c r="G9">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="J9">
-        <v>0.909090909</v>
+        <v>0.83333333300000001</v>
       </c>
       <c r="K9">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="L9">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="N9">
-        <v>0.909090909</v>
+        <v>0.83333333300000001</v>
       </c>
       <c r="O9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>10628</v>
+        <v>10676</v>
       </c>
       <c r="B10">
-        <v>324</v>
+        <v>213</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D10" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E10" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F10">
-        <v>20105</v>
+        <v>20058</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K10">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="L10">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10627</v>
+        <v>10674</v>
       </c>
       <c r="B11">
-        <v>323</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
+        <v>240</v>
+      </c>
+      <c r="C11">
+        <v>240</v>
       </c>
       <c r="D11" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E11" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F11">
-        <v>20076</v>
+        <v>20006</v>
       </c>
       <c r="G11">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H11">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J11">
-        <v>1.4705882349999999</v>
+        <v>1.30952381</v>
       </c>
       <c r="K11">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="L11">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="M11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N11">
-        <v>1.4705882349999999</v>
+        <v>1.30952381</v>
       </c>
       <c r="O11" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10618</v>
+        <v>10662</v>
       </c>
       <c r="B12">
-        <v>312</v>
+        <v>211</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="D12" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E12" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F12">
-        <v>20086</v>
+        <v>20106</v>
       </c>
       <c r="G12">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H12">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
-        <v>0.928571429</v>
+        <v>1.25</v>
       </c>
       <c r="K12">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L12">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>0.928571429</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>10629</v>
+        <v>10661</v>
       </c>
       <c r="B13">
-        <v>331</v>
-      </c>
-      <c r="C13">
-        <v>331</v>
+        <v>210</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
       </c>
       <c r="D13" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E13" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F13">
-        <v>20006</v>
+        <v>20066</v>
       </c>
       <c r="G13">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H13">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="J13">
-        <v>0.85714285700000004</v>
+        <v>0.77777777800000003</v>
       </c>
       <c r="K13">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-21</v>
+        <v>-2</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>0.77777777800000003</v>
       </c>
       <c r="O13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>10619</v>
+        <v>10647</v>
       </c>
       <c r="B14">
-        <v>313</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
+        <v>439</v>
+      </c>
+      <c r="C14">
+        <v>439</v>
       </c>
       <c r="D14" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E14" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F14">
-        <v>20106</v>
+        <v>20008</v>
       </c>
       <c r="G14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H14">
         <v>10</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K14">
+        <v>15</v>
+      </c>
+      <c r="L14">
         <v>10</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
       <c r="M14">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O14" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>10622</v>
+        <v>10673</v>
       </c>
       <c r="B15">
-        <v>316</v>
-      </c>
-      <c r="C15" t="s">
-        <v>61</v>
+        <v>239</v>
+      </c>
+      <c r="C15">
+        <v>239</v>
       </c>
       <c r="D15" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="E15" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F15">
-        <v>20155</v>
+        <v>20008</v>
       </c>
       <c r="G15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H15">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J15">
-        <v>1.136363636</v>
+        <v>0.9</v>
       </c>
       <c r="K15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M15">
-        <v>-22</v>
+        <v>-2</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>10623</v>
+        <v>10708</v>
       </c>
       <c r="B16">
-        <v>317</v>
+        <v>800</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="D16" s="1">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="E16" s="1">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="F16">
-        <v>20043</v>
+        <v>200150</v>
       </c>
       <c r="G16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>-1</v>
-      </c>
-      <c r="J16">
-        <v>0.95833333300000001</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>-24</v>
-      </c>
-      <c r="N16">
         <v>0</v>
       </c>
       <c r="O16" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>10632</v>
+        <v>10698</v>
       </c>
       <c r="B17">
-        <v>335</v>
-      </c>
-      <c r="C17">
-        <v>335</v>
+        <v>321</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
       </c>
       <c r="D17" s="1">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="E17" s="1">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="F17">
-        <v>20113</v>
+        <v>20005</v>
       </c>
       <c r="G17">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="H17">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0.75757575799999999</v>
       </c>
       <c r="K17">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="L17">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>0.75757575799999999</v>
       </c>
       <c r="O17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>10649</v>
+        <v>10699</v>
       </c>
       <c r="B18">
-        <v>500</v>
+        <v>322</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="E18" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F18">
-        <v>20043</v>
+        <v>20130</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="J18">
+        <v>0.1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="N18">
+        <v>0.1</v>
       </c>
       <c r="O18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>10639</v>
+        <v>10702</v>
       </c>
       <c r="B19">
-        <v>400</v>
+        <v>325</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D19" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="E19" s="1">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="F19">
-        <v>20076</v>
+        <v>20113</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J19">
+        <v>0.88</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N19">
+        <v>0.88</v>
       </c>
       <c r="O19" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>10641</v>
+        <v>10701</v>
       </c>
       <c r="B20">
-        <v>433</v>
-      </c>
-      <c r="C20">
-        <v>433</v>
+        <v>324</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
       </c>
       <c r="D20" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="E20" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F20">
         <v>200158</v>
       </c>
       <c r="G20">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H20">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0.83333333300000001</v>
       </c>
       <c r="K20">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="L20">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>0.83333333300000001</v>
       </c>
       <c r="O20" t="s">
         <v>15</v>
@@ -1547,295 +1589,283 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>10643</v>
+        <v>10705</v>
       </c>
       <c r="B21">
-        <v>435</v>
+        <v>328</v>
       </c>
       <c r="C21">
-        <v>435</v>
+        <v>328</v>
       </c>
       <c r="D21" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="E21" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F21">
-        <v>20113</v>
+        <v>20007</v>
       </c>
       <c r="G21">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H21">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I21">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="J21">
-        <v>0.8</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K21">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L21">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="M21">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="N21">
-        <v>0.8</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>10644</v>
+        <v>10707</v>
       </c>
       <c r="B22">
-        <v>436</v>
+        <v>330</v>
       </c>
       <c r="C22">
-        <v>436</v>
+        <v>330</v>
       </c>
       <c r="D22" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="E22" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F22">
-        <v>20111</v>
+        <v>20006</v>
       </c>
       <c r="G22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I22">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="J22">
-        <v>0.69565217400000001</v>
+        <v>0.75</v>
       </c>
       <c r="K22">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L22">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M22">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="N22">
-        <v>0.69565217400000001</v>
+        <v>0.75</v>
       </c>
       <c r="O22" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>10645</v>
+        <v>10691</v>
       </c>
       <c r="B23">
-        <v>437</v>
-      </c>
-      <c r="C23">
-        <v>437</v>
+        <v>308</v>
+      </c>
+      <c r="C23" t="s">
+        <v>36</v>
       </c>
       <c r="D23" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="E23" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F23">
-        <v>20003</v>
+        <v>20057</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H23">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="J23">
-        <v>1.5</v>
+        <v>0.94230769199999997</v>
       </c>
       <c r="K23">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="L23">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="N23">
-        <v>1.5</v>
+        <v>0.94230769199999997</v>
       </c>
       <c r="O23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>10646</v>
+        <v>10639</v>
       </c>
       <c r="B24">
-        <v>438</v>
-      </c>
-      <c r="C24">
-        <v>438</v>
+        <v>400</v>
+      </c>
+      <c r="C24" t="s">
+        <v>77</v>
       </c>
       <c r="D24" s="1">
         <v>46237</v>
       </c>
       <c r="E24" s="1">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="F24">
-        <v>20007</v>
+        <v>20076</v>
       </c>
       <c r="G24">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
       <c r="K24">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
       <c r="O24" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>10648</v>
+        <v>10751</v>
       </c>
       <c r="B25">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="C25">
-        <v>440</v>
+        <v>238</v>
       </c>
       <c r="D25" s="1">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="E25" s="1">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F25">
-        <v>20006</v>
+        <v>20007</v>
       </c>
       <c r="G25">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I25">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="J25">
-        <v>0.81818181800000001</v>
+        <v>0.71428571399999996</v>
       </c>
       <c r="K25">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L25">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M25">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="N25">
-        <v>0.81818181800000001</v>
+        <v>0.71428571399999996</v>
       </c>
       <c r="O25" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>10640</v>
+        <v>10752</v>
       </c>
       <c r="B26">
-        <v>431</v>
+        <v>239</v>
       </c>
       <c r="C26">
-        <v>431</v>
+        <v>239</v>
       </c>
       <c r="D26" s="1">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E26" s="1">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F26">
-        <v>20005</v>
+        <v>20008</v>
       </c>
       <c r="G26">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <v>-5</v>
-      </c>
-      <c r="J26">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L26">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>-5</v>
-      </c>
-      <c r="N26">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>10675</v>
+        <v>10641</v>
       </c>
       <c r="B27">
-        <v>502</v>
-      </c>
-      <c r="C27" t="s">
-        <v>51</v>
+        <v>433</v>
+      </c>
+      <c r="C27">
+        <v>433</v>
       </c>
       <c r="D27" s="1">
         <v>46237</v>
@@ -1844,321 +1874,321 @@
         <v>46237</v>
       </c>
       <c r="F27">
-        <v>200150</v>
+        <v>200158</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
       <c r="K27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
       <c r="O27" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>10634</v>
+        <v>10689</v>
       </c>
       <c r="B28">
-        <v>337</v>
-      </c>
-      <c r="C28">
-        <v>337</v>
+        <v>305</v>
+      </c>
+      <c r="C28" t="s">
+        <v>40</v>
       </c>
       <c r="D28" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="E28" s="1">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="F28">
-        <v>20003</v>
+        <v>20066</v>
       </c>
       <c r="G28">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H28">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K28">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="L28">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O28" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>10617</v>
+        <v>10679</v>
       </c>
       <c r="B29">
-        <v>311</v>
+        <v>800</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D29" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="E29" s="1">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="F29">
-        <v>20057</v>
+        <v>200150</v>
       </c>
       <c r="G29">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>-5</v>
-      </c>
-      <c r="J29">
-        <v>0.92063492099999999</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>-5</v>
-      </c>
-      <c r="N29">
-        <v>0.92063492099999999</v>
+        <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>10610</v>
+        <v>10643</v>
       </c>
       <c r="B30">
-        <v>303</v>
-      </c>
-      <c r="C30" t="s">
-        <v>67</v>
+        <v>435</v>
+      </c>
+      <c r="C30">
+        <v>435</v>
       </c>
       <c r="D30" s="1">
         <v>46237</v>
       </c>
       <c r="E30" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F30">
-        <v>20047</v>
+        <v>20113</v>
       </c>
       <c r="G30">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H30">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K30">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L30">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O30" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>10609</v>
+        <v>10644</v>
       </c>
       <c r="B31">
-        <v>302</v>
-      </c>
-      <c r="C31" t="s">
-        <v>38</v>
+        <v>436</v>
+      </c>
+      <c r="C31">
+        <v>436</v>
       </c>
       <c r="D31" s="1">
         <v>46237</v>
       </c>
       <c r="E31" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F31">
-        <v>20106</v>
+        <v>20111</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0.69565217400000001</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0.69565217400000001</v>
       </c>
       <c r="O31" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>10612</v>
+        <v>10645</v>
       </c>
       <c r="B32">
-        <v>305</v>
-      </c>
-      <c r="C32" t="s">
-        <v>40</v>
+        <v>437</v>
+      </c>
+      <c r="C32">
+        <v>437</v>
       </c>
       <c r="D32" s="1">
         <v>46237</v>
       </c>
       <c r="E32" s="1">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="F32">
-        <v>20105</v>
+        <v>20003</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O32" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>10614</v>
+        <v>10611</v>
       </c>
       <c r="B33">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C33" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D33" s="1">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="E33" s="1">
         <v>46234</v>
       </c>
       <c r="F33">
-        <v>20153</v>
+        <v>20086</v>
       </c>
       <c r="G33">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="H33">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="I33">
-        <v>-15</v>
+        <v>-4</v>
       </c>
       <c r="J33">
-        <v>0.44444444399999999</v>
+        <v>0.90697674399999995</v>
       </c>
       <c r="K33">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="L33">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="M33">
-        <v>-15</v>
+        <v>-4</v>
       </c>
       <c r="N33">
-        <v>0.44444444399999999</v>
+        <v>0.90697674399999995</v>
       </c>
       <c r="O33" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>10650</v>
+        <v>10646</v>
       </c>
       <c r="B34">
-        <v>800</v>
-      </c>
-      <c r="C34" t="s">
-        <v>28</v>
+        <v>438</v>
+      </c>
+      <c r="C34">
+        <v>438</v>
       </c>
       <c r="D34" s="1">
         <v>46237</v>
@@ -2167,80 +2197,92 @@
         <v>46237</v>
       </c>
       <c r="F34">
-        <v>200150</v>
+        <v>20007</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
       <c r="K34">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
       <c r="O34" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>10660</v>
+        <v>10696</v>
       </c>
       <c r="B35">
-        <v>209</v>
+        <v>314</v>
       </c>
       <c r="C35" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D35" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="E35" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F35">
-        <v>20105</v>
+        <v>20047</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
       <c r="K35">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
       <c r="O35" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>10664</v>
+        <v>10648</v>
       </c>
       <c r="B36">
-        <v>213</v>
-      </c>
-      <c r="C36" t="s">
-        <v>57</v>
+        <v>440</v>
+      </c>
+      <c r="C36">
+        <v>440</v>
       </c>
       <c r="D36" s="1">
         <v>46237</v>
@@ -2249,39 +2291,45 @@
         <v>46237</v>
       </c>
       <c r="F36">
-        <v>20058</v>
+        <v>20006</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="J36">
+        <v>0.81818181800000001</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="N36">
+        <v>0.81818181800000001</v>
       </c>
       <c r="O36" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>10668</v>
+        <v>10640</v>
       </c>
       <c r="B37">
-        <v>234</v>
+        <v>431</v>
       </c>
       <c r="C37">
-        <v>234</v>
+        <v>431</v>
       </c>
       <c r="D37" s="1">
         <v>46237</v>
@@ -2290,48 +2338,54 @@
         <v>46237</v>
       </c>
       <c r="F37">
-        <v>20112</v>
+        <v>20005</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J37">
+        <v>0.6875</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N37">
+        <v>0.6875</v>
       </c>
       <c r="O37" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>10669</v>
+        <v>10615</v>
       </c>
       <c r="B38">
-        <v>235</v>
-      </c>
-      <c r="C38">
-        <v>235</v>
+        <v>308</v>
+      </c>
+      <c r="C38" t="s">
+        <v>36</v>
       </c>
       <c r="D38" s="1">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="E38" s="1">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="F38">
-        <v>20113</v>
+        <v>20095</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -2352,147 +2406,159 @@
         <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>10678</v>
+        <v>10613</v>
       </c>
       <c r="B39">
-        <v>800</v>
+        <v>306</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="D39" s="1">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="E39" s="1">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="F39">
-        <v>200150</v>
+        <v>11215</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>-30</v>
+      </c>
+      <c r="J39">
+        <v>0.31818181800000001</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>-30</v>
+      </c>
+      <c r="N39">
+        <v>0.31818181800000001</v>
       </c>
       <c r="O39" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>10681</v>
+        <v>10608</v>
       </c>
       <c r="B40">
-        <v>800</v>
+        <v>301</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D40" s="1">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="E40" s="1">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="F40">
-        <v>200150</v>
+        <v>20066</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="J40">
+        <v>5</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="N40">
+        <v>5</v>
       </c>
       <c r="O40" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>10656</v>
+        <v>10616</v>
       </c>
       <c r="B41">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="C41" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D41" s="1">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="E41" s="1">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="F41">
-        <v>20095</v>
+        <v>20155</v>
       </c>
       <c r="G41">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="H41">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="I41">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J41">
-        <v>0.81481481499999997</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="L41">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="M41">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>0.81481481499999997</v>
+        <v>1</v>
       </c>
       <c r="O41" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>10658</v>
+        <v>10653</v>
       </c>
       <c r="B42">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D42" s="1">
         <v>46238</v>
@@ -2501,233 +2567,233 @@
         <v>46237</v>
       </c>
       <c r="F42">
-        <v>20076</v>
+        <v>20153</v>
       </c>
       <c r="G42">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>0.83333333300000001</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="L42">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="M42">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="N42">
-        <v>0.83333333300000001</v>
+        <v>1</v>
       </c>
       <c r="O42" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>10676</v>
+        <v>10620</v>
       </c>
       <c r="B43">
-        <v>213</v>
+        <v>314</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D43" s="1">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="E43" s="1">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="F43">
-        <v>20058</v>
+        <v>20047</v>
       </c>
       <c r="G43">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H43">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I43">
-        <v>-19</v>
+        <v>-1</v>
       </c>
       <c r="J43">
-        <v>0.5</v>
+        <v>0.909090909</v>
       </c>
       <c r="K43">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="L43">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="M43">
-        <v>-19</v>
+        <v>-1</v>
       </c>
       <c r="N43">
-        <v>0.5</v>
+        <v>0.909090909</v>
       </c>
       <c r="O43" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>10674</v>
+        <v>10628</v>
       </c>
       <c r="B44">
-        <v>240</v>
-      </c>
-      <c r="C44">
-        <v>240</v>
+        <v>324</v>
+      </c>
+      <c r="C44" t="s">
+        <v>63</v>
       </c>
       <c r="D44" s="1">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="E44" s="1">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="F44">
-        <v>20006</v>
+        <v>20105</v>
       </c>
       <c r="G44">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="H44">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="I44">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J44">
-        <v>1.30952381</v>
+        <v>1</v>
       </c>
       <c r="K44">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="L44">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="M44">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N44">
-        <v>1.30952381</v>
+        <v>1</v>
       </c>
       <c r="O44" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>10662</v>
+        <v>10627</v>
       </c>
       <c r="B45">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C45" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D45" s="1">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="E45" s="1">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="F45">
-        <v>20106</v>
+        <v>20076</v>
       </c>
       <c r="G45">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H45">
         <v>25</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J45">
-        <v>1.25</v>
+        <v>1.4705882349999999</v>
       </c>
       <c r="K45">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L45">
         <v>25</v>
       </c>
       <c r="M45">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N45">
-        <v>1.25</v>
+        <v>1.4705882349999999</v>
       </c>
       <c r="O45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>10661</v>
+        <v>10618</v>
       </c>
       <c r="B46">
-        <v>210</v>
+        <v>312</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D46" s="1">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="E46" s="1">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="F46">
-        <v>20066</v>
+        <v>20086</v>
       </c>
       <c r="G46">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H46">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I46">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="J46">
-        <v>0.77777777800000003</v>
+        <v>0.928571429</v>
       </c>
       <c r="K46">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L46">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M46">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="N46">
-        <v>0.77777777800000003</v>
+        <v>0.928571429</v>
       </c>
       <c r="O46" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>10647</v>
+        <v>10651</v>
       </c>
       <c r="B47">
-        <v>439</v>
-      </c>
-      <c r="C47">
-        <v>439</v>
+        <v>501</v>
+      </c>
+      <c r="C47" t="s">
+        <v>49</v>
       </c>
       <c r="D47" s="1">
         <v>46238</v>
@@ -2736,92 +2802,80 @@
         <v>46237</v>
       </c>
       <c r="F47">
-        <v>20008</v>
+        <v>200150</v>
       </c>
       <c r="G47">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>-5</v>
-      </c>
-      <c r="J47">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K47">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L47">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M47">
-        <v>-5</v>
-      </c>
-      <c r="N47">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="O47" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>10673</v>
+        <v>10675</v>
       </c>
       <c r="B48">
-        <v>239</v>
-      </c>
-      <c r="C48">
-        <v>239</v>
+        <v>502</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
       </c>
       <c r="D48" s="1">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E48" s="1">
         <v>46237</v>
       </c>
       <c r="F48">
-        <v>20008</v>
+        <v>200150</v>
       </c>
       <c r="G48">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>-2</v>
-      </c>
-      <c r="J48">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K48">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>-2</v>
-      </c>
-      <c r="N48">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O48" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>10679</v>
+        <v>10682</v>
       </c>
       <c r="B49">
-        <v>800</v>
+        <v>501</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D49" s="1">
         <v>46238</v>
@@ -2856,60 +2910,54 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>10653</v>
+        <v>10685</v>
       </c>
       <c r="B50">
-        <v>201</v>
+        <v>800</v>
       </c>
       <c r="C50" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="D50" s="1">
         <v>46238</v>
       </c>
       <c r="E50" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F50">
-        <v>20153</v>
+        <v>200150</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
       <c r="K50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50">
         <v>0</v>
       </c>
-      <c r="N50">
-        <v>1</v>
-      </c>
       <c r="O50" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>10651</v>
+        <v>10670</v>
       </c>
       <c r="B51">
-        <v>501</v>
-      </c>
-      <c r="C51" t="s">
-        <v>49</v>
+        <v>236</v>
+      </c>
+      <c r="C51">
+        <v>236</v>
       </c>
       <c r="D51" s="1">
         <v>46238</v>
@@ -2918,121 +2966,139 @@
         <v>46237</v>
       </c>
       <c r="F51">
-        <v>200150</v>
+        <v>20111</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J51">
+        <v>0.71428571399999996</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="N51">
+        <v>0.71428571399999996</v>
       </c>
       <c r="O51" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>10682</v>
+        <v>10672</v>
       </c>
       <c r="B52">
-        <v>501</v>
-      </c>
-      <c r="C52" t="s">
-        <v>49</v>
+        <v>238</v>
+      </c>
+      <c r="C52">
+        <v>238</v>
       </c>
       <c r="D52" s="1">
         <v>46238</v>
       </c>
       <c r="E52" s="1">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="F52">
-        <v>200150</v>
+        <v>20007</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J52">
+        <v>0.68421052599999999</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M52">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N52">
+        <v>0.68421052599999999</v>
       </c>
       <c r="O52" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>10685</v>
+        <v>10666</v>
       </c>
       <c r="B53">
-        <v>800</v>
-      </c>
-      <c r="C53" t="s">
-        <v>28</v>
+        <v>232</v>
+      </c>
+      <c r="C53">
+        <v>232</v>
       </c>
       <c r="D53" s="1">
         <v>46238</v>
       </c>
       <c r="E53" s="1">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="F53">
-        <v>200150</v>
+        <v>20130</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J53">
+        <v>0.75</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N53">
+        <v>0.75</v>
       </c>
       <c r="O53" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>10670</v>
+        <v>10642</v>
       </c>
       <c r="B54">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="C54">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="D54" s="1">
         <v>46238</v>
@@ -3041,189 +3107,189 @@
         <v>46237</v>
       </c>
       <c r="F54">
-        <v>20111</v>
+        <v>20112</v>
       </c>
       <c r="G54">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I54">
-        <v>-8</v>
-      </c>
-      <c r="J54">
-        <v>0.71428571399999996</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L54">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M54">
-        <v>-8</v>
-      </c>
-      <c r="N54">
-        <v>0.71428571399999996</v>
+        <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10672</v>
+        <v>10732</v>
       </c>
       <c r="B55">
-        <v>238</v>
-      </c>
-      <c r="C55">
-        <v>238</v>
+        <v>202</v>
+      </c>
+      <c r="C55" t="s">
+        <v>53</v>
       </c>
       <c r="D55" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="E55" s="1">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F55">
-        <v>20007</v>
+        <v>20057</v>
       </c>
       <c r="G55">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="H55">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="I55">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="J55">
-        <v>0.68421052599999999</v>
+        <v>0.909090909</v>
       </c>
       <c r="K55">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L55">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="M55">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="N55">
-        <v>0.68421052599999999</v>
+        <v>0.909090909</v>
       </c>
       <c r="O55" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10666</v>
+        <v>10733</v>
       </c>
       <c r="B56">
-        <v>232</v>
-      </c>
-      <c r="C56">
-        <v>232</v>
+        <v>203</v>
+      </c>
+      <c r="C56" t="s">
+        <v>56</v>
       </c>
       <c r="D56" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="E56" s="1">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F56">
-        <v>20130</v>
+        <v>20043</v>
       </c>
       <c r="G56">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H56">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="I56">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="J56">
-        <v>0.75</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K56">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L56">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="M56">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="N56">
-        <v>0.75</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="O56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>10642</v>
+        <v>10734</v>
       </c>
       <c r="B57">
-        <v>434</v>
-      </c>
-      <c r="C57">
-        <v>434</v>
+        <v>204</v>
+      </c>
+      <c r="C57" t="s">
+        <v>70</v>
       </c>
       <c r="D57" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="E57" s="1">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F57">
-        <v>20112</v>
+        <v>20066</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>-25</v>
+      </c>
+      <c r="J57">
+        <v>0.324324324</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>-25</v>
+      </c>
+      <c r="N57">
+        <v>0.324324324</v>
       </c>
       <c r="O57" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10686</v>
+        <v>10735</v>
       </c>
       <c r="B58">
-        <v>302</v>
+        <v>205</v>
       </c>
       <c r="C58" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D58" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E58" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F58">
-        <v>20058</v>
+        <v>20047</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -3244,27 +3310,27 @@
         <v>0</v>
       </c>
       <c r="O58" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>10683</v>
+        <v>10736</v>
       </c>
       <c r="B59">
-        <v>330</v>
-      </c>
-      <c r="C59">
-        <v>330</v>
+        <v>206</v>
+      </c>
+      <c r="C59" t="s">
+        <v>55</v>
       </c>
       <c r="D59" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E59" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F59">
-        <v>20006</v>
+        <v>11215</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -3285,156 +3351,162 @@
         <v>0</v>
       </c>
       <c r="O59" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>10654</v>
+        <v>10737</v>
       </c>
       <c r="B60">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D60" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E60" s="1">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="F60">
-        <v>20086</v>
+        <v>20076</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I60">
         <v>0</v>
       </c>
-      <c r="J60">
-        <v>1</v>
-      </c>
       <c r="K60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60">
         <v>0</v>
       </c>
-      <c r="N60">
-        <v>1</v>
-      </c>
       <c r="O60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>10684</v>
+        <v>10738</v>
       </c>
       <c r="B61">
-        <v>700</v>
+        <v>209</v>
       </c>
       <c r="C61" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D61" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="E61" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F61">
-        <v>200150</v>
+        <v>20105</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="J61">
+        <v>0.76923076899999998</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="N61">
+        <v>0.76923076899999998</v>
       </c>
       <c r="O61" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>10687</v>
+        <v>10739</v>
       </c>
       <c r="B62">
-        <v>303</v>
+        <v>210</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D62" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="E62" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F62">
-        <v>20153</v>
+        <v>20095</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J62">
+        <v>0.77142857099999995</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="N62">
+        <v>0.77142857099999995</v>
       </c>
       <c r="O62" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>10688</v>
+        <v>10740</v>
       </c>
       <c r="B63">
-        <v>304</v>
+        <v>212</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D63" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E63" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F63">
-        <v>20112</v>
+        <v>20155</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -3455,27 +3527,27 @@
         <v>0</v>
       </c>
       <c r="O63" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>10689</v>
+        <v>10741</v>
       </c>
       <c r="B64">
-        <v>305</v>
+        <v>213</v>
       </c>
       <c r="C64" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D64" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E64" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F64">
-        <v>20066</v>
+        <v>20106</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3496,27 +3568,27 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>10690</v>
+        <v>10742</v>
       </c>
       <c r="B65">
-        <v>307</v>
+        <v>214</v>
       </c>
       <c r="C65" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="D65" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E65" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F65">
-        <v>20105</v>
+        <v>20058</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -3537,27 +3609,27 @@
         <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>10691</v>
+        <v>10743</v>
       </c>
       <c r="B66">
-        <v>308</v>
+        <v>215</v>
       </c>
       <c r="C66" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="D66" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E66" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F66">
-        <v>20057</v>
+        <v>20153</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3578,68 +3650,74 @@
         <v>0</v>
       </c>
       <c r="O66" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>10692</v>
+        <v>10744</v>
       </c>
       <c r="B67">
-        <v>310</v>
-      </c>
-      <c r="C67" t="s">
-        <v>75</v>
+        <v>231</v>
+      </c>
+      <c r="C67">
+        <v>231</v>
       </c>
       <c r="D67" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="E67" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F67">
-        <v>20043</v>
+        <v>20005</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="J67">
+        <v>0.63157894699999995</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>-14</v>
+      </c>
+      <c r="N67">
+        <v>0.63157894699999995</v>
       </c>
       <c r="O67" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10693</v>
+        <v>10745</v>
       </c>
       <c r="B68">
-        <v>311</v>
-      </c>
-      <c r="C68" t="s">
-        <v>41</v>
+        <v>232</v>
+      </c>
+      <c r="C68">
+        <v>232</v>
       </c>
       <c r="D68" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E68" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F68">
-        <v>20106</v>
+        <v>20130</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -3660,27 +3738,27 @@
         <v>0</v>
       </c>
       <c r="O68" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10694</v>
+        <v>10746</v>
       </c>
       <c r="B69">
-        <v>312</v>
-      </c>
-      <c r="C69" t="s">
-        <v>44</v>
+        <v>233</v>
+      </c>
+      <c r="C69">
+        <v>233</v>
       </c>
       <c r="D69" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E69" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F69">
-        <v>20095</v>
+        <v>200158</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -3701,27 +3779,27 @@
         <v>0</v>
       </c>
       <c r="O69" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>10695</v>
+        <v>10747</v>
       </c>
       <c r="B70">
-        <v>313</v>
-      </c>
-      <c r="C70" t="s">
-        <v>46</v>
+        <v>234</v>
+      </c>
+      <c r="C70">
+        <v>234</v>
       </c>
       <c r="D70" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E70" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F70">
-        <v>20076</v>
+        <v>20112</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -3742,68 +3820,74 @@
         <v>0</v>
       </c>
       <c r="O70" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10696</v>
+        <v>10748</v>
       </c>
       <c r="B71">
-        <v>314</v>
-      </c>
-      <c r="C71" t="s">
-        <v>45</v>
+        <v>235</v>
+      </c>
+      <c r="C71">
+        <v>235</v>
       </c>
       <c r="D71" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="E71" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F71">
-        <v>20047</v>
+        <v>20113</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J71">
+        <v>0.68181818199999999</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N71">
+        <v>0.68181818199999999</v>
       </c>
       <c r="O71" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>10698</v>
+        <v>10749</v>
       </c>
       <c r="B72">
-        <v>321</v>
-      </c>
-      <c r="C72" t="s">
-        <v>59</v>
+        <v>236</v>
+      </c>
+      <c r="C72">
+        <v>236</v>
       </c>
       <c r="D72" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E72" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F72">
-        <v>20005</v>
+        <v>20111</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -3824,27 +3908,27 @@
         <v>0</v>
       </c>
       <c r="O72" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>10699</v>
+        <v>10750</v>
       </c>
       <c r="B73">
-        <v>322</v>
-      </c>
-      <c r="C73" t="s">
-        <v>65</v>
+        <v>237</v>
+      </c>
+      <c r="C73">
+        <v>237</v>
       </c>
       <c r="D73" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E73" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F73">
-        <v>20130</v>
+        <v>20003</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -3865,27 +3949,27 @@
         <v>0</v>
       </c>
       <c r="O73" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>10700</v>
+        <v>10730</v>
       </c>
       <c r="B74">
-        <v>323</v>
-      </c>
-      <c r="C74" t="s">
-        <v>68</v>
+        <v>139</v>
+      </c>
+      <c r="C74">
+        <v>139</v>
       </c>
       <c r="D74" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="E74" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F74">
-        <v>200158</v>
+        <v>20008</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -3906,150 +3990,168 @@
         <v>0</v>
       </c>
       <c r="O74" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>10701</v>
+        <v>10723</v>
       </c>
       <c r="B75">
-        <v>324</v>
-      </c>
-      <c r="C75" t="s">
-        <v>63</v>
+        <v>132</v>
+      </c>
+      <c r="C75">
+        <v>132</v>
       </c>
       <c r="D75" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E75" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F75">
-        <v>200158</v>
+        <v>20130</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J75">
+        <v>0.80645161300000001</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N75">
+        <v>0.80645161300000001</v>
       </c>
       <c r="O75" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>10702</v>
+        <v>10724</v>
       </c>
       <c r="B76">
-        <v>325</v>
-      </c>
-      <c r="C76" t="s">
-        <v>62</v>
+        <v>133</v>
+      </c>
+      <c r="C76">
+        <v>133</v>
       </c>
       <c r="D76" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E76" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F76">
-        <v>20113</v>
+        <v>200158</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J76">
+        <v>0.869565217</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N76">
+        <v>0.869565217</v>
       </c>
       <c r="O76" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>10703</v>
+        <v>10710</v>
       </c>
       <c r="B77">
-        <v>326</v>
-      </c>
-      <c r="C77">
-        <v>326</v>
+        <v>102</v>
+      </c>
+      <c r="C77" t="s">
+        <v>80</v>
       </c>
       <c r="D77" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E77" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F77">
-        <v>20111</v>
+        <v>20047</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>-20</v>
+      </c>
+      <c r="J77">
+        <v>0.63636363600000001</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>-20</v>
+      </c>
+      <c r="N77">
+        <v>0.63636363600000001</v>
       </c>
       <c r="O77" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>10704</v>
+        <v>10756</v>
       </c>
       <c r="B78">
-        <v>327</v>
-      </c>
-      <c r="C78">
-        <v>327</v>
+        <v>502</v>
+      </c>
+      <c r="C78" t="s">
+        <v>51</v>
       </c>
       <c r="D78" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="E78" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="F78">
-        <v>20003</v>
+        <v>200150</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -4070,27 +4172,27 @@
         <v>0</v>
       </c>
       <c r="O78" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>10705</v>
+        <v>10725</v>
       </c>
       <c r="B79">
-        <v>328</v>
+        <v>134</v>
       </c>
       <c r="C79">
-        <v>328</v>
+        <v>134</v>
       </c>
       <c r="D79" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="E79" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F79">
-        <v>20007</v>
+        <v>20112</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -4111,68 +4213,74 @@
         <v>0</v>
       </c>
       <c r="O79" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>10706</v>
+        <v>10719</v>
       </c>
       <c r="B80">
-        <v>329</v>
-      </c>
-      <c r="C80">
-        <v>329</v>
+        <v>111</v>
+      </c>
+      <c r="C80" t="s">
+        <v>81</v>
       </c>
       <c r="D80" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E80" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="F80">
-        <v>20008</v>
+        <v>20043</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="J80">
+        <v>1.0697674420000001</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="N80">
+        <v>1.0697674420000001</v>
       </c>
       <c r="O80" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>10707</v>
+        <v>10754</v>
       </c>
       <c r="B81">
-        <v>330</v>
-      </c>
-      <c r="C81">
-        <v>330</v>
+        <v>501</v>
+      </c>
+      <c r="C81" t="s">
+        <v>49</v>
       </c>
       <c r="D81" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="E81" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="F81">
-        <v>20006</v>
+        <v>200150</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -4193,471 +4301,4073 @@
         <v>0</v>
       </c>
       <c r="O81" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>10655</v>
+        <v>10706</v>
       </c>
       <c r="B82">
-        <v>203</v>
-      </c>
-      <c r="C82" t="s">
-        <v>56</v>
+        <v>329</v>
+      </c>
+      <c r="C82">
+        <v>329</v>
       </c>
       <c r="D82" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E82" s="1">
         <v>46238</v>
       </c>
-      <c r="E82" s="1">
-        <v>46237</v>
-      </c>
       <c r="F82">
-        <v>20155</v>
+        <v>20008</v>
       </c>
       <c r="G82">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="H82">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I82">
-        <v>-22</v>
+        <v>-4</v>
       </c>
       <c r="J82">
-        <v>0.54166666699999999</v>
+        <v>0.8</v>
       </c>
       <c r="K82">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="L82">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="M82">
-        <v>-22</v>
+        <v>-4</v>
       </c>
       <c r="N82">
-        <v>0.54166666699999999</v>
+        <v>0.8</v>
       </c>
       <c r="O82" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>10657</v>
+        <v>10718</v>
       </c>
       <c r="B83">
-        <v>205</v>
+        <v>110</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D83" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="E83" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="F83">
-        <v>20047</v>
+        <v>20066</v>
       </c>
       <c r="G83">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I83">
-        <v>-2</v>
-      </c>
-      <c r="J83">
-        <v>0.94444444400000005</v>
+        <v>0</v>
       </c>
       <c r="K83">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L83">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>-2</v>
-      </c>
-      <c r="N83">
-        <v>0.94444444400000005</v>
+        <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>10659</v>
+        <v>10721</v>
       </c>
       <c r="B84">
-        <v>208</v>
+        <v>113</v>
       </c>
       <c r="C84" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D84" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="E84" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="F84">
-        <v>11215</v>
+        <v>200150</v>
       </c>
       <c r="G84">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I84">
-        <v>-13</v>
-      </c>
-      <c r="J84">
-        <v>0.67500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K84">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L84">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>-13</v>
-      </c>
-      <c r="N84">
-        <v>0.67500000000000004</v>
+        <v>0</v>
       </c>
       <c r="O84" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>10663</v>
+        <v>10695</v>
       </c>
       <c r="B85">
-        <v>212</v>
+        <v>313</v>
       </c>
       <c r="C85" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D85" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E85" s="1">
         <v>46238</v>
       </c>
-      <c r="E85" s="1">
-        <v>46237</v>
-      </c>
       <c r="F85">
-        <v>20057</v>
+        <v>20076</v>
       </c>
       <c r="G85">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="H85">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="I85">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="J85">
-        <v>0.88235294099999995</v>
+        <v>0.81818181800000001</v>
       </c>
       <c r="K85">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="L85">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="M85">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="N85">
-        <v>0.88235294099999995</v>
+        <v>0.81818181800000001</v>
       </c>
       <c r="O85" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>10665</v>
+        <v>10688</v>
       </c>
       <c r="B86">
-        <v>231</v>
-      </c>
-      <c r="C86">
-        <v>231</v>
+        <v>304</v>
+      </c>
+      <c r="C86" t="s">
+        <v>58</v>
       </c>
       <c r="D86" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E86" s="1">
         <v>46238</v>
       </c>
-      <c r="E86" s="1">
-        <v>46237</v>
-      </c>
       <c r="F86">
-        <v>20005</v>
+        <v>20086</v>
       </c>
       <c r="G86">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H86">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I86">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="J86">
-        <v>0.820512821</v>
+        <v>0.79166666699999999</v>
       </c>
       <c r="K86">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="L86">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M86">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="N86">
-        <v>0.820512821</v>
+        <v>0.79166666699999999</v>
       </c>
       <c r="O86" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>10667</v>
+        <v>10694</v>
       </c>
       <c r="B87">
-        <v>233</v>
-      </c>
-      <c r="C87">
-        <v>233</v>
+        <v>312</v>
+      </c>
+      <c r="C87" t="s">
+        <v>44</v>
       </c>
       <c r="D87" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E87" s="1">
         <v>46238</v>
       </c>
-      <c r="E87" s="1">
-        <v>46237</v>
-      </c>
       <c r="F87">
-        <v>200158</v>
+        <v>20095</v>
       </c>
       <c r="G87">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H87">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="J87">
-        <v>1</v>
+        <v>0.72727272700000001</v>
       </c>
       <c r="K87">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L87">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="N87">
-        <v>1</v>
+        <v>0.72727272700000001</v>
       </c>
       <c r="O87" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>10671</v>
+        <v>10692</v>
       </c>
       <c r="B88">
-        <v>237</v>
-      </c>
-      <c r="C88">
-        <v>237</v>
+        <v>310</v>
+      </c>
+      <c r="C88" t="s">
+        <v>75</v>
       </c>
       <c r="D88" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E88" s="1">
         <v>46238</v>
       </c>
-      <c r="E88" s="1">
-        <v>46237</v>
-      </c>
       <c r="F88">
-        <v>20003</v>
+        <v>20043</v>
       </c>
       <c r="G88">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H88">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I88">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="J88">
-        <v>0.91304347799999996</v>
+        <v>0.5</v>
       </c>
       <c r="K88">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L88">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="M88">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="N88">
-        <v>0.91304347799999996</v>
+        <v>0.5</v>
       </c>
       <c r="O88" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>10677</v>
+        <v>10693</v>
       </c>
       <c r="B89">
-        <v>209</v>
+        <v>311</v>
       </c>
       <c r="C89" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D89" s="1">
         <v>46238</v>
       </c>
       <c r="E89" s="1">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="F89">
-        <v>20105</v>
+        <v>20106</v>
       </c>
       <c r="G89">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="H89">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I89">
-        <v>-6</v>
+        <v>9</v>
       </c>
       <c r="J89">
-        <v>0.86666666699999995</v>
+        <v>1.346153846</v>
       </c>
       <c r="K89">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="L89">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M89">
-        <v>-6</v>
+        <v>9</v>
       </c>
       <c r="N89">
-        <v>0.86666666699999995</v>
+        <v>1.346153846</v>
       </c>
       <c r="O89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>10708</v>
+        <v>10668</v>
       </c>
       <c r="B90">
-        <v>800</v>
-      </c>
-      <c r="C90" t="s">
-        <v>28</v>
+        <v>234</v>
+      </c>
+      <c r="C90">
+        <v>234</v>
       </c>
       <c r="D90" s="1">
-        <v>46239</v>
+        <v>46238</v>
       </c>
       <c r="E90" s="1">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="F90">
-        <v>200150</v>
+        <v>20112</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J90">
+        <v>0.66666666699999999</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N90">
+        <v>0.66666666699999999</v>
       </c>
       <c r="O90" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
+        <v>10669</v>
+      </c>
+      <c r="B91">
+        <v>235</v>
+      </c>
+      <c r="C91">
+        <v>235</v>
+      </c>
+      <c r="D91" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E91" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F91">
+        <v>20113</v>
+      </c>
+      <c r="G91">
+        <v>8</v>
+      </c>
+      <c r="H91">
+        <v>8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91">
+        <v>8</v>
+      </c>
+      <c r="L91">
+        <v>8</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>10690</v>
+      </c>
+      <c r="B92">
+        <v>307</v>
+      </c>
+      <c r="C92" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E92" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F92">
+        <v>20105</v>
+      </c>
+      <c r="G92">
+        <v>32</v>
+      </c>
+      <c r="H92">
+        <v>28</v>
+      </c>
+      <c r="I92">
+        <v>-4</v>
+      </c>
+      <c r="J92">
+        <v>0.875</v>
+      </c>
+      <c r="K92">
+        <v>32</v>
+      </c>
+      <c r="L92">
+        <v>28</v>
+      </c>
+      <c r="M92">
+        <v>-4</v>
+      </c>
+      <c r="N92">
+        <v>0.875</v>
+      </c>
+      <c r="O92" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>10703</v>
+      </c>
+      <c r="B93">
+        <v>326</v>
+      </c>
+      <c r="C93">
+        <v>326</v>
+      </c>
+      <c r="D93" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E93" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F93">
+        <v>20111</v>
+      </c>
+      <c r="G93">
+        <v>20</v>
+      </c>
+      <c r="H93">
+        <v>14</v>
+      </c>
+      <c r="I93">
+        <v>-6</v>
+      </c>
+      <c r="J93">
+        <v>0.7</v>
+      </c>
+      <c r="K93">
+        <v>20</v>
+      </c>
+      <c r="L93">
+        <v>14</v>
+      </c>
+      <c r="M93">
+        <v>-6</v>
+      </c>
+      <c r="N93">
+        <v>0.7</v>
+      </c>
+      <c r="O93" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>10788</v>
+      </c>
+      <c r="B94">
+        <v>339</v>
+      </c>
+      <c r="C94">
+        <v>339</v>
+      </c>
+      <c r="D94" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E94" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F94">
+        <v>20008</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="O94" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>10789</v>
+      </c>
+      <c r="B95">
+        <v>340</v>
+      </c>
+      <c r="C95">
+        <v>340</v>
+      </c>
+      <c r="D95" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E95" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F95">
+        <v>20006</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="O95" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>10768</v>
+      </c>
+      <c r="B96">
+        <v>312</v>
+      </c>
+      <c r="C96" t="s">
+        <v>44</v>
+      </c>
+      <c r="D96" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E96" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F96">
+        <v>20153</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="O96" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>10769</v>
+      </c>
+      <c r="B97">
+        <v>313</v>
+      </c>
+      <c r="C97" t="s">
+        <v>46</v>
+      </c>
+      <c r="D97" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E97" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F97">
+        <v>20106</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="O97" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>10770</v>
+      </c>
+      <c r="B98">
+        <v>314</v>
+      </c>
+      <c r="C98" t="s">
+        <v>45</v>
+      </c>
+      <c r="D98" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E98" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F98">
+        <v>20047</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="O98" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>10771</v>
+      </c>
+      <c r="B99">
+        <v>315</v>
+      </c>
+      <c r="C99" t="s">
+        <v>43</v>
+      </c>
+      <c r="D99" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E99" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F99">
+        <v>11215</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="O99" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>10772</v>
+      </c>
+      <c r="B100">
+        <v>316</v>
+      </c>
+      <c r="C100" t="s">
+        <v>61</v>
+      </c>
+      <c r="D100" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E100" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F100">
+        <v>20155</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="O100" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>10773</v>
+      </c>
+      <c r="B101">
+        <v>317</v>
+      </c>
+      <c r="C101" t="s">
+        <v>76</v>
+      </c>
+      <c r="D101" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E101" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F101">
+        <v>20043</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="O101" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>10774</v>
+      </c>
+      <c r="B102">
+        <v>318</v>
+      </c>
+      <c r="C102" t="s">
+        <v>84</v>
+      </c>
+      <c r="D102" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E102" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F102">
+        <v>20058</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="O102" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>10775</v>
+      </c>
+      <c r="B103">
+        <v>321</v>
+      </c>
+      <c r="C103" t="s">
+        <v>59</v>
+      </c>
+      <c r="D103" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E103" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F103">
+        <v>20095</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="O103" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>10776</v>
+      </c>
+      <c r="B104">
+        <v>324</v>
+      </c>
+      <c r="C104" t="s">
+        <v>63</v>
+      </c>
+      <c r="D104" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E104" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F104">
+        <v>20105</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="O104" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>10778</v>
+      </c>
+      <c r="B105">
+        <v>326</v>
+      </c>
+      <c r="C105">
+        <v>326</v>
+      </c>
+      <c r="D105" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E105" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F105">
+        <v>20057</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="O105" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>10779</v>
+      </c>
+      <c r="B106">
+        <v>327</v>
+      </c>
+      <c r="C106">
+        <v>327</v>
+      </c>
+      <c r="D106" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E106" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F106">
+        <v>20076</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="O106" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>10780</v>
+      </c>
+      <c r="B107">
+        <v>331</v>
+      </c>
+      <c r="C107">
+        <v>331</v>
+      </c>
+      <c r="D107" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E107" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F107">
+        <v>20005</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="O107" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>10781</v>
+      </c>
+      <c r="B108">
+        <v>332</v>
+      </c>
+      <c r="C108">
+        <v>332</v>
+      </c>
+      <c r="D108" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E108" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F108">
+        <v>20130</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="O108" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>10782</v>
+      </c>
+      <c r="B109">
+        <v>333</v>
+      </c>
+      <c r="C109">
+        <v>333</v>
+      </c>
+      <c r="D109" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E109" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F109">
+        <v>200158</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="O109" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>10783</v>
+      </c>
+      <c r="B110">
+        <v>334</v>
+      </c>
+      <c r="C110">
+        <v>334</v>
+      </c>
+      <c r="D110" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E110" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F110">
+        <v>20112</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="O110" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>10784</v>
+      </c>
+      <c r="B111">
+        <v>335</v>
+      </c>
+      <c r="C111">
+        <v>335</v>
+      </c>
+      <c r="D111" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E111" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F111">
+        <v>20113</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="O111" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>10785</v>
+      </c>
+      <c r="B112">
+        <v>336</v>
+      </c>
+      <c r="C112">
+        <v>336</v>
+      </c>
+      <c r="D112" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E112" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F112">
+        <v>20111</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="O112" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>10786</v>
+      </c>
+      <c r="B113">
+        <v>337</v>
+      </c>
+      <c r="C113">
+        <v>337</v>
+      </c>
+      <c r="D113" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E113" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F113">
+        <v>20003</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="O113" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>10787</v>
+      </c>
+      <c r="B114">
+        <v>338</v>
+      </c>
+      <c r="C114">
+        <v>338</v>
+      </c>
+      <c r="D114" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E114" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F114">
+        <v>20112</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="O114" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>10758</v>
+      </c>
+      <c r="B115">
+        <v>301</v>
+      </c>
+      <c r="C115" t="s">
+        <v>64</v>
+      </c>
+      <c r="D115" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E115" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F115">
+        <v>20066</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="O115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>10759</v>
+      </c>
+      <c r="B116">
+        <v>302</v>
+      </c>
+      <c r="C116" t="s">
+        <v>38</v>
+      </c>
+      <c r="D116" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E116" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F116">
+        <v>20058</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="O116" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>10760</v>
+      </c>
+      <c r="B117">
+        <v>303</v>
+      </c>
+      <c r="C117" t="s">
+        <v>67</v>
+      </c>
+      <c r="D117" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E117" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F117">
+        <v>20047</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="O117" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>10761</v>
+      </c>
+      <c r="B118">
+        <v>304</v>
+      </c>
+      <c r="C118" t="s">
+        <v>58</v>
+      </c>
+      <c r="D118" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E118" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F118">
+        <v>20095</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="O118" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>10762</v>
+      </c>
+      <c r="B119">
+        <v>305</v>
+      </c>
+      <c r="C119" t="s">
+        <v>40</v>
+      </c>
+      <c r="D119" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E119" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F119">
+        <v>20106</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="O119" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>10763</v>
+      </c>
+      <c r="B120">
+        <v>306</v>
+      </c>
+      <c r="C120" t="s">
+        <v>74</v>
+      </c>
+      <c r="D120" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E120" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F120">
+        <v>20105</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="O120" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>10764</v>
+      </c>
+      <c r="B121">
+        <v>307</v>
+      </c>
+      <c r="C121" t="s">
+        <v>42</v>
+      </c>
+      <c r="D121" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E121" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F121">
+        <v>11215</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="O121" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>10765</v>
+      </c>
+      <c r="B122">
+        <v>308</v>
+      </c>
+      <c r="C122" t="s">
+        <v>36</v>
+      </c>
+      <c r="D122" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E122" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F122">
+        <v>20153</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="O122" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>10766</v>
+      </c>
+      <c r="B123">
+        <v>310</v>
+      </c>
+      <c r="C123" t="s">
+        <v>75</v>
+      </c>
+      <c r="D123" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E123" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F123">
+        <v>20155</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="O123" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>10767</v>
+      </c>
+      <c r="B124">
+        <v>311</v>
+      </c>
+      <c r="C124" t="s">
+        <v>41</v>
+      </c>
+      <c r="D124" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E124" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F124">
+        <v>20057</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="O124" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>10777</v>
+      </c>
+      <c r="B125">
+        <v>325</v>
+      </c>
+      <c r="C125" t="s">
+        <v>62</v>
+      </c>
+      <c r="D125" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E125" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F125">
+        <v>20043</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="O125" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>10757</v>
+      </c>
+      <c r="B126">
+        <v>501</v>
+      </c>
+      <c r="C126" t="s">
+        <v>49</v>
+      </c>
+      <c r="D126" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E126" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F126">
+        <v>200150</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="O126" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>10634</v>
+      </c>
+      <c r="B127">
+        <v>337</v>
+      </c>
+      <c r="C127">
+        <v>337</v>
+      </c>
+      <c r="D127" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E127" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F127">
+        <v>20003</v>
+      </c>
+      <c r="G127">
+        <v>13</v>
+      </c>
+      <c r="H127">
+        <v>13</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>1</v>
+      </c>
+      <c r="K127">
+        <v>13</v>
+      </c>
+      <c r="L127">
+        <v>13</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>10629</v>
+      </c>
+      <c r="B128">
+        <v>331</v>
+      </c>
+      <c r="C128">
+        <v>331</v>
+      </c>
+      <c r="D128" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E128" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F128">
+        <v>20006</v>
+      </c>
+      <c r="G128">
+        <v>21</v>
+      </c>
+      <c r="H128">
+        <v>18</v>
+      </c>
+      <c r="I128">
+        <v>-3</v>
+      </c>
+      <c r="J128">
+        <v>0.85714285700000004</v>
+      </c>
+      <c r="K128">
+        <v>21</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>-21</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>10617</v>
+      </c>
+      <c r="B129">
+        <v>311</v>
+      </c>
+      <c r="C129" t="s">
+        <v>41</v>
+      </c>
+      <c r="D129" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E129" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F129">
+        <v>20057</v>
+      </c>
+      <c r="G129">
+        <v>63</v>
+      </c>
+      <c r="H129">
+        <v>58</v>
+      </c>
+      <c r="I129">
+        <v>-5</v>
+      </c>
+      <c r="J129">
+        <v>0.92063492099999999</v>
+      </c>
+      <c r="K129">
+        <v>63</v>
+      </c>
+      <c r="L129">
+        <v>58</v>
+      </c>
+      <c r="M129">
+        <v>-5</v>
+      </c>
+      <c r="N129">
+        <v>0.92063492099999999</v>
+      </c>
+      <c r="O129" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>10610</v>
+      </c>
+      <c r="B130">
+        <v>303</v>
+      </c>
+      <c r="C130" t="s">
+        <v>67</v>
+      </c>
+      <c r="D130" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E130" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F130">
+        <v>20047</v>
+      </c>
+      <c r="G130">
+        <v>27</v>
+      </c>
+      <c r="H130">
+        <v>27</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>27</v>
+      </c>
+      <c r="L130">
+        <v>27</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>1</v>
+      </c>
+      <c r="O130" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>10619</v>
+      </c>
+      <c r="B131">
+        <v>313</v>
+      </c>
+      <c r="C131" t="s">
+        <v>46</v>
+      </c>
+      <c r="D131" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E131" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F131">
+        <v>20106</v>
+      </c>
+      <c r="G131">
+        <v>10</v>
+      </c>
+      <c r="H131">
+        <v>10</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>10</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>-10</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>10622</v>
+      </c>
+      <c r="B132">
+        <v>316</v>
+      </c>
+      <c r="C132" t="s">
+        <v>61</v>
+      </c>
+      <c r="D132" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E132" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F132">
+        <v>20155</v>
+      </c>
+      <c r="G132">
+        <v>22</v>
+      </c>
+      <c r="H132">
+        <v>25</v>
+      </c>
+      <c r="I132">
+        <v>3</v>
+      </c>
+      <c r="J132">
+        <v>1.136363636</v>
+      </c>
+      <c r="K132">
+        <v>22</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>-22</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>10609</v>
+      </c>
+      <c r="B133">
+        <v>302</v>
+      </c>
+      <c r="C133" t="s">
+        <v>38</v>
+      </c>
+      <c r="D133" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E133" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F133">
+        <v>20106</v>
+      </c>
+      <c r="G133">
+        <v>1</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>1</v>
+      </c>
+      <c r="O133" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>10612</v>
+      </c>
+      <c r="B134">
+        <v>305</v>
+      </c>
+      <c r="C134" t="s">
+        <v>40</v>
+      </c>
+      <c r="D134" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E134" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F134">
+        <v>20105</v>
+      </c>
+      <c r="G134">
+        <v>1</v>
+      </c>
+      <c r="H134">
+        <v>1</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>10614</v>
+      </c>
+      <c r="B135">
+        <v>307</v>
+      </c>
+      <c r="C135" t="s">
+        <v>42</v>
+      </c>
+      <c r="D135" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E135" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F135">
+        <v>20153</v>
+      </c>
+      <c r="G135">
+        <v>27</v>
+      </c>
+      <c r="H135">
+        <v>12</v>
+      </c>
+      <c r="I135">
+        <v>-15</v>
+      </c>
+      <c r="J135">
+        <v>0.44444444399999999</v>
+      </c>
+      <c r="K135">
+        <v>27</v>
+      </c>
+      <c r="L135">
+        <v>12</v>
+      </c>
+      <c r="M135">
+        <v>-15</v>
+      </c>
+      <c r="N135">
+        <v>0.44444444399999999</v>
+      </c>
+      <c r="O135" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>10683</v>
+      </c>
+      <c r="B136">
+        <v>330</v>
+      </c>
+      <c r="C136">
+        <v>330</v>
+      </c>
+      <c r="D136" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E136" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F136">
+        <v>20006</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="O136" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>10654</v>
+      </c>
+      <c r="B137">
+        <v>202</v>
+      </c>
+      <c r="C137" t="s">
+        <v>53</v>
+      </c>
+      <c r="D137" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E137" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F137">
+        <v>20086</v>
+      </c>
+      <c r="G137">
+        <v>2</v>
+      </c>
+      <c r="H137">
+        <v>2</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>2</v>
+      </c>
+      <c r="L137">
+        <v>2</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>1</v>
+      </c>
+      <c r="O137" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>10684</v>
+      </c>
+      <c r="B138">
+        <v>700</v>
+      </c>
+      <c r="C138" t="s">
+        <v>48</v>
+      </c>
+      <c r="D138" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E138" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F138">
+        <v>200150</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="O138" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>10709</v>
+      </c>
+      <c r="B139">
+        <v>101</v>
+      </c>
+      <c r="C139" t="s">
+        <v>85</v>
+      </c>
+      <c r="D139" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E139" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F139">
+        <v>20076</v>
+      </c>
+      <c r="G139">
+        <v>42</v>
+      </c>
+      <c r="H139">
+        <v>32</v>
+      </c>
+      <c r="I139">
+        <v>-10</v>
+      </c>
+      <c r="J139">
+        <v>0.76190476200000001</v>
+      </c>
+      <c r="K139">
+        <v>42</v>
+      </c>
+      <c r="L139">
+        <v>32</v>
+      </c>
+      <c r="M139">
+        <v>-10</v>
+      </c>
+      <c r="N139">
+        <v>0.76190476200000001</v>
+      </c>
+      <c r="O139" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>10712</v>
+      </c>
+      <c r="B140">
+        <v>104</v>
+      </c>
+      <c r="C140" t="s">
+        <v>86</v>
+      </c>
+      <c r="D140" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E140" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F140">
+        <v>20095</v>
+      </c>
+      <c r="G140">
+        <v>42</v>
+      </c>
+      <c r="H140">
+        <v>35</v>
+      </c>
+      <c r="I140">
+        <v>-7</v>
+      </c>
+      <c r="J140">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K140">
+        <v>42</v>
+      </c>
+      <c r="L140">
+        <v>35</v>
+      </c>
+      <c r="M140">
+        <v>-7</v>
+      </c>
+      <c r="N140">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O140" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>10713</v>
+      </c>
+      <c r="B141">
+        <v>105</v>
+      </c>
+      <c r="C141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D141" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E141" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F141">
+        <v>20058</v>
+      </c>
+      <c r="G141">
+        <v>70</v>
+      </c>
+      <c r="H141">
+        <v>43</v>
+      </c>
+      <c r="I141">
+        <v>-27</v>
+      </c>
+      <c r="J141">
+        <v>0.61428571399999998</v>
+      </c>
+      <c r="K141">
+        <v>70</v>
+      </c>
+      <c r="L141">
+        <v>43</v>
+      </c>
+      <c r="M141">
+        <v>-27</v>
+      </c>
+      <c r="N141">
+        <v>0.61428571399999998</v>
+      </c>
+      <c r="O141" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>10722</v>
+      </c>
+      <c r="B142">
+        <v>131</v>
+      </c>
+      <c r="C142">
+        <v>131</v>
+      </c>
+      <c r="D142" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E142" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F142">
+        <v>20005</v>
+      </c>
+      <c r="G142">
+        <v>20</v>
+      </c>
+      <c r="H142">
+        <v>17</v>
+      </c>
+      <c r="I142">
+        <v>-3</v>
+      </c>
+      <c r="J142">
+        <v>0.85</v>
+      </c>
+      <c r="K142">
+        <v>20</v>
+      </c>
+      <c r="L142">
+        <v>17</v>
+      </c>
+      <c r="M142">
+        <v>-3</v>
+      </c>
+      <c r="N142">
+        <v>0.85</v>
+      </c>
+      <c r="O142" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143">
         <v>10697</v>
       </c>
-      <c r="B91">
+      <c r="B143">
         <v>315</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C143" t="s">
         <v>43</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D143" s="1">
         <v>46239</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E143" s="1">
         <v>46238</v>
       </c>
-      <c r="F91">
+      <c r="F143">
         <v>11215</v>
       </c>
-      <c r="G91">
+      <c r="G143">
         <v>27</v>
       </c>
-      <c r="H91">
-        <v>0</v>
-      </c>
-      <c r="I91">
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
         <v>-27</v>
       </c>
-      <c r="J91">
-        <v>0</v>
-      </c>
-      <c r="K91">
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
         <v>27</v>
       </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
         <v>-27</v>
       </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91" t="s">
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>10700</v>
+      </c>
+      <c r="B144">
+        <v>323</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E144" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F144">
+        <v>200158</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="O144" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>10623</v>
+      </c>
+      <c r="B145">
+        <v>317</v>
+      </c>
+      <c r="C145" t="s">
+        <v>76</v>
+      </c>
+      <c r="D145" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E145" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F145">
+        <v>20043</v>
+      </c>
+      <c r="G145">
+        <v>24</v>
+      </c>
+      <c r="H145">
+        <v>23</v>
+      </c>
+      <c r="I145">
+        <v>-1</v>
+      </c>
+      <c r="J145">
+        <v>0.95833333300000001</v>
+      </c>
+      <c r="K145">
+        <v>24</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>-24</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>10650</v>
+      </c>
+      <c r="B146">
+        <v>800</v>
+      </c>
+      <c r="C146" t="s">
+        <v>28</v>
+      </c>
+      <c r="D146" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E146" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F146">
+        <v>200150</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="O146" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>10655</v>
+      </c>
+      <c r="B147">
+        <v>203</v>
+      </c>
+      <c r="C147" t="s">
+        <v>56</v>
+      </c>
+      <c r="D147" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E147" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F147">
+        <v>20155</v>
+      </c>
+      <c r="G147">
+        <v>48</v>
+      </c>
+      <c r="H147">
+        <v>26</v>
+      </c>
+      <c r="I147">
+        <v>-22</v>
+      </c>
+      <c r="J147">
+        <v>0.54166666699999999</v>
+      </c>
+      <c r="K147">
+        <v>48</v>
+      </c>
+      <c r="L147">
+        <v>26</v>
+      </c>
+      <c r="M147">
+        <v>-22</v>
+      </c>
+      <c r="N147">
+        <v>0.54166666699999999</v>
+      </c>
+      <c r="O147" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>10716</v>
+      </c>
+      <c r="B148">
+        <v>108</v>
+      </c>
+      <c r="C148" t="s">
+        <v>88</v>
+      </c>
+      <c r="D148" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E148" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F148">
+        <v>20057</v>
+      </c>
+      <c r="G148">
+        <v>59</v>
+      </c>
+      <c r="H148">
+        <v>51</v>
+      </c>
+      <c r="I148">
+        <v>-8</v>
+      </c>
+      <c r="J148">
+        <v>0.86440678000000004</v>
+      </c>
+      <c r="K148">
+        <v>59</v>
+      </c>
+      <c r="L148">
+        <v>51</v>
+      </c>
+      <c r="M148">
+        <v>-8</v>
+      </c>
+      <c r="N148">
+        <v>0.86440678000000004</v>
+      </c>
+      <c r="O148" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>10657</v>
+      </c>
+      <c r="B149">
+        <v>205</v>
+      </c>
+      <c r="C149" t="s">
+        <v>60</v>
+      </c>
+      <c r="D149" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E149" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F149">
+        <v>20047</v>
+      </c>
+      <c r="G149">
+        <v>36</v>
+      </c>
+      <c r="H149">
+        <v>34</v>
+      </c>
+      <c r="I149">
+        <v>-2</v>
+      </c>
+      <c r="J149">
+        <v>0.94444444400000005</v>
+      </c>
+      <c r="K149">
+        <v>36</v>
+      </c>
+      <c r="L149">
+        <v>34</v>
+      </c>
+      <c r="M149">
+        <v>-2</v>
+      </c>
+      <c r="N149">
+        <v>0.94444444400000005</v>
+      </c>
+      <c r="O149" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>10704</v>
+      </c>
+      <c r="B150">
+        <v>327</v>
+      </c>
+      <c r="C150">
+        <v>327</v>
+      </c>
+      <c r="D150" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E150" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F150">
+        <v>20003</v>
+      </c>
+      <c r="G150">
+        <v>30</v>
+      </c>
+      <c r="H150">
+        <v>15</v>
+      </c>
+      <c r="I150">
+        <v>-15</v>
+      </c>
+      <c r="J150">
+        <v>0.5</v>
+      </c>
+      <c r="K150">
+        <v>30</v>
+      </c>
+      <c r="L150">
+        <v>15</v>
+      </c>
+      <c r="M150">
+        <v>-15</v>
+      </c>
+      <c r="N150">
+        <v>0.5</v>
+      </c>
+      <c r="O150" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>10659</v>
+      </c>
+      <c r="B151">
+        <v>208</v>
+      </c>
+      <c r="C151" t="s">
+        <v>71</v>
+      </c>
+      <c r="D151" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E151" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F151">
+        <v>11215</v>
+      </c>
+      <c r="G151">
+        <v>40</v>
+      </c>
+      <c r="H151">
+        <v>27</v>
+      </c>
+      <c r="I151">
+        <v>-13</v>
+      </c>
+      <c r="J151">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="K151">
+        <v>40</v>
+      </c>
+      <c r="L151">
+        <v>27</v>
+      </c>
+      <c r="M151">
+        <v>-13</v>
+      </c>
+      <c r="N151">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="O151" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>10660</v>
+      </c>
+      <c r="B152">
+        <v>209</v>
+      </c>
+      <c r="C152" t="s">
+        <v>54</v>
+      </c>
+      <c r="D152" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E152" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F152">
+        <v>20105</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="O152" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>10687</v>
+      </c>
+      <c r="B153">
+        <v>303</v>
+      </c>
+      <c r="C153" t="s">
+        <v>67</v>
+      </c>
+      <c r="D153" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E153" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F153">
+        <v>20153</v>
+      </c>
+      <c r="G153">
+        <v>37</v>
+      </c>
+      <c r="H153">
+        <v>28</v>
+      </c>
+      <c r="I153">
+        <v>-9</v>
+      </c>
+      <c r="J153">
+        <v>0.756756757</v>
+      </c>
+      <c r="K153">
+        <v>37</v>
+      </c>
+      <c r="L153">
+        <v>28</v>
+      </c>
+      <c r="M153">
+        <v>-9</v>
+      </c>
+      <c r="N153">
+        <v>0.756756757</v>
+      </c>
+      <c r="O153" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>10686</v>
+      </c>
+      <c r="B154">
+        <v>302</v>
+      </c>
+      <c r="C154" t="s">
+        <v>38</v>
+      </c>
+      <c r="D154" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E154" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F154">
+        <v>20058</v>
+      </c>
+      <c r="G154">
+        <v>41</v>
+      </c>
+      <c r="H154">
+        <v>23</v>
+      </c>
+      <c r="I154">
+        <v>-18</v>
+      </c>
+      <c r="J154">
+        <v>0.56097560999999996</v>
+      </c>
+      <c r="K154">
+        <v>41</v>
+      </c>
+      <c r="L154">
+        <v>23</v>
+      </c>
+      <c r="M154">
+        <v>-18</v>
+      </c>
+      <c r="N154">
+        <v>0.56097560999999996</v>
+      </c>
+      <c r="O154" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>10663</v>
+      </c>
+      <c r="B155">
+        <v>212</v>
+      </c>
+      <c r="C155" t="s">
+        <v>50</v>
+      </c>
+      <c r="D155" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E155" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F155">
+        <v>20057</v>
+      </c>
+      <c r="G155">
+        <v>85</v>
+      </c>
+      <c r="H155">
+        <v>75</v>
+      </c>
+      <c r="I155">
+        <v>-10</v>
+      </c>
+      <c r="J155">
+        <v>0.88235294099999995</v>
+      </c>
+      <c r="K155">
+        <v>85</v>
+      </c>
+      <c r="L155">
+        <v>75</v>
+      </c>
+      <c r="M155">
+        <v>-10</v>
+      </c>
+      <c r="N155">
+        <v>0.88235294099999995</v>
+      </c>
+      <c r="O155" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>10664</v>
+      </c>
+      <c r="B156">
+        <v>213</v>
+      </c>
+      <c r="C156" t="s">
+        <v>57</v>
+      </c>
+      <c r="D156" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E156" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F156">
+        <v>20058</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="O156" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>10665</v>
+      </c>
+      <c r="B157">
+        <v>231</v>
+      </c>
+      <c r="C157">
+        <v>231</v>
+      </c>
+      <c r="D157" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E157" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F157">
+        <v>20005</v>
+      </c>
+      <c r="G157">
+        <v>39</v>
+      </c>
+      <c r="H157">
+        <v>32</v>
+      </c>
+      <c r="I157">
+        <v>-7</v>
+      </c>
+      <c r="J157">
+        <v>0.820512821</v>
+      </c>
+      <c r="K157">
+        <v>39</v>
+      </c>
+      <c r="L157">
+        <v>32</v>
+      </c>
+      <c r="M157">
+        <v>-7</v>
+      </c>
+      <c r="N157">
+        <v>0.820512821</v>
+      </c>
+      <c r="O157" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>10731</v>
+      </c>
+      <c r="B158">
+        <v>140</v>
+      </c>
+      <c r="C158">
+        <v>140</v>
+      </c>
+      <c r="D158" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E158" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F158">
+        <v>20006</v>
+      </c>
+      <c r="G158">
+        <v>22</v>
+      </c>
+      <c r="H158">
+        <v>19</v>
+      </c>
+      <c r="I158">
+        <v>-3</v>
+      </c>
+      <c r="J158">
+        <v>0.86363636399999999</v>
+      </c>
+      <c r="K158">
+        <v>22</v>
+      </c>
+      <c r="L158">
+        <v>19</v>
+      </c>
+      <c r="M158">
+        <v>-3</v>
+      </c>
+      <c r="N158">
+        <v>0.86363636399999999</v>
+      </c>
+      <c r="O158" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>10667</v>
+      </c>
+      <c r="B159">
+        <v>233</v>
+      </c>
+      <c r="C159">
+        <v>233</v>
+      </c>
+      <c r="D159" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E159" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F159">
+        <v>200158</v>
+      </c>
+      <c r="G159">
+        <v>28</v>
+      </c>
+      <c r="H159">
+        <v>28</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>28</v>
+      </c>
+      <c r="L159">
+        <v>28</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>1</v>
+      </c>
+      <c r="O159" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>10729</v>
+      </c>
+      <c r="B160">
+        <v>138</v>
+      </c>
+      <c r="C160">
+        <v>138</v>
+      </c>
+      <c r="D160" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E160" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F160">
+        <v>20007</v>
+      </c>
+      <c r="G160">
+        <v>27</v>
+      </c>
+      <c r="H160">
+        <v>19</v>
+      </c>
+      <c r="I160">
+        <v>-8</v>
+      </c>
+      <c r="J160">
+        <v>0.70370370400000004</v>
+      </c>
+      <c r="K160">
+        <v>27</v>
+      </c>
+      <c r="L160">
+        <v>19</v>
+      </c>
+      <c r="M160">
+        <v>-8</v>
+      </c>
+      <c r="N160">
+        <v>0.70370370400000004</v>
+      </c>
+      <c r="O160" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>10727</v>
+      </c>
+      <c r="B161">
+        <v>136</v>
+      </c>
+      <c r="C161">
+        <v>136</v>
+      </c>
+      <c r="D161" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E161" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F161">
+        <v>20111</v>
+      </c>
+      <c r="G161">
+        <v>12</v>
+      </c>
+      <c r="H161">
+        <v>10</v>
+      </c>
+      <c r="I161">
+        <v>-2</v>
+      </c>
+      <c r="J161">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K161">
+        <v>12</v>
+      </c>
+      <c r="L161">
+        <v>10</v>
+      </c>
+      <c r="M161">
+        <v>-2</v>
+      </c>
+      <c r="N161">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O161" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>10720</v>
+      </c>
+      <c r="B162">
+        <v>112</v>
+      </c>
+      <c r="C162" t="s">
+        <v>89</v>
+      </c>
+      <c r="D162" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E162" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F162">
+        <v>20106</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>1</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>1</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="O162" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>10671</v>
+      </c>
+      <c r="B163">
+        <v>237</v>
+      </c>
+      <c r="C163">
+        <v>237</v>
+      </c>
+      <c r="D163" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E163" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F163">
+        <v>20003</v>
+      </c>
+      <c r="G163">
+        <v>23</v>
+      </c>
+      <c r="H163">
+        <v>21</v>
+      </c>
+      <c r="I163">
+        <v>-2</v>
+      </c>
+      <c r="J163">
+        <v>0.91304347799999996</v>
+      </c>
+      <c r="K163">
+        <v>23</v>
+      </c>
+      <c r="L163">
+        <v>21</v>
+      </c>
+      <c r="M163">
+        <v>-2</v>
+      </c>
+      <c r="N163">
+        <v>0.91304347799999996</v>
+      </c>
+      <c r="O163" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>10717</v>
+      </c>
+      <c r="B164">
+        <v>109</v>
+      </c>
+      <c r="C164" t="s">
+        <v>90</v>
+      </c>
+      <c r="D164" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E164" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F164">
+        <v>20105</v>
+      </c>
+      <c r="G164">
+        <v>46</v>
+      </c>
+      <c r="H164">
+        <v>33</v>
+      </c>
+      <c r="I164">
+        <v>-13</v>
+      </c>
+      <c r="J164">
+        <v>0.71739130399999995</v>
+      </c>
+      <c r="K164">
+        <v>46</v>
+      </c>
+      <c r="L164">
+        <v>33</v>
+      </c>
+      <c r="M164">
+        <v>-13</v>
+      </c>
+      <c r="N164">
+        <v>0.71739130399999995</v>
+      </c>
+      <c r="O164" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>10711</v>
+      </c>
+      <c r="B165">
+        <v>103</v>
+      </c>
+      <c r="C165" t="s">
+        <v>91</v>
+      </c>
+      <c r="D165" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E165" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F165">
+        <v>20153</v>
+      </c>
+      <c r="G165">
+        <v>50</v>
+      </c>
+      <c r="H165">
+        <v>33</v>
+      </c>
+      <c r="I165">
+        <v>-17</v>
+      </c>
+      <c r="J165">
+        <v>0.66</v>
+      </c>
+      <c r="K165">
+        <v>50</v>
+      </c>
+      <c r="L165">
+        <v>33</v>
+      </c>
+      <c r="M165">
+        <v>-17</v>
+      </c>
+      <c r="N165">
+        <v>0.66</v>
+      </c>
+      <c r="O165" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>10714</v>
+      </c>
+      <c r="B166">
+        <v>106</v>
+      </c>
+      <c r="C166" t="s">
+        <v>92</v>
+      </c>
+      <c r="D166" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E166" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F166">
+        <v>11215</v>
+      </c>
+      <c r="G166">
+        <v>48</v>
+      </c>
+      <c r="H166">
+        <v>47</v>
+      </c>
+      <c r="I166">
+        <v>-1</v>
+      </c>
+      <c r="J166">
+        <v>0.97916666699999999</v>
+      </c>
+      <c r="K166">
+        <v>48</v>
+      </c>
+      <c r="L166">
+        <v>47</v>
+      </c>
+      <c r="M166">
+        <v>-1</v>
+      </c>
+      <c r="N166">
+        <v>0.97916666699999999</v>
+      </c>
+      <c r="O166" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>10677</v>
+      </c>
+      <c r="B167">
+        <v>209</v>
+      </c>
+      <c r="C167" t="s">
+        <v>54</v>
+      </c>
+      <c r="D167" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E167" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F167">
+        <v>20105</v>
+      </c>
+      <c r="G167">
+        <v>45</v>
+      </c>
+      <c r="H167">
+        <v>39</v>
+      </c>
+      <c r="I167">
+        <v>-6</v>
+      </c>
+      <c r="J167">
+        <v>0.86666666699999995</v>
+      </c>
+      <c r="K167">
+        <v>45</v>
+      </c>
+      <c r="L167">
+        <v>39</v>
+      </c>
+      <c r="M167">
+        <v>-6</v>
+      </c>
+      <c r="N167">
+        <v>0.86666666699999995</v>
+      </c>
+      <c r="O167" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>10715</v>
+      </c>
+      <c r="B168">
+        <v>107</v>
+      </c>
+      <c r="C168" t="s">
+        <v>93</v>
+      </c>
+      <c r="D168" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E168" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F168">
+        <v>20155</v>
+      </c>
+      <c r="G168">
+        <v>38</v>
+      </c>
+      <c r="H168">
+        <v>36</v>
+      </c>
+      <c r="I168">
+        <v>-2</v>
+      </c>
+      <c r="J168">
+        <v>0.94736842099999996</v>
+      </c>
+      <c r="K168">
+        <v>38</v>
+      </c>
+      <c r="L168">
+        <v>36</v>
+      </c>
+      <c r="M168">
+        <v>-2</v>
+      </c>
+      <c r="N168">
+        <v>0.94736842099999996</v>
+      </c>
+      <c r="O168" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>10755</v>
+      </c>
+      <c r="B169">
+        <v>800</v>
+      </c>
+      <c r="C169" t="s">
+        <v>28</v>
+      </c>
+      <c r="D169" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E169" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F169">
+        <v>200150</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="O169" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>10632</v>
+      </c>
+      <c r="B170">
+        <v>335</v>
+      </c>
+      <c r="C170">
+        <v>335</v>
+      </c>
+      <c r="D170" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E170" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F170">
+        <v>20113</v>
+      </c>
+      <c r="G170">
+        <v>13</v>
+      </c>
+      <c r="H170">
+        <v>13</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>13</v>
+      </c>
+      <c r="L170">
+        <v>13</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>1</v>
+      </c>
+      <c r="O170" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>10726</v>
+      </c>
+      <c r="B171">
+        <v>135</v>
+      </c>
+      <c r="C171">
+        <v>135</v>
+      </c>
+      <c r="D171" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E171" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F171">
+        <v>20113</v>
+      </c>
+      <c r="G171">
+        <v>13</v>
+      </c>
+      <c r="H171">
+        <v>13</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>13</v>
+      </c>
+      <c r="L171">
+        <v>13</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171">
+        <v>1</v>
+      </c>
+      <c r="O171" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>10728</v>
+      </c>
+      <c r="B172">
+        <v>137</v>
+      </c>
+      <c r="C172">
+        <v>137</v>
+      </c>
+      <c r="D172" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E172" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F172">
+        <v>20003</v>
+      </c>
+      <c r="G172">
+        <v>8</v>
+      </c>
+      <c r="H172">
+        <v>5</v>
+      </c>
+      <c r="I172">
+        <v>-3</v>
+      </c>
+      <c r="J172">
+        <v>0.625</v>
+      </c>
+      <c r="K172">
+        <v>8</v>
+      </c>
+      <c r="L172">
+        <v>5</v>
+      </c>
+      <c r="M172">
+        <v>-3</v>
+      </c>
+      <c r="N172">
+        <v>0.625</v>
+      </c>
+      <c r="O172" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>10753</v>
+      </c>
+      <c r="B173">
+        <v>240</v>
+      </c>
+      <c r="C173">
+        <v>240</v>
+      </c>
+      <c r="D173" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E173" s="1">
+        <v>46240</v>
+      </c>
+      <c r="F173">
+        <v>20006</v>
+      </c>
+      <c r="G173">
+        <v>24</v>
+      </c>
+      <c r="H173">
+        <v>20</v>
+      </c>
+      <c r="I173">
+        <v>-4</v>
+      </c>
+      <c r="J173">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K173">
+        <v>24</v>
+      </c>
+      <c r="L173">
+        <v>20</v>
+      </c>
+      <c r="M173">
+        <v>-4</v>
+      </c>
+      <c r="N173">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O173" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/cartones.xlsx
+++ b/data/cartones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\sistema 611\datos agosto 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D5BC11-48EC-4CF1-8F99-556D35105847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{447E5F44-A7AE-410F-9C1C-717B16A3FAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{EE42AFD4-3D44-431D-BF0C-DB1E709F72DE}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="15375" windowHeight="7785" xr2:uid="{EE42AFD4-3D44-431D-BF0C-DB1E709F72DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="98">
   <si>
     <t>codigo</t>
   </si>
@@ -316,6 +316,18 @@
   </si>
   <si>
     <t>107 CAM 7 LUNES</t>
+  </si>
+  <si>
+    <t>207 CAM 7 MARTES</t>
+  </si>
+  <si>
+    <t>309 CAM 9 MIÉRCOLES</t>
+  </si>
+  <si>
+    <t>802 VSB Cuyo</t>
+  </si>
+  <si>
+    <t>801 PyP La Francia</t>
   </si>
 </sst>
 </file>
@@ -668,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74F70945-99D5-4C4A-8C8A-BA7E0A7AEEC0}">
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O235"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1818,22 +1830,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>10752</v>
+        <v>10801</v>
       </c>
       <c r="B26">
-        <v>239</v>
-      </c>
-      <c r="C26">
-        <v>239</v>
+        <v>800</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
       </c>
       <c r="D26" s="1">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="E26" s="1">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="F26">
-        <v>20008</v>
+        <v>200150</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1854,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -3274,43 +3286,49 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10735</v>
+        <v>10741</v>
       </c>
       <c r="B58">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C58" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D58" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E58" s="1">
         <v>46240</v>
       </c>
       <c r="F58">
-        <v>20047</v>
+        <v>20106</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="J58">
+        <v>0.4</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>-18</v>
+      </c>
+      <c r="N58">
+        <v>0.4</v>
       </c>
       <c r="O58" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -3324,7 +3342,7 @@
         <v>55</v>
       </c>
       <c r="D59" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E59" s="1">
         <v>46240</v>
@@ -3333,22 +3351,28 @@
         <v>11215</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>-16</v>
+      </c>
+      <c r="J59">
+        <v>0.54285714299999999</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>-16</v>
+      </c>
+      <c r="N59">
+        <v>0.54285714299999999</v>
       </c>
       <c r="O59" t="s">
         <v>47</v>
@@ -3365,7 +3389,7 @@
         <v>71</v>
       </c>
       <c r="D60" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E60" s="1">
         <v>46240</v>
@@ -3374,22 +3398,28 @@
         <v>20076</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J60">
+        <v>0.88888888899999996</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N60">
+        <v>0.88888888899999996</v>
       </c>
       <c r="O60" t="s">
         <v>22</v>
@@ -3500,7 +3530,7 @@
         <v>50</v>
       </c>
       <c r="D63" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E63" s="1">
         <v>46240</v>
@@ -3509,22 +3539,28 @@
         <v>20155</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>-16</v>
+      </c>
+      <c r="J63">
+        <v>0.60975609799999997</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>-16</v>
+      </c>
+      <c r="N63">
+        <v>0.60975609799999997</v>
       </c>
       <c r="O63" t="s">
         <v>26</v>
@@ -3532,22 +3568,22 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>10741</v>
+        <v>10790</v>
       </c>
       <c r="B64">
-        <v>213</v>
-      </c>
-      <c r="C64" t="s">
-        <v>57</v>
+        <v>328</v>
+      </c>
+      <c r="C64">
+        <v>328</v>
       </c>
       <c r="D64" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="E64" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="F64">
-        <v>20106</v>
+        <v>20076</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -3568,27 +3604,27 @@
         <v>0</v>
       </c>
       <c r="O64" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>10742</v>
+        <v>10684</v>
       </c>
       <c r="B65">
-        <v>214</v>
+        <v>700</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D65" s="1">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="E65" s="1">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="F65">
-        <v>20058</v>
+        <v>200150</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -3609,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="O65" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
@@ -3623,7 +3659,7 @@
         <v>79</v>
       </c>
       <c r="D66" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E66" s="1">
         <v>46240</v>
@@ -3632,22 +3668,28 @@
         <v>20153</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J66">
+        <v>0.68</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M66">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="N66">
+        <v>0.68</v>
       </c>
       <c r="O66" t="s">
         <v>25</v>
@@ -3702,1245 +3744,1293 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>10745</v>
+        <v>10749</v>
       </c>
       <c r="B68">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C68">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D68" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E68" s="1">
         <v>46240</v>
       </c>
       <c r="F68">
-        <v>20130</v>
+        <v>20111</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>-13</v>
+      </c>
+      <c r="J68">
+        <v>0.48</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>-13</v>
+      </c>
+      <c r="N68">
+        <v>0.48</v>
       </c>
       <c r="O68" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>10746</v>
+        <v>10747</v>
       </c>
       <c r="B69">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C69">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D69" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E69" s="1">
         <v>46240</v>
       </c>
       <c r="F69">
-        <v>200158</v>
+        <v>20112</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J69">
+        <v>0.5</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M69">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="N69">
+        <v>0.5</v>
       </c>
       <c r="O69" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>10747</v>
+        <v>10748</v>
       </c>
       <c r="B70">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C70">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D70" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E70" s="1">
         <v>46240</v>
       </c>
       <c r="F70">
-        <v>20112</v>
+        <v>20113</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J70">
+        <v>0.68181818199999999</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M70">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N70">
+        <v>0.68181818199999999</v>
       </c>
       <c r="O70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>10748</v>
+        <v>10767</v>
       </c>
       <c r="B71">
-        <v>235</v>
-      </c>
-      <c r="C71">
-        <v>235</v>
+        <v>311</v>
+      </c>
+      <c r="C71" t="s">
+        <v>41</v>
       </c>
       <c r="D71" s="1">
+        <v>46242</v>
+      </c>
+      <c r="E71" s="1">
         <v>46241</v>
       </c>
-      <c r="E71" s="1">
-        <v>46240</v>
-      </c>
       <c r="F71">
-        <v>20113</v>
+        <v>20057</v>
       </c>
       <c r="G71">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H71">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="I71">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="J71">
-        <v>0.68181818199999999</v>
+        <v>0.96</v>
       </c>
       <c r="K71">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="L71">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="M71">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="N71">
-        <v>0.68181818199999999</v>
+        <v>0.96</v>
       </c>
       <c r="O71" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>10749</v>
+        <v>10723</v>
       </c>
       <c r="B72">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c r="C72">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c r="D72" s="1">
         <v>46240</v>
       </c>
       <c r="E72" s="1">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="F72">
-        <v>20111</v>
+        <v>20130</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J72">
+        <v>0.80645161300000001</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N72">
+        <v>0.80645161300000001</v>
       </c>
       <c r="O72" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>10750</v>
+        <v>10724</v>
       </c>
       <c r="B73">
-        <v>237</v>
+        <v>133</v>
       </c>
       <c r="C73">
-        <v>237</v>
+        <v>133</v>
       </c>
       <c r="D73" s="1">
         <v>46240</v>
       </c>
       <c r="E73" s="1">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="F73">
-        <v>20003</v>
+        <v>200158</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I73">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="J73">
+        <v>0.869565217</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="N73">
+        <v>0.869565217</v>
       </c>
       <c r="O73" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>10730</v>
+        <v>10710</v>
       </c>
       <c r="B74">
-        <v>139</v>
-      </c>
-      <c r="C74">
-        <v>139</v>
+        <v>102</v>
+      </c>
+      <c r="C74" t="s">
+        <v>80</v>
       </c>
       <c r="D74" s="1">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="E74" s="1">
         <v>46239</v>
       </c>
       <c r="F74">
-        <v>20008</v>
+        <v>20047</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>-20</v>
+      </c>
+      <c r="J74">
+        <v>0.63636363600000001</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>-20</v>
+      </c>
+      <c r="N74">
+        <v>0.63636363600000001</v>
       </c>
       <c r="O74" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>10723</v>
+        <v>10756</v>
       </c>
       <c r="B75">
-        <v>132</v>
-      </c>
-      <c r="C75">
-        <v>132</v>
+        <v>502</v>
+      </c>
+      <c r="C75" t="s">
+        <v>51</v>
       </c>
       <c r="D75" s="1">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E75" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F75">
-        <v>20130</v>
+        <v>200150</v>
       </c>
       <c r="G75">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I75">
-        <v>-6</v>
-      </c>
-      <c r="J75">
-        <v>0.80645161300000001</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L75">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M75">
-        <v>-6</v>
-      </c>
-      <c r="N75">
-        <v>0.80645161300000001</v>
+        <v>0</v>
       </c>
       <c r="O75" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>10724</v>
+        <v>10768</v>
       </c>
       <c r="B76">
-        <v>133</v>
-      </c>
-      <c r="C76">
-        <v>133</v>
+        <v>312</v>
+      </c>
+      <c r="C76" t="s">
+        <v>44</v>
       </c>
       <c r="D76" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="E76" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F76">
-        <v>200158</v>
+        <v>20153</v>
       </c>
       <c r="G76">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H76">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I76">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="J76">
-        <v>0.869565217</v>
+        <v>0.57894736800000002</v>
       </c>
       <c r="K76">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L76">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="M76">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="N76">
-        <v>0.869565217</v>
+        <v>0.57894736800000002</v>
       </c>
       <c r="O76" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>10710</v>
+        <v>10774</v>
       </c>
       <c r="B77">
-        <v>102</v>
+        <v>318</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D77" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="E77" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F77">
-        <v>20047</v>
+        <v>20058</v>
       </c>
       <c r="G77">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="H77">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="I77">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="J77">
-        <v>0.63636363600000001</v>
+        <v>0.30434782599999999</v>
       </c>
       <c r="K77">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="L77">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="N77">
-        <v>0.63636363600000001</v>
+        <v>0</v>
       </c>
       <c r="O77" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>10756</v>
+        <v>10719</v>
       </c>
       <c r="B78">
-        <v>502</v>
+        <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="D78" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="E78" s="1">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="F78">
-        <v>200150</v>
+        <v>20043</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="J78">
+        <v>1.0697674420000001</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="N78">
+        <v>1.0697674420000001</v>
       </c>
       <c r="O78" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>10725</v>
+        <v>10780</v>
       </c>
       <c r="B79">
-        <v>134</v>
+        <v>331</v>
       </c>
       <c r="C79">
-        <v>134</v>
+        <v>331</v>
       </c>
       <c r="D79" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="E79" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F79">
-        <v>20112</v>
+        <v>20005</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H79">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="J79">
+        <v>0.590909091</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="N79">
+        <v>0.590909091</v>
       </c>
       <c r="O79" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>10719</v>
+        <v>10754</v>
       </c>
       <c r="B80">
-        <v>111</v>
+        <v>501</v>
       </c>
       <c r="C80" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="D80" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E80" s="1">
         <v>46240</v>
       </c>
-      <c r="E80" s="1">
-        <v>46239</v>
-      </c>
       <c r="F80">
-        <v>20043</v>
+        <v>200150</v>
       </c>
       <c r="G80">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="H80">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="I80">
-        <v>3</v>
-      </c>
-      <c r="J80">
-        <v>1.0697674420000001</v>
+        <v>0</v>
       </c>
       <c r="K80">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L80">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M80">
-        <v>3</v>
-      </c>
-      <c r="N80">
-        <v>1.0697674420000001</v>
+        <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>10754</v>
+        <v>10706</v>
       </c>
       <c r="B81">
-        <v>501</v>
-      </c>
-      <c r="C81" t="s">
-        <v>49</v>
+        <v>329</v>
+      </c>
+      <c r="C81">
+        <v>329</v>
       </c>
       <c r="D81" s="1">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="E81" s="1">
-        <v>46240</v>
+        <v>46238</v>
       </c>
       <c r="F81">
-        <v>200150</v>
+        <v>20008</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J81">
+        <v>0.8</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N81">
+        <v>0.8</v>
       </c>
       <c r="O81" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>10706</v>
+        <v>10775</v>
       </c>
       <c r="B82">
-        <v>329</v>
-      </c>
-      <c r="C82">
-        <v>329</v>
+        <v>321</v>
+      </c>
+      <c r="C82" t="s">
+        <v>59</v>
       </c>
       <c r="D82" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="E82" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="F82">
-        <v>20008</v>
+        <v>20095</v>
       </c>
       <c r="G82">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H82">
+        <v>9</v>
+      </c>
+      <c r="I82">
+        <v>-7</v>
+      </c>
+      <c r="J82">
+        <v>0.5625</v>
+      </c>
+      <c r="K82">
         <v>16</v>
       </c>
-      <c r="I82">
-        <v>-4</v>
-      </c>
-      <c r="J82">
-        <v>0.8</v>
-      </c>
-      <c r="K82">
-        <v>20</v>
-      </c>
       <c r="L82">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M82">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="N82">
-        <v>0.8</v>
+        <v>0.5625</v>
       </c>
       <c r="O82" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>10718</v>
+        <v>10789</v>
       </c>
       <c r="B83">
-        <v>110</v>
-      </c>
-      <c r="C83" t="s">
-        <v>82</v>
+        <v>340</v>
+      </c>
+      <c r="C83">
+        <v>340</v>
       </c>
       <c r="D83" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="E83" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F83">
-        <v>20066</v>
+        <v>20006</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J83">
+        <v>0.83333333300000001</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
       <c r="M83">
+        <v>-24</v>
+      </c>
+      <c r="N83">
         <v>0</v>
       </c>
       <c r="O83" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>10721</v>
+        <v>10776</v>
       </c>
       <c r="B84">
-        <v>113</v>
+        <v>324</v>
       </c>
       <c r="C84" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="D84" s="1">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="E84" s="1">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="F84">
-        <v>200150</v>
+        <v>20105</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J84">
+        <v>0.61538461499999997</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="N84">
+        <v>0.61538461499999997</v>
       </c>
       <c r="O84" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>10695</v>
+        <v>10770</v>
       </c>
       <c r="B85">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C85" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D85" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="E85" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="F85">
-        <v>20076</v>
+        <v>20047</v>
       </c>
       <c r="G85">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H85">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I85">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="J85">
-        <v>0.81818181800000001</v>
+        <v>1</v>
       </c>
       <c r="K85">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L85">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M85">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="N85">
-        <v>0.81818181800000001</v>
+        <v>1</v>
       </c>
       <c r="O85" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>10688</v>
+        <v>10769</v>
       </c>
       <c r="B86">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C86" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D86" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="E86" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="F86">
-        <v>20086</v>
+        <v>20106</v>
       </c>
       <c r="G86">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H86">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="I86">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="J86">
-        <v>0.79166666699999999</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="K86">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="L86">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="M86">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="N86">
-        <v>0.79166666699999999</v>
+        <v>0.66666666699999999</v>
       </c>
       <c r="O86" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>10694</v>
+        <v>10772</v>
       </c>
       <c r="B87">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C87" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D87" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="E87" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="F87">
-        <v>20095</v>
+        <v>20155</v>
       </c>
       <c r="G87">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H87">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I87">
-        <v>-9</v>
-      </c>
-      <c r="J87">
-        <v>0.72727272700000001</v>
+        <v>0</v>
       </c>
       <c r="K87">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L87">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>-9</v>
-      </c>
-      <c r="N87">
-        <v>0.72727272700000001</v>
+        <v>0</v>
       </c>
       <c r="O87" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>10692</v>
+        <v>10771</v>
       </c>
       <c r="B88">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C88" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D88" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="E88" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="F88">
-        <v>20043</v>
+        <v>11215</v>
       </c>
       <c r="G88">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H88">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I88">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="J88">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K88">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="L88">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M88">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="N88">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="O88" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>10693</v>
+        <v>10700</v>
       </c>
       <c r="B89">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C89" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D89" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="E89" s="1">
         <v>46238</v>
       </c>
       <c r="F89">
-        <v>20106</v>
+        <v>200158</v>
       </c>
       <c r="G89">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H89">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I89">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J89">
-        <v>1.346153846</v>
+        <v>1</v>
       </c>
       <c r="K89">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="L89">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="M89">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N89">
-        <v>1.346153846</v>
+        <v>1</v>
       </c>
       <c r="O89" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>10668</v>
+        <v>10718</v>
       </c>
       <c r="B90">
-        <v>234</v>
-      </c>
-      <c r="C90">
-        <v>234</v>
+        <v>110</v>
+      </c>
+      <c r="C90" t="s">
+        <v>82</v>
       </c>
       <c r="D90" s="1">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="E90" s="1">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="F90">
-        <v>20112</v>
+        <v>20066</v>
       </c>
       <c r="G90">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I90">
-        <v>-4</v>
-      </c>
-      <c r="J90">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="K90">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L90">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>-4</v>
-      </c>
-      <c r="N90">
-        <v>0.66666666699999999</v>
+        <v>0</v>
       </c>
       <c r="O90" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>10669</v>
+        <v>10773</v>
       </c>
       <c r="B91">
-        <v>235</v>
-      </c>
-      <c r="C91">
-        <v>235</v>
+        <v>317</v>
+      </c>
+      <c r="C91" t="s">
+        <v>76</v>
       </c>
       <c r="D91" s="1">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="E91" s="1">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="F91">
-        <v>20113</v>
+        <v>20043</v>
       </c>
       <c r="G91">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H91">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I91">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="J91">
-        <v>1</v>
+        <v>0.86363636399999999</v>
       </c>
       <c r="K91">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L91">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="N91">
-        <v>1</v>
+        <v>0.86363636399999999</v>
       </c>
       <c r="O91" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>10690</v>
+        <v>10781</v>
       </c>
       <c r="B92">
-        <v>307</v>
-      </c>
-      <c r="C92" t="s">
-        <v>42</v>
+        <v>332</v>
+      </c>
+      <c r="C92">
+        <v>332</v>
       </c>
       <c r="D92" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="E92" s="1">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="F92">
-        <v>20105</v>
+        <v>20130</v>
       </c>
       <c r="G92">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H92">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="I92">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="J92">
-        <v>0.875</v>
+        <v>0.75862068999999999</v>
       </c>
       <c r="K92">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L92">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M92">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="N92">
-        <v>0.875</v>
+        <v>0.75862068999999999</v>
       </c>
       <c r="O92" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>10703</v>
+        <v>10721</v>
       </c>
       <c r="B93">
-        <v>326</v>
-      </c>
-      <c r="C93">
-        <v>326</v>
+        <v>113</v>
+      </c>
+      <c r="C93" t="s">
+        <v>83</v>
       </c>
       <c r="D93" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E93" s="1">
         <v>46239</v>
       </c>
-      <c r="E93" s="1">
-        <v>46238</v>
-      </c>
       <c r="F93">
-        <v>20111</v>
+        <v>200150</v>
       </c>
       <c r="G93">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I93">
-        <v>-6</v>
-      </c>
-      <c r="J93">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K93">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L93">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M93">
-        <v>-6</v>
-      </c>
-      <c r="N93">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O93" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>10788</v>
+        <v>10695</v>
       </c>
       <c r="B94">
-        <v>339</v>
-      </c>
-      <c r="C94">
-        <v>339</v>
+        <v>313</v>
+      </c>
+      <c r="C94" t="s">
+        <v>46</v>
       </c>
       <c r="D94" s="1">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="E94" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="F94">
-        <v>20008</v>
+        <v>20076</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J94">
+        <v>0.81818181800000001</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N94">
+        <v>0.81818181800000001</v>
       </c>
       <c r="O94" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>10789</v>
+        <v>10688</v>
       </c>
       <c r="B95">
-        <v>340</v>
-      </c>
-      <c r="C95">
-        <v>340</v>
+        <v>304</v>
+      </c>
+      <c r="C95" t="s">
+        <v>58</v>
       </c>
       <c r="D95" s="1">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="E95" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="F95">
-        <v>20006</v>
+        <v>20086</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I95">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="J95">
+        <v>0.79166666699999999</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L95">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>-10</v>
+      </c>
+      <c r="N95">
+        <v>0.79166666699999999</v>
       </c>
       <c r="O95" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>10768</v>
+        <v>10694</v>
       </c>
       <c r="B96">
         <v>312</v>
@@ -4949,300 +5039,342 @@
         <v>44</v>
       </c>
       <c r="D96" s="1">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="E96" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="F96">
-        <v>20153</v>
+        <v>20095</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="J96">
+        <v>0.72727272700000001</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M96">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="N96">
+        <v>0.72727272700000001</v>
       </c>
       <c r="O96" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>10769</v>
+        <v>10692</v>
       </c>
       <c r="B97">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C97" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="D97" s="1">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="E97" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="F97">
-        <v>20106</v>
+        <v>20043</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I97">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J97">
+        <v>0.5</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M97">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N97">
+        <v>0.5</v>
       </c>
       <c r="O97" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>10770</v>
+        <v>10693</v>
       </c>
       <c r="B98">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C98" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D98" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="E98" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="F98">
-        <v>20047</v>
+        <v>20106</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I98">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="J98">
+        <v>1.346153846</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L98">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M98">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="N98">
+        <v>1.346153846</v>
       </c>
       <c r="O98" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>10771</v>
+        <v>10668</v>
       </c>
       <c r="B99">
-        <v>315</v>
-      </c>
-      <c r="C99" t="s">
-        <v>43</v>
+        <v>234</v>
+      </c>
+      <c r="C99">
+        <v>234</v>
       </c>
       <c r="D99" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="E99" s="1">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="F99">
-        <v>11215</v>
+        <v>20112</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I99">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J99">
+        <v>0.66666666699999999</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M99">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N99">
+        <v>0.66666666699999999</v>
       </c>
       <c r="O99" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>10772</v>
+        <v>10669</v>
       </c>
       <c r="B100">
-        <v>316</v>
-      </c>
-      <c r="C100" t="s">
-        <v>61</v>
+        <v>235</v>
+      </c>
+      <c r="C100">
+        <v>235</v>
       </c>
       <c r="D100" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="E100" s="1">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="F100">
-        <v>20155</v>
+        <v>20113</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I100">
         <v>0</v>
       </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
       <c r="K100">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L100">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M100">
         <v>0</v>
       </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
       <c r="O100" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>10773</v>
+        <v>10690</v>
       </c>
       <c r="B101">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C101" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="D101" s="1">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="E101" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="F101">
-        <v>20043</v>
+        <v>20105</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I101">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J101">
+        <v>0.875</v>
       </c>
       <c r="K101">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N101">
+        <v>0.875</v>
       </c>
       <c r="O101" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>10774</v>
+        <v>10703</v>
       </c>
       <c r="B102">
-        <v>318</v>
-      </c>
-      <c r="C102" t="s">
-        <v>84</v>
+        <v>326</v>
+      </c>
+      <c r="C102">
+        <v>326</v>
       </c>
       <c r="D102" s="1">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="E102" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="F102">
-        <v>20058</v>
+        <v>20111</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J102">
+        <v>0.7</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L102">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M102">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N102">
+        <v>0.7</v>
       </c>
       <c r="O102" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>10775</v>
+        <v>10757</v>
       </c>
       <c r="B103">
-        <v>321</v>
+        <v>501</v>
       </c>
       <c r="C103" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D103" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E103" s="1">
         <v>46241</v>
       </c>
       <c r="F103">
-        <v>20095</v>
+        <v>200150</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -5263,27 +5395,27 @@
         <v>0</v>
       </c>
       <c r="O103" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>10776</v>
+        <v>10778</v>
       </c>
       <c r="B104">
-        <v>324</v>
-      </c>
-      <c r="C104" t="s">
-        <v>63</v>
+        <v>326</v>
+      </c>
+      <c r="C104">
+        <v>326</v>
       </c>
       <c r="D104" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E104" s="1">
         <v>46241</v>
       </c>
       <c r="F104">
-        <v>20105</v>
+        <v>20057</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -5304,346 +5436,394 @@
         <v>0</v>
       </c>
       <c r="O104" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>10778</v>
+        <v>10800</v>
       </c>
       <c r="B105">
-        <v>326</v>
+        <v>140</v>
       </c>
       <c r="C105">
-        <v>326</v>
+        <v>140</v>
       </c>
       <c r="D105" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="E105" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F105">
-        <v>20057</v>
+        <v>20006</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I105">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="J105">
+        <v>0.73913043499999997</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L105">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M105">
-        <v>0</v>
+        <v>-6</v>
+      </c>
+      <c r="N105">
+        <v>0.73913043499999997</v>
       </c>
       <c r="O105" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>10779</v>
+        <v>10798</v>
       </c>
       <c r="B106">
-        <v>327</v>
+        <v>138</v>
       </c>
       <c r="C106">
-        <v>327</v>
+        <v>138</v>
       </c>
       <c r="D106" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="E106" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F106">
-        <v>20076</v>
+        <v>20007</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>-34</v>
+      </c>
+      <c r="J106">
+        <v>2.8571428999999999E-2</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106">
-        <v>0</v>
+        <v>-34</v>
+      </c>
+      <c r="N106">
+        <v>2.8571428999999999E-2</v>
       </c>
       <c r="O106" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>10780</v>
+        <v>10797</v>
       </c>
       <c r="B107">
-        <v>331</v>
+        <v>137</v>
       </c>
       <c r="C107">
-        <v>331</v>
+        <v>137</v>
       </c>
       <c r="D107" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="E107" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F107">
-        <v>20005</v>
+        <v>20003</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I107">
         <v>0</v>
       </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
       <c r="K107">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M107">
         <v>0</v>
       </c>
+      <c r="N107">
+        <v>1</v>
+      </c>
       <c r="O107" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>10781</v>
+        <v>10792</v>
       </c>
       <c r="B108">
-        <v>332</v>
+        <v>131</v>
       </c>
       <c r="C108">
-        <v>332</v>
+        <v>131</v>
       </c>
       <c r="D108" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="E108" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="F108">
-        <v>20130</v>
+        <v>20005</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I108">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J108">
+        <v>0.77777777800000003</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L108">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M108">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N108">
+        <v>0.77777777800000003</v>
       </c>
       <c r="O108" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>10782</v>
+        <v>10785</v>
       </c>
       <c r="B109">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C109">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D109" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E109" s="1">
         <v>46241</v>
       </c>
       <c r="F109">
-        <v>200158</v>
+        <v>20111</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I109">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="J109">
+        <v>0.77777777800000003</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M109">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="N109">
+        <v>0.77777777800000003</v>
       </c>
       <c r="O109" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>10783</v>
+        <v>10759</v>
       </c>
       <c r="B110">
-        <v>334</v>
-      </c>
-      <c r="C110">
-        <v>334</v>
+        <v>302</v>
+      </c>
+      <c r="C110" t="s">
+        <v>38</v>
       </c>
       <c r="D110" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E110" s="1">
         <v>46241</v>
       </c>
       <c r="F110">
-        <v>20112</v>
+        <v>20058</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I110">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J110">
+        <v>2</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M110">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>2</v>
       </c>
       <c r="O110" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>10784</v>
+        <v>10761</v>
       </c>
       <c r="B111">
-        <v>335</v>
-      </c>
-      <c r="C111">
-        <v>335</v>
+        <v>304</v>
+      </c>
+      <c r="C111" t="s">
+        <v>58</v>
       </c>
       <c r="D111" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E111" s="1">
         <v>46241</v>
       </c>
       <c r="F111">
-        <v>20113</v>
+        <v>20095</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I111">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="J111">
+        <v>0.72413793100000001</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>-8</v>
+      </c>
+      <c r="N111">
+        <v>0.72413793100000001</v>
       </c>
       <c r="O111" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>10785</v>
+        <v>10764</v>
       </c>
       <c r="B112">
-        <v>336</v>
-      </c>
-      <c r="C112">
-        <v>336</v>
+        <v>307</v>
+      </c>
+      <c r="C112" t="s">
+        <v>42</v>
       </c>
       <c r="D112" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E112" s="1">
         <v>46241</v>
       </c>
       <c r="F112">
-        <v>20111</v>
+        <v>11215</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>-20</v>
+      </c>
+      <c r="J112">
+        <v>0.45945945900000001</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M112">
-        <v>0</v>
+        <v>-20</v>
+      </c>
+      <c r="N112">
+        <v>0.45945945900000001</v>
       </c>
       <c r="O112" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>10786</v>
+        <v>10782</v>
       </c>
       <c r="B113">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C113">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D113" s="1">
         <v>46241</v>
@@ -5652,7 +5832,7 @@
         <v>46241</v>
       </c>
       <c r="F113">
-        <v>20003</v>
+        <v>200158</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -5673,45 +5853,51 @@
         <v>0</v>
       </c>
       <c r="O113" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>10787</v>
+        <v>10725</v>
       </c>
       <c r="B114">
-        <v>338</v>
+        <v>134</v>
       </c>
       <c r="C114">
-        <v>338</v>
+        <v>134</v>
       </c>
       <c r="D114" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="E114" s="1">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="F114">
         <v>20112</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I114">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J114">
+        <v>0.9</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L114">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M114">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="N114">
+        <v>0.9</v>
       </c>
       <c r="O114" t="s">
         <v>31</v>
@@ -5719,80 +5905,92 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>10758</v>
+        <v>10745</v>
       </c>
       <c r="B115">
-        <v>301</v>
-      </c>
-      <c r="C115" t="s">
-        <v>64</v>
+        <v>232</v>
+      </c>
+      <c r="C115">
+        <v>232</v>
       </c>
       <c r="D115" s="1">
         <v>46241</v>
       </c>
       <c r="E115" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="F115">
-        <v>20066</v>
+        <v>20130</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I115">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="J115">
+        <v>0.70833333300000001</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M115">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="N115">
+        <v>0.70833333300000001</v>
       </c>
       <c r="O115" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>10759</v>
+        <v>10742</v>
       </c>
       <c r="B116">
-        <v>302</v>
+        <v>214</v>
       </c>
       <c r="C116" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D116" s="1">
         <v>46241</v>
       </c>
       <c r="E116" s="1">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="F116">
         <v>20058</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>-50</v>
+      </c>
+      <c r="J116">
+        <v>0.19354838699999999</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="L116">
         <v>0</v>
       </c>
       <c r="M116">
+        <v>-62</v>
+      </c>
+      <c r="N116">
         <v>0</v>
       </c>
       <c r="O116" t="s">
@@ -5801,104 +5999,116 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>10760</v>
+        <v>10783</v>
       </c>
       <c r="B117">
-        <v>303</v>
-      </c>
-      <c r="C117" t="s">
-        <v>67</v>
+        <v>334</v>
+      </c>
+      <c r="C117">
+        <v>334</v>
       </c>
       <c r="D117" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E117" s="1">
         <v>46241</v>
       </c>
       <c r="F117">
-        <v>20047</v>
+        <v>20112</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I117">
         <v>0</v>
       </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
       <c r="K117">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
       <c r="M117">
+        <v>-15</v>
+      </c>
+      <c r="N117">
         <v>0</v>
       </c>
       <c r="O117" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>10761</v>
+        <v>10779</v>
       </c>
       <c r="B118">
-        <v>304</v>
-      </c>
-      <c r="C118" t="s">
-        <v>58</v>
+        <v>327</v>
+      </c>
+      <c r="C118">
+        <v>327</v>
       </c>
       <c r="D118" s="1">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="E118" s="1">
         <v>46241</v>
       </c>
       <c r="F118">
-        <v>20095</v>
+        <v>20076</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>-12</v>
+      </c>
+      <c r="J118">
+        <v>0.675675676</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L118">
         <v>0</v>
       </c>
       <c r="M118">
+        <v>-37</v>
+      </c>
+      <c r="N118">
         <v>0</v>
       </c>
       <c r="O118" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>10762</v>
+        <v>10828</v>
       </c>
       <c r="B119">
-        <v>305</v>
+        <v>502</v>
       </c>
       <c r="C119" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D119" s="1">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="E119" s="1">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="F119">
-        <v>20106</v>
+        <v>20043</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -5919,150 +6129,168 @@
         <v>0</v>
       </c>
       <c r="O119" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>10763</v>
+        <v>10803</v>
       </c>
       <c r="B120">
-        <v>306</v>
+        <v>201</v>
       </c>
       <c r="C120" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D120" s="1">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="E120" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="F120">
-        <v>20105</v>
+        <v>20153</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I120">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J120">
+        <v>0.91666666699999999</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L120">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M120">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="N120">
+        <v>0.91666666699999999</v>
       </c>
       <c r="O120" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>10764</v>
+        <v>10806</v>
       </c>
       <c r="B121">
-        <v>307</v>
+        <v>204</v>
       </c>
       <c r="C121" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="D121" s="1">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="E121" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="F121">
-        <v>11215</v>
+        <v>20095</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I121">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="J121">
+        <v>0.76315789499999998</v>
       </c>
       <c r="K121">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L121">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M121">
-        <v>0</v>
+        <v>-9</v>
+      </c>
+      <c r="N121">
+        <v>0.76315789499999998</v>
       </c>
       <c r="O121" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>10765</v>
+        <v>10807</v>
       </c>
       <c r="B122">
-        <v>308</v>
+        <v>205</v>
       </c>
       <c r="C122" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D122" s="1">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="E122" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="F122">
-        <v>20153</v>
+        <v>20047</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I122">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="J122">
+        <v>0.96296296299999995</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M122">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="N122">
+        <v>0.96296296299999995</v>
       </c>
       <c r="O122" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>10766</v>
+        <v>10811</v>
       </c>
       <c r="B123">
-        <v>310</v>
+        <v>209</v>
       </c>
       <c r="C123" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D123" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="E123" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="F123">
-        <v>20155</v>
+        <v>20105</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -6083,27 +6311,27 @@
         <v>0</v>
       </c>
       <c r="O123" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>10767</v>
+        <v>10816</v>
       </c>
       <c r="B124">
-        <v>311</v>
-      </c>
-      <c r="C124" t="s">
-        <v>41</v>
+        <v>232</v>
+      </c>
+      <c r="C124">
+        <v>232</v>
       </c>
       <c r="D124" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="E124" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="F124">
-        <v>20057</v>
+        <v>20130</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -6124,27 +6352,27 @@
         <v>0</v>
       </c>
       <c r="O124" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>10777</v>
+        <v>10818</v>
       </c>
       <c r="B125">
-        <v>325</v>
-      </c>
-      <c r="C125" t="s">
-        <v>62</v>
+        <v>234</v>
+      </c>
+      <c r="C125">
+        <v>234</v>
       </c>
       <c r="D125" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="E125" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="F125">
-        <v>20043</v>
+        <v>20112</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -6165,27 +6393,27 @@
         <v>0</v>
       </c>
       <c r="O125" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>10757</v>
+        <v>10819</v>
       </c>
       <c r="B126">
-        <v>501</v>
-      </c>
-      <c r="C126" t="s">
-        <v>49</v>
+        <v>235</v>
+      </c>
+      <c r="C126">
+        <v>235</v>
       </c>
       <c r="D126" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="E126" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="F126">
-        <v>200150</v>
+        <v>20113</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -6206,51 +6434,45 @@
         <v>0</v>
       </c>
       <c r="O126" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>10634</v>
+        <v>10821</v>
       </c>
       <c r="B127">
-        <v>337</v>
+        <v>237</v>
       </c>
       <c r="C127">
-        <v>337</v>
+        <v>237</v>
       </c>
       <c r="D127" s="1">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="E127" s="1">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="F127">
         <v>20003</v>
       </c>
       <c r="G127">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I127">
         <v>0</v>
       </c>
-      <c r="J127">
-        <v>1</v>
-      </c>
       <c r="K127">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L127">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M127">
         <v>0</v>
-      </c>
-      <c r="N127">
-        <v>1</v>
       </c>
       <c r="O127" t="s">
         <v>33</v>
@@ -6258,445 +6480,439 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>10629</v>
+        <v>10822</v>
       </c>
       <c r="B128">
-        <v>331</v>
+        <v>238</v>
       </c>
       <c r="C128">
-        <v>331</v>
+        <v>238</v>
       </c>
       <c r="D128" s="1">
-        <v>46235</v>
+        <v>46244</v>
       </c>
       <c r="E128" s="1">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="F128">
-        <v>20006</v>
+        <v>20007</v>
       </c>
       <c r="G128">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I128">
-        <v>-3</v>
-      </c>
-      <c r="J128">
-        <v>0.85714285700000004</v>
+        <v>0</v>
       </c>
       <c r="K128">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="L128">
         <v>0</v>
       </c>
       <c r="M128">
-        <v>-21</v>
-      </c>
-      <c r="N128">
         <v>0</v>
       </c>
       <c r="O128" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>10617</v>
+        <v>10762</v>
       </c>
       <c r="B129">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C129" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D129" s="1">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="E129" s="1">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="F129">
-        <v>20057</v>
+        <v>20106</v>
       </c>
       <c r="G129">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="H129">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="I129">
-        <v>-5</v>
+        <v>-27</v>
       </c>
       <c r="J129">
-        <v>0.92063492099999999</v>
+        <v>0.20588235299999999</v>
       </c>
       <c r="K129">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="L129">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="M129">
-        <v>-5</v>
+        <v>-27</v>
       </c>
       <c r="N129">
-        <v>0.92063492099999999</v>
+        <v>0.20588235299999999</v>
       </c>
       <c r="O129" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>10610</v>
+        <v>10794</v>
       </c>
       <c r="B130">
-        <v>303</v>
-      </c>
-      <c r="C130" t="s">
-        <v>67</v>
+        <v>133</v>
+      </c>
+      <c r="C130">
+        <v>133</v>
       </c>
       <c r="D130" s="1">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="E130" s="1">
-        <v>46234</v>
+        <v>46242</v>
       </c>
       <c r="F130">
-        <v>20047</v>
+        <v>200158</v>
       </c>
       <c r="G130">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H130">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="J130">
-        <v>1</v>
+        <v>0.675675676</v>
       </c>
       <c r="K130">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L130">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M130">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="N130">
-        <v>1</v>
+        <v>0.675675676</v>
       </c>
       <c r="O130" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>10619</v>
+        <v>10784</v>
       </c>
       <c r="B131">
-        <v>313</v>
-      </c>
-      <c r="C131" t="s">
-        <v>46</v>
+        <v>335</v>
+      </c>
+      <c r="C131">
+        <v>335</v>
       </c>
       <c r="D131" s="1">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="E131" s="1">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="F131">
-        <v>20106</v>
+        <v>20113</v>
       </c>
       <c r="G131">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H131">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="J131">
-        <v>1</v>
+        <v>0.71428571399999996</v>
       </c>
       <c r="K131">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L131">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M131">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>0.71428571399999996</v>
       </c>
       <c r="O131" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>10622</v>
+        <v>10760</v>
       </c>
       <c r="B132">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="C132" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D132" s="1">
-        <v>46235</v>
+        <v>46242</v>
       </c>
       <c r="E132" s="1">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="F132">
-        <v>20155</v>
+        <v>20047</v>
       </c>
       <c r="G132">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="H132">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I132">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="J132">
-        <v>1.136363636</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="K132">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="L132">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M132">
-        <v>-22</v>
+        <v>-3</v>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="O132" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>10609</v>
+        <v>10795</v>
       </c>
       <c r="B133">
-        <v>302</v>
-      </c>
-      <c r="C133" t="s">
-        <v>38</v>
+        <v>135</v>
+      </c>
+      <c r="C133">
+        <v>135</v>
       </c>
       <c r="D133" s="1">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="E133" s="1">
-        <v>46234</v>
+        <v>46242</v>
       </c>
       <c r="F133">
-        <v>20106</v>
+        <v>20113</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H133">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I133">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0.73913043499999997</v>
       </c>
       <c r="K133">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="L133">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="N133">
-        <v>1</v>
+        <v>0.73913043499999997</v>
       </c>
       <c r="O133" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>10612</v>
+        <v>10758</v>
       </c>
       <c r="B134">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C134" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D134" s="1">
-        <v>46237</v>
+        <v>46242</v>
       </c>
       <c r="E134" s="1">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="F134">
-        <v>20105</v>
+        <v>20066</v>
       </c>
       <c r="G134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134">
         <v>0</v>
       </c>
-      <c r="J134">
-        <v>1</v>
-      </c>
       <c r="K134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134">
         <v>0</v>
       </c>
-      <c r="N134">
-        <v>1</v>
-      </c>
       <c r="O134" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>10614</v>
+        <v>10808</v>
       </c>
       <c r="B135">
-        <v>307</v>
+        <v>206</v>
       </c>
       <c r="C135" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D135" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E135" s="1">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="F135">
-        <v>20153</v>
+        <v>20076</v>
       </c>
       <c r="G135">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H135">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="I135">
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="J135">
-        <v>0.44444444399999999</v>
+        <v>0.90322580600000002</v>
       </c>
       <c r="K135">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L135">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="M135">
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="N135">
-        <v>0.44444444399999999</v>
+        <v>0.90322580600000002</v>
       </c>
       <c r="O135" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>10683</v>
+        <v>10799</v>
       </c>
       <c r="B136">
-        <v>330</v>
+        <v>139</v>
       </c>
       <c r="C136">
-        <v>330</v>
+        <v>139</v>
       </c>
       <c r="D136" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E136" s="1">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="F136">
-        <v>20006</v>
+        <v>20008</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H136">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I136">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J136">
+        <v>0.66666666699999999</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L136">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M136">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="N136">
+        <v>0.66666666699999999</v>
       </c>
       <c r="O136" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>10654</v>
+        <v>10825</v>
       </c>
       <c r="B137">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C137" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D137" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E137" s="1">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="F137">
-        <v>20086</v>
+        <v>20105</v>
       </c>
       <c r="G137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I137">
         <v>0</v>
@@ -6705,10 +6921,10 @@
         <v>1</v>
       </c>
       <c r="K137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M137">
         <v>0</v>
@@ -6717,667 +6933,655 @@
         <v>1</v>
       </c>
       <c r="O137" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>10684</v>
+        <v>10805</v>
       </c>
       <c r="B138">
-        <v>700</v>
+        <v>203</v>
       </c>
       <c r="C138" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D138" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E138" s="1">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="F138">
-        <v>200150</v>
+        <v>20155</v>
       </c>
       <c r="G138">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H138">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I138">
         <v>0</v>
       </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
       <c r="K138">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L138">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M138">
         <v>0</v>
       </c>
+      <c r="N138">
+        <v>1</v>
+      </c>
       <c r="O138" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>10709</v>
+        <v>10817</v>
       </c>
       <c r="B139">
-        <v>101</v>
-      </c>
-      <c r="C139" t="s">
-        <v>85</v>
+        <v>233</v>
+      </c>
+      <c r="C139">
+        <v>233</v>
       </c>
       <c r="D139" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E139" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="F139">
-        <v>20076</v>
+        <v>200158</v>
       </c>
       <c r="G139">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H139">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I139">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J139">
-        <v>0.76190476200000001</v>
+        <v>1</v>
       </c>
       <c r="K139">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L139">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="M139">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="N139">
-        <v>0.76190476200000001</v>
+        <v>1</v>
       </c>
       <c r="O139" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>10712</v>
+        <v>10824</v>
       </c>
       <c r="B140">
-        <v>104</v>
-      </c>
-      <c r="C140" t="s">
-        <v>86</v>
+        <v>240</v>
+      </c>
+      <c r="C140">
+        <v>240</v>
       </c>
       <c r="D140" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E140" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="F140">
-        <v>20095</v>
+        <v>20006</v>
       </c>
       <c r="G140">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H140">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I140">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="J140">
-        <v>0.83333333300000001</v>
+        <v>1</v>
       </c>
       <c r="K140">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="L140">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M140">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="N140">
-        <v>0.83333333300000001</v>
+        <v>1</v>
       </c>
       <c r="O140" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>10713</v>
+        <v>10804</v>
       </c>
       <c r="B141">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="C141" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="D141" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E141" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="F141">
-        <v>20058</v>
+        <v>20066</v>
       </c>
       <c r="G141">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="H141">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="I141">
-        <v>-27</v>
+        <v>4</v>
       </c>
       <c r="J141">
-        <v>0.61428571399999998</v>
+        <v>3</v>
       </c>
       <c r="K141">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="L141">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="M141">
-        <v>-27</v>
+        <v>4</v>
       </c>
       <c r="N141">
-        <v>0.61428571399999998</v>
+        <v>3</v>
       </c>
       <c r="O141" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>10722</v>
+        <v>10796</v>
       </c>
       <c r="B142">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C142">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D142" s="1">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="E142" s="1">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="F142">
-        <v>20005</v>
+        <v>20111</v>
       </c>
       <c r="G142">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H142">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I142">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="J142">
-        <v>0.85</v>
+        <v>0.83333333300000001</v>
       </c>
       <c r="K142">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L142">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="M142">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="N142">
-        <v>0.85</v>
+        <v>0.83333333300000001</v>
       </c>
       <c r="O142" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>10697</v>
+        <v>10809</v>
       </c>
       <c r="B143">
-        <v>315</v>
+        <v>207</v>
       </c>
       <c r="C143" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D143" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="E143" s="1">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="F143">
-        <v>11215</v>
+        <v>20043</v>
       </c>
       <c r="G143">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I143">
-        <v>-27</v>
+        <v>-30</v>
       </c>
       <c r="J143">
-        <v>0</v>
+        <v>0.33333333300000001</v>
       </c>
       <c r="K143">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="L143">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M143">
-        <v>-27</v>
+        <v>-30</v>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>0.33333333300000001</v>
       </c>
       <c r="O143" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>10700</v>
+        <v>10815</v>
       </c>
       <c r="B144">
-        <v>323</v>
-      </c>
-      <c r="C144" t="s">
-        <v>68</v>
+        <v>231</v>
+      </c>
+      <c r="C144">
+        <v>231</v>
       </c>
       <c r="D144" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E144" s="1">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="F144">
-        <v>200158</v>
+        <v>20005</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I144">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="J144">
+        <v>0.78</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L144">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M144">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="N144">
+        <v>0.78</v>
       </c>
       <c r="O144" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>10623</v>
+        <v>10813</v>
       </c>
       <c r="B145">
-        <v>317</v>
+        <v>212</v>
       </c>
       <c r="C145" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D145" s="1">
-        <v>46235</v>
+        <v>46245</v>
       </c>
       <c r="E145" s="1">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="F145">
-        <v>20043</v>
+        <v>20057</v>
       </c>
       <c r="G145">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="H145">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="I145">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="J145">
-        <v>0.95833333300000001</v>
+        <v>0.88235294099999995</v>
       </c>
       <c r="K145">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L145">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M145">
-        <v>-24</v>
+        <v>-8</v>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>0.88235294099999995</v>
       </c>
       <c r="O145" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>10650</v>
+        <v>10820</v>
       </c>
       <c r="B146">
-        <v>800</v>
-      </c>
-      <c r="C146" t="s">
-        <v>28</v>
+        <v>236</v>
+      </c>
+      <c r="C146">
+        <v>236</v>
       </c>
       <c r="D146" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E146" s="1">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="F146">
-        <v>200150</v>
+        <v>20111</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="J146">
+        <v>0.66666666699999999</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L146">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M146">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="N146">
+        <v>0.66666666699999999</v>
       </c>
       <c r="O146" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>10655</v>
+        <v>10830</v>
       </c>
       <c r="B147">
-        <v>203</v>
+        <v>303</v>
       </c>
       <c r="C147" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D147" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E147" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F147">
-        <v>20155</v>
+        <v>20153</v>
       </c>
       <c r="G147">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I147">
-        <v>-22</v>
-      </c>
-      <c r="J147">
-        <v>0.54166666699999999</v>
+        <v>0</v>
       </c>
       <c r="K147">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L147">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M147">
-        <v>-22</v>
-      </c>
-      <c r="N147">
-        <v>0.54166666699999999</v>
+        <v>0</v>
       </c>
       <c r="O147" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>10716</v>
+        <v>10831</v>
       </c>
       <c r="B148">
-        <v>108</v>
+        <v>304</v>
       </c>
       <c r="C148" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="D148" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E148" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="F148">
-        <v>20057</v>
+        <v>20155</v>
       </c>
       <c r="G148">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H148">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I148">
-        <v>-8</v>
-      </c>
-      <c r="J148">
-        <v>0.86440678000000004</v>
+        <v>0</v>
       </c>
       <c r="K148">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L148">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M148">
-        <v>-8</v>
-      </c>
-      <c r="N148">
-        <v>0.86440678000000004</v>
+        <v>0</v>
       </c>
       <c r="O148" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>10657</v>
+        <v>10832</v>
       </c>
       <c r="B149">
-        <v>205</v>
+        <v>305</v>
       </c>
       <c r="C149" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D149" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E149" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F149">
-        <v>20047</v>
+        <v>20076</v>
       </c>
       <c r="G149">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I149">
-        <v>-2</v>
-      </c>
-      <c r="J149">
-        <v>0.94444444400000005</v>
+        <v>0</v>
       </c>
       <c r="K149">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L149">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M149">
-        <v>-2</v>
-      </c>
-      <c r="N149">
-        <v>0.94444444400000005</v>
+        <v>0</v>
       </c>
       <c r="O149" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>10704</v>
+        <v>10833</v>
       </c>
       <c r="B150">
-        <v>327</v>
-      </c>
-      <c r="C150">
-        <v>327</v>
+        <v>307</v>
+      </c>
+      <c r="C150" t="s">
+        <v>42</v>
       </c>
       <c r="D150" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="E150" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="F150">
-        <v>20003</v>
+        <v>20105</v>
       </c>
       <c r="G150">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H150">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I150">
-        <v>-15</v>
-      </c>
-      <c r="J150">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K150">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L150">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M150">
-        <v>-15</v>
-      </c>
-      <c r="N150">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O150" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>10659</v>
+        <v>10834</v>
       </c>
       <c r="B151">
-        <v>208</v>
+        <v>308</v>
       </c>
       <c r="C151" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="D151" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E151" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F151">
-        <v>11215</v>
+        <v>20043</v>
       </c>
       <c r="G151">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H151">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I151">
-        <v>-13</v>
-      </c>
-      <c r="J151">
-        <v>0.67500000000000004</v>
+        <v>0</v>
       </c>
       <c r="K151">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L151">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M151">
-        <v>-13</v>
-      </c>
-      <c r="N151">
-        <v>0.67500000000000004</v>
+        <v>0</v>
       </c>
       <c r="O151" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>10660</v>
+        <v>10835</v>
       </c>
       <c r="B152">
-        <v>209</v>
+        <v>309</v>
       </c>
       <c r="C152" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="D152" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E152" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F152">
-        <v>20105</v>
+        <v>20047</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -7398,168 +7602,150 @@
         <v>0</v>
       </c>
       <c r="O152" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>10687</v>
+        <v>10836</v>
       </c>
       <c r="B153">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C153" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D153" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="E153" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="F153">
-        <v>20153</v>
+        <v>20106</v>
       </c>
       <c r="G153">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I153">
-        <v>-9</v>
-      </c>
-      <c r="J153">
-        <v>0.756756757</v>
+        <v>0</v>
       </c>
       <c r="K153">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L153">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M153">
-        <v>-9</v>
-      </c>
-      <c r="N153">
-        <v>0.756756757</v>
+        <v>0</v>
       </c>
       <c r="O153" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>10686</v>
+        <v>10837</v>
       </c>
       <c r="B154">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C154" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D154" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="E154" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="F154">
-        <v>20058</v>
+        <v>20095</v>
       </c>
       <c r="G154">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I154">
-        <v>-18</v>
-      </c>
-      <c r="J154">
-        <v>0.56097560999999996</v>
+        <v>0</v>
       </c>
       <c r="K154">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L154">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M154">
-        <v>-18</v>
-      </c>
-      <c r="N154">
-        <v>0.56097560999999996</v>
+        <v>0</v>
       </c>
       <c r="O154" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>10663</v>
+        <v>10838</v>
       </c>
       <c r="B155">
-        <v>212</v>
+        <v>313</v>
       </c>
       <c r="C155" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D155" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E155" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F155">
-        <v>20057</v>
+        <v>11215</v>
       </c>
       <c r="G155">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I155">
-        <v>-10</v>
-      </c>
-      <c r="J155">
-        <v>0.88235294099999995</v>
+        <v>0</v>
       </c>
       <c r="K155">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="L155">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M155">
-        <v>-10</v>
-      </c>
-      <c r="N155">
-        <v>0.88235294099999995</v>
+        <v>0</v>
       </c>
       <c r="O155" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>10664</v>
+        <v>10839</v>
       </c>
       <c r="B156">
-        <v>213</v>
+        <v>314</v>
       </c>
       <c r="C156" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D156" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E156" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F156">
-        <v>20058</v>
+        <v>20066</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -7580,51 +7766,45 @@
         <v>0</v>
       </c>
       <c r="O156" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>10665</v>
+        <v>10840</v>
       </c>
       <c r="B157">
-        <v>231</v>
-      </c>
-      <c r="C157">
-        <v>231</v>
+        <v>321</v>
+      </c>
+      <c r="C157" t="s">
+        <v>59</v>
       </c>
       <c r="D157" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E157" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F157">
         <v>20005</v>
       </c>
       <c r="G157">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I157">
-        <v>-7</v>
-      </c>
-      <c r="J157">
-        <v>0.820512821</v>
+        <v>0</v>
       </c>
       <c r="K157">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L157">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M157">
-        <v>-7</v>
-      </c>
-      <c r="N157">
-        <v>0.820512821</v>
+        <v>0</v>
       </c>
       <c r="O157" t="s">
         <v>27</v>
@@ -7632,93 +7812,81 @@
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>10731</v>
+        <v>10841</v>
       </c>
       <c r="B158">
-        <v>140</v>
-      </c>
-      <c r="C158">
-        <v>140</v>
+        <v>322</v>
+      </c>
+      <c r="C158" t="s">
+        <v>65</v>
       </c>
       <c r="D158" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E158" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="F158">
-        <v>20006</v>
+        <v>20130</v>
       </c>
       <c r="G158">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I158">
-        <v>-3</v>
-      </c>
-      <c r="J158">
-        <v>0.86363636399999999</v>
+        <v>0</v>
       </c>
       <c r="K158">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L158">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M158">
-        <v>-3</v>
-      </c>
-      <c r="N158">
-        <v>0.86363636399999999</v>
+        <v>0</v>
       </c>
       <c r="O158" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>10667</v>
+        <v>10842</v>
       </c>
       <c r="B159">
-        <v>233</v>
-      </c>
-      <c r="C159">
-        <v>233</v>
+        <v>323</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
       </c>
       <c r="D159" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E159" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F159">
         <v>200158</v>
       </c>
       <c r="G159">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I159">
         <v>0</v>
       </c>
-      <c r="J159">
-        <v>1</v>
-      </c>
       <c r="K159">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L159">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M159">
         <v>0</v>
-      </c>
-      <c r="N159">
-        <v>1</v>
       </c>
       <c r="O159" t="s">
         <v>15</v>
@@ -7726,181 +7894,163 @@
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>10729</v>
+        <v>10843</v>
       </c>
       <c r="B160">
-        <v>138</v>
-      </c>
-      <c r="C160">
-        <v>138</v>
+        <v>324</v>
+      </c>
+      <c r="C160" t="s">
+        <v>63</v>
       </c>
       <c r="D160" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E160" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="F160">
-        <v>20007</v>
+        <v>20112</v>
       </c>
       <c r="G160">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H160">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I160">
-        <v>-8</v>
-      </c>
-      <c r="J160">
-        <v>0.70370370400000004</v>
+        <v>0</v>
       </c>
       <c r="K160">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L160">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M160">
-        <v>-8</v>
-      </c>
-      <c r="N160">
-        <v>0.70370370400000004</v>
+        <v>0</v>
       </c>
       <c r="O160" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>10727</v>
+        <v>10844</v>
       </c>
       <c r="B161">
-        <v>136</v>
-      </c>
-      <c r="C161">
-        <v>136</v>
+        <v>325</v>
+      </c>
+      <c r="C161" t="s">
+        <v>62</v>
       </c>
       <c r="D161" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E161" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="F161">
-        <v>20111</v>
+        <v>20113</v>
       </c>
       <c r="G161">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I161">
-        <v>-2</v>
-      </c>
-      <c r="J161">
-        <v>0.83333333300000001</v>
+        <v>0</v>
       </c>
       <c r="K161">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L161">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M161">
-        <v>-2</v>
-      </c>
-      <c r="N161">
-        <v>0.83333333300000001</v>
+        <v>0</v>
       </c>
       <c r="O161" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>10720</v>
+        <v>10845</v>
       </c>
       <c r="B162">
-        <v>112</v>
-      </c>
-      <c r="C162" t="s">
-        <v>89</v>
+        <v>326</v>
+      </c>
+      <c r="C162">
+        <v>326</v>
       </c>
       <c r="D162" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E162" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="F162">
-        <v>20106</v>
+        <v>20111</v>
       </c>
       <c r="G162">
         <v>0</v>
       </c>
       <c r="H162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162">
         <v>0</v>
       </c>
       <c r="L162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O162" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>10671</v>
+        <v>10846</v>
       </c>
       <c r="B163">
-        <v>237</v>
+        <v>327</v>
       </c>
       <c r="C163">
-        <v>237</v>
+        <v>327</v>
       </c>
       <c r="D163" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E163" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F163">
         <v>20003</v>
       </c>
       <c r="G163">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I163">
-        <v>-2</v>
-      </c>
-      <c r="J163">
-        <v>0.91304347799999996</v>
+        <v>0</v>
       </c>
       <c r="K163">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L163">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M163">
-        <v>-2</v>
-      </c>
-      <c r="N163">
-        <v>0.91304347799999996</v>
+        <v>0</v>
       </c>
       <c r="O163" t="s">
         <v>33</v>
@@ -7908,466 +8058,3290 @@
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>10717</v>
+        <v>10847</v>
       </c>
       <c r="B164">
-        <v>109</v>
-      </c>
-      <c r="C164" t="s">
-        <v>90</v>
+        <v>328</v>
+      </c>
+      <c r="C164">
+        <v>328</v>
       </c>
       <c r="D164" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E164" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="F164">
-        <v>20105</v>
+        <v>20007</v>
       </c>
       <c r="G164">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I164">
-        <v>-13</v>
-      </c>
-      <c r="J164">
-        <v>0.71739130399999995</v>
+        <v>0</v>
       </c>
       <c r="K164">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L164">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M164">
-        <v>-13</v>
-      </c>
-      <c r="N164">
-        <v>0.71739130399999995</v>
+        <v>0</v>
       </c>
       <c r="O164" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>10711</v>
+        <v>10848</v>
       </c>
       <c r="B165">
-        <v>103</v>
-      </c>
-      <c r="C165" t="s">
-        <v>91</v>
+        <v>329</v>
+      </c>
+      <c r="C165">
+        <v>329</v>
       </c>
       <c r="D165" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E165" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="F165">
-        <v>20153</v>
+        <v>20008</v>
       </c>
       <c r="G165">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I165">
-        <v>-17</v>
-      </c>
-      <c r="J165">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="K165">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L165">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M165">
-        <v>-17</v>
-      </c>
-      <c r="N165">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="O165" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>10714</v>
+        <v>10849</v>
       </c>
       <c r="B166">
-        <v>106</v>
-      </c>
-      <c r="C166" t="s">
-        <v>92</v>
+        <v>330</v>
+      </c>
+      <c r="C166">
+        <v>330</v>
       </c>
       <c r="D166" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E166" s="1">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="F166">
-        <v>11215</v>
+        <v>20006</v>
       </c>
       <c r="G166">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I166">
-        <v>-1</v>
-      </c>
-      <c r="J166">
-        <v>0.97916666699999999</v>
+        <v>0</v>
       </c>
       <c r="K166">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L166">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M166">
-        <v>-1</v>
-      </c>
-      <c r="N166">
-        <v>0.97916666699999999</v>
+        <v>0</v>
       </c>
       <c r="O166" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>10677</v>
+        <v>10829</v>
       </c>
       <c r="B167">
-        <v>209</v>
+        <v>302</v>
       </c>
       <c r="C167" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D167" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="E167" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="F167">
-        <v>20105</v>
+        <v>20058</v>
       </c>
       <c r="G167">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="O167" t="s">
         <v>39</v>
-      </c>
-      <c r="I167">
-        <v>-6</v>
-      </c>
-      <c r="J167">
-        <v>0.86666666699999995</v>
-      </c>
-      <c r="K167">
-        <v>45</v>
-      </c>
-      <c r="L167">
-        <v>39</v>
-      </c>
-      <c r="M167">
-        <v>-6</v>
-      </c>
-      <c r="N167">
-        <v>0.86666666699999995</v>
-      </c>
-      <c r="O167" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>10715</v>
+        <v>10810</v>
       </c>
       <c r="B168">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="C168" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D168" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E168" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="F168">
-        <v>20155</v>
+        <v>11215</v>
       </c>
       <c r="G168">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H168">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I168">
-        <v>-2</v>
+        <v>-15</v>
       </c>
       <c r="J168">
-        <v>0.94736842099999996</v>
+        <v>0.594594595</v>
       </c>
       <c r="K168">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L168">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M168">
-        <v>-2</v>
+        <v>-15</v>
       </c>
       <c r="N168">
-        <v>0.94736842099999996</v>
+        <v>0.594594595</v>
       </c>
       <c r="O168" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>10755</v>
+        <v>10812</v>
       </c>
       <c r="B169">
-        <v>800</v>
+        <v>211</v>
       </c>
       <c r="C169" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="D169" s="1">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="E169" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="F169">
-        <v>200150</v>
+        <v>20058</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I169">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="J169">
+        <v>0.65625</v>
       </c>
       <c r="K169">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L169">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M169">
-        <v>0</v>
+        <v>-11</v>
+      </c>
+      <c r="N169">
+        <v>0.65625</v>
       </c>
       <c r="O169" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>10632</v>
+        <v>10823</v>
       </c>
       <c r="B170">
-        <v>335</v>
+        <v>239</v>
       </c>
       <c r="C170">
-        <v>335</v>
+        <v>239</v>
       </c>
       <c r="D170" s="1">
-        <v>46235</v>
+        <v>46245</v>
       </c>
       <c r="E170" s="1">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="F170">
-        <v>20113</v>
+        <v>20008</v>
       </c>
       <c r="G170">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H170">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I170">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="J170">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="K170">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="L170">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="M170">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="N170">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="O170" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>10726</v>
+        <v>10814</v>
       </c>
       <c r="B171">
-        <v>135</v>
-      </c>
-      <c r="C171">
-        <v>135</v>
+        <v>213</v>
+      </c>
+      <c r="C171" t="s">
+        <v>57</v>
       </c>
       <c r="D171" s="1">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="E171" s="1">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="F171">
-        <v>20113</v>
+        <v>20106</v>
       </c>
       <c r="G171">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="H171">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I171">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J171">
-        <v>1</v>
+        <v>0.94117647100000001</v>
       </c>
       <c r="K171">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="L171">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="M171">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="N171">
-        <v>1</v>
+        <v>0.94117647100000001</v>
       </c>
       <c r="O171" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>10728</v>
+        <v>10850</v>
       </c>
       <c r="B172">
-        <v>137</v>
-      </c>
-      <c r="C172">
-        <v>137</v>
+        <v>800</v>
+      </c>
+      <c r="C172" t="s">
+        <v>28</v>
       </c>
       <c r="D172" s="1">
-        <v>46240</v>
+        <v>46246</v>
       </c>
       <c r="E172" s="1">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="F172">
-        <v>20003</v>
+        <v>200150</v>
       </c>
       <c r="G172">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I172">
-        <v>-3</v>
-      </c>
-      <c r="J172">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="K172">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L172">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M172">
-        <v>-3</v>
-      </c>
-      <c r="N172">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="O172" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173">
+        <v>10634</v>
+      </c>
+      <c r="B173">
+        <v>337</v>
+      </c>
+      <c r="C173">
+        <v>337</v>
+      </c>
+      <c r="D173" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E173" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F173">
+        <v>20003</v>
+      </c>
+      <c r="G173">
+        <v>13</v>
+      </c>
+      <c r="H173">
+        <v>13</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>13</v>
+      </c>
+      <c r="L173">
+        <v>13</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>1</v>
+      </c>
+      <c r="O173" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>10629</v>
+      </c>
+      <c r="B174">
+        <v>331</v>
+      </c>
+      <c r="C174">
+        <v>331</v>
+      </c>
+      <c r="D174" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E174" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F174">
+        <v>20006</v>
+      </c>
+      <c r="G174">
+        <v>21</v>
+      </c>
+      <c r="H174">
+        <v>18</v>
+      </c>
+      <c r="I174">
+        <v>-3</v>
+      </c>
+      <c r="J174">
+        <v>0.85714285700000004</v>
+      </c>
+      <c r="K174">
+        <v>21</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>-21</v>
+      </c>
+      <c r="N174">
+        <v>0</v>
+      </c>
+      <c r="O174" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>10617</v>
+      </c>
+      <c r="B175">
+        <v>311</v>
+      </c>
+      <c r="C175" t="s">
+        <v>41</v>
+      </c>
+      <c r="D175" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E175" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F175">
+        <v>20057</v>
+      </c>
+      <c r="G175">
+        <v>63</v>
+      </c>
+      <c r="H175">
+        <v>58</v>
+      </c>
+      <c r="I175">
+        <v>-5</v>
+      </c>
+      <c r="J175">
+        <v>0.92063492099999999</v>
+      </c>
+      <c r="K175">
+        <v>63</v>
+      </c>
+      <c r="L175">
+        <v>58</v>
+      </c>
+      <c r="M175">
+        <v>-5</v>
+      </c>
+      <c r="N175">
+        <v>0.92063492099999999</v>
+      </c>
+      <c r="O175" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>10610</v>
+      </c>
+      <c r="B176">
+        <v>303</v>
+      </c>
+      <c r="C176" t="s">
+        <v>67</v>
+      </c>
+      <c r="D176" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E176" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F176">
+        <v>20047</v>
+      </c>
+      <c r="G176">
+        <v>27</v>
+      </c>
+      <c r="H176">
+        <v>27</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176">
+        <v>27</v>
+      </c>
+      <c r="L176">
+        <v>27</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>10619</v>
+      </c>
+      <c r="B177">
+        <v>313</v>
+      </c>
+      <c r="C177" t="s">
+        <v>46</v>
+      </c>
+      <c r="D177" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E177" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F177">
+        <v>20106</v>
+      </c>
+      <c r="G177">
+        <v>10</v>
+      </c>
+      <c r="H177">
+        <v>10</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>1</v>
+      </c>
+      <c r="K177">
+        <v>10</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <v>-10</v>
+      </c>
+      <c r="N177">
+        <v>0</v>
+      </c>
+      <c r="O177" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>10622</v>
+      </c>
+      <c r="B178">
+        <v>316</v>
+      </c>
+      <c r="C178" t="s">
+        <v>61</v>
+      </c>
+      <c r="D178" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E178" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F178">
+        <v>20155</v>
+      </c>
+      <c r="G178">
+        <v>22</v>
+      </c>
+      <c r="H178">
+        <v>25</v>
+      </c>
+      <c r="I178">
+        <v>3</v>
+      </c>
+      <c r="J178">
+        <v>1.136363636</v>
+      </c>
+      <c r="K178">
+        <v>22</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <v>-22</v>
+      </c>
+      <c r="N178">
+        <v>0</v>
+      </c>
+      <c r="O178" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>10609</v>
+      </c>
+      <c r="B179">
+        <v>302</v>
+      </c>
+      <c r="C179" t="s">
+        <v>38</v>
+      </c>
+      <c r="D179" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E179" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F179">
+        <v>20106</v>
+      </c>
+      <c r="G179">
+        <v>1</v>
+      </c>
+      <c r="H179">
+        <v>1</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>1</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>1</v>
+      </c>
+      <c r="O179" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>10612</v>
+      </c>
+      <c r="B180">
+        <v>305</v>
+      </c>
+      <c r="C180" t="s">
+        <v>40</v>
+      </c>
+      <c r="D180" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E180" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F180">
+        <v>20105</v>
+      </c>
+      <c r="G180">
+        <v>1</v>
+      </c>
+      <c r="H180">
+        <v>1</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>1</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180">
+        <v>1</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
+      </c>
+      <c r="N180">
+        <v>1</v>
+      </c>
+      <c r="O180" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>10614</v>
+      </c>
+      <c r="B181">
+        <v>307</v>
+      </c>
+      <c r="C181" t="s">
+        <v>42</v>
+      </c>
+      <c r="D181" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E181" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F181">
+        <v>20153</v>
+      </c>
+      <c r="G181">
+        <v>27</v>
+      </c>
+      <c r="H181">
+        <v>12</v>
+      </c>
+      <c r="I181">
+        <v>-15</v>
+      </c>
+      <c r="J181">
+        <v>0.44444444399999999</v>
+      </c>
+      <c r="K181">
+        <v>27</v>
+      </c>
+      <c r="L181">
+        <v>12</v>
+      </c>
+      <c r="M181">
+        <v>-15</v>
+      </c>
+      <c r="N181">
+        <v>0.44444444399999999</v>
+      </c>
+      <c r="O181" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>10680</v>
+      </c>
+      <c r="B182">
+        <v>802</v>
+      </c>
+      <c r="C182" t="s">
+        <v>96</v>
+      </c>
+      <c r="D182" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E182" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F182">
+        <v>200150</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
+      </c>
+      <c r="O182" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>10752</v>
+      </c>
+      <c r="B183">
+        <v>239</v>
+      </c>
+      <c r="C183">
+        <v>239</v>
+      </c>
+      <c r="D183" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E183" s="1">
+        <v>46240</v>
+      </c>
+      <c r="F183">
+        <v>20008</v>
+      </c>
+      <c r="G183">
+        <v>29</v>
+      </c>
+      <c r="H183">
+        <v>16</v>
+      </c>
+      <c r="I183">
+        <v>-13</v>
+      </c>
+      <c r="J183">
+        <v>0.55172413799999998</v>
+      </c>
+      <c r="K183">
+        <v>29</v>
+      </c>
+      <c r="L183">
+        <v>16</v>
+      </c>
+      <c r="M183">
+        <v>-13</v>
+      </c>
+      <c r="N183">
+        <v>0.55172413799999998</v>
+      </c>
+      <c r="O183" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>10683</v>
+      </c>
+      <c r="B184">
+        <v>330</v>
+      </c>
+      <c r="C184">
+        <v>330</v>
+      </c>
+      <c r="D184" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E184" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F184">
+        <v>20006</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="O184" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>10654</v>
+      </c>
+      <c r="B185">
+        <v>202</v>
+      </c>
+      <c r="C185" t="s">
+        <v>53</v>
+      </c>
+      <c r="D185" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E185" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F185">
+        <v>20086</v>
+      </c>
+      <c r="G185">
+        <v>2</v>
+      </c>
+      <c r="H185">
+        <v>2</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185">
+        <v>2</v>
+      </c>
+      <c r="L185">
+        <v>2</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>1</v>
+      </c>
+      <c r="O185" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>10826</v>
+      </c>
+      <c r="B186">
+        <v>801</v>
+      </c>
+      <c r="C186" t="s">
+        <v>97</v>
+      </c>
+      <c r="D186" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E186" s="1">
+        <v>46245</v>
+      </c>
+      <c r="F186">
+        <v>200150</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="O186" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>10735</v>
+      </c>
+      <c r="B187">
+        <v>205</v>
+      </c>
+      <c r="C187" t="s">
+        <v>60</v>
+      </c>
+      <c r="D187" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E187" s="1">
+        <v>46240</v>
+      </c>
+      <c r="F187">
+        <v>20047</v>
+      </c>
+      <c r="G187">
+        <v>58</v>
+      </c>
+      <c r="H187">
+        <v>54</v>
+      </c>
+      <c r="I187">
+        <v>-4</v>
+      </c>
+      <c r="J187">
+        <v>0.93103448300000002</v>
+      </c>
+      <c r="K187">
+        <v>58</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>-58</v>
+      </c>
+      <c r="N187">
+        <v>0</v>
+      </c>
+      <c r="O187" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>10709</v>
+      </c>
+      <c r="B188">
+        <v>101</v>
+      </c>
+      <c r="C188" t="s">
+        <v>85</v>
+      </c>
+      <c r="D188" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E188" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F188">
+        <v>20076</v>
+      </c>
+      <c r="G188">
+        <v>42</v>
+      </c>
+      <c r="H188">
+        <v>32</v>
+      </c>
+      <c r="I188">
+        <v>-10</v>
+      </c>
+      <c r="J188">
+        <v>0.76190476200000001</v>
+      </c>
+      <c r="K188">
+        <v>42</v>
+      </c>
+      <c r="L188">
+        <v>32</v>
+      </c>
+      <c r="M188">
+        <v>-10</v>
+      </c>
+      <c r="N188">
+        <v>0.76190476200000001</v>
+      </c>
+      <c r="O188" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>10787</v>
+      </c>
+      <c r="B189">
+        <v>338</v>
+      </c>
+      <c r="C189">
+        <v>338</v>
+      </c>
+      <c r="D189" s="1">
+        <v>46242</v>
+      </c>
+      <c r="E189" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F189">
+        <v>20112</v>
+      </c>
+      <c r="G189">
+        <v>20</v>
+      </c>
+      <c r="H189">
+        <v>20</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189">
+        <v>20</v>
+      </c>
+      <c r="L189">
+        <v>20</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>1</v>
+      </c>
+      <c r="O189" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>10712</v>
+      </c>
+      <c r="B190">
+        <v>104</v>
+      </c>
+      <c r="C190" t="s">
+        <v>86</v>
+      </c>
+      <c r="D190" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E190" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F190">
+        <v>20095</v>
+      </c>
+      <c r="G190">
+        <v>42</v>
+      </c>
+      <c r="H190">
+        <v>35</v>
+      </c>
+      <c r="I190">
+        <v>-7</v>
+      </c>
+      <c r="J190">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K190">
+        <v>42</v>
+      </c>
+      <c r="L190">
+        <v>35</v>
+      </c>
+      <c r="M190">
+        <v>-7</v>
+      </c>
+      <c r="N190">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O190" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>10713</v>
+      </c>
+      <c r="B191">
+        <v>105</v>
+      </c>
+      <c r="C191" t="s">
+        <v>87</v>
+      </c>
+      <c r="D191" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E191" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F191">
+        <v>20058</v>
+      </c>
+      <c r="G191">
+        <v>70</v>
+      </c>
+      <c r="H191">
+        <v>43</v>
+      </c>
+      <c r="I191">
+        <v>-27</v>
+      </c>
+      <c r="J191">
+        <v>0.61428571399999998</v>
+      </c>
+      <c r="K191">
+        <v>70</v>
+      </c>
+      <c r="L191">
+        <v>43</v>
+      </c>
+      <c r="M191">
+        <v>-27</v>
+      </c>
+      <c r="N191">
+        <v>0.61428571399999998</v>
+      </c>
+      <c r="O191" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>10722</v>
+      </c>
+      <c r="B192">
+        <v>131</v>
+      </c>
+      <c r="C192">
+        <v>131</v>
+      </c>
+      <c r="D192" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E192" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F192">
+        <v>20005</v>
+      </c>
+      <c r="G192">
+        <v>20</v>
+      </c>
+      <c r="H192">
+        <v>17</v>
+      </c>
+      <c r="I192">
+        <v>-3</v>
+      </c>
+      <c r="J192">
+        <v>0.85</v>
+      </c>
+      <c r="K192">
+        <v>20</v>
+      </c>
+      <c r="L192">
+        <v>17</v>
+      </c>
+      <c r="M192">
+        <v>-3</v>
+      </c>
+      <c r="N192">
+        <v>0.85</v>
+      </c>
+      <c r="O192" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>10746</v>
+      </c>
+      <c r="B193">
+        <v>233</v>
+      </c>
+      <c r="C193">
+        <v>233</v>
+      </c>
+      <c r="D193" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E193" s="1">
+        <v>46240</v>
+      </c>
+      <c r="F193">
+        <v>200158</v>
+      </c>
+      <c r="G193">
+        <v>30</v>
+      </c>
+      <c r="H193">
+        <v>25</v>
+      </c>
+      <c r="I193">
+        <v>-5</v>
+      </c>
+      <c r="J193">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K193">
+        <v>30</v>
+      </c>
+      <c r="L193">
+        <v>25</v>
+      </c>
+      <c r="M193">
+        <v>-5</v>
+      </c>
+      <c r="N193">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O193" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>10750</v>
+      </c>
+      <c r="B194">
+        <v>237</v>
+      </c>
+      <c r="C194">
+        <v>237</v>
+      </c>
+      <c r="D194" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E194" s="1">
+        <v>46240</v>
+      </c>
+      <c r="F194">
+        <v>20003</v>
+      </c>
+      <c r="G194">
+        <v>28</v>
+      </c>
+      <c r="H194">
+        <v>20</v>
+      </c>
+      <c r="I194">
+        <v>-8</v>
+      </c>
+      <c r="J194">
+        <v>0.71428571399999996</v>
+      </c>
+      <c r="K194">
+        <v>28</v>
+      </c>
+      <c r="L194">
+        <v>20</v>
+      </c>
+      <c r="M194">
+        <v>-8</v>
+      </c>
+      <c r="N194">
+        <v>0.71428571399999996</v>
+      </c>
+      <c r="O194" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>10765</v>
+      </c>
+      <c r="B195">
+        <v>308</v>
+      </c>
+      <c r="C195" t="s">
+        <v>36</v>
+      </c>
+      <c r="D195" s="1">
+        <v>46242</v>
+      </c>
+      <c r="E195" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F195">
+        <v>20153</v>
+      </c>
+      <c r="G195">
+        <v>2</v>
+      </c>
+      <c r="H195">
+        <v>2</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>1</v>
+      </c>
+      <c r="K195">
+        <v>2</v>
+      </c>
+      <c r="L195">
+        <v>2</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>1</v>
+      </c>
+      <c r="O195" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>10777</v>
+      </c>
+      <c r="B196">
+        <v>325</v>
+      </c>
+      <c r="C196" t="s">
+        <v>62</v>
+      </c>
+      <c r="D196" s="1">
+        <v>46242</v>
+      </c>
+      <c r="E196" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F196">
+        <v>20043</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
+      </c>
+      <c r="O196" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>10697</v>
+      </c>
+      <c r="B197">
+        <v>315</v>
+      </c>
+      <c r="C197" t="s">
+        <v>43</v>
+      </c>
+      <c r="D197" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E197" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F197">
+        <v>11215</v>
+      </c>
+      <c r="G197">
+        <v>27</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>-27</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>27</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>-27</v>
+      </c>
+      <c r="N197">
+        <v>0</v>
+      </c>
+      <c r="O197" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>10791</v>
+      </c>
+      <c r="B198">
+        <v>328</v>
+      </c>
+      <c r="C198">
+        <v>328</v>
+      </c>
+      <c r="D198" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E198" s="1">
+        <v>46242</v>
+      </c>
+      <c r="F198">
+        <v>20076</v>
+      </c>
+      <c r="G198">
+        <v>3</v>
+      </c>
+      <c r="H198">
+        <v>3</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198">
+        <v>3</v>
+      </c>
+      <c r="L198">
+        <v>3</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="N198">
+        <v>1</v>
+      </c>
+      <c r="O198" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>10788</v>
+      </c>
+      <c r="B199">
+        <v>339</v>
+      </c>
+      <c r="C199">
+        <v>339</v>
+      </c>
+      <c r="D199" s="1">
+        <v>46242</v>
+      </c>
+      <c r="E199" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F199">
+        <v>20008</v>
+      </c>
+      <c r="G199">
+        <v>28</v>
+      </c>
+      <c r="H199">
+        <v>22</v>
+      </c>
+      <c r="I199">
+        <v>-6</v>
+      </c>
+      <c r="J199">
+        <v>0.78571428600000004</v>
+      </c>
+      <c r="K199">
+        <v>28</v>
+      </c>
+      <c r="L199">
+        <v>22</v>
+      </c>
+      <c r="M199">
+        <v>-6</v>
+      </c>
+      <c r="N199">
+        <v>0.78571428600000004</v>
+      </c>
+      <c r="O199" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>10766</v>
+      </c>
+      <c r="B200">
+        <v>310</v>
+      </c>
+      <c r="C200" t="s">
+        <v>75</v>
+      </c>
+      <c r="D200" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E200" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F200">
+        <v>20155</v>
+      </c>
+      <c r="G200">
+        <v>34</v>
+      </c>
+      <c r="H200">
+        <v>27</v>
+      </c>
+      <c r="I200">
+        <v>-7</v>
+      </c>
+      <c r="J200">
+        <v>0.79411764699999998</v>
+      </c>
+      <c r="K200">
+        <v>34</v>
+      </c>
+      <c r="L200">
+        <v>27</v>
+      </c>
+      <c r="M200">
+        <v>-7</v>
+      </c>
+      <c r="N200">
+        <v>0.79411764699999998</v>
+      </c>
+      <c r="O200" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>10763</v>
+      </c>
+      <c r="B201">
+        <v>306</v>
+      </c>
+      <c r="C201" t="s">
+        <v>74</v>
+      </c>
+      <c r="D201" s="1">
+        <v>46242</v>
+      </c>
+      <c r="E201" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F201">
+        <v>20105</v>
+      </c>
+      <c r="G201">
+        <v>56</v>
+      </c>
+      <c r="H201">
+        <v>32</v>
+      </c>
+      <c r="I201">
+        <v>-24</v>
+      </c>
+      <c r="J201">
+        <v>0.571428571</v>
+      </c>
+      <c r="K201">
+        <v>56</v>
+      </c>
+      <c r="L201">
+        <v>32</v>
+      </c>
+      <c r="M201">
+        <v>-24</v>
+      </c>
+      <c r="N201">
+        <v>0.571428571</v>
+      </c>
+      <c r="O201" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>10786</v>
+      </c>
+      <c r="B202">
+        <v>337</v>
+      </c>
+      <c r="C202">
+        <v>337</v>
+      </c>
+      <c r="D202" s="1">
+        <v>46242</v>
+      </c>
+      <c r="E202" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F202">
+        <v>20003</v>
+      </c>
+      <c r="G202">
+        <v>20</v>
+      </c>
+      <c r="H202">
+        <v>16</v>
+      </c>
+      <c r="I202">
+        <v>-4</v>
+      </c>
+      <c r="J202">
+        <v>0.8</v>
+      </c>
+      <c r="K202">
+        <v>20</v>
+      </c>
+      <c r="L202">
+        <v>16</v>
+      </c>
+      <c r="M202">
+        <v>-4</v>
+      </c>
+      <c r="N202">
+        <v>0.8</v>
+      </c>
+      <c r="O202" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>10793</v>
+      </c>
+      <c r="B203">
+        <v>132</v>
+      </c>
+      <c r="C203">
+        <v>132</v>
+      </c>
+      <c r="D203" s="1">
+        <v>46244</v>
+      </c>
+      <c r="E203" s="1">
+        <v>46242</v>
+      </c>
+      <c r="F203">
+        <v>20130</v>
+      </c>
+      <c r="G203">
+        <v>10</v>
+      </c>
+      <c r="H203">
+        <v>10</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>1</v>
+      </c>
+      <c r="K203">
+        <v>10</v>
+      </c>
+      <c r="L203">
+        <v>10</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
+      </c>
+      <c r="N203">
+        <v>1</v>
+      </c>
+      <c r="O203" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>10827</v>
+      </c>
+      <c r="B204">
+        <v>500</v>
+      </c>
+      <c r="C204" t="s">
+        <v>66</v>
+      </c>
+      <c r="D204" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E204" s="1">
+        <v>46245</v>
+      </c>
+      <c r="F204">
+        <v>200150</v>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
+      </c>
+      <c r="O204" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>10802</v>
+      </c>
+      <c r="B205">
+        <v>501</v>
+      </c>
+      <c r="C205" t="s">
+        <v>49</v>
+      </c>
+      <c r="D205" s="1">
+        <v>46245</v>
+      </c>
+      <c r="E205" s="1">
+        <v>46244</v>
+      </c>
+      <c r="F205">
+        <v>200150</v>
+      </c>
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+      <c r="M205">
+        <v>0</v>
+      </c>
+      <c r="O205" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>10623</v>
+      </c>
+      <c r="B206">
+        <v>317</v>
+      </c>
+      <c r="C206" t="s">
+        <v>76</v>
+      </c>
+      <c r="D206" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E206" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F206">
+        <v>20043</v>
+      </c>
+      <c r="G206">
+        <v>24</v>
+      </c>
+      <c r="H206">
+        <v>23</v>
+      </c>
+      <c r="I206">
+        <v>-1</v>
+      </c>
+      <c r="J206">
+        <v>0.95833333300000001</v>
+      </c>
+      <c r="K206">
+        <v>24</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+      <c r="M206">
+        <v>-24</v>
+      </c>
+      <c r="N206">
+        <v>0</v>
+      </c>
+      <c r="O206" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>10650</v>
+      </c>
+      <c r="B207">
+        <v>800</v>
+      </c>
+      <c r="C207" t="s">
+        <v>28</v>
+      </c>
+      <c r="D207" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E207" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F207">
+        <v>200150</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>0</v>
+      </c>
+      <c r="O207" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>10655</v>
+      </c>
+      <c r="B208">
+        <v>203</v>
+      </c>
+      <c r="C208" t="s">
+        <v>56</v>
+      </c>
+      <c r="D208" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E208" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F208">
+        <v>20155</v>
+      </c>
+      <c r="G208">
+        <v>48</v>
+      </c>
+      <c r="H208">
+        <v>26</v>
+      </c>
+      <c r="I208">
+        <v>-22</v>
+      </c>
+      <c r="J208">
+        <v>0.54166666699999999</v>
+      </c>
+      <c r="K208">
+        <v>48</v>
+      </c>
+      <c r="L208">
+        <v>26</v>
+      </c>
+      <c r="M208">
+        <v>-22</v>
+      </c>
+      <c r="N208">
+        <v>0.54166666699999999</v>
+      </c>
+      <c r="O208" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>10716</v>
+      </c>
+      <c r="B209">
+        <v>108</v>
+      </c>
+      <c r="C209" t="s">
+        <v>88</v>
+      </c>
+      <c r="D209" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E209" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F209">
+        <v>20057</v>
+      </c>
+      <c r="G209">
+        <v>59</v>
+      </c>
+      <c r="H209">
+        <v>51</v>
+      </c>
+      <c r="I209">
+        <v>-8</v>
+      </c>
+      <c r="J209">
+        <v>0.86440678000000004</v>
+      </c>
+      <c r="K209">
+        <v>59</v>
+      </c>
+      <c r="L209">
+        <v>51</v>
+      </c>
+      <c r="M209">
+        <v>-8</v>
+      </c>
+      <c r="N209">
+        <v>0.86440678000000004</v>
+      </c>
+      <c r="O209" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>10657</v>
+      </c>
+      <c r="B210">
+        <v>205</v>
+      </c>
+      <c r="C210" t="s">
+        <v>60</v>
+      </c>
+      <c r="D210" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E210" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F210">
+        <v>20047</v>
+      </c>
+      <c r="G210">
+        <v>36</v>
+      </c>
+      <c r="H210">
+        <v>34</v>
+      </c>
+      <c r="I210">
+        <v>-2</v>
+      </c>
+      <c r="J210">
+        <v>0.94444444400000005</v>
+      </c>
+      <c r="K210">
+        <v>36</v>
+      </c>
+      <c r="L210">
+        <v>34</v>
+      </c>
+      <c r="M210">
+        <v>-2</v>
+      </c>
+      <c r="N210">
+        <v>0.94444444400000005</v>
+      </c>
+      <c r="O210" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>10704</v>
+      </c>
+      <c r="B211">
+        <v>327</v>
+      </c>
+      <c r="C211">
+        <v>327</v>
+      </c>
+      <c r="D211" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E211" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F211">
+        <v>20003</v>
+      </c>
+      <c r="G211">
+        <v>30</v>
+      </c>
+      <c r="H211">
+        <v>15</v>
+      </c>
+      <c r="I211">
+        <v>-15</v>
+      </c>
+      <c r="J211">
+        <v>0.5</v>
+      </c>
+      <c r="K211">
+        <v>30</v>
+      </c>
+      <c r="L211">
+        <v>15</v>
+      </c>
+      <c r="M211">
+        <v>-15</v>
+      </c>
+      <c r="N211">
+        <v>0.5</v>
+      </c>
+      <c r="O211" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>10659</v>
+      </c>
+      <c r="B212">
+        <v>208</v>
+      </c>
+      <c r="C212" t="s">
+        <v>71</v>
+      </c>
+      <c r="D212" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E212" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F212">
+        <v>11215</v>
+      </c>
+      <c r="G212">
+        <v>40</v>
+      </c>
+      <c r="H212">
+        <v>27</v>
+      </c>
+      <c r="I212">
+        <v>-13</v>
+      </c>
+      <c r="J212">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="K212">
+        <v>40</v>
+      </c>
+      <c r="L212">
+        <v>27</v>
+      </c>
+      <c r="M212">
+        <v>-13</v>
+      </c>
+      <c r="N212">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="O212" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>10660</v>
+      </c>
+      <c r="B213">
+        <v>209</v>
+      </c>
+      <c r="C213" t="s">
+        <v>54</v>
+      </c>
+      <c r="D213" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E213" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F213">
+        <v>20105</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+      <c r="M213">
+        <v>0</v>
+      </c>
+      <c r="O213" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>10687</v>
+      </c>
+      <c r="B214">
+        <v>303</v>
+      </c>
+      <c r="C214" t="s">
+        <v>67</v>
+      </c>
+      <c r="D214" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E214" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F214">
+        <v>20153</v>
+      </c>
+      <c r="G214">
+        <v>37</v>
+      </c>
+      <c r="H214">
+        <v>28</v>
+      </c>
+      <c r="I214">
+        <v>-9</v>
+      </c>
+      <c r="J214">
+        <v>0.756756757</v>
+      </c>
+      <c r="K214">
+        <v>37</v>
+      </c>
+      <c r="L214">
+        <v>28</v>
+      </c>
+      <c r="M214">
+        <v>-9</v>
+      </c>
+      <c r="N214">
+        <v>0.756756757</v>
+      </c>
+      <c r="O214" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>10686</v>
+      </c>
+      <c r="B215">
+        <v>302</v>
+      </c>
+      <c r="C215" t="s">
+        <v>38</v>
+      </c>
+      <c r="D215" s="1">
+        <v>46239</v>
+      </c>
+      <c r="E215" s="1">
+        <v>46238</v>
+      </c>
+      <c r="F215">
+        <v>20058</v>
+      </c>
+      <c r="G215">
+        <v>41</v>
+      </c>
+      <c r="H215">
+        <v>23</v>
+      </c>
+      <c r="I215">
+        <v>-18</v>
+      </c>
+      <c r="J215">
+        <v>0.56097560999999996</v>
+      </c>
+      <c r="K215">
+        <v>41</v>
+      </c>
+      <c r="L215">
+        <v>23</v>
+      </c>
+      <c r="M215">
+        <v>-18</v>
+      </c>
+      <c r="N215">
+        <v>0.56097560999999996</v>
+      </c>
+      <c r="O215" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>10663</v>
+      </c>
+      <c r="B216">
+        <v>212</v>
+      </c>
+      <c r="C216" t="s">
+        <v>50</v>
+      </c>
+      <c r="D216" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E216" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F216">
+        <v>20057</v>
+      </c>
+      <c r="G216">
+        <v>85</v>
+      </c>
+      <c r="H216">
+        <v>75</v>
+      </c>
+      <c r="I216">
+        <v>-10</v>
+      </c>
+      <c r="J216">
+        <v>0.88235294099999995</v>
+      </c>
+      <c r="K216">
+        <v>85</v>
+      </c>
+      <c r="L216">
+        <v>75</v>
+      </c>
+      <c r="M216">
+        <v>-10</v>
+      </c>
+      <c r="N216">
+        <v>0.88235294099999995</v>
+      </c>
+      <c r="O216" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>10664</v>
+      </c>
+      <c r="B217">
+        <v>213</v>
+      </c>
+      <c r="C217" t="s">
+        <v>57</v>
+      </c>
+      <c r="D217" s="1">
+        <v>46237</v>
+      </c>
+      <c r="E217" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F217">
+        <v>20058</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
+      </c>
+      <c r="O217" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>10665</v>
+      </c>
+      <c r="B218">
+        <v>231</v>
+      </c>
+      <c r="C218">
+        <v>231</v>
+      </c>
+      <c r="D218" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E218" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F218">
+        <v>20005</v>
+      </c>
+      <c r="G218">
+        <v>39</v>
+      </c>
+      <c r="H218">
+        <v>32</v>
+      </c>
+      <c r="I218">
+        <v>-7</v>
+      </c>
+      <c r="J218">
+        <v>0.820512821</v>
+      </c>
+      <c r="K218">
+        <v>39</v>
+      </c>
+      <c r="L218">
+        <v>32</v>
+      </c>
+      <c r="M218">
+        <v>-7</v>
+      </c>
+      <c r="N218">
+        <v>0.820512821</v>
+      </c>
+      <c r="O218" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>10731</v>
+      </c>
+      <c r="B219">
+        <v>140</v>
+      </c>
+      <c r="C219">
+        <v>140</v>
+      </c>
+      <c r="D219" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E219" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F219">
+        <v>20006</v>
+      </c>
+      <c r="G219">
+        <v>22</v>
+      </c>
+      <c r="H219">
+        <v>19</v>
+      </c>
+      <c r="I219">
+        <v>-3</v>
+      </c>
+      <c r="J219">
+        <v>0.86363636399999999</v>
+      </c>
+      <c r="K219">
+        <v>22</v>
+      </c>
+      <c r="L219">
+        <v>19</v>
+      </c>
+      <c r="M219">
+        <v>-3</v>
+      </c>
+      <c r="N219">
+        <v>0.86363636399999999</v>
+      </c>
+      <c r="O219" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>10667</v>
+      </c>
+      <c r="B220">
+        <v>233</v>
+      </c>
+      <c r="C220">
+        <v>233</v>
+      </c>
+      <c r="D220" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E220" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F220">
+        <v>200158</v>
+      </c>
+      <c r="G220">
+        <v>28</v>
+      </c>
+      <c r="H220">
+        <v>28</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>1</v>
+      </c>
+      <c r="K220">
+        <v>28</v>
+      </c>
+      <c r="L220">
+        <v>28</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>1</v>
+      </c>
+      <c r="O220" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>10729</v>
+      </c>
+      <c r="B221">
+        <v>138</v>
+      </c>
+      <c r="C221">
+        <v>138</v>
+      </c>
+      <c r="D221" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E221" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F221">
+        <v>20007</v>
+      </c>
+      <c r="G221">
+        <v>27</v>
+      </c>
+      <c r="H221">
+        <v>19</v>
+      </c>
+      <c r="I221">
+        <v>-8</v>
+      </c>
+      <c r="J221">
+        <v>0.70370370400000004</v>
+      </c>
+      <c r="K221">
+        <v>27</v>
+      </c>
+      <c r="L221">
+        <v>19</v>
+      </c>
+      <c r="M221">
+        <v>-8</v>
+      </c>
+      <c r="N221">
+        <v>0.70370370400000004</v>
+      </c>
+      <c r="O221" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>10727</v>
+      </c>
+      <c r="B222">
+        <v>136</v>
+      </c>
+      <c r="C222">
+        <v>136</v>
+      </c>
+      <c r="D222" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E222" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F222">
+        <v>20111</v>
+      </c>
+      <c r="G222">
+        <v>12</v>
+      </c>
+      <c r="H222">
+        <v>10</v>
+      </c>
+      <c r="I222">
+        <v>-2</v>
+      </c>
+      <c r="J222">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K222">
+        <v>12</v>
+      </c>
+      <c r="L222">
+        <v>10</v>
+      </c>
+      <c r="M222">
+        <v>-2</v>
+      </c>
+      <c r="N222">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O222" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>10720</v>
+      </c>
+      <c r="B223">
+        <v>112</v>
+      </c>
+      <c r="C223" t="s">
+        <v>89</v>
+      </c>
+      <c r="D223" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E223" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F223">
+        <v>20106</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>1</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="K223">
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="M223">
+        <v>1</v>
+      </c>
+      <c r="O223" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>10671</v>
+      </c>
+      <c r="B224">
+        <v>237</v>
+      </c>
+      <c r="C224">
+        <v>237</v>
+      </c>
+      <c r="D224" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E224" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F224">
+        <v>20003</v>
+      </c>
+      <c r="G224">
+        <v>23</v>
+      </c>
+      <c r="H224">
+        <v>21</v>
+      </c>
+      <c r="I224">
+        <v>-2</v>
+      </c>
+      <c r="J224">
+        <v>0.91304347799999996</v>
+      </c>
+      <c r="K224">
+        <v>23</v>
+      </c>
+      <c r="L224">
+        <v>21</v>
+      </c>
+      <c r="M224">
+        <v>-2</v>
+      </c>
+      <c r="N224">
+        <v>0.91304347799999996</v>
+      </c>
+      <c r="O224" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>10717</v>
+      </c>
+      <c r="B225">
+        <v>109</v>
+      </c>
+      <c r="C225" t="s">
+        <v>90</v>
+      </c>
+      <c r="D225" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E225" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F225">
+        <v>20105</v>
+      </c>
+      <c r="G225">
+        <v>46</v>
+      </c>
+      <c r="H225">
+        <v>33</v>
+      </c>
+      <c r="I225">
+        <v>-13</v>
+      </c>
+      <c r="J225">
+        <v>0.71739130399999995</v>
+      </c>
+      <c r="K225">
+        <v>46</v>
+      </c>
+      <c r="L225">
+        <v>33</v>
+      </c>
+      <c r="M225">
+        <v>-13</v>
+      </c>
+      <c r="N225">
+        <v>0.71739130399999995</v>
+      </c>
+      <c r="O225" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>10711</v>
+      </c>
+      <c r="B226">
+        <v>103</v>
+      </c>
+      <c r="C226" t="s">
+        <v>91</v>
+      </c>
+      <c r="D226" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E226" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F226">
+        <v>20153</v>
+      </c>
+      <c r="G226">
+        <v>50</v>
+      </c>
+      <c r="H226">
+        <v>33</v>
+      </c>
+      <c r="I226">
+        <v>-17</v>
+      </c>
+      <c r="J226">
+        <v>0.66</v>
+      </c>
+      <c r="K226">
+        <v>50</v>
+      </c>
+      <c r="L226">
+        <v>33</v>
+      </c>
+      <c r="M226">
+        <v>-17</v>
+      </c>
+      <c r="N226">
+        <v>0.66</v>
+      </c>
+      <c r="O226" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>10714</v>
+      </c>
+      <c r="B227">
+        <v>106</v>
+      </c>
+      <c r="C227" t="s">
+        <v>92</v>
+      </c>
+      <c r="D227" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E227" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F227">
+        <v>11215</v>
+      </c>
+      <c r="G227">
+        <v>48</v>
+      </c>
+      <c r="H227">
+        <v>47</v>
+      </c>
+      <c r="I227">
+        <v>-1</v>
+      </c>
+      <c r="J227">
+        <v>0.97916666699999999</v>
+      </c>
+      <c r="K227">
+        <v>48</v>
+      </c>
+      <c r="L227">
+        <v>47</v>
+      </c>
+      <c r="M227">
+        <v>-1</v>
+      </c>
+      <c r="N227">
+        <v>0.97916666699999999</v>
+      </c>
+      <c r="O227" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>10677</v>
+      </c>
+      <c r="B228">
+        <v>209</v>
+      </c>
+      <c r="C228" t="s">
+        <v>54</v>
+      </c>
+      <c r="D228" s="1">
+        <v>46238</v>
+      </c>
+      <c r="E228" s="1">
+        <v>46237</v>
+      </c>
+      <c r="F228">
+        <v>20105</v>
+      </c>
+      <c r="G228">
+        <v>45</v>
+      </c>
+      <c r="H228">
+        <v>39</v>
+      </c>
+      <c r="I228">
+        <v>-6</v>
+      </c>
+      <c r="J228">
+        <v>0.86666666699999995</v>
+      </c>
+      <c r="K228">
+        <v>45</v>
+      </c>
+      <c r="L228">
+        <v>39</v>
+      </c>
+      <c r="M228">
+        <v>-6</v>
+      </c>
+      <c r="N228">
+        <v>0.86666666699999995</v>
+      </c>
+      <c r="O228" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>10715</v>
+      </c>
+      <c r="B229">
+        <v>107</v>
+      </c>
+      <c r="C229" t="s">
+        <v>93</v>
+      </c>
+      <c r="D229" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E229" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F229">
+        <v>20155</v>
+      </c>
+      <c r="G229">
+        <v>38</v>
+      </c>
+      <c r="H229">
+        <v>36</v>
+      </c>
+      <c r="I229">
+        <v>-2</v>
+      </c>
+      <c r="J229">
+        <v>0.94736842099999996</v>
+      </c>
+      <c r="K229">
+        <v>38</v>
+      </c>
+      <c r="L229">
+        <v>36</v>
+      </c>
+      <c r="M229">
+        <v>-2</v>
+      </c>
+      <c r="N229">
+        <v>0.94736842099999996</v>
+      </c>
+      <c r="O229" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>10755</v>
+      </c>
+      <c r="B230">
+        <v>800</v>
+      </c>
+      <c r="C230" t="s">
+        <v>28</v>
+      </c>
+      <c r="D230" s="1">
+        <v>46241</v>
+      </c>
+      <c r="E230" s="1">
+        <v>46241</v>
+      </c>
+      <c r="F230">
+        <v>200150</v>
+      </c>
+      <c r="G230">
+        <v>0</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
+      </c>
+      <c r="O230" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>10632</v>
+      </c>
+      <c r="B231">
+        <v>335</v>
+      </c>
+      <c r="C231">
+        <v>335</v>
+      </c>
+      <c r="D231" s="1">
+        <v>46235</v>
+      </c>
+      <c r="E231" s="1">
+        <v>46234</v>
+      </c>
+      <c r="F231">
+        <v>20113</v>
+      </c>
+      <c r="G231">
+        <v>13</v>
+      </c>
+      <c r="H231">
+        <v>13</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231">
+        <v>13</v>
+      </c>
+      <c r="L231">
+        <v>13</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>1</v>
+      </c>
+      <c r="O231" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>10726</v>
+      </c>
+      <c r="B232">
+        <v>135</v>
+      </c>
+      <c r="C232">
+        <v>135</v>
+      </c>
+      <c r="D232" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E232" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F232">
+        <v>20113</v>
+      </c>
+      <c r="G232">
+        <v>13</v>
+      </c>
+      <c r="H232">
+        <v>13</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>1</v>
+      </c>
+      <c r="K232">
+        <v>13</v>
+      </c>
+      <c r="L232">
+        <v>13</v>
+      </c>
+      <c r="M232">
+        <v>0</v>
+      </c>
+      <c r="N232">
+        <v>1</v>
+      </c>
+      <c r="O232" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>10728</v>
+      </c>
+      <c r="B233">
+        <v>137</v>
+      </c>
+      <c r="C233">
+        <v>137</v>
+      </c>
+      <c r="D233" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E233" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F233">
+        <v>20003</v>
+      </c>
+      <c r="G233">
+        <v>8</v>
+      </c>
+      <c r="H233">
+        <v>5</v>
+      </c>
+      <c r="I233">
+        <v>-3</v>
+      </c>
+      <c r="J233">
+        <v>0.625</v>
+      </c>
+      <c r="K233">
+        <v>8</v>
+      </c>
+      <c r="L233">
+        <v>5</v>
+      </c>
+      <c r="M233">
+        <v>-3</v>
+      </c>
+      <c r="N233">
+        <v>0.625</v>
+      </c>
+      <c r="O233" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A234">
         <v>10753</v>
       </c>
-      <c r="B173">
+      <c r="B234">
         <v>240</v>
       </c>
-      <c r="C173">
+      <c r="C234">
         <v>240</v>
       </c>
-      <c r="D173" s="1">
+      <c r="D234" s="1">
         <v>46241</v>
       </c>
-      <c r="E173" s="1">
+      <c r="E234" s="1">
         <v>46240</v>
       </c>
-      <c r="F173">
+      <c r="F234">
         <v>20006</v>
       </c>
-      <c r="G173">
+      <c r="G234">
         <v>24</v>
       </c>
-      <c r="H173">
+      <c r="H234">
         <v>20</v>
       </c>
-      <c r="I173">
+      <c r="I234">
         <v>-4</v>
       </c>
-      <c r="J173">
+      <c r="J234">
         <v>0.83333333300000001</v>
       </c>
-      <c r="K173">
+      <c r="K234">
         <v>24</v>
       </c>
-      <c r="L173">
+      <c r="L234">
         <v>20</v>
       </c>
-      <c r="M173">
+      <c r="M234">
         <v>-4</v>
       </c>
-      <c r="N173">
+      <c r="N234">
         <v>0.83333333300000001</v>
       </c>
-      <c r="O173" t="s">
+      <c r="O234" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>10730</v>
+      </c>
+      <c r="B235">
+        <v>139</v>
+      </c>
+      <c r="C235">
+        <v>139</v>
+      </c>
+      <c r="D235" s="1">
+        <v>46240</v>
+      </c>
+      <c r="E235" s="1">
+        <v>46239</v>
+      </c>
+      <c r="F235">
+        <v>20008</v>
+      </c>
+      <c r="G235">
+        <v>12</v>
+      </c>
+      <c r="H235">
+        <v>10</v>
+      </c>
+      <c r="I235">
+        <v>-2</v>
+      </c>
+      <c r="J235">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="K235">
+        <v>12</v>
+      </c>
+      <c r="L235">
+        <v>10</v>
+      </c>
+      <c r="M235">
+        <v>-2</v>
+      </c>
+      <c r="N235">
+        <v>0.83333333300000001</v>
+      </c>
+      <c r="O235" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
